--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -13111,7 +13111,7 @@
         <v>67.98999999999999</v>
       </c>
       <c r="E167" t="n">
-        <v>66.84</v>
+        <v>66.83</v>
       </c>
       <c r="F167" t="n">
         <v>67.38</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -13111,7 +13111,7 @@
         <v>67.98999999999999</v>
       </c>
       <c r="E167" t="n">
-        <v>66.83</v>
+        <v>66.84</v>
       </c>
       <c r="F167" t="n">
         <v>67.38</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -1507,13 +1507,13 @@
         <v>55.75</v>
       </c>
       <c r="F14" t="n">
-        <v>55.92</v>
+        <v>55.91</v>
       </c>
       <c r="G14" t="n">
         <v>4503400</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>-2.53</v>
+        <v>-2.54</v>
       </c>
       <c r="I14" t="n">
         <v>5.3</v>
@@ -1522,7 +1522,7 @@
         <v>55.61</v>
       </c>
       <c r="K14" t="n">
-        <v>55.43</v>
+        <v>55.42</v>
       </c>
       <c r="L14" t="n">
         <v>52.32</v>
@@ -1531,7 +1531,7 @@
         <v>49.92</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>49.96</v>
+        <v>49.93</v>
       </c>
       <c r="O14" t="n">
         <v>38</v>
@@ -1588,7 +1588,7 @@
         <v>2721000</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I15" t="n">
         <v>5.3</v>
@@ -1756,7 +1756,7 @@
         <v>50.18</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>45.24</v>
+        <v>45.25</v>
       </c>
       <c r="O17" t="n">
         <v>41</v>
@@ -1831,7 +1831,7 @@
         <v>50.27</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>53.84</v>
+        <v>53.83</v>
       </c>
       <c r="O18" t="n">
         <v>47</v>
@@ -1906,7 +1906,7 @@
         <v>50.36</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>72.43000000000001</v>
+        <v>72.39</v>
       </c>
       <c r="O19" t="n">
         <v>44</v>
@@ -1981,7 +1981,7 @@
         <v>50.46</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>68.47</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="O20" t="n">
         <v>47</v>
@@ -2056,7 +2056,7 @@
         <v>50.56</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>70.23999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="O21" t="n">
         <v>48</v>
@@ -2131,7 +2131,7 @@
         <v>50.65</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>64.87</v>
+        <v>64.84</v>
       </c>
       <c r="O22" t="n">
         <v>44</v>
@@ -2206,7 +2206,7 @@
         <v>50.73</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>52.39</v>
+        <v>52.38</v>
       </c>
       <c r="O23" t="n">
         <v>37</v>
@@ -2364,7 +2364,7 @@
         <v>50.85</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>39.2</v>
+        <v>39.22</v>
       </c>
       <c r="O25" t="n">
         <v>24</v>
@@ -2439,7 +2439,7 @@
         <v>50.91</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>37.99</v>
+        <v>38.01</v>
       </c>
       <c r="O26" t="n">
         <v>21</v>
@@ -2514,7 +2514,7 @@
         <v>50.95</v>
       </c>
       <c r="N27" s="7" t="n">
-        <v>27.65</v>
+        <v>27.68</v>
       </c>
       <c r="O27" s="4" t="n">
         <v>13</v>
@@ -2593,7 +2593,7 @@
         <v>51</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>38.21</v>
+        <v>38.26</v>
       </c>
       <c r="O28" t="n">
         <v>21</v>
@@ -7712,7 +7712,7 @@
         <v>46.13</v>
       </c>
       <c r="L95" t="n">
-        <v>50.67</v>
+        <v>50.66</v>
       </c>
       <c r="M95" t="n">
         <v>50.63</v>
@@ -11548,7 +11548,7 @@
         <v>51.95</v>
       </c>
       <c r="M146" t="n">
-        <v>53.3</v>
+        <v>53.29</v>
       </c>
       <c r="N146" s="2" t="n">
         <v>49.89</v>
@@ -12072,7 +12072,7 @@
         <v>5.3</v>
       </c>
       <c r="J153" t="n">
-        <v>62.39</v>
+        <v>62.38</v>
       </c>
       <c r="K153" t="n">
         <v>59.44</v>
@@ -14176,7 +14176,7 @@
         <v>5.3</v>
       </c>
       <c r="J181" t="n">
-        <v>68</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="K181" t="n">
         <v>64.08</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -1507,13 +1507,13 @@
         <v>55.75</v>
       </c>
       <c r="F14" t="n">
-        <v>55.91</v>
+        <v>55.92</v>
       </c>
       <c r="G14" t="n">
         <v>4503400</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>-2.54</v>
+        <v>-2.53</v>
       </c>
       <c r="I14" t="n">
         <v>5.3</v>
@@ -1522,7 +1522,7 @@
         <v>55.61</v>
       </c>
       <c r="K14" t="n">
-        <v>55.42</v>
+        <v>55.43</v>
       </c>
       <c r="L14" t="n">
         <v>52.32</v>
@@ -1531,7 +1531,7 @@
         <v>49.92</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>49.93</v>
+        <v>49.96</v>
       </c>
       <c r="O14" t="n">
         <v>38</v>
@@ -1588,7 +1588,7 @@
         <v>2721000</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I15" t="n">
         <v>5.3</v>
@@ -1756,7 +1756,7 @@
         <v>50.18</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>45.25</v>
+        <v>45.24</v>
       </c>
       <c r="O17" t="n">
         <v>41</v>
@@ -1831,7 +1831,7 @@
         <v>50.27</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>53.83</v>
+        <v>53.84</v>
       </c>
       <c r="O18" t="n">
         <v>47</v>
@@ -1906,7 +1906,7 @@
         <v>50.36</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>72.39</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="O19" t="n">
         <v>44</v>
@@ -1981,7 +1981,7 @@
         <v>50.46</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>68.43000000000001</v>
+        <v>68.47</v>
       </c>
       <c r="O20" t="n">
         <v>47</v>
@@ -2056,7 +2056,7 @@
         <v>50.56</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>70.2</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="O21" t="n">
         <v>48</v>
@@ -2131,7 +2131,7 @@
         <v>50.65</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>64.84</v>
+        <v>64.87</v>
       </c>
       <c r="O22" t="n">
         <v>44</v>
@@ -2206,7 +2206,7 @@
         <v>50.73</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>52.38</v>
+        <v>52.39</v>
       </c>
       <c r="O23" t="n">
         <v>37</v>
@@ -2364,7 +2364,7 @@
         <v>50.85</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>39.22</v>
+        <v>39.2</v>
       </c>
       <c r="O25" t="n">
         <v>24</v>
@@ -2439,7 +2439,7 @@
         <v>50.91</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>38.01</v>
+        <v>37.99</v>
       </c>
       <c r="O26" t="n">
         <v>21</v>
@@ -2514,7 +2514,7 @@
         <v>50.95</v>
       </c>
       <c r="N27" s="7" t="n">
-        <v>27.68</v>
+        <v>27.65</v>
       </c>
       <c r="O27" s="4" t="n">
         <v>13</v>
@@ -2593,7 +2593,7 @@
         <v>51</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>38.26</v>
+        <v>38.21</v>
       </c>
       <c r="O28" t="n">
         <v>21</v>
@@ -7712,7 +7712,7 @@
         <v>46.13</v>
       </c>
       <c r="L95" t="n">
-        <v>50.66</v>
+        <v>50.67</v>
       </c>
       <c r="M95" t="n">
         <v>50.63</v>
@@ -11548,7 +11548,7 @@
         <v>51.95</v>
       </c>
       <c r="M146" t="n">
-        <v>53.29</v>
+        <v>53.3</v>
       </c>
       <c r="N146" s="2" t="n">
         <v>49.89</v>
@@ -12072,7 +12072,7 @@
         <v>5.3</v>
       </c>
       <c r="J153" t="n">
-        <v>62.38</v>
+        <v>62.39</v>
       </c>
       <c r="K153" t="n">
         <v>59.44</v>
@@ -14176,7 +14176,7 @@
         <v>5.3</v>
       </c>
       <c r="J181" t="n">
-        <v>67.98999999999999</v>
+        <v>68</v>
       </c>
       <c r="K181" t="n">
         <v>64.08</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3138,7 +3138,7 @@
         <v>5.3</v>
       </c>
       <c r="J35" t="n">
-        <v>53</v>
+        <v>52.99</v>
       </c>
       <c r="K35" t="n">
         <v>55</v>
@@ -28473,7 +28473,7 @@
         <v>5.3</v>
       </c>
       <c r="J370" t="n">
-        <v>93.14</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="K370" t="n">
         <v>90.17</v>
@@ -31619,6 +31619,79 @@
         <v>154.5</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>86.64</v>
+      </c>
+      <c r="D413" t="n">
+        <v>89.03</v>
+      </c>
+      <c r="E413" t="n">
+        <v>86.48</v>
+      </c>
+      <c r="F413" t="n">
+        <v>88.81</v>
+      </c>
+      <c r="G413" t="n">
+        <v>2896982</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="I413" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J413" t="n">
+        <v>89.73</v>
+      </c>
+      <c r="K413" t="n">
+        <v>89.84</v>
+      </c>
+      <c r="L413" t="n">
+        <v>86.11</v>
+      </c>
+      <c r="M413" t="n">
+        <v>79.59</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>53.65</v>
+      </c>
+      <c r="O413" t="n">
+        <v>31</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31640,22 +31640,22 @@
         <v>86.48</v>
       </c>
       <c r="F413" t="n">
-        <v>88.81</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="G413" t="n">
-        <v>2896982</v>
+        <v>3869366</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>-0.83</v>
+        <v>-1.62</v>
       </c>
       <c r="I413" t="n">
         <v>5.3</v>
       </c>
       <c r="J413" t="n">
-        <v>89.73</v>
+        <v>89.7</v>
       </c>
       <c r="K413" t="n">
-        <v>89.84</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="L413" t="n">
         <v>86.11</v>
@@ -31664,7 +31664,7 @@
         <v>79.59</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>53.65</v>
+        <v>51.21</v>
       </c>
       <c r="O413" t="n">
         <v>31</v>
@@ -31681,16 +31681,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>16.7</v>
+        <v>17.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>152.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31495,7 +31495,7 @@
         <v>89.55</v>
       </c>
       <c r="G411" t="n">
-        <v>3329400</v>
+        <v>3360100</v>
       </c>
       <c r="H411" s="6" t="n">
         <v>1.74</v>
@@ -31555,28 +31555,44 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>86.64</v>
+      </c>
+      <c r="D412" t="n">
+        <v>89.03</v>
+      </c>
+      <c r="E412" t="n">
+        <v>86.48</v>
+      </c>
+      <c r="F412" t="n">
+        <v>88.09999999999999</v>
+      </c>
       <c r="G412" t="n">
-        <v>3869366</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
+        <v>3876400</v>
+      </c>
+      <c r="H412" s="1" t="n">
+        <v>-1.62</v>
       </c>
       <c r="I412" t="n">
         <v>5.3</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="K412" t="n">
+        <v>89.81999999999999</v>
+      </c>
+      <c r="L412" t="n">
+        <v>86.11</v>
+      </c>
+      <c r="M412" t="n">
+        <v>79.59</v>
+      </c>
       <c r="N412" s="2" t="n">
-        <v>56.44</v>
+        <v>51.21</v>
       </c>
       <c r="O412" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31595,9 +31611,7 @@
       <c r="T412" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U412" s="2" t="n">
-        <v>12</v>
-      </c>
+      <c r="U412" s="2" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="n">
         <v>152.1</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31592,7 +31592,7 @@
         <v>51.21</v>
       </c>
       <c r="O412" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31617,6 +31617,79 @@
         <v>152.1</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>87.98</v>
+      </c>
+      <c r="D413" t="n">
+        <v>88.17</v>
+      </c>
+      <c r="E413" t="n">
+        <v>86.79000000000001</v>
+      </c>
+      <c r="F413" t="n">
+        <v>87.04000000000001</v>
+      </c>
+      <c r="G413" t="n">
+        <v>1800411</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="I413" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J413" t="n">
+        <v>89.36</v>
+      </c>
+      <c r="K413" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="L413" t="n">
+        <v>86.31</v>
+      </c>
+      <c r="M413" t="n">
+        <v>79.67</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="O413" t="n">
+        <v>29</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -645,9 +645,7 @@
       <c r="T2" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U2" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="U2" s="2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" s="1" t="n">
         <v>173.2</v>
@@ -724,9 +722,7 @@
       <c r="T3" s="5" t="n">
         <v>17.9</v>
       </c>
-      <c r="U3" s="5" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U3" s="5" t="inlineStr"/>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" s="4" t="n">
         <v>168.6</v>
@@ -799,9 +795,7 @@
       <c r="T4" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U4" s="2" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="U4" s="2" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" s="1" t="n">
         <v>163.6</v>
@@ -874,9 +868,7 @@
       <c r="T5" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U5" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U5" s="2" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="1" t="n">
         <v>157.4</v>
@@ -949,9 +941,7 @@
       <c r="T6" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U6" s="2" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U6" s="2" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="1" t="n">
         <v>156.7</v>
@@ -1024,9 +1014,7 @@
       <c r="T7" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U7" s="2" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U7" s="2" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="1" t="n">
         <v>158.5</v>
@@ -1103,9 +1091,7 @@
       <c r="T8" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U8" s="2" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U8" s="2" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="1" t="n">
         <v>155.4</v>
@@ -1178,9 +1164,7 @@
       <c r="T9" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U9" s="2" t="n">
-        <v>15</v>
-      </c>
+      <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" s="1" t="n">
         <v>159.4</v>
@@ -1253,9 +1237,7 @@
       <c r="T10" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U10" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" s="1" t="n">
         <v>162.6</v>
@@ -1328,9 +1310,7 @@
       <c r="T11" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U11" s="2" t="n">
-        <v>15.8</v>
-      </c>
+      <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" s="1" t="n">
         <v>163.6</v>
@@ -1403,9 +1383,7 @@
       <c r="T12" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U12" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" s="1" t="n">
         <v>166.5</v>
@@ -1478,9 +1456,7 @@
       <c r="T13" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U13" s="2" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" s="1" t="n">
         <v>166.9</v>
@@ -1553,9 +1529,7 @@
       <c r="T14" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U14" s="2" t="n">
-        <v>14.1</v>
-      </c>
+      <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" s="1" t="n">
         <v>168.8</v>
@@ -1628,9 +1602,7 @@
       <c r="T15" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U15" s="2" t="n">
-        <v>12.8</v>
-      </c>
+      <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" s="1" t="n">
         <v>166.1</v>
@@ -1703,9 +1675,7 @@
       <c r="T16" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U16" s="2" t="n">
-        <v>11</v>
-      </c>
+      <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" s="1" t="n">
         <v>163.4</v>
@@ -1778,9 +1748,7 @@
       <c r="T17" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U17" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" s="1" t="n">
         <v>168</v>
@@ -1853,9 +1821,7 @@
       <c r="T18" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U18" s="2" t="n">
-        <v>9.300000000000001</v>
-      </c>
+      <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" s="1" t="n">
         <v>183.1</v>
@@ -1928,9 +1894,7 @@
       <c r="T19" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U19" s="2" t="n">
-        <v>9.300000000000001</v>
-      </c>
+      <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" s="1" t="n">
         <v>175.8</v>
@@ -2003,9 +1967,7 @@
       <c r="T20" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U20" s="2" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" s="1" t="n">
         <v>178.6</v>
@@ -2082,9 +2044,7 @@
       <c r="T21" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U21" s="2" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" s="1" t="n">
         <v>165</v>
@@ -2161,9 +2121,7 @@
       <c r="T22" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U22" s="2" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" s="1" t="n">
         <v>156.9</v>
@@ -2236,9 +2194,7 @@
       <c r="T23" s="2" t="n">
         <v>19.4</v>
       </c>
-      <c r="U23" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" s="1" t="n">
         <v>157.6</v>
@@ -2311,9 +2267,7 @@
       <c r="T24" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U24" s="2" t="n">
-        <v>20.5</v>
-      </c>
+      <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" s="2" t="n">
         <v>153.4</v>
@@ -2390,9 +2344,7 @@
       <c r="T25" s="5" t="n">
         <v>21.1</v>
       </c>
-      <c r="U25" s="5" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="U25" s="5" t="inlineStr"/>
       <c r="V25" s="3" t="inlineStr"/>
       <c r="W25" s="5" t="n">
         <v>149.3</v>
@@ -2465,9 +2417,7 @@
       <c r="T26" s="2" t="n">
         <v>19.6</v>
       </c>
-      <c r="U26" s="2" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" s="1" t="n">
         <v>157.9</v>
@@ -2544,9 +2494,7 @@
       <c r="T27" s="2" t="n">
         <v>22.8</v>
       </c>
-      <c r="U27" s="2" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" s="2" t="n">
         <v>154.3</v>
@@ -2623,9 +2571,7 @@
       <c r="T28" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U28" s="2" t="n">
-        <v>24.6</v>
-      </c>
+      <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" s="2" t="n">
         <v>151.4</v>
@@ -2698,9 +2644,7 @@
       <c r="T29" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="U29" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" s="2" t="n">
         <v>138.9</v>
@@ -2777,9 +2721,7 @@
       <c r="T30" s="5" t="n">
         <v>24.9</v>
       </c>
-      <c r="U30" s="7" t="n">
-        <v>31.1</v>
-      </c>
+      <c r="U30" s="5" t="inlineStr"/>
       <c r="V30" s="3" t="inlineStr"/>
       <c r="W30" s="5" t="n">
         <v>137.6</v>
@@ -2856,9 +2798,7 @@
       <c r="T31" s="2" t="n">
         <v>23.4</v>
       </c>
-      <c r="U31" s="2" t="n">
-        <v>24.7</v>
-      </c>
+      <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
       <c r="W31" s="2" t="n">
         <v>139.9</v>
@@ -2935,14 +2875,8 @@
       <c r="T32" s="7" t="n">
         <v>27.9</v>
       </c>
-      <c r="U32" s="7" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="V32" s="7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U32" s="5" t="inlineStr"/>
+      <c r="V32" s="3" t="inlineStr"/>
       <c r="W32" s="5" t="n">
         <v>146</v>
       </c>
@@ -3018,14 +2952,8 @@
       <c r="T33" s="6" t="n">
         <v>26.9</v>
       </c>
-      <c r="U33" s="6" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="V33" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" s="2" t="n">
         <v>132.8</v>
       </c>
@@ -3101,9 +3029,7 @@
       <c r="T34" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U34" s="2" t="n">
-        <v>23.2</v>
-      </c>
+      <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
       <c r="W34" s="2" t="n">
         <v>128.7</v>
@@ -3180,9 +3106,7 @@
       <c r="T35" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U35" s="2" t="n">
-        <v>23.4</v>
-      </c>
+      <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
       <c r="W35" s="2" t="n">
         <v>128.9</v>
@@ -3255,9 +3179,7 @@
       <c r="T36" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U36" s="2" t="n">
-        <v>21.4</v>
-      </c>
+      <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
       <c r="W36" s="2" t="n">
         <v>130.3</v>
@@ -3330,9 +3252,7 @@
       <c r="T37" s="2" t="n">
         <v>20.5</v>
       </c>
-      <c r="U37" s="2" t="n">
-        <v>16.4</v>
-      </c>
+      <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" s="2" t="n">
         <v>133.9</v>
@@ -3405,9 +3325,7 @@
       <c r="T38" s="2" t="n">
         <v>21.7</v>
       </c>
-      <c r="U38" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" s="2" t="n">
         <v>136.8</v>
@@ -3480,9 +3398,7 @@
       <c r="T39" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U39" s="2" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
       <c r="W39" s="2" t="n">
         <v>136.4</v>
@@ -3555,9 +3471,7 @@
       <c r="T40" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U40" s="2" t="n">
-        <v>18.6</v>
-      </c>
+      <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
       <c r="W40" s="2" t="n">
         <v>140.8</v>
@@ -3630,9 +3544,7 @@
       <c r="T41" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U41" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
       <c r="W41" s="2" t="n">
         <v>141.7</v>
@@ -3705,9 +3617,7 @@
       <c r="T42" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U42" s="2" t="n">
-        <v>13</v>
-      </c>
+      <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
       <c r="W42" s="2" t="n">
         <v>144</v>
@@ -3780,9 +3690,7 @@
       <c r="T43" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U43" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
       <c r="W43" s="2" t="n">
         <v>148.7</v>
@@ -3859,9 +3767,7 @@
       <c r="T44" s="2" t="n">
         <v>18.3</v>
       </c>
-      <c r="U44" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
       <c r="W44" s="2" t="n">
         <v>144.8</v>
@@ -3934,9 +3840,7 @@
       <c r="T45" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U45" s="2" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
       <c r="W45" s="2" t="n">
         <v>140.9</v>
@@ -4009,9 +3913,7 @@
       <c r="T46" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="U46" s="6" t="n">
-        <v>25.4</v>
-      </c>
+      <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
       <c r="W46" s="2" t="n">
         <v>139</v>
@@ -4084,9 +3986,7 @@
       <c r="T47" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="U47" s="2" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" t="inlineStr"/>
       <c r="W47" s="2" t="n">
         <v>148.6</v>
@@ -4159,9 +4059,7 @@
       <c r="T48" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U48" s="2" t="n">
-        <v>20.1</v>
-      </c>
+      <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" t="inlineStr"/>
       <c r="W48" s="2" t="n">
         <v>143</v>
@@ -4234,9 +4132,7 @@
       <c r="T49" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="U49" s="6" t="n">
-        <v>26.7</v>
-      </c>
+      <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" t="inlineStr"/>
       <c r="W49" s="2" t="n">
         <v>144.3</v>
@@ -4309,14 +4205,8 @@
       <c r="T50" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="U50" s="7" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="V50" s="7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U50" s="5" t="inlineStr"/>
+      <c r="V50" s="3" t="inlineStr"/>
       <c r="W50" s="5" t="n">
         <v>139.2</v>
       </c>
@@ -4392,14 +4282,8 @@
       <c r="T51" s="7" t="n">
         <v>45.3</v>
       </c>
-      <c r="U51" s="7" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="V51" s="7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U51" s="5" t="inlineStr"/>
+      <c r="V51" s="3" t="inlineStr"/>
       <c r="W51" s="5" t="n">
         <v>136.5</v>
       </c>
@@ -4475,14 +4359,8 @@
       <c r="T52" s="6" t="n">
         <v>47</v>
       </c>
-      <c r="U52" s="6" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="V52" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
       <c r="W52" s="2" t="n">
         <v>133.8</v>
       </c>
@@ -4558,14 +4436,8 @@
       <c r="T53" s="6" t="n">
         <v>52.3</v>
       </c>
-      <c r="U53" s="6" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="V53" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" s="2" t="n">
         <v>135.7</v>
       </c>
@@ -4637,14 +4509,8 @@
       <c r="T54" s="6" t="n">
         <v>33.6</v>
       </c>
-      <c r="U54" s="6" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="V54" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" s="2" t="n">
         <v>142.2</v>
       </c>
@@ -4716,14 +4582,8 @@
       <c r="T55" s="7" t="n">
         <v>40.7</v>
       </c>
-      <c r="U55" s="7" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="V55" s="7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U55" s="5" t="inlineStr"/>
+      <c r="V55" s="3" t="inlineStr"/>
       <c r="W55" s="5" t="n">
         <v>127.5</v>
       </c>
@@ -4795,14 +4655,8 @@
       <c r="T56" s="6" t="n">
         <v>37.6</v>
       </c>
-      <c r="U56" s="6" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="V56" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" s="2" t="n">
         <v>128.6</v>
       </c>
@@ -4874,9 +4728,7 @@
       <c r="T57" s="6" t="n">
         <v>30.9</v>
       </c>
-      <c r="U57" s="6" t="n">
-        <v>28.5</v>
-      </c>
+      <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
       <c r="W57" s="2" t="n">
         <v>135.7</v>
@@ -4949,9 +4801,7 @@
       <c r="T58" s="6" t="n">
         <v>30.1</v>
       </c>
-      <c r="U58" s="6" t="n">
-        <v>26</v>
-      </c>
+      <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
       <c r="W58" s="2" t="n">
         <v>135.8</v>
@@ -5024,14 +4874,8 @@
       <c r="T59" s="7" t="n">
         <v>32.6</v>
       </c>
-      <c r="U59" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="V59" s="7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U59" s="5" t="inlineStr"/>
+      <c r="V59" s="3" t="inlineStr"/>
       <c r="W59" s="5" t="n">
         <v>131.3</v>
       </c>
@@ -5103,14 +4947,8 @@
       <c r="T60" s="6" t="n">
         <v>29.6</v>
       </c>
-      <c r="U60" s="6" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="V60" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" s="2" t="n">
         <v>130</v>
       </c>
@@ -5182,9 +5020,7 @@
       <c r="T61" s="6" t="n">
         <v>33.8</v>
       </c>
-      <c r="U61" s="6" t="n">
-        <v>30.6</v>
-      </c>
+      <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" t="inlineStr"/>
       <c r="W61" s="6" t="n">
         <v>125.8</v>
@@ -5257,9 +5093,7 @@
       <c r="T62" s="6" t="n">
         <v>30.6</v>
       </c>
-      <c r="U62" s="6" t="n">
-        <v>29.1</v>
-      </c>
+      <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" t="inlineStr"/>
       <c r="W62" s="6" t="n">
         <v>125.9</v>
@@ -5332,14 +5166,8 @@
       <c r="T63" s="6" t="n">
         <v>28.5</v>
       </c>
-      <c r="U63" s="6" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="V63" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
       <c r="W63" s="6" t="n">
         <v>126.7</v>
       </c>
@@ -5411,9 +5239,7 @@
       <c r="T64" s="6" t="n">
         <v>26.5</v>
       </c>
-      <c r="U64" s="6" t="n">
-        <v>25.7</v>
-      </c>
+      <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
       <c r="W64" s="2" t="n">
         <v>129</v>
@@ -5486,9 +5312,7 @@
       <c r="T65" s="2" t="n">
         <v>24.8</v>
       </c>
-      <c r="U65" s="2" t="n">
-        <v>23.6</v>
-      </c>
+      <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" t="inlineStr"/>
       <c r="W65" s="2" t="n">
         <v>132.4</v>
@@ -5561,9 +5385,7 @@
       <c r="T66" s="6" t="n">
         <v>25.1</v>
       </c>
-      <c r="U66" s="2" t="n">
-        <v>21.4</v>
-      </c>
+      <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" t="inlineStr"/>
       <c r="W66" s="2" t="n">
         <v>131.3</v>
@@ -5636,9 +5458,7 @@
       <c r="T67" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U67" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" s="2" t="n">
         <v>134.3</v>
@@ -5711,9 +5531,7 @@
       <c r="T68" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U68" s="2" t="n">
-        <v>22.9</v>
-      </c>
+      <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" s="2" t="n">
         <v>132.7</v>
@@ -5786,9 +5604,7 @@
       <c r="T69" s="2" t="n">
         <v>24.6</v>
       </c>
-      <c r="U69" s="6" t="n">
-        <v>27.5</v>
-      </c>
+      <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" t="inlineStr"/>
       <c r="W69" s="2" t="n">
         <v>134.1</v>
@@ -5861,9 +5677,7 @@
       <c r="T70" s="2" t="n">
         <v>22.7</v>
       </c>
-      <c r="U70" s="2" t="n">
-        <v>20</v>
-      </c>
+      <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
       <c r="W70" s="2" t="n">
         <v>134.8</v>
@@ -5936,9 +5750,7 @@
       <c r="T71" s="2" t="n">
         <v>23.6</v>
       </c>
-      <c r="U71" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" t="inlineStr"/>
       <c r="W71" s="2" t="n">
         <v>134.1</v>
@@ -6011,9 +5823,7 @@
       <c r="T72" s="2" t="n">
         <v>24.8</v>
       </c>
-      <c r="U72" s="2" t="n">
-        <v>22.2</v>
-      </c>
+      <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" t="inlineStr"/>
       <c r="W72" s="2" t="n">
         <v>133.2</v>
@@ -6086,9 +5896,7 @@
       <c r="T73" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U73" s="2" t="n">
-        <v>19.8</v>
-      </c>
+      <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" t="inlineStr"/>
       <c r="W73" s="2" t="n">
         <v>132.2</v>
@@ -6161,9 +5969,7 @@
       <c r="T74" s="2" t="n">
         <v>22.5</v>
       </c>
-      <c r="U74" s="2" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" t="inlineStr"/>
       <c r="W74" s="2" t="n">
         <v>131.5</v>
@@ -6236,9 +6042,7 @@
       <c r="T75" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="U75" s="6" t="n">
-        <v>26.9</v>
-      </c>
+      <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" t="inlineStr"/>
       <c r="W75" s="2" t="n">
         <v>128.4</v>
@@ -6311,9 +6115,7 @@
       <c r="T76" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U76" s="2" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" t="inlineStr"/>
       <c r="W76" s="2" t="n">
         <v>137.7</v>
@@ -6386,9 +6188,7 @@
       <c r="T77" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U77" s="2" t="n">
-        <v>15.4</v>
-      </c>
+      <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" t="inlineStr"/>
       <c r="W77" s="2" t="n">
         <v>140.5</v>
@@ -6461,9 +6261,7 @@
       <c r="T78" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U78" s="2" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" t="inlineStr"/>
       <c r="W78" s="2" t="n">
         <v>138.9</v>
@@ -6536,9 +6334,7 @@
       <c r="T79" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U79" s="2" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" t="inlineStr"/>
       <c r="W79" s="2" t="n">
         <v>140.9</v>
@@ -6611,9 +6407,7 @@
       <c r="T80" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U80" s="2" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
       <c r="W80" s="2" t="n">
         <v>136</v>
@@ -6686,9 +6480,7 @@
       <c r="T81" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U81" s="2" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" t="inlineStr"/>
       <c r="W81" s="2" t="n">
         <v>135.9</v>
@@ -6761,9 +6553,7 @@
       <c r="T82" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U82" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" t="inlineStr"/>
       <c r="W82" s="2" t="n">
         <v>137.3</v>
@@ -6836,9 +6626,7 @@
       <c r="T83" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="U83" s="2" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" t="inlineStr"/>
       <c r="W83" s="2" t="n">
         <v>137.3</v>
@@ -6911,9 +6699,7 @@
       <c r="T84" s="2" t="n">
         <v>20.3</v>
       </c>
-      <c r="U84" s="2" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" t="inlineStr"/>
       <c r="W84" s="2" t="n">
         <v>139</v>
@@ -6990,9 +6776,7 @@
       <c r="T85" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="U85" s="2" t="n">
-        <v>21.7</v>
-      </c>
+      <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" t="inlineStr"/>
       <c r="W85" s="2" t="n">
         <v>139.3</v>
@@ -7065,9 +6849,7 @@
       <c r="T86" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U86" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" t="inlineStr"/>
       <c r="W86" s="2" t="n">
         <v>140.9</v>
@@ -7140,9 +6922,7 @@
       <c r="T87" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U87" s="2" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" t="inlineStr"/>
       <c r="W87" s="2" t="n">
         <v>137.6</v>
@@ -7215,9 +6995,7 @@
       <c r="T88" s="2" t="n">
         <v>19.2</v>
       </c>
-      <c r="U88" s="2" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" t="inlineStr"/>
       <c r="W88" s="2" t="n">
         <v>137.3</v>
@@ -7290,9 +7068,7 @@
       <c r="T89" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U89" s="2" t="n">
-        <v>17</v>
-      </c>
+      <c r="U89" s="2" t="inlineStr"/>
       <c r="V89" t="inlineStr"/>
       <c r="W89" s="2" t="n">
         <v>138.2</v>
@@ -7365,9 +7141,7 @@
       <c r="T90" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U90" s="2" t="n">
-        <v>13.3</v>
-      </c>
+      <c r="U90" s="2" t="inlineStr"/>
       <c r="V90" t="inlineStr"/>
       <c r="W90" s="2" t="n">
         <v>141</v>
@@ -7440,9 +7214,7 @@
       <c r="T91" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U91" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U91" s="2" t="inlineStr"/>
       <c r="V91" t="inlineStr"/>
       <c r="W91" s="2" t="n">
         <v>141.6</v>
@@ -7515,9 +7287,7 @@
       <c r="T92" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U92" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U92" s="2" t="inlineStr"/>
       <c r="V92" t="inlineStr"/>
       <c r="W92" s="2" t="n">
         <v>137.5</v>
@@ -7590,9 +7360,7 @@
       <c r="T93" s="2" t="n">
         <v>18.5</v>
       </c>
-      <c r="U93" s="2" t="n">
-        <v>19</v>
-      </c>
+      <c r="U93" s="2" t="inlineStr"/>
       <c r="V93" t="inlineStr"/>
       <c r="W93" s="2" t="n">
         <v>140.1</v>
@@ -7665,9 +7433,7 @@
       <c r="T94" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U94" s="2" t="n">
-        <v>14.3</v>
-      </c>
+      <c r="U94" s="2" t="inlineStr"/>
       <c r="V94" t="inlineStr"/>
       <c r="W94" s="2" t="n">
         <v>138.9</v>
@@ -7740,9 +7506,7 @@
       <c r="T95" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U95" s="2" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U95" s="2" t="inlineStr"/>
       <c r="V95" t="inlineStr"/>
       <c r="W95" s="2" t="n">
         <v>139.2</v>
@@ -7815,9 +7579,7 @@
       <c r="T96" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U96" s="2" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U96" s="2" t="inlineStr"/>
       <c r="V96" t="inlineStr"/>
       <c r="W96" s="2" t="n">
         <v>141.2</v>
@@ -7890,9 +7652,7 @@
       <c r="T97" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U97" s="2" t="n">
-        <v>13.9</v>
-      </c>
+      <c r="U97" s="2" t="inlineStr"/>
       <c r="V97" t="inlineStr"/>
       <c r="W97" s="2" t="n">
         <v>141.4</v>
@@ -7965,9 +7725,7 @@
       <c r="T98" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U98" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U98" s="2" t="inlineStr"/>
       <c r="V98" t="inlineStr"/>
       <c r="W98" s="2" t="n">
         <v>145.6</v>
@@ -8040,9 +7798,7 @@
       <c r="T99" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U99" s="2" t="n">
-        <v>21.7</v>
-      </c>
+      <c r="U99" s="2" t="inlineStr"/>
       <c r="V99" t="inlineStr"/>
       <c r="W99" s="2" t="n">
         <v>149.6</v>
@@ -8115,9 +7871,7 @@
       <c r="T100" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U100" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U100" s="2" t="inlineStr"/>
       <c r="V100" t="inlineStr"/>
       <c r="W100" s="1" t="n">
         <v>156.6</v>
@@ -8190,9 +7944,7 @@
       <c r="T101" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="U101" s="2" t="n">
-        <v>21</v>
-      </c>
+      <c r="U101" s="2" t="inlineStr"/>
       <c r="V101" t="inlineStr"/>
       <c r="W101" s="2" t="n">
         <v>154.4</v>
@@ -8265,9 +8017,7 @@
       <c r="T102" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="U102" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U102" s="2" t="inlineStr"/>
       <c r="V102" t="inlineStr"/>
       <c r="W102" s="2" t="n">
         <v>148.4</v>
@@ -8340,9 +8090,7 @@
       <c r="T103" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U103" s="2" t="n">
-        <v>18.4</v>
-      </c>
+      <c r="U103" s="2" t="inlineStr"/>
       <c r="V103" t="inlineStr"/>
       <c r="W103" s="2" t="n">
         <v>149.2</v>
@@ -8415,9 +8163,7 @@
       <c r="T104" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U104" s="2" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U104" s="2" t="inlineStr"/>
       <c r="V104" t="inlineStr"/>
       <c r="W104" s="2" t="n">
         <v>154.8</v>
@@ -8490,9 +8236,7 @@
       <c r="T105" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U105" s="2" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U105" s="2" t="inlineStr"/>
       <c r="V105" t="inlineStr"/>
       <c r="W105" s="1" t="n">
         <v>155</v>
@@ -8565,9 +8309,7 @@
       <c r="T106" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U106" s="2" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="U106" s="2" t="inlineStr"/>
       <c r="V106" t="inlineStr"/>
       <c r="W106" s="2" t="n">
         <v>152.2</v>
@@ -8640,9 +8382,7 @@
       <c r="T107" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U107" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U107" s="2" t="inlineStr"/>
       <c r="V107" t="inlineStr"/>
       <c r="W107" s="2" t="n">
         <v>147.5</v>
@@ -8715,9 +8455,7 @@
       <c r="T108" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U108" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U108" s="2" t="inlineStr"/>
       <c r="V108" t="inlineStr"/>
       <c r="W108" s="2" t="n">
         <v>143.4</v>
@@ -8790,9 +8528,7 @@
       <c r="T109" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U109" s="2" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U109" s="2" t="inlineStr"/>
       <c r="V109" t="inlineStr"/>
       <c r="W109" s="2" t="n">
         <v>139.6</v>
@@ -8865,9 +8601,7 @@
       <c r="T110" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U110" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="U110" s="2" t="inlineStr"/>
       <c r="V110" t="inlineStr"/>
       <c r="W110" s="2" t="n">
         <v>140.1</v>
@@ -8940,9 +8674,7 @@
       <c r="T111" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U111" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U111" s="2" t="inlineStr"/>
       <c r="V111" t="inlineStr"/>
       <c r="W111" s="2" t="n">
         <v>139.3</v>
@@ -9015,9 +8747,7 @@
       <c r="T112" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U112" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U112" s="2" t="inlineStr"/>
       <c r="V112" t="inlineStr"/>
       <c r="W112" s="2" t="n">
         <v>141.4</v>
@@ -9090,9 +8820,7 @@
       <c r="T113" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U113" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U113" s="2" t="inlineStr"/>
       <c r="V113" t="inlineStr"/>
       <c r="W113" s="2" t="n">
         <v>138</v>
@@ -9165,9 +8893,7 @@
       <c r="T114" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U114" s="2" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="U114" s="2" t="inlineStr"/>
       <c r="V114" t="inlineStr"/>
       <c r="W114" s="2" t="n">
         <v>140.8</v>
@@ -9240,9 +8966,7 @@
       <c r="T115" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U115" s="2" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U115" s="2" t="inlineStr"/>
       <c r="V115" t="inlineStr"/>
       <c r="W115" s="2" t="n">
         <v>141.8</v>
@@ -9315,9 +9039,7 @@
       <c r="T116" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U116" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U116" s="2" t="inlineStr"/>
       <c r="V116" t="inlineStr"/>
       <c r="W116" s="2" t="n">
         <v>143.3</v>
@@ -9390,9 +9112,7 @@
       <c r="T117" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U117" s="2" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U117" s="2" t="inlineStr"/>
       <c r="V117" t="inlineStr"/>
       <c r="W117" s="2" t="n">
         <v>145</v>
@@ -9465,9 +9185,7 @@
       <c r="T118" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U118" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U118" s="2" t="inlineStr"/>
       <c r="V118" t="inlineStr"/>
       <c r="W118" s="2" t="n">
         <v>147</v>
@@ -9540,9 +9258,7 @@
       <c r="T119" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U119" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U119" s="2" t="inlineStr"/>
       <c r="V119" t="inlineStr"/>
       <c r="W119" s="2" t="n">
         <v>143.7</v>
@@ -9615,9 +9331,7 @@
       <c r="T120" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U120" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U120" s="2" t="inlineStr"/>
       <c r="V120" t="inlineStr"/>
       <c r="W120" s="2" t="n">
         <v>146.7</v>
@@ -9690,9 +9404,7 @@
       <c r="T121" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U121" s="2" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U121" s="2" t="inlineStr"/>
       <c r="V121" t="inlineStr"/>
       <c r="W121" s="2" t="n">
         <v>151.1</v>
@@ -9765,9 +9477,7 @@
       <c r="T122" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U122" s="2" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U122" s="2" t="inlineStr"/>
       <c r="V122" t="inlineStr"/>
       <c r="W122" s="2" t="n">
         <v>150.4</v>
@@ -9840,9 +9550,7 @@
       <c r="T123" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U123" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U123" s="2" t="inlineStr"/>
       <c r="V123" t="inlineStr"/>
       <c r="W123" s="2" t="n">
         <v>154.8</v>
@@ -9915,9 +9623,7 @@
       <c r="T124" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U124" s="2" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="U124" s="2" t="inlineStr"/>
       <c r="V124" t="inlineStr"/>
       <c r="W124" s="2" t="n">
         <v>153.4</v>
@@ -9990,9 +9696,7 @@
       <c r="T125" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U125" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U125" s="2" t="inlineStr"/>
       <c r="V125" t="inlineStr"/>
       <c r="W125" s="1" t="n">
         <v>159.3</v>
@@ -10065,9 +9769,7 @@
       <c r="T126" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U126" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U126" s="2" t="inlineStr"/>
       <c r="V126" t="inlineStr"/>
       <c r="W126" s="1" t="n">
         <v>159.4</v>
@@ -10140,9 +9842,7 @@
       <c r="T127" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U127" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U127" s="2" t="inlineStr"/>
       <c r="V127" t="inlineStr"/>
       <c r="W127" s="2" t="n">
         <v>145.6</v>
@@ -10215,9 +9915,7 @@
       <c r="T128" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U128" s="2" t="n">
-        <v>7.9</v>
-      </c>
+      <c r="U128" s="2" t="inlineStr"/>
       <c r="V128" t="inlineStr"/>
       <c r="W128" s="2" t="n">
         <v>147.6</v>
@@ -10290,9 +9988,7 @@
       <c r="T129" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U129" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U129" s="2" t="inlineStr"/>
       <c r="V129" t="inlineStr"/>
       <c r="W129" s="2" t="n">
         <v>149.1</v>
@@ -10365,9 +10061,7 @@
       <c r="T130" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U130" s="2" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U130" s="2" t="inlineStr"/>
       <c r="V130" t="inlineStr"/>
       <c r="W130" s="2" t="n">
         <v>154.1</v>
@@ -10440,9 +10134,7 @@
       <c r="T131" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U131" s="2" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U131" s="2" t="inlineStr"/>
       <c r="V131" t="inlineStr"/>
       <c r="W131" s="2" t="n">
         <v>152.3</v>
@@ -10519,9 +10211,7 @@
       <c r="T132" s="2" t="n">
         <v>20.4</v>
       </c>
-      <c r="U132" s="2" t="n">
-        <v>20</v>
-      </c>
+      <c r="U132" s="2" t="inlineStr"/>
       <c r="V132" t="inlineStr"/>
       <c r="W132" s="1" t="n">
         <v>155.5</v>
@@ -10594,9 +10284,7 @@
       <c r="T133" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U133" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U133" s="2" t="inlineStr"/>
       <c r="V133" t="inlineStr"/>
       <c r="W133" s="1" t="n">
         <v>159.3</v>
@@ -10673,9 +10361,7 @@
       <c r="T134" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U134" s="2" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U134" s="2" t="inlineStr"/>
       <c r="V134" t="inlineStr"/>
       <c r="W134" s="2" t="n">
         <v>149.9</v>
@@ -10748,9 +10434,7 @@
       <c r="T135" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U135" s="2" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="U135" s="2" t="inlineStr"/>
       <c r="V135" t="inlineStr"/>
       <c r="W135" s="2" t="n">
         <v>149.7</v>
@@ -10823,9 +10507,7 @@
       <c r="T136" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U136" s="2" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U136" s="2" t="inlineStr"/>
       <c r="V136" t="inlineStr"/>
       <c r="W136" s="2" t="n">
         <v>147</v>
@@ -10898,9 +10580,7 @@
       <c r="T137" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U137" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U137" s="2" t="inlineStr"/>
       <c r="V137" t="inlineStr"/>
       <c r="W137" s="2" t="n">
         <v>147.5</v>
@@ -10973,9 +10653,7 @@
       <c r="T138" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U138" s="2" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U138" s="2" t="inlineStr"/>
       <c r="V138" t="inlineStr"/>
       <c r="W138" s="2" t="n">
         <v>148.6</v>
@@ -11048,9 +10726,7 @@
       <c r="T139" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="U139" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U139" s="2" t="inlineStr"/>
       <c r="V139" t="inlineStr"/>
       <c r="W139" s="2" t="n">
         <v>151.4</v>
@@ -11123,9 +10799,7 @@
       <c r="T140" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U140" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U140" s="2" t="inlineStr"/>
       <c r="V140" t="inlineStr"/>
       <c r="W140" s="2" t="n">
         <v>153.1</v>
@@ -11198,9 +10872,7 @@
       <c r="T141" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U141" s="2" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U141" s="2" t="inlineStr"/>
       <c r="V141" t="inlineStr"/>
       <c r="W141" s="2" t="n">
         <v>150.6</v>
@@ -11273,9 +10945,7 @@
       <c r="T142" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U142" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U142" s="2" t="inlineStr"/>
       <c r="V142" t="inlineStr"/>
       <c r="W142" s="2" t="n">
         <v>153.8</v>
@@ -11348,9 +11018,7 @@
       <c r="T143" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U143" s="2" t="n">
-        <v>7.8</v>
-      </c>
+      <c r="U143" s="2" t="inlineStr"/>
       <c r="V143" t="inlineStr"/>
       <c r="W143" s="2" t="n">
         <v>153.9</v>
@@ -11427,9 +11095,7 @@
       <c r="T144" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U144" s="2" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U144" s="2" t="inlineStr"/>
       <c r="V144" t="inlineStr"/>
       <c r="W144" s="2" t="n">
         <v>153.2</v>
@@ -11502,9 +11168,7 @@
       <c r="T145" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U145" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U145" s="2" t="inlineStr"/>
       <c r="V145" t="inlineStr"/>
       <c r="W145" s="2" t="n">
         <v>144.6</v>
@@ -11577,9 +11241,7 @@
       <c r="T146" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U146" s="2" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U146" s="2" t="inlineStr"/>
       <c r="V146" t="inlineStr"/>
       <c r="W146" s="2" t="n">
         <v>144.3</v>
@@ -11652,9 +11314,7 @@
       <c r="T147" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="U147" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U147" s="2" t="inlineStr"/>
       <c r="V147" t="inlineStr"/>
       <c r="W147" s="2" t="n">
         <v>146.4</v>
@@ -11731,9 +11391,7 @@
       <c r="T148" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U148" s="2" t="n">
-        <v>8.1</v>
-      </c>
+      <c r="U148" s="2" t="inlineStr"/>
       <c r="V148" t="inlineStr"/>
       <c r="W148" s="2" t="n">
         <v>150</v>
@@ -11806,9 +11464,7 @@
       <c r="T149" s="2" t="n">
         <v>14.6</v>
       </c>
-      <c r="U149" s="2" t="n">
-        <v>7.8</v>
-      </c>
+      <c r="U149" s="2" t="inlineStr"/>
       <c r="V149" t="inlineStr"/>
       <c r="W149" s="1" t="n">
         <v>156.5</v>
@@ -11881,9 +11537,7 @@
       <c r="T150" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U150" s="2" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U150" s="2" t="inlineStr"/>
       <c r="V150" t="inlineStr"/>
       <c r="W150" s="2" t="n">
         <v>150.9</v>
@@ -11956,9 +11610,7 @@
       <c r="T151" s="2" t="n">
         <v>14.4</v>
       </c>
-      <c r="U151" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U151" s="2" t="inlineStr"/>
       <c r="V151" t="inlineStr"/>
       <c r="W151" s="2" t="n">
         <v>152.5</v>
@@ -12035,9 +11687,7 @@
       <c r="T152" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U152" s="2" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U152" s="2" t="inlineStr"/>
       <c r="V152" t="inlineStr"/>
       <c r="W152" s="2" t="n">
         <v>152.1</v>
@@ -12110,9 +11760,7 @@
       <c r="T153" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U153" s="2" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="U153" s="2" t="inlineStr"/>
       <c r="V153" t="inlineStr"/>
       <c r="W153" s="2" t="n">
         <v>151.5</v>
@@ -12185,9 +11833,7 @@
       <c r="T154" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U154" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U154" s="2" t="inlineStr"/>
       <c r="V154" t="inlineStr"/>
       <c r="W154" s="2" t="n">
         <v>150.2</v>
@@ -12260,9 +11906,7 @@
       <c r="T155" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U155" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U155" s="2" t="inlineStr"/>
       <c r="V155" t="inlineStr"/>
       <c r="W155" s="2" t="n">
         <v>154</v>
@@ -12335,9 +11979,7 @@
       <c r="T156" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="U156" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U156" s="2" t="inlineStr"/>
       <c r="V156" t="inlineStr"/>
       <c r="W156" s="2" t="n">
         <v>148.2</v>
@@ -12410,9 +12052,7 @@
       <c r="T157" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U157" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
+      <c r="U157" s="2" t="inlineStr"/>
       <c r="V157" t="inlineStr"/>
       <c r="W157" s="2" t="n">
         <v>148.8</v>
@@ -12485,9 +12125,7 @@
       <c r="T158" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U158" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U158" s="2" t="inlineStr"/>
       <c r="V158" t="inlineStr"/>
       <c r="W158" s="2" t="n">
         <v>150.9</v>
@@ -12560,9 +12198,7 @@
       <c r="T159" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U159" s="2" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U159" s="2" t="inlineStr"/>
       <c r="V159" t="inlineStr"/>
       <c r="W159" s="2" t="n">
         <v>151.9</v>
@@ -12635,9 +12271,7 @@
       <c r="T160" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="U160" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U160" s="2" t="inlineStr"/>
       <c r="V160" t="inlineStr"/>
       <c r="W160" s="2" t="n">
         <v>147.6</v>
@@ -12710,9 +12344,7 @@
       <c r="T161" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U161" s="2" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U161" s="2" t="inlineStr"/>
       <c r="V161" t="inlineStr"/>
       <c r="W161" s="2" t="n">
         <v>149.5</v>
@@ -12785,9 +12417,7 @@
       <c r="T162" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U162" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="U162" s="2" t="inlineStr"/>
       <c r="V162" t="inlineStr"/>
       <c r="W162" s="2" t="n">
         <v>152.1</v>
@@ -12860,9 +12490,7 @@
       <c r="T163" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U163" s="2" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U163" s="2" t="inlineStr"/>
       <c r="V163" t="inlineStr"/>
       <c r="W163" s="2" t="n">
         <v>148.2</v>
@@ -12935,9 +12563,7 @@
       <c r="T164" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U164" s="2" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="U164" s="2" t="inlineStr"/>
       <c r="V164" t="inlineStr"/>
       <c r="W164" s="2" t="n">
         <v>146.4</v>
@@ -12961,7 +12587,7 @@
         <v>67.98999999999999</v>
       </c>
       <c r="E165" t="n">
-        <v>66.84</v>
+        <v>66.83</v>
       </c>
       <c r="F165" t="n">
         <v>67.38</v>
@@ -13010,9 +12636,7 @@
       <c r="T165" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U165" s="2" t="n">
-        <v>14.4</v>
-      </c>
+      <c r="U165" s="2" t="inlineStr"/>
       <c r="V165" t="inlineStr"/>
       <c r="W165" s="2" t="n">
         <v>148.2</v>
@@ -13085,9 +12709,7 @@
       <c r="T166" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U166" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U166" s="2" t="inlineStr"/>
       <c r="V166" t="inlineStr"/>
       <c r="W166" s="2" t="n">
         <v>147</v>
@@ -13160,9 +12782,7 @@
       <c r="T167" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U167" s="2" t="n">
-        <v>9.1</v>
-      </c>
+      <c r="U167" s="2" t="inlineStr"/>
       <c r="V167" t="inlineStr"/>
       <c r="W167" s="2" t="n">
         <v>145.5</v>
@@ -13235,9 +12855,7 @@
       <c r="T168" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U168" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="U168" s="2" t="inlineStr"/>
       <c r="V168" t="inlineStr"/>
       <c r="W168" s="2" t="n">
         <v>146.5</v>
@@ -13310,9 +12928,7 @@
       <c r="T169" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U169" s="2" t="n">
-        <v>9.4</v>
-      </c>
+      <c r="U169" s="2" t="inlineStr"/>
       <c r="V169" t="inlineStr"/>
       <c r="W169" s="2" t="n">
         <v>145.9</v>
@@ -13385,9 +13001,7 @@
       <c r="T170" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U170" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U170" s="2" t="inlineStr"/>
       <c r="V170" t="inlineStr"/>
       <c r="W170" s="2" t="n">
         <v>145.9</v>
@@ -13460,9 +13074,7 @@
       <c r="T171" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U171" s="2" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U171" s="2" t="inlineStr"/>
       <c r="V171" t="inlineStr"/>
       <c r="W171" s="2" t="n">
         <v>141.5</v>
@@ -13535,9 +13147,7 @@
       <c r="T172" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U172" s="2" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U172" s="2" t="inlineStr"/>
       <c r="V172" t="inlineStr"/>
       <c r="W172" s="2" t="n">
         <v>143</v>
@@ -13610,9 +13220,7 @@
       <c r="T173" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U173" s="2" t="n">
-        <v>12</v>
-      </c>
+      <c r="U173" s="2" t="inlineStr"/>
       <c r="V173" t="inlineStr"/>
       <c r="W173" s="2" t="n">
         <v>143.4</v>
@@ -13685,9 +13293,7 @@
       <c r="T174" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U174" s="2" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U174" s="2" t="inlineStr"/>
       <c r="V174" t="inlineStr"/>
       <c r="W174" s="2" t="n">
         <v>143.7</v>
@@ -13760,9 +13366,7 @@
       <c r="T175" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U175" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U175" s="2" t="inlineStr"/>
       <c r="V175" t="inlineStr"/>
       <c r="W175" s="2" t="n">
         <v>145.9</v>
@@ -13835,9 +13439,7 @@
       <c r="T176" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U176" s="2" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U176" s="2" t="inlineStr"/>
       <c r="V176" t="inlineStr"/>
       <c r="W176" s="2" t="n">
         <v>144.6</v>
@@ -13910,9 +13512,7 @@
       <c r="T177" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U177" s="2" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="U177" s="2" t="inlineStr"/>
       <c r="V177" t="inlineStr"/>
       <c r="W177" s="2" t="n">
         <v>142.5</v>
@@ -13985,9 +13585,7 @@
       <c r="T178" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U178" s="2" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U178" s="2" t="inlineStr"/>
       <c r="V178" t="inlineStr"/>
       <c r="W178" s="2" t="n">
         <v>145.2</v>
@@ -14060,9 +13658,7 @@
       <c r="T179" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U179" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U179" s="2" t="inlineStr"/>
       <c r="V179" t="inlineStr"/>
       <c r="W179" s="2" t="n">
         <v>145.8</v>
@@ -14135,9 +13731,7 @@
       <c r="T180" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U180" s="2" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U180" s="2" t="inlineStr"/>
       <c r="V180" t="inlineStr"/>
       <c r="W180" s="2" t="n">
         <v>145.3</v>
@@ -14214,9 +13808,7 @@
       <c r="T181" s="5" t="n">
         <v>21.7</v>
       </c>
-      <c r="U181" s="7" t="n">
-        <v>25.7</v>
-      </c>
+      <c r="U181" s="5" t="inlineStr"/>
       <c r="V181" s="3" t="inlineStr"/>
       <c r="W181" s="5" t="n">
         <v>138.9</v>
@@ -14289,9 +13881,7 @@
       <c r="T182" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U182" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U182" s="2" t="inlineStr"/>
       <c r="V182" t="inlineStr"/>
       <c r="W182" s="2" t="n">
         <v>142.8</v>
@@ -14368,9 +13958,7 @@
       <c r="T183" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U183" s="2" t="n">
-        <v>17.7</v>
-      </c>
+      <c r="U183" s="2" t="inlineStr"/>
       <c r="V183" t="inlineStr"/>
       <c r="W183" s="2" t="n">
         <v>146.5</v>
@@ -14443,9 +14031,7 @@
       <c r="T184" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U184" s="2" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U184" s="2" t="inlineStr"/>
       <c r="V184" t="inlineStr"/>
       <c r="W184" s="2" t="n">
         <v>145</v>
@@ -14522,9 +14108,7 @@
       <c r="T185" s="6" t="n">
         <v>25.3</v>
       </c>
-      <c r="U185" s="2" t="n">
-        <v>23.8</v>
-      </c>
+      <c r="U185" s="2" t="inlineStr"/>
       <c r="V185" t="inlineStr"/>
       <c r="W185" s="2" t="n">
         <v>147.1</v>
@@ -14597,9 +14181,7 @@
       <c r="T186" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U186" s="2" t="n">
-        <v>17.9</v>
-      </c>
+      <c r="U186" s="2" t="inlineStr"/>
       <c r="V186" t="inlineStr"/>
       <c r="W186" s="2" t="n">
         <v>147.6</v>
@@ -14672,9 +14254,7 @@
       <c r="T187" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U187" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U187" s="2" t="inlineStr"/>
       <c r="V187" t="inlineStr"/>
       <c r="W187" s="2" t="n">
         <v>151.3</v>
@@ -14747,9 +14327,7 @@
       <c r="T188" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U188" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U188" s="2" t="inlineStr"/>
       <c r="V188" t="inlineStr"/>
       <c r="W188" s="2" t="n">
         <v>149.9</v>
@@ -14822,9 +14400,7 @@
       <c r="T189" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U189" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U189" s="2" t="inlineStr"/>
       <c r="V189" t="inlineStr"/>
       <c r="W189" s="2" t="n">
         <v>152.9</v>
@@ -14897,9 +14473,7 @@
       <c r="T190" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U190" s="2" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U190" s="2" t="inlineStr"/>
       <c r="V190" t="inlineStr"/>
       <c r="W190" s="2" t="n">
         <v>154.3</v>
@@ -14972,9 +14546,7 @@
       <c r="T191" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U191" s="2" t="n">
-        <v>14.5</v>
-      </c>
+      <c r="U191" s="2" t="inlineStr"/>
       <c r="V191" t="inlineStr"/>
       <c r="W191" s="2" t="n">
         <v>153.5</v>
@@ -15047,9 +14619,7 @@
       <c r="T192" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U192" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U192" s="2" t="inlineStr"/>
       <c r="V192" t="inlineStr"/>
       <c r="W192" s="2" t="n">
         <v>148.5</v>
@@ -15122,9 +14692,7 @@
       <c r="T193" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U193" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U193" s="2" t="inlineStr"/>
       <c r="V193" t="inlineStr"/>
       <c r="W193" s="2" t="n">
         <v>140.4</v>
@@ -15197,9 +14765,7 @@
       <c r="T194" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U194" s="2" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U194" s="2" t="inlineStr"/>
       <c r="V194" t="inlineStr"/>
       <c r="W194" s="2" t="n">
         <v>139.4</v>
@@ -15272,9 +14838,7 @@
       <c r="T195" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U195" s="2" t="n">
-        <v>14.2</v>
-      </c>
+      <c r="U195" s="2" t="inlineStr"/>
       <c r="V195" t="inlineStr"/>
       <c r="W195" s="2" t="n">
         <v>141.1</v>
@@ -15347,9 +14911,7 @@
       <c r="T196" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U196" s="2" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U196" s="2" t="inlineStr"/>
       <c r="V196" t="inlineStr"/>
       <c r="W196" s="2" t="n">
         <v>142.8</v>
@@ -15422,9 +14984,7 @@
       <c r="T197" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U197" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U197" s="2" t="inlineStr"/>
       <c r="V197" t="inlineStr"/>
       <c r="W197" s="2" t="n">
         <v>142</v>
@@ -15497,9 +15057,7 @@
       <c r="T198" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U198" s="2" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U198" s="2" t="inlineStr"/>
       <c r="V198" t="inlineStr"/>
       <c r="W198" s="2" t="n">
         <v>144</v>
@@ -15572,9 +15130,7 @@
       <c r="T199" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U199" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U199" s="2" t="inlineStr"/>
       <c r="V199" t="inlineStr"/>
       <c r="W199" s="2" t="n">
         <v>143.6</v>
@@ -15651,9 +15207,7 @@
       <c r="T200" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U200" s="2" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U200" s="2" t="inlineStr"/>
       <c r="V200" t="inlineStr"/>
       <c r="W200" s="2" t="n">
         <v>143.5</v>
@@ -15726,9 +15280,7 @@
       <c r="T201" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U201" s="2" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U201" s="2" t="inlineStr"/>
       <c r="V201" t="inlineStr"/>
       <c r="W201" s="2" t="n">
         <v>141.3</v>
@@ -15801,9 +15353,7 @@
       <c r="T202" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U202" s="2" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U202" s="2" t="inlineStr"/>
       <c r="V202" t="inlineStr"/>
       <c r="W202" s="2" t="n">
         <v>142.9</v>
@@ -15876,9 +15426,7 @@
       <c r="T203" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U203" s="2" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U203" s="2" t="inlineStr"/>
       <c r="V203" t="inlineStr"/>
       <c r="W203" s="2" t="n">
         <v>143.4</v>
@@ -15951,9 +15499,7 @@
       <c r="T204" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U204" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U204" s="2" t="inlineStr"/>
       <c r="V204" t="inlineStr"/>
       <c r="W204" s="2" t="n">
         <v>138.6</v>
@@ -16030,9 +15576,7 @@
       <c r="T205" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="U205" s="2" t="n">
-        <v>17</v>
-      </c>
+      <c r="U205" s="2" t="inlineStr"/>
       <c r="V205" t="inlineStr"/>
       <c r="W205" s="2" t="n">
         <v>142.5</v>
@@ -16105,9 +15649,7 @@
       <c r="T206" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U206" s="2" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="U206" s="2" t="inlineStr"/>
       <c r="V206" t="inlineStr"/>
       <c r="W206" s="2" t="n">
         <v>137.9</v>
@@ -16184,9 +15726,7 @@
       <c r="T207" s="2" t="n">
         <v>22.4</v>
       </c>
-      <c r="U207" s="2" t="n">
-        <v>19.4</v>
-      </c>
+      <c r="U207" s="2" t="inlineStr"/>
       <c r="V207" t="inlineStr"/>
       <c r="W207" s="2" t="n">
         <v>140.9</v>
@@ -16259,9 +15799,7 @@
       <c r="T208" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U208" s="2" t="n">
-        <v>20.9</v>
-      </c>
+      <c r="U208" s="2" t="inlineStr"/>
       <c r="V208" t="inlineStr"/>
       <c r="W208" s="2" t="n">
         <v>143</v>
@@ -16334,9 +15872,7 @@
       <c r="T209" s="2" t="n">
         <v>23.7</v>
       </c>
-      <c r="U209" s="6" t="n">
-        <v>26.9</v>
-      </c>
+      <c r="U209" s="2" t="inlineStr"/>
       <c r="V209" t="inlineStr"/>
       <c r="W209" s="2" t="n">
         <v>143.1</v>
@@ -16409,14 +15945,8 @@
       <c r="T210" s="6" t="n">
         <v>26.4</v>
       </c>
-      <c r="U210" s="6" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="V210" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U210" s="2" t="inlineStr"/>
+      <c r="V210" t="inlineStr"/>
       <c r="W210" s="2" t="n">
         <v>145</v>
       </c>
@@ -16488,9 +16018,7 @@
       <c r="T211" s="2" t="n">
         <v>23.4</v>
       </c>
-      <c r="U211" s="2" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="U211" s="2" t="inlineStr"/>
       <c r="V211" t="inlineStr"/>
       <c r="W211" s="2" t="n">
         <v>148.3</v>
@@ -16563,9 +16091,7 @@
       <c r="T212" s="2" t="n">
         <v>20.5</v>
       </c>
-      <c r="U212" s="2" t="n">
-        <v>14.3</v>
-      </c>
+      <c r="U212" s="2" t="inlineStr"/>
       <c r="V212" t="inlineStr"/>
       <c r="W212" s="2" t="n">
         <v>148.6</v>
@@ -16638,9 +16164,7 @@
       <c r="T213" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U213" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U213" s="2" t="inlineStr"/>
       <c r="V213" t="inlineStr"/>
       <c r="W213" s="2" t="n">
         <v>151.7</v>
@@ -16713,9 +16237,7 @@
       <c r="T214" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U214" s="2" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U214" s="2" t="inlineStr"/>
       <c r="V214" t="inlineStr"/>
       <c r="W214" s="2" t="n">
         <v>145</v>
@@ -16788,9 +16310,7 @@
       <c r="T215" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U215" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U215" s="2" t="inlineStr"/>
       <c r="V215" t="inlineStr"/>
       <c r="W215" s="2" t="n">
         <v>143</v>
@@ -16863,9 +16383,7 @@
       <c r="T216" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U216" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U216" s="2" t="inlineStr"/>
       <c r="V216" t="inlineStr"/>
       <c r="W216" s="2" t="n">
         <v>144.9</v>
@@ -16938,9 +16456,7 @@
       <c r="T217" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U217" s="2" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="U217" s="2" t="inlineStr"/>
       <c r="V217" t="inlineStr"/>
       <c r="W217" s="2" t="n">
         <v>144.9</v>
@@ -17013,9 +16529,7 @@
       <c r="T218" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U218" s="2" t="n">
-        <v>9.800000000000001</v>
-      </c>
+      <c r="U218" s="2" t="inlineStr"/>
       <c r="V218" t="inlineStr"/>
       <c r="W218" s="2" t="n">
         <v>149.2</v>
@@ -17088,9 +16602,7 @@
       <c r="T219" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U219" s="2" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U219" s="2" t="inlineStr"/>
       <c r="V219" t="inlineStr"/>
       <c r="W219" s="2" t="n">
         <v>148.9</v>
@@ -17163,9 +16675,7 @@
       <c r="T220" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U220" s="2" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U220" s="2" t="inlineStr"/>
       <c r="V220" t="inlineStr"/>
       <c r="W220" s="2" t="n">
         <v>148.8</v>
@@ -17238,9 +16748,7 @@
       <c r="T221" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U221" s="2" t="n">
-        <v>9.4</v>
-      </c>
+      <c r="U221" s="2" t="inlineStr"/>
       <c r="V221" t="inlineStr"/>
       <c r="W221" s="2" t="n">
         <v>150.6</v>
@@ -17313,9 +16821,7 @@
       <c r="T222" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U222" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U222" s="2" t="inlineStr"/>
       <c r="V222" t="inlineStr"/>
       <c r="W222" s="2" t="n">
         <v>150.3</v>
@@ -17388,9 +16894,7 @@
       <c r="T223" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U223" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U223" s="2" t="inlineStr"/>
       <c r="V223" t="inlineStr"/>
       <c r="W223" s="2" t="n">
         <v>147.6</v>
@@ -17463,9 +16967,7 @@
       <c r="T224" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U224" s="2" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U224" s="2" t="inlineStr"/>
       <c r="V224" t="inlineStr"/>
       <c r="W224" s="2" t="n">
         <v>148.3</v>
@@ -17542,9 +17044,7 @@
       <c r="T225" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U225" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U225" s="2" t="inlineStr"/>
       <c r="V225" t="inlineStr"/>
       <c r="W225" s="2" t="n">
         <v>153.6</v>
@@ -17617,9 +17117,7 @@
       <c r="T226" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U226" s="2" t="n">
-        <v>12.9</v>
-      </c>
+      <c r="U226" s="2" t="inlineStr"/>
       <c r="V226" t="inlineStr"/>
       <c r="W226" s="1" t="n">
         <v>161.9</v>
@@ -17692,9 +17190,7 @@
       <c r="T227" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U227" s="2" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U227" s="2" t="inlineStr"/>
       <c r="V227" t="inlineStr"/>
       <c r="W227" s="1" t="n">
         <v>157</v>
@@ -17767,9 +17263,7 @@
       <c r="T228" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U228" s="2" t="n">
-        <v>16.9</v>
-      </c>
+      <c r="U228" s="2" t="inlineStr"/>
       <c r="V228" t="inlineStr"/>
       <c r="W228" s="2" t="n">
         <v>153.5</v>
@@ -17842,9 +17336,7 @@
       <c r="T229" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U229" s="2" t="n">
-        <v>15.8</v>
-      </c>
+      <c r="U229" s="2" t="inlineStr"/>
       <c r="V229" t="inlineStr"/>
       <c r="W229" s="1" t="n">
         <v>155.4</v>
@@ -17917,9 +17409,7 @@
       <c r="T230" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U230" s="2" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="U230" s="2" t="inlineStr"/>
       <c r="V230" t="inlineStr"/>
       <c r="W230" s="1" t="n">
         <v>155.9</v>
@@ -17992,9 +17482,7 @@
       <c r="T231" s="2" t="n">
         <v>14.1</v>
       </c>
-      <c r="U231" s="2" t="n">
-        <v>7.7</v>
-      </c>
+      <c r="U231" s="2" t="inlineStr"/>
       <c r="V231" t="inlineStr"/>
       <c r="W231" s="1" t="n">
         <v>159.9</v>
@@ -18067,9 +17555,7 @@
       <c r="T232" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="U232" s="2" t="n">
-        <v>7.6</v>
-      </c>
+      <c r="U232" s="2" t="inlineStr"/>
       <c r="V232" t="inlineStr"/>
       <c r="W232" s="1" t="n">
         <v>160.5</v>
@@ -18142,9 +17628,7 @@
       <c r="T233" s="2" t="n">
         <v>13.5</v>
       </c>
-      <c r="U233" s="2" t="n">
-        <v>7.4</v>
-      </c>
+      <c r="U233" s="2" t="inlineStr"/>
       <c r="V233" t="inlineStr"/>
       <c r="W233" s="1" t="n">
         <v>160.5</v>
@@ -18217,9 +17701,7 @@
       <c r="T234" s="2" t="n">
         <v>13.6</v>
       </c>
-      <c r="U234" s="2" t="n">
-        <v>7.7</v>
-      </c>
+      <c r="U234" s="2" t="inlineStr"/>
       <c r="V234" t="inlineStr"/>
       <c r="W234" s="2" t="n">
         <v>151.4</v>
@@ -18292,9 +17774,7 @@
       <c r="T235" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="U235" s="2" t="n">
-        <v>8.800000000000001</v>
-      </c>
+      <c r="U235" s="2" t="inlineStr"/>
       <c r="V235" t="inlineStr"/>
       <c r="W235" s="2" t="n">
         <v>150.5</v>
@@ -18371,9 +17851,7 @@
       <c r="T236" s="2" t="n">
         <v>14.3</v>
       </c>
-      <c r="U236" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U236" s="2" t="inlineStr"/>
       <c r="V236" t="inlineStr"/>
       <c r="W236" s="2" t="n">
         <v>148.3</v>
@@ -18450,9 +17928,7 @@
       <c r="T237" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U237" s="2" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U237" s="2" t="inlineStr"/>
       <c r="V237" t="inlineStr"/>
       <c r="W237" s="2" t="n">
         <v>148.7</v>
@@ -18525,9 +18001,7 @@
       <c r="T238" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U238" s="2" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U238" s="2" t="inlineStr"/>
       <c r="V238" t="inlineStr"/>
       <c r="W238" s="2" t="n">
         <v>141.9</v>
@@ -18600,9 +18074,7 @@
       <c r="T239" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U239" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
+      <c r="U239" s="2" t="inlineStr"/>
       <c r="V239" t="inlineStr"/>
       <c r="W239" s="2" t="n">
         <v>142.4</v>
@@ -18675,9 +18147,7 @@
       <c r="T240" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U240" s="2" t="n">
-        <v>8</v>
-      </c>
+      <c r="U240" s="2" t="inlineStr"/>
       <c r="V240" t="inlineStr"/>
       <c r="W240" s="2" t="n">
         <v>146.2</v>
@@ -18750,9 +18220,7 @@
       <c r="T241" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U241" s="2" t="n">
-        <v>9.199999999999999</v>
-      </c>
+      <c r="U241" s="2" t="inlineStr"/>
       <c r="V241" t="inlineStr"/>
       <c r="W241" s="2" t="n">
         <v>143.6</v>
@@ -18825,9 +18293,7 @@
       <c r="T242" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U242" s="2" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U242" s="2" t="inlineStr"/>
       <c r="V242" t="inlineStr"/>
       <c r="W242" s="2" t="n">
         <v>147.1</v>
@@ -18900,9 +18366,7 @@
       <c r="T243" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U243" s="2" t="n">
-        <v>8.5</v>
-      </c>
+      <c r="U243" s="2" t="inlineStr"/>
       <c r="V243" t="inlineStr"/>
       <c r="W243" s="2" t="n">
         <v>146</v>
@@ -18975,9 +18439,7 @@
       <c r="T244" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U244" s="2" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U244" s="2" t="inlineStr"/>
       <c r="V244" t="inlineStr"/>
       <c r="W244" s="2" t="n">
         <v>149.8</v>
@@ -19050,9 +18512,7 @@
       <c r="T245" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U245" s="2" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U245" s="2" t="inlineStr"/>
       <c r="V245" t="inlineStr"/>
       <c r="W245" s="2" t="n">
         <v>151.6</v>
@@ -19125,9 +18585,7 @@
       <c r="T246" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U246" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U246" s="2" t="inlineStr"/>
       <c r="V246" t="inlineStr"/>
       <c r="W246" s="2" t="n">
         <v>152.5</v>
@@ -19200,9 +18658,7 @@
       <c r="T247" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U247" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U247" s="2" t="inlineStr"/>
       <c r="V247" t="inlineStr"/>
       <c r="W247" s="2" t="n">
         <v>151.6</v>
@@ -19279,9 +18735,7 @@
       <c r="T248" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U248" s="2" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U248" s="2" t="inlineStr"/>
       <c r="V248" t="inlineStr"/>
       <c r="W248" s="2" t="n">
         <v>153.6</v>
@@ -19358,9 +18812,7 @@
       <c r="T249" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="U249" s="2" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U249" s="2" t="inlineStr"/>
       <c r="V249" t="inlineStr"/>
       <c r="W249" s="1" t="n">
         <v>155</v>
@@ -19433,9 +18885,7 @@
       <c r="T250" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U250" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U250" s="2" t="inlineStr"/>
       <c r="V250" t="inlineStr"/>
       <c r="W250" s="2" t="n">
         <v>144.4</v>
@@ -19508,9 +18958,7 @@
       <c r="T251" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U251" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U251" s="2" t="inlineStr"/>
       <c r="V251" t="inlineStr"/>
       <c r="W251" s="2" t="n">
         <v>141.3</v>
@@ -19583,9 +19031,7 @@
       <c r="T252" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U252" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U252" s="2" t="inlineStr"/>
       <c r="V252" t="inlineStr"/>
       <c r="W252" s="2" t="n">
         <v>144</v>
@@ -19658,9 +19104,7 @@
       <c r="T253" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U253" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="U253" s="2" t="inlineStr"/>
       <c r="V253" t="inlineStr"/>
       <c r="W253" s="2" t="n">
         <v>148.1</v>
@@ -19733,9 +19177,7 @@
       <c r="T254" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U254" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U254" s="2" t="inlineStr"/>
       <c r="V254" t="inlineStr"/>
       <c r="W254" s="2" t="n">
         <v>147.2</v>
@@ -19808,9 +19250,7 @@
       <c r="T255" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U255" s="2" t="n">
-        <v>13.2</v>
-      </c>
+      <c r="U255" s="2" t="inlineStr"/>
       <c r="V255" t="inlineStr"/>
       <c r="W255" s="2" t="n">
         <v>145</v>
@@ -19883,9 +19323,7 @@
       <c r="T256" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U256" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U256" s="2" t="inlineStr"/>
       <c r="V256" t="inlineStr"/>
       <c r="W256" s="2" t="n">
         <v>143.7</v>
@@ -19962,9 +19400,7 @@
       <c r="T257" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U257" s="2" t="n">
-        <v>16.4</v>
-      </c>
+      <c r="U257" s="2" t="inlineStr"/>
       <c r="V257" t="inlineStr"/>
       <c r="W257" s="2" t="n">
         <v>143.6</v>
@@ -20037,9 +19473,7 @@
       <c r="T258" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U258" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U258" s="2" t="inlineStr"/>
       <c r="V258" t="inlineStr"/>
       <c r="W258" s="2" t="n">
         <v>146.6</v>
@@ -20116,9 +19550,7 @@
       <c r="T259" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U259" s="2" t="n">
-        <v>14.5</v>
-      </c>
+      <c r="U259" s="2" t="inlineStr"/>
       <c r="V259" t="inlineStr"/>
       <c r="W259" s="2" t="n">
         <v>143.9</v>
@@ -20195,9 +19627,7 @@
       <c r="T260" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U260" s="2" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="U260" s="2" t="inlineStr"/>
       <c r="V260" t="inlineStr"/>
       <c r="W260" s="2" t="n">
         <v>143.2</v>
@@ -20270,9 +19700,7 @@
       <c r="T261" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U261" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U261" s="2" t="inlineStr"/>
       <c r="V261" t="inlineStr"/>
       <c r="W261" s="2" t="n">
         <v>137.2</v>
@@ -20345,9 +19773,7 @@
       <c r="T262" s="2" t="n">
         <v>20.4</v>
       </c>
-      <c r="U262" s="2" t="n">
-        <v>15</v>
-      </c>
+      <c r="U262" s="2" t="inlineStr"/>
       <c r="V262" t="inlineStr"/>
       <c r="W262" s="2" t="n">
         <v>140.3</v>
@@ -20420,9 +19846,7 @@
       <c r="T263" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U263" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U263" s="2" t="inlineStr"/>
       <c r="V263" t="inlineStr"/>
       <c r="W263" s="2" t="n">
         <v>145.2</v>
@@ -20499,9 +19923,7 @@
       <c r="T264" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U264" s="2" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U264" s="2" t="inlineStr"/>
       <c r="V264" t="inlineStr"/>
       <c r="W264" s="2" t="n">
         <v>145.7</v>
@@ -20574,9 +19996,7 @@
       <c r="T265" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U265" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U265" s="2" t="inlineStr"/>
       <c r="V265" t="inlineStr"/>
       <c r="W265" s="2" t="n">
         <v>143.8</v>
@@ -20649,9 +20069,7 @@
       <c r="T266" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U266" s="2" t="n">
-        <v>21.5</v>
-      </c>
+      <c r="U266" s="2" t="inlineStr"/>
       <c r="V266" t="inlineStr"/>
       <c r="W266" s="2" t="n">
         <v>142.5</v>
@@ -20724,9 +20142,7 @@
       <c r="T267" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U267" s="2" t="n">
-        <v>22.4</v>
-      </c>
+      <c r="U267" s="2" t="inlineStr"/>
       <c r="V267" t="inlineStr"/>
       <c r="W267" s="2" t="n">
         <v>139.4</v>
@@ -20799,9 +20215,7 @@
       <c r="T268" s="2" t="n">
         <v>20.3</v>
       </c>
-      <c r="U268" s="2" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U268" s="2" t="inlineStr"/>
       <c r="V268" t="inlineStr"/>
       <c r="W268" s="2" t="n">
         <v>140.3</v>
@@ -20874,9 +20288,7 @@
       <c r="T269" s="2" t="n">
         <v>19.6</v>
       </c>
-      <c r="U269" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U269" s="2" t="inlineStr"/>
       <c r="V269" t="inlineStr"/>
       <c r="W269" s="2" t="n">
         <v>139.2</v>
@@ -20949,9 +20361,7 @@
       <c r="T270" s="2" t="n">
         <v>20.2</v>
       </c>
-      <c r="U270" s="2" t="n">
-        <v>16.6</v>
-      </c>
+      <c r="U270" s="2" t="inlineStr"/>
       <c r="V270" t="inlineStr"/>
       <c r="W270" s="2" t="n">
         <v>141.2</v>
@@ -21024,9 +20434,7 @@
       <c r="T271" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U271" s="2" t="n">
-        <v>17.8</v>
-      </c>
+      <c r="U271" s="2" t="inlineStr"/>
       <c r="V271" t="inlineStr"/>
       <c r="W271" s="2" t="n">
         <v>145.5</v>
@@ -21099,9 +20507,7 @@
       <c r="T272" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="U272" s="2" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U272" s="2" t="inlineStr"/>
       <c r="V272" t="inlineStr"/>
       <c r="W272" s="2" t="n">
         <v>141.4</v>
@@ -21174,9 +20580,7 @@
       <c r="T273" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U273" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U273" s="2" t="inlineStr"/>
       <c r="V273" t="inlineStr"/>
       <c r="W273" s="2" t="n">
         <v>141.9</v>
@@ -21249,9 +20653,7 @@
       <c r="T274" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U274" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U274" s="2" t="inlineStr"/>
       <c r="V274" t="inlineStr"/>
       <c r="W274" s="2" t="n">
         <v>146.1</v>
@@ -21328,9 +20730,7 @@
       <c r="T275" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U275" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U275" s="2" t="inlineStr"/>
       <c r="V275" t="inlineStr"/>
       <c r="W275" s="2" t="n">
         <v>146.6</v>
@@ -21403,9 +20803,7 @@
       <c r="T276" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U276" s="2" t="n">
-        <v>19</v>
-      </c>
+      <c r="U276" s="2" t="inlineStr"/>
       <c r="V276" t="inlineStr"/>
       <c r="W276" s="2" t="n">
         <v>146.7</v>
@@ -21478,9 +20876,7 @@
       <c r="T277" s="2" t="n">
         <v>21.4</v>
       </c>
-      <c r="U277" s="2" t="n">
-        <v>16.3</v>
-      </c>
+      <c r="U277" s="2" t="inlineStr"/>
       <c r="V277" t="inlineStr"/>
       <c r="W277" s="2" t="n">
         <v>151.8</v>
@@ -21553,9 +20949,7 @@
       <c r="T278" s="2" t="n">
         <v>23.6</v>
       </c>
-      <c r="U278" s="2" t="n">
-        <v>20.3</v>
-      </c>
+      <c r="U278" s="2" t="inlineStr"/>
       <c r="V278" t="inlineStr"/>
       <c r="W278" s="2" t="n">
         <v>152.8</v>
@@ -21628,9 +21022,7 @@
       <c r="T279" s="2" t="n">
         <v>21.1</v>
       </c>
-      <c r="U279" s="2" t="n">
-        <v>17.8</v>
-      </c>
+      <c r="U279" s="2" t="inlineStr"/>
       <c r="V279" t="inlineStr"/>
       <c r="W279" s="2" t="n">
         <v>152.9</v>
@@ -21703,9 +21095,7 @@
       <c r="T280" s="2" t="n">
         <v>23.8</v>
       </c>
-      <c r="U280" s="2" t="n">
-        <v>21.9</v>
-      </c>
+      <c r="U280" s="2" t="inlineStr"/>
       <c r="V280" t="inlineStr"/>
       <c r="W280" s="2" t="n">
         <v>153.9</v>
@@ -21782,14 +21172,8 @@
       <c r="T281" s="6" t="n">
         <v>29.5</v>
       </c>
-      <c r="U281" s="6" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="V281" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U281" s="2" t="inlineStr"/>
+      <c r="V281" t="inlineStr"/>
       <c r="W281" s="2" t="n">
         <v>151.8</v>
       </c>
@@ -21861,9 +21245,7 @@
       <c r="T282" s="6" t="n">
         <v>25.5</v>
       </c>
-      <c r="U282" s="2" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="U282" s="2" t="inlineStr"/>
       <c r="V282" t="inlineStr"/>
       <c r="W282" s="1" t="n">
         <v>158</v>
@@ -21936,9 +21318,7 @@
       <c r="T283" s="2" t="n">
         <v>24.9</v>
       </c>
-      <c r="U283" s="2" t="n">
-        <v>21.3</v>
-      </c>
+      <c r="U283" s="2" t="inlineStr"/>
       <c r="V283" t="inlineStr"/>
       <c r="W283" s="2" t="n">
         <v>154.5</v>
@@ -22011,9 +21391,7 @@
       <c r="T284" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U284" s="2" t="n">
-        <v>19</v>
-      </c>
+      <c r="U284" s="2" t="inlineStr"/>
       <c r="V284" t="inlineStr"/>
       <c r="W284" s="2" t="n">
         <v>152.4</v>
@@ -22084,9 +21462,7 @@
       <c r="T285" s="6" t="n">
         <v>27.3</v>
       </c>
-      <c r="U285" s="2" t="n">
-        <v>24.2</v>
-      </c>
+      <c r="U285" s="2" t="inlineStr"/>
       <c r="V285" t="inlineStr"/>
       <c r="W285" s="2" t="n">
         <v>139.9</v>
@@ -22159,14 +21535,8 @@
       <c r="T286" s="6" t="n">
         <v>27.2</v>
       </c>
-      <c r="U286" s="6" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="V286" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U286" s="2" t="inlineStr"/>
+      <c r="V286" t="inlineStr"/>
       <c r="W286" s="2" t="n">
         <v>137.8</v>
       </c>
@@ -22238,9 +21608,7 @@
       <c r="T287" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U287" s="2" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U287" s="2" t="inlineStr"/>
       <c r="V287" t="inlineStr"/>
       <c r="W287" s="2" t="n">
         <v>141.5</v>
@@ -22313,9 +21681,7 @@
       <c r="T288" s="2" t="n">
         <v>22.4</v>
       </c>
-      <c r="U288" s="2" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="U288" s="2" t="inlineStr"/>
       <c r="V288" t="inlineStr"/>
       <c r="W288" s="2" t="n">
         <v>145</v>
@@ -22388,9 +21754,7 @@
       <c r="T289" s="6" t="n">
         <v>25.1</v>
       </c>
-      <c r="U289" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U289" s="2" t="inlineStr"/>
       <c r="V289" t="inlineStr"/>
       <c r="W289" s="2" t="n">
         <v>136.5</v>
@@ -22463,9 +21827,7 @@
       <c r="T290" s="2" t="n">
         <v>24.1</v>
       </c>
-      <c r="U290" s="2" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U290" s="2" t="inlineStr"/>
       <c r="V290" t="inlineStr"/>
       <c r="W290" s="2" t="n">
         <v>138.3</v>
@@ -22538,14 +21900,8 @@
       <c r="T291" s="6" t="n">
         <v>26.8</v>
       </c>
-      <c r="U291" s="6" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="V291" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U291" s="2" t="inlineStr"/>
+      <c r="V291" t="inlineStr"/>
       <c r="W291" s="2" t="n">
         <v>139.1</v>
       </c>
@@ -22617,9 +21973,7 @@
       <c r="T292" s="6" t="n">
         <v>26.1</v>
       </c>
-      <c r="U292" s="2" t="n">
-        <v>23.2</v>
-      </c>
+      <c r="U292" s="2" t="inlineStr"/>
       <c r="V292" t="inlineStr"/>
       <c r="W292" s="2" t="n">
         <v>142</v>
@@ -22692,9 +22046,7 @@
       <c r="T293" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="U293" s="2" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U293" s="2" t="inlineStr"/>
       <c r="V293" t="inlineStr"/>
       <c r="W293" s="2" t="n">
         <v>142.6</v>
@@ -22767,9 +22119,7 @@
       <c r="T294" s="6" t="n">
         <v>25.3</v>
       </c>
-      <c r="U294" s="2" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U294" s="2" t="inlineStr"/>
       <c r="V294" t="inlineStr"/>
       <c r="W294" s="2" t="n">
         <v>140.9</v>
@@ -22842,9 +22192,7 @@
       <c r="T295" s="6" t="n">
         <v>27.4</v>
       </c>
-      <c r="U295" s="2" t="n">
-        <v>23.9</v>
-      </c>
+      <c r="U295" s="2" t="inlineStr"/>
       <c r="V295" t="inlineStr"/>
       <c r="W295" s="2" t="n">
         <v>144</v>
@@ -22921,14 +22269,8 @@
       <c r="T296" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="U296" s="6" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="V296" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U296" s="2" t="inlineStr"/>
+      <c r="V296" t="inlineStr"/>
       <c r="W296" s="2" t="n">
         <v>139</v>
       </c>
@@ -23004,9 +22346,7 @@
       <c r="T297" s="6" t="n">
         <v>30.6</v>
       </c>
-      <c r="U297" s="2" t="n">
-        <v>23</v>
-      </c>
+      <c r="U297" s="2" t="inlineStr"/>
       <c r="V297" t="inlineStr"/>
       <c r="W297" s="2" t="n">
         <v>142.2</v>
@@ -23079,9 +22419,7 @@
       <c r="T298" s="6" t="n">
         <v>25.2</v>
       </c>
-      <c r="U298" s="2" t="n">
-        <v>19</v>
-      </c>
+      <c r="U298" s="2" t="inlineStr"/>
       <c r="V298" t="inlineStr"/>
       <c r="W298" s="2" t="n">
         <v>145.4</v>
@@ -23154,9 +22492,7 @@
       <c r="T299" s="2" t="n">
         <v>24.5</v>
       </c>
-      <c r="U299" s="2" t="n">
-        <v>23</v>
-      </c>
+      <c r="U299" s="2" t="inlineStr"/>
       <c r="V299" t="inlineStr"/>
       <c r="W299" s="2" t="n">
         <v>143.8</v>
@@ -23229,9 +22565,7 @@
       <c r="T300" s="2" t="n">
         <v>23.9</v>
       </c>
-      <c r="U300" s="6" t="n">
-        <v>27.6</v>
-      </c>
+      <c r="U300" s="2" t="inlineStr"/>
       <c r="V300" t="inlineStr"/>
       <c r="W300" s="2" t="n">
         <v>146.9</v>
@@ -23304,9 +22638,7 @@
       <c r="T301" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U301" s="2" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U301" s="2" t="inlineStr"/>
       <c r="V301" t="inlineStr"/>
       <c r="W301" s="2" t="n">
         <v>147.6</v>
@@ -23379,14 +22711,8 @@
       <c r="T302" s="6" t="n">
         <v>25.8</v>
       </c>
-      <c r="U302" s="6" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="V302" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U302" s="2" t="inlineStr"/>
+      <c r="V302" t="inlineStr"/>
       <c r="W302" s="2" t="n">
         <v>148.4</v>
       </c>
@@ -23458,9 +22784,7 @@
       <c r="T303" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="U303" s="2" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U303" s="2" t="inlineStr"/>
       <c r="V303" t="inlineStr"/>
       <c r="W303" s="2" t="n">
         <v>150.4</v>
@@ -23533,9 +22857,7 @@
       <c r="T304" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U304" s="2" t="n">
-        <v>14.1</v>
-      </c>
+      <c r="U304" s="2" t="inlineStr"/>
       <c r="V304" t="inlineStr"/>
       <c r="W304" s="2" t="n">
         <v>143.3</v>
@@ -23608,9 +22930,7 @@
       <c r="T305" s="2" t="n">
         <v>19.2</v>
       </c>
-      <c r="U305" s="2" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U305" s="2" t="inlineStr"/>
       <c r="V305" t="inlineStr"/>
       <c r="W305" s="2" t="n">
         <v>144.2</v>
@@ -23683,9 +23003,7 @@
       <c r="T306" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U306" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U306" s="2" t="inlineStr"/>
       <c r="V306" t="inlineStr"/>
       <c r="W306" s="1" t="n">
         <v>156.9</v>
@@ -23758,9 +23076,7 @@
       <c r="T307" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U307" s="2" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U307" s="2" t="inlineStr"/>
       <c r="V307" t="inlineStr"/>
       <c r="W307" s="2" t="n">
         <v>149.9</v>
@@ -23833,9 +23149,7 @@
       <c r="T308" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U308" s="2" t="n">
-        <v>12.6</v>
-      </c>
+      <c r="U308" s="2" t="inlineStr"/>
       <c r="V308" t="inlineStr"/>
       <c r="W308" s="2" t="n">
         <v>139.2</v>
@@ -23908,9 +23222,7 @@
       <c r="T309" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U309" s="2" t="n">
-        <v>12</v>
-      </c>
+      <c r="U309" s="2" t="inlineStr"/>
       <c r="V309" t="inlineStr"/>
       <c r="W309" s="2" t="n">
         <v>140.7</v>
@@ -23983,9 +23295,7 @@
       <c r="T310" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U310" s="2" t="n">
-        <v>14.2</v>
-      </c>
+      <c r="U310" s="2" t="inlineStr"/>
       <c r="V310" t="inlineStr"/>
       <c r="W310" s="2" t="n">
         <v>141.8</v>
@@ -24058,9 +23368,7 @@
       <c r="T311" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U311" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U311" s="2" t="inlineStr"/>
       <c r="V311" t="inlineStr"/>
       <c r="W311" s="2" t="n">
         <v>141.9</v>
@@ -24133,9 +23441,7 @@
       <c r="T312" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U312" s="2" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U312" s="2" t="inlineStr"/>
       <c r="V312" t="inlineStr"/>
       <c r="W312" s="2" t="n">
         <v>140.9</v>
@@ -24208,9 +23514,7 @@
       <c r="T313" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U313" s="2" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U313" s="2" t="inlineStr"/>
       <c r="V313" t="inlineStr"/>
       <c r="W313" s="2" t="n">
         <v>140.8</v>
@@ -24283,9 +23587,7 @@
       <c r="T314" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U314" s="2" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="U314" s="2" t="inlineStr"/>
       <c r="V314" t="inlineStr"/>
       <c r="W314" s="2" t="n">
         <v>139.6</v>
@@ -24358,9 +23660,7 @@
       <c r="T315" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U315" s="2" t="n">
-        <v>16.6</v>
-      </c>
+      <c r="U315" s="2" t="inlineStr"/>
       <c r="V315" t="inlineStr"/>
       <c r="W315" s="2" t="n">
         <v>139.1</v>
@@ -24433,9 +23733,7 @@
       <c r="T316" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U316" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U316" s="2" t="inlineStr"/>
       <c r="V316" t="inlineStr"/>
       <c r="W316" s="2" t="n">
         <v>139.6</v>
@@ -24508,9 +23806,7 @@
       <c r="T317" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U317" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U317" s="2" t="inlineStr"/>
       <c r="V317" t="inlineStr"/>
       <c r="W317" s="2" t="n">
         <v>138.2</v>
@@ -24583,9 +23879,7 @@
       <c r="T318" s="2" t="n">
         <v>18.8</v>
       </c>
-      <c r="U318" s="2" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U318" s="2" t="inlineStr"/>
       <c r="V318" t="inlineStr"/>
       <c r="W318" s="2" t="n">
         <v>141.9</v>
@@ -24658,9 +23952,7 @@
       <c r="T319" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U319" s="2" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U319" s="2" t="inlineStr"/>
       <c r="V319" t="inlineStr"/>
       <c r="W319" s="2" t="n">
         <v>143.3</v>
@@ -24733,9 +24025,7 @@
       <c r="T320" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U320" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U320" s="2" t="inlineStr"/>
       <c r="V320" t="inlineStr"/>
       <c r="W320" s="2" t="n">
         <v>141.4</v>
@@ -24808,9 +24098,7 @@
       <c r="T321" s="2" t="n">
         <v>18.3</v>
       </c>
-      <c r="U321" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U321" s="2" t="inlineStr"/>
       <c r="V321" t="inlineStr"/>
       <c r="W321" s="2" t="n">
         <v>141.7</v>
@@ -24883,9 +24171,7 @@
       <c r="T322" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U322" s="2" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U322" s="2" t="inlineStr"/>
       <c r="V322" t="inlineStr"/>
       <c r="W322" s="2" t="n">
         <v>138.7</v>
@@ -24958,9 +24244,7 @@
       <c r="T323" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U323" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U323" s="2" t="inlineStr"/>
       <c r="V323" t="inlineStr"/>
       <c r="W323" s="2" t="n">
         <v>135.4</v>
@@ -25033,9 +24317,7 @@
       <c r="T324" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U324" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U324" s="2" t="inlineStr"/>
       <c r="V324" t="inlineStr"/>
       <c r="W324" s="2" t="n">
         <v>136.1</v>
@@ -25108,9 +24390,7 @@
       <c r="T325" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U325" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U325" s="2" t="inlineStr"/>
       <c r="V325" t="inlineStr"/>
       <c r="W325" s="2" t="n">
         <v>138.2</v>
@@ -25183,9 +24463,7 @@
       <c r="T326" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U326" s="2" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U326" s="2" t="inlineStr"/>
       <c r="V326" t="inlineStr"/>
       <c r="W326" s="2" t="n">
         <v>140.2</v>
@@ -25258,9 +24536,7 @@
       <c r="T327" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U327" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U327" s="2" t="inlineStr"/>
       <c r="V327" t="inlineStr"/>
       <c r="W327" s="2" t="n">
         <v>139.4</v>
@@ -25333,9 +24609,7 @@
       <c r="T328" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U328" s="2" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U328" s="2" t="inlineStr"/>
       <c r="V328" t="inlineStr"/>
       <c r="W328" s="2" t="n">
         <v>141.5</v>
@@ -25408,9 +24682,7 @@
       <c r="T329" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U329" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U329" s="2" t="inlineStr"/>
       <c r="V329" t="inlineStr"/>
       <c r="W329" s="2" t="n">
         <v>139.3</v>
@@ -25483,9 +24755,7 @@
       <c r="T330" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U330" s="2" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U330" s="2" t="inlineStr"/>
       <c r="V330" t="inlineStr"/>
       <c r="W330" s="2" t="n">
         <v>145.8</v>
@@ -25558,9 +24828,7 @@
       <c r="T331" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U331" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U331" s="2" t="inlineStr"/>
       <c r="V331" t="inlineStr"/>
       <c r="W331" s="2" t="n">
         <v>138.4</v>
@@ -25633,9 +24901,7 @@
       <c r="T332" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U332" s="2" t="n">
-        <v>13.3</v>
-      </c>
+      <c r="U332" s="2" t="inlineStr"/>
       <c r="V332" t="inlineStr"/>
       <c r="W332" s="2" t="n">
         <v>135.5</v>
@@ -25708,9 +24974,7 @@
       <c r="T333" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U333" s="2" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U333" s="2" t="inlineStr"/>
       <c r="V333" t="inlineStr"/>
       <c r="W333" s="2" t="n">
         <v>132.3</v>
@@ -25783,9 +25047,7 @@
       <c r="T334" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U334" s="2" t="n">
-        <v>14</v>
-      </c>
+      <c r="U334" s="2" t="inlineStr"/>
       <c r="V334" t="inlineStr"/>
       <c r="W334" s="2" t="n">
         <v>137</v>
@@ -25858,9 +25120,7 @@
       <c r="T335" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U335" s="2" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U335" s="2" t="inlineStr"/>
       <c r="V335" t="inlineStr"/>
       <c r="W335" s="2" t="n">
         <v>137.4</v>
@@ -25933,9 +25193,7 @@
       <c r="T336" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U336" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U336" s="2" t="inlineStr"/>
       <c r="V336" t="inlineStr"/>
       <c r="W336" s="2" t="n">
         <v>139</v>
@@ -26008,9 +25266,7 @@
       <c r="T337" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U337" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U337" s="2" t="inlineStr"/>
       <c r="V337" t="inlineStr"/>
       <c r="W337" s="2" t="n">
         <v>138.6</v>
@@ -26083,9 +25339,7 @@
       <c r="T338" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U338" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U338" s="2" t="inlineStr"/>
       <c r="V338" t="inlineStr"/>
       <c r="W338" s="2" t="n">
         <v>139.5</v>
@@ -26158,9 +25412,7 @@
       <c r="T339" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U339" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U339" s="2" t="inlineStr"/>
       <c r="V339" t="inlineStr"/>
       <c r="W339" s="2" t="n">
         <v>144.2</v>
@@ -26233,9 +25485,7 @@
       <c r="T340" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U340" s="2" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U340" s="2" t="inlineStr"/>
       <c r="V340" t="inlineStr"/>
       <c r="W340" s="2" t="n">
         <v>142.5</v>
@@ -26308,9 +25558,7 @@
       <c r="T341" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U341" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U341" s="2" t="inlineStr"/>
       <c r="V341" t="inlineStr"/>
       <c r="W341" s="2" t="n">
         <v>143.2</v>
@@ -26383,9 +25631,7 @@
       <c r="T342" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U342" s="2" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U342" s="2" t="inlineStr"/>
       <c r="V342" t="inlineStr"/>
       <c r="W342" s="2" t="n">
         <v>136.9</v>
@@ -26458,9 +25704,7 @@
       <c r="T343" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U343" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U343" s="2" t="inlineStr"/>
       <c r="V343" t="inlineStr"/>
       <c r="W343" s="2" t="n">
         <v>142.1</v>
@@ -26537,9 +25781,7 @@
       <c r="T344" s="5" t="n">
         <v>21.5</v>
       </c>
-      <c r="U344" s="7" t="n">
-        <v>28.7</v>
-      </c>
+      <c r="U344" s="5" t="inlineStr"/>
       <c r="V344" s="3" t="inlineStr"/>
       <c r="W344" s="5" t="n">
         <v>152.2</v>
@@ -26612,9 +25854,7 @@
       <c r="T345" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U345" s="2" t="n">
-        <v>16</v>
-      </c>
+      <c r="U345" s="2" t="inlineStr"/>
       <c r="V345" t="inlineStr"/>
       <c r="W345" s="2" t="n">
         <v>145</v>
@@ -26687,9 +25927,7 @@
       <c r="T346" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U346" s="2" t="n">
-        <v>20.6</v>
-      </c>
+      <c r="U346" s="2" t="inlineStr"/>
       <c r="V346" t="inlineStr"/>
       <c r="W346" s="2" t="n">
         <v>142</v>
@@ -26762,9 +26000,7 @@
       <c r="T347" s="2" t="n">
         <v>22.2</v>
       </c>
-      <c r="U347" s="2" t="n">
-        <v>23.9</v>
-      </c>
+      <c r="U347" s="2" t="inlineStr"/>
       <c r="V347" t="inlineStr"/>
       <c r="W347" s="2" t="n">
         <v>143.1</v>
@@ -26837,9 +26073,7 @@
       <c r="T348" s="2" t="n">
         <v>19.4</v>
       </c>
-      <c r="U348" s="2" t="n">
-        <v>21.1</v>
-      </c>
+      <c r="U348" s="2" t="inlineStr"/>
       <c r="V348" t="inlineStr"/>
       <c r="W348" s="2" t="n">
         <v>143</v>
@@ -26912,9 +26146,7 @@
       <c r="T349" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U349" s="2" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U349" s="2" t="inlineStr"/>
       <c r="V349" t="inlineStr"/>
       <c r="W349" s="2" t="n">
         <v>142.6</v>
@@ -26987,9 +26219,7 @@
       <c r="T350" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U350" s="2" t="n">
-        <v>12.9</v>
-      </c>
+      <c r="U350" s="2" t="inlineStr"/>
       <c r="V350" t="inlineStr"/>
       <c r="W350" s="2" t="n">
         <v>144.3</v>
@@ -27062,9 +26292,7 @@
       <c r="T351" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U351" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U351" s="2" t="inlineStr"/>
       <c r="V351" t="inlineStr"/>
       <c r="W351" s="2" t="n">
         <v>142.7</v>
@@ -27141,9 +26369,7 @@
       <c r="T352" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U352" s="2" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U352" s="2" t="inlineStr"/>
       <c r="V352" t="inlineStr"/>
       <c r="W352" s="2" t="n">
         <v>142.6</v>
@@ -27216,9 +26442,7 @@
       <c r="T353" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U353" s="2" t="n">
-        <v>15.7</v>
-      </c>
+      <c r="U353" s="2" t="inlineStr"/>
       <c r="V353" t="inlineStr"/>
       <c r="W353" s="2" t="n">
         <v>146.7</v>
@@ -27291,9 +26515,7 @@
       <c r="T354" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U354" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U354" s="2" t="inlineStr"/>
       <c r="V354" t="inlineStr"/>
       <c r="W354" s="2" t="n">
         <v>141.9</v>
@@ -27370,9 +26592,7 @@
       <c r="T355" s="5" t="n">
         <v>19.5</v>
       </c>
-      <c r="U355" s="5" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U355" s="5" t="inlineStr"/>
       <c r="V355" s="3" t="inlineStr"/>
       <c r="W355" s="5" t="n">
         <v>143.1</v>
@@ -27445,9 +26665,7 @@
       <c r="T356" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U356" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U356" s="2" t="inlineStr"/>
       <c r="V356" t="inlineStr"/>
       <c r="W356" s="2" t="n">
         <v>145.3</v>
@@ -27520,9 +26738,7 @@
       <c r="T357" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U357" s="2" t="n">
-        <v>16</v>
-      </c>
+      <c r="U357" s="2" t="inlineStr"/>
       <c r="V357" t="inlineStr"/>
       <c r="W357" s="2" t="n">
         <v>139.9</v>
@@ -27595,9 +26811,7 @@
       <c r="T358" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U358" s="2" t="n">
-        <v>17.6</v>
-      </c>
+      <c r="U358" s="2" t="inlineStr"/>
       <c r="V358" t="inlineStr"/>
       <c r="W358" s="2" t="n">
         <v>139.4</v>
@@ -27670,9 +26884,7 @@
       <c r="T359" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U359" s="2" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U359" s="2" t="inlineStr"/>
       <c r="V359" t="inlineStr"/>
       <c r="W359" s="2" t="n">
         <v>144.5</v>
@@ -27745,9 +26957,7 @@
       <c r="T360" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U360" s="2" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U360" s="2" t="inlineStr"/>
       <c r="V360" t="inlineStr"/>
       <c r="W360" s="2" t="n">
         <v>149.6</v>
@@ -27820,9 +27030,7 @@
       <c r="T361" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U361" s="2" t="n">
-        <v>13</v>
-      </c>
+      <c r="U361" s="2" t="inlineStr"/>
       <c r="V361" t="inlineStr"/>
       <c r="W361" s="2" t="n">
         <v>154.8</v>
@@ -27899,9 +27107,7 @@
       <c r="T362" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U362" s="2" t="n">
-        <v>13.2</v>
-      </c>
+      <c r="U362" s="2" t="inlineStr"/>
       <c r="V362" t="inlineStr"/>
       <c r="W362" s="2" t="n">
         <v>150</v>
@@ -27974,9 +27180,7 @@
       <c r="T363" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U363" s="2" t="n">
-        <v>8.699999999999999</v>
-      </c>
+      <c r="U363" s="2" t="inlineStr"/>
       <c r="V363" t="inlineStr"/>
       <c r="W363" s="2" t="n">
         <v>145.4</v>
@@ -28053,9 +27257,7 @@
       <c r="T364" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U364" s="2" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U364" s="2" t="inlineStr"/>
       <c r="V364" t="inlineStr"/>
       <c r="W364" s="2" t="n">
         <v>145.7</v>
@@ -28128,9 +27330,7 @@
       <c r="T365" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U365" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U365" s="2" t="inlineStr"/>
       <c r="V365" t="inlineStr"/>
       <c r="W365" s="2" t="n">
         <v>149.8</v>
@@ -28203,9 +27403,7 @@
       <c r="T366" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U366" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U366" s="2" t="inlineStr"/>
       <c r="V366" t="inlineStr"/>
       <c r="W366" s="2" t="n">
         <v>144.7</v>
@@ -28278,9 +27476,7 @@
       <c r="T367" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U367" s="2" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U367" s="2" t="inlineStr"/>
       <c r="V367" t="inlineStr"/>
       <c r="W367" s="2" t="n">
         <v>144.3</v>
@@ -28357,9 +27553,7 @@
       <c r="T368" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U368" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U368" s="2" t="inlineStr"/>
       <c r="V368" t="inlineStr"/>
       <c r="W368" s="2" t="n">
         <v>145.7</v>
@@ -28432,9 +27626,7 @@
       <c r="T369" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U369" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U369" s="2" t="inlineStr"/>
       <c r="V369" t="inlineStr"/>
       <c r="W369" s="2" t="n">
         <v>145.1</v>
@@ -28507,9 +27699,7 @@
       <c r="T370" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U370" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U370" s="2" t="inlineStr"/>
       <c r="V370" t="inlineStr"/>
       <c r="W370" s="2" t="n">
         <v>148.5</v>
@@ -28586,9 +27776,7 @@
       <c r="T371" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U371" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U371" s="2" t="inlineStr"/>
       <c r="V371" t="inlineStr"/>
       <c r="W371" s="2" t="n">
         <v>145.7</v>
@@ -28661,9 +27849,7 @@
       <c r="T372" s="2" t="n">
         <v>18.8</v>
       </c>
-      <c r="U372" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U372" s="2" t="inlineStr"/>
       <c r="V372" t="inlineStr"/>
       <c r="W372" s="2" t="n">
         <v>147.3</v>
@@ -31568,7 +30754,7 @@
         <v>88.09999999999999</v>
       </c>
       <c r="G412" t="n">
-        <v>3876400</v>
+        <v>3904300</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>-1.62</v>
@@ -31635,22 +30821,22 @@
         <v>88.17</v>
       </c>
       <c r="E413" t="n">
-        <v>86.79000000000001</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="F413" t="n">
-        <v>87.04000000000001</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="G413" t="n">
-        <v>1800411</v>
+        <v>2632034</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>-1.2</v>
+        <v>-1.29</v>
       </c>
       <c r="I413" t="n">
         <v>5.3</v>
       </c>
       <c r="J413" t="n">
-        <v>89.36</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="K413" t="n">
         <v>89.64</v>
@@ -31662,7 +30848,7 @@
         <v>79.67</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>44.37</v>
+        <v>44.15</v>
       </c>
       <c r="O413" t="n">
         <v>29</v>
@@ -31679,16 +30865,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>17.6</v>
+        <v>17.2</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>14.8</v>
+        <v>17.1</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>146.6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -30741,28 +30741,44 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>87.98</v>
+      </c>
+      <c r="D412" t="n">
+        <v>88.17</v>
+      </c>
+      <c r="E412" t="n">
+        <v>86.70999999999999</v>
+      </c>
+      <c r="F412" t="n">
+        <v>86.95999999999999</v>
+      </c>
       <c r="G412" t="n">
-        <v>2632034</v>
-      </c>
-      <c r="H412" s="5" t="n">
-        <v>0</v>
+        <v>2653800</v>
+      </c>
+      <c r="H412" s="6" t="n">
+        <v>-1.29</v>
       </c>
       <c r="I412" t="n">
         <v>5.3</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>89.34999999999999</v>
+      </c>
+      <c r="K412" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="L412" t="n">
+        <v>86.31</v>
+      </c>
+      <c r="M412" t="n">
+        <v>79.67</v>
+      </c>
       <c r="N412" s="5" t="n">
-        <v>47.6</v>
+        <v>44.15</v>
       </c>
       <c r="O412" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -30797,13 +30797,84 @@
       <c r="T412" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U412" s="5" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U412" s="5" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="5" t="n">
         <v>146.6</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>87.78</v>
+      </c>
+      <c r="D413" t="n">
+        <v>88.73</v>
+      </c>
+      <c r="E413" t="n">
+        <v>87.70999999999999</v>
+      </c>
+      <c r="F413" t="n">
+        <v>88.29000000000001</v>
+      </c>
+      <c r="G413" t="n">
+        <v>1454664</v>
+      </c>
+      <c r="H413" s="4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I413" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J413" t="n">
+        <v>89.23</v>
+      </c>
+      <c r="K413" t="n">
+        <v>89.48999999999999</v>
+      </c>
+      <c r="L413" t="n">
+        <v>86.52</v>
+      </c>
+      <c r="M413" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="N413" s="5" t="n">
+        <v>48.11</v>
+      </c>
+      <c r="O413" t="n">
+        <v>29</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="T413" s="5" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="U413" s="5" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -30754,7 +30754,7 @@
         <v>86.95999999999999</v>
       </c>
       <c r="G412" t="n">
-        <v>2653800</v>
+        <v>2665600</v>
       </c>
       <c r="H412" s="6" t="n">
         <v>-1.29</v>
@@ -30821,37 +30821,37 @@
         <v>88.73</v>
       </c>
       <c r="E413" t="n">
-        <v>87.70999999999999</v>
+        <v>85.81</v>
       </c>
       <c r="F413" t="n">
-        <v>88.29000000000001</v>
+        <v>86.87</v>
       </c>
       <c r="G413" t="n">
-        <v>1454664</v>
-      </c>
-      <c r="H413" s="4" t="n">
-        <v>1.53</v>
+        <v>3542465</v>
+      </c>
+      <c r="H413" s="6" t="n">
+        <v>-0.1</v>
       </c>
       <c r="I413" t="n">
         <v>5.3</v>
       </c>
       <c r="J413" t="n">
-        <v>89.23</v>
+        <v>89.16</v>
       </c>
       <c r="K413" t="n">
-        <v>89.48999999999999</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="L413" t="n">
-        <v>86.52</v>
+        <v>86.5</v>
       </c>
       <c r="M413" t="n">
-        <v>79.76000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="N413" s="5" t="n">
-        <v>48.11</v>
+        <v>43.43</v>
       </c>
       <c r="O413" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -30865,13 +30865,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>4.96</v>
+        <v>5.01</v>
       </c>
       <c r="T413" s="5" t="n">
-        <v>16.8</v>
+        <v>18.1</v>
       </c>
       <c r="U413" s="5" t="n">
-        <v>16.2</v>
+        <v>18</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="5" t="inlineStr"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -2918,7 +2918,7 @@
         <v>5.3</v>
       </c>
       <c r="J33" t="n">
-        <v>52.99</v>
+        <v>53</v>
       </c>
       <c r="K33" t="n">
         <v>55</v>
@@ -27519,7 +27519,7 @@
         <v>5.3</v>
       </c>
       <c r="J368" t="n">
-        <v>93.15000000000001</v>
+        <v>93.14</v>
       </c>
       <c r="K368" t="n">
         <v>90.17</v>
@@ -30824,31 +30824,31 @@
         <v>85.81</v>
       </c>
       <c r="F413" t="n">
-        <v>86.87</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="G413" t="n">
-        <v>3542465</v>
-      </c>
-      <c r="H413" s="6" t="n">
-        <v>-0.1</v>
+        <v>3840928</v>
+      </c>
+      <c r="H413" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I413" t="n">
         <v>5.3</v>
       </c>
       <c r="J413" t="n">
-        <v>89.16</v>
+        <v>89.17</v>
       </c>
       <c r="K413" t="n">
-        <v>89.45999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="L413" t="n">
         <v>86.5</v>
       </c>
       <c r="M413" t="n">
-        <v>79.75</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="N413" s="5" t="n">
-        <v>43.43</v>
+        <v>43.68</v>
       </c>
       <c r="O413" t="n">
         <v>26</v>
@@ -30868,13 +30868,15 @@
         <v>5.01</v>
       </c>
       <c r="T413" s="5" t="n">
-        <v>18.1</v>
+        <v>17.7</v>
       </c>
       <c r="U413" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="5" t="inlineStr"/>
+      <c r="W413" s="5" t="n">
+        <v>145.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -30827,7 +30827,7 @@
         <v>86.95999999999999</v>
       </c>
       <c r="G413" t="n">
-        <v>3840928</v>
+        <v>3840900</v>
       </c>
       <c r="H413" s="5" t="n">
         <v>0</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -1264,13 +1264,13 @@
         <v>55.75</v>
       </c>
       <c r="F11" t="n">
-        <v>55.92</v>
+        <v>55.91</v>
       </c>
       <c r="G11" t="n">
         <v>4503400</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-2.53</v>
+        <v>-2.54</v>
       </c>
       <c r="I11" t="n">
         <v>5.3</v>
@@ -1279,7 +1279,7 @@
         <v>55.61</v>
       </c>
       <c r="K11" t="n">
-        <v>55.43</v>
+        <v>55.42</v>
       </c>
       <c r="L11" t="n">
         <v>52.32</v>
@@ -1288,7 +1288,7 @@
         <v>49.92</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>49.96</v>
+        <v>49.93</v>
       </c>
       <c r="O11" t="n">
         <v>38</v>
@@ -1343,7 +1343,7 @@
         <v>2721000</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I12" t="n">
         <v>5.3</v>
@@ -1507,7 +1507,7 @@
         <v>50.18</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>45.24</v>
+        <v>45.25</v>
       </c>
       <c r="O14" t="n">
         <v>41</v>
@@ -1580,7 +1580,7 @@
         <v>50.27</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>53.84</v>
+        <v>53.83</v>
       </c>
       <c r="O15" t="n">
         <v>47</v>
@@ -1653,7 +1653,7 @@
         <v>50.36</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>72.43000000000001</v>
+        <v>72.39</v>
       </c>
       <c r="O16" t="n">
         <v>44</v>
@@ -1726,7 +1726,7 @@
         <v>50.46</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>68.47</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="O17" t="n">
         <v>47</v>
@@ -1799,7 +1799,7 @@
         <v>50.56</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>70.23999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="O18" t="n">
         <v>48</v>
@@ -1872,7 +1872,7 @@
         <v>50.65</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>64.87</v>
+        <v>64.84</v>
       </c>
       <c r="O19" t="n">
         <v>44</v>
@@ -1945,7 +1945,7 @@
         <v>50.73</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>52.39</v>
+        <v>52.38</v>
       </c>
       <c r="O20" t="n">
         <v>37</v>
@@ -2099,7 +2099,7 @@
         <v>50.85</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>39.2</v>
+        <v>39.22</v>
       </c>
       <c r="O22" t="n">
         <v>24</v>
@@ -2172,7 +2172,7 @@
         <v>50.91</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>37.99</v>
+        <v>38.01</v>
       </c>
       <c r="O23" t="n">
         <v>21</v>
@@ -2245,7 +2245,7 @@
         <v>50.95</v>
       </c>
       <c r="N24" s="7" t="n">
-        <v>27.65</v>
+        <v>27.68</v>
       </c>
       <c r="O24" s="1" t="n">
         <v>13</v>
@@ -2322,7 +2322,7 @@
         <v>51</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>38.21</v>
+        <v>38.26</v>
       </c>
       <c r="O25" t="n">
         <v>21</v>
@@ -7259,7 +7259,7 @@
         <v>46.13</v>
       </c>
       <c r="L92" t="n">
-        <v>50.67</v>
+        <v>50.66</v>
       </c>
       <c r="M92" t="n">
         <v>50.63</v>
@@ -10993,7 +10993,7 @@
         <v>51.95</v>
       </c>
       <c r="M143" t="n">
-        <v>53.3</v>
+        <v>53.29</v>
       </c>
       <c r="N143" s="5" t="n">
         <v>49.89</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1264,13 +1264,13 @@
         <v>55.75</v>
       </c>
       <c r="F11" t="n">
-        <v>55.91</v>
+        <v>55.92</v>
       </c>
       <c r="G11" t="n">
         <v>4503400</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-2.54</v>
+        <v>-2.53</v>
       </c>
       <c r="I11" t="n">
         <v>5.3</v>
@@ -1279,7 +1279,7 @@
         <v>55.61</v>
       </c>
       <c r="K11" t="n">
-        <v>55.42</v>
+        <v>55.43</v>
       </c>
       <c r="L11" t="n">
         <v>52.32</v>
@@ -1288,7 +1288,7 @@
         <v>49.92</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>49.93</v>
+        <v>49.96</v>
       </c>
       <c r="O11" t="n">
         <v>38</v>
@@ -1343,7 +1343,7 @@
         <v>2721000</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I12" t="n">
         <v>5.3</v>
@@ -1507,7 +1507,7 @@
         <v>50.18</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>45.25</v>
+        <v>45.24</v>
       </c>
       <c r="O14" t="n">
         <v>41</v>
@@ -1580,7 +1580,7 @@
         <v>50.27</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>53.83</v>
+        <v>53.84</v>
       </c>
       <c r="O15" t="n">
         <v>47</v>
@@ -1653,7 +1653,7 @@
         <v>50.36</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>72.39</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="O16" t="n">
         <v>44</v>
@@ -1726,7 +1726,7 @@
         <v>50.46</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>68.43000000000001</v>
+        <v>68.47</v>
       </c>
       <c r="O17" t="n">
         <v>47</v>
@@ -1799,7 +1799,7 @@
         <v>50.56</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>70.2</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="O18" t="n">
         <v>48</v>
@@ -1872,7 +1872,7 @@
         <v>50.65</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>64.84</v>
+        <v>64.87</v>
       </c>
       <c r="O19" t="n">
         <v>44</v>
@@ -1945,7 +1945,7 @@
         <v>50.73</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>52.38</v>
+        <v>52.39</v>
       </c>
       <c r="O20" t="n">
         <v>37</v>
@@ -2099,7 +2099,7 @@
         <v>50.85</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>39.22</v>
+        <v>39.2</v>
       </c>
       <c r="O22" t="n">
         <v>24</v>
@@ -2172,7 +2172,7 @@
         <v>50.91</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>38.01</v>
+        <v>37.99</v>
       </c>
       <c r="O23" t="n">
         <v>21</v>
@@ -2245,7 +2245,7 @@
         <v>50.95</v>
       </c>
       <c r="N24" s="7" t="n">
-        <v>27.68</v>
+        <v>27.65</v>
       </c>
       <c r="O24" s="1" t="n">
         <v>13</v>
@@ -2322,7 +2322,7 @@
         <v>51</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>38.26</v>
+        <v>38.21</v>
       </c>
       <c r="O25" t="n">
         <v>21</v>
@@ -7259,7 +7259,7 @@
         <v>46.13</v>
       </c>
       <c r="L92" t="n">
-        <v>50.66</v>
+        <v>50.67</v>
       </c>
       <c r="M92" t="n">
         <v>50.63</v>
@@ -10993,7 +10993,7 @@
         <v>51.95</v>
       </c>
       <c r="M143" t="n">
-        <v>53.29</v>
+        <v>53.3</v>
       </c>
       <c r="N143" s="5" t="n">
         <v>49.89</v>
@@ -12514,7 +12514,7 @@
         <v>67.98999999999999</v>
       </c>
       <c r="E164" t="n">
-        <v>66.84</v>
+        <v>66.83</v>
       </c>
       <c r="F164" t="n">
         <v>67.38</v>
@@ -30851,7 +30851,7 @@
         <v>43.68</v>
       </c>
       <c r="O413" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -30870,13 +30870,84 @@
       <c r="T413" s="5" t="n">
         <v>17.7</v>
       </c>
-      <c r="U413" s="5" t="n">
-        <v>17</v>
-      </c>
+      <c r="U413" s="5" t="inlineStr"/>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="5" t="n">
         <v>145.9</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>89.77</v>
+      </c>
+      <c r="D414" t="n">
+        <v>90.02</v>
+      </c>
+      <c r="E414" t="n">
+        <v>89.09</v>
+      </c>
+      <c r="F414" t="n">
+        <v>89.89</v>
+      </c>
+      <c r="G414" t="n">
+        <v>1863081</v>
+      </c>
+      <c r="H414" s="4" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="I414" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J414" t="n">
+        <v>89.15000000000001</v>
+      </c>
+      <c r="K414" t="n">
+        <v>89.44</v>
+      </c>
+      <c r="L414" t="n">
+        <v>86.75</v>
+      </c>
+      <c r="M414" t="n">
+        <v>79.84999999999999</v>
+      </c>
+      <c r="N414" s="5" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="O414" t="n">
+        <v>29</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T414" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="U414" s="5" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -12514,7 +12514,7 @@
         <v>67.98999999999999</v>
       </c>
       <c r="E164" t="n">
-        <v>66.83</v>
+        <v>66.84</v>
       </c>
       <c r="F164" t="n">
         <v>67.38</v>
@@ -30827,7 +30827,7 @@
         <v>86.95999999999999</v>
       </c>
       <c r="G413" t="n">
-        <v>3840900</v>
+        <v>3945900</v>
       </c>
       <c r="H413" s="5" t="n">
         <v>0</v>
@@ -30891,19 +30891,19 @@
         <v>89.77</v>
       </c>
       <c r="D414" t="n">
-        <v>90.02</v>
+        <v>90.22</v>
       </c>
       <c r="E414" t="n">
         <v>89.09</v>
       </c>
       <c r="F414" t="n">
-        <v>89.89</v>
+        <v>89.94</v>
       </c>
       <c r="G414" t="n">
-        <v>1863081</v>
+        <v>2795502</v>
       </c>
       <c r="H414" s="4" t="n">
-        <v>3.37</v>
+        <v>3.43</v>
       </c>
       <c r="I414" t="n">
         <v>5.3</v>
@@ -30912,7 +30912,7 @@
         <v>89.15000000000001</v>
       </c>
       <c r="K414" t="n">
-        <v>89.44</v>
+        <v>89.45</v>
       </c>
       <c r="L414" t="n">
         <v>86.75</v>
@@ -30921,7 +30921,7 @@
         <v>79.84999999999999</v>
       </c>
       <c r="N414" s="5" t="n">
-        <v>45.36</v>
+        <v>45.53</v>
       </c>
       <c r="O414" t="n">
         <v>29</v>
@@ -30941,13 +30941,15 @@
         <v>4.95</v>
       </c>
       <c r="T414" s="5" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="U414" s="5" t="n">
-        <v>11.7</v>
+        <v>13.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="5" t="inlineStr"/>
+      <c r="W414" s="5" t="n">
+        <v>145.7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -30891,7 +30891,7 @@
         <v>89.77</v>
       </c>
       <c r="D414" t="n">
-        <v>90.22</v>
+        <v>90.23</v>
       </c>
       <c r="E414" t="n">
         <v>89.09</v>
@@ -30900,7 +30900,7 @@
         <v>89.94</v>
       </c>
       <c r="G414" t="n">
-        <v>2795502</v>
+        <v>2809800</v>
       </c>
       <c r="H414" s="4" t="n">
         <v>3.43</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -30924,7 +30924,7 @@
         <v>45.53</v>
       </c>
       <c r="O414" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -30943,13 +30943,84 @@
       <c r="T414" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U414" s="5" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U414" s="5" t="inlineStr"/>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="5" t="n">
         <v>145.7</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>90.41</v>
+      </c>
+      <c r="D415" t="n">
+        <v>90.58</v>
+      </c>
+      <c r="E415" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="F415" t="n">
+        <v>89.95</v>
+      </c>
+      <c r="G415" t="n">
+        <v>743989</v>
+      </c>
+      <c r="H415" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I415" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J415" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="K415" t="n">
+        <v>89.44</v>
+      </c>
+      <c r="L415" t="n">
+        <v>87.02</v>
+      </c>
+      <c r="M415" t="n">
+        <v>79.94</v>
+      </c>
+      <c r="N415" s="5" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="O415" t="n">
+        <v>29</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5</v>
+      </c>
+      <c r="T415" s="5" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U415" s="5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -649,7 +649,9 @@
       <c r="T2" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="U2" s="3" t="inlineStr"/>
+      <c r="U2" s="3" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V2" s="1" t="inlineStr"/>
       <c r="W2" s="2" t="n">
         <v>168.6</v>
@@ -722,7 +724,9 @@
       <c r="T3" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U3" s="5" t="inlineStr"/>
+      <c r="U3" s="5" t="n">
+        <v>13.5</v>
+      </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" s="6" t="n">
         <v>163.6</v>
@@ -795,7 +799,9 @@
       <c r="T4" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" s="6" t="n">
         <v>157.4</v>
@@ -868,7 +874,9 @@
       <c r="T5" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U5" s="5" t="inlineStr"/>
+      <c r="U5" s="5" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="6" t="n">
         <v>156.7</v>
@@ -941,7 +949,9 @@
       <c r="T6" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="6" t="n">
         <v>158.5</v>
@@ -1018,7 +1028,9 @@
       <c r="T7" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U7" s="5" t="inlineStr"/>
+      <c r="U7" s="5" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="6" t="n">
         <v>155.4</v>
@@ -1091,7 +1103,9 @@
       <c r="T8" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U8" s="5" t="inlineStr"/>
+      <c r="U8" s="5" t="n">
+        <v>15</v>
+      </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="6" t="n">
         <v>159.4</v>
@@ -1164,7 +1178,9 @@
       <c r="T9" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U9" s="5" t="inlineStr"/>
+      <c r="U9" s="5" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" s="6" t="n">
         <v>162.6</v>
@@ -1237,7 +1253,9 @@
       <c r="T10" s="5" t="n">
         <v>15.5</v>
       </c>
-      <c r="U10" s="5" t="inlineStr"/>
+      <c r="U10" s="5" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" s="6" t="n">
         <v>163.6</v>
@@ -1310,7 +1328,9 @@
       <c r="T11" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U11" s="5" t="inlineStr"/>
+      <c r="U11" s="5" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" s="6" t="n">
         <v>166.5</v>
@@ -1383,7 +1403,9 @@
       <c r="T12" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U12" s="5" t="inlineStr"/>
+      <c r="U12" s="5" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" s="6" t="n">
         <v>166.9</v>
@@ -1456,7 +1478,9 @@
       <c r="T13" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="U13" s="5" t="inlineStr"/>
+      <c r="U13" s="5" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" s="6" t="n">
         <v>168.8</v>
@@ -1529,7 +1553,9 @@
       <c r="T14" s="5" t="n">
         <v>15.9</v>
       </c>
-      <c r="U14" s="5" t="inlineStr"/>
+      <c r="U14" s="5" t="n">
+        <v>12.8</v>
+      </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" s="6" t="n">
         <v>166.1</v>
@@ -1602,7 +1628,9 @@
       <c r="T15" s="5" t="n">
         <v>15.1</v>
       </c>
-      <c r="U15" s="5" t="inlineStr"/>
+      <c r="U15" s="5" t="n">
+        <v>11</v>
+      </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" s="6" t="n">
         <v>163.4</v>
@@ -1675,7 +1703,9 @@
       <c r="T16" s="5" t="n">
         <v>14.8</v>
       </c>
-      <c r="U16" s="5" t="inlineStr"/>
+      <c r="U16" s="5" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" s="6" t="n">
         <v>168</v>
@@ -1748,7 +1778,9 @@
       <c r="T17" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U17" s="5" t="inlineStr"/>
+      <c r="U17" s="5" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" s="6" t="n">
         <v>183.1</v>
@@ -1821,7 +1853,9 @@
       <c r="T18" s="5" t="n">
         <v>15.3</v>
       </c>
-      <c r="U18" s="5" t="inlineStr"/>
+      <c r="U18" s="5" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" s="6" t="n">
         <v>175.8</v>
@@ -1894,7 +1928,9 @@
       <c r="T19" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U19" s="5" t="inlineStr"/>
+      <c r="U19" s="5" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" s="6" t="n">
         <v>178.6</v>
@@ -1971,7 +2007,9 @@
       <c r="T20" s="5" t="n">
         <v>18.2</v>
       </c>
-      <c r="U20" s="5" t="inlineStr"/>
+      <c r="U20" s="5" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" s="6" t="n">
         <v>165</v>
@@ -2048,7 +2086,9 @@
       <c r="T21" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="U21" s="5" t="inlineStr"/>
+      <c r="U21" s="5" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" s="6" t="n">
         <v>156.9</v>
@@ -2121,7 +2161,9 @@
       <c r="T22" s="5" t="n">
         <v>19.4</v>
       </c>
-      <c r="U22" s="5" t="inlineStr"/>
+      <c r="U22" s="5" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V22" t="inlineStr"/>
       <c r="W22" s="6" t="n">
         <v>157.6</v>
@@ -2194,7 +2236,9 @@
       <c r="T23" s="5" t="n">
         <v>19.1</v>
       </c>
-      <c r="U23" s="5" t="inlineStr"/>
+      <c r="U23" s="5" t="n">
+        <v>20.5</v>
+      </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" s="5" t="n">
         <v>153.4</v>
@@ -2271,7 +2315,9 @@
       <c r="T24" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="U24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V24" s="1" t="inlineStr"/>
       <c r="W24" s="3" t="n">
         <v>149.3</v>
@@ -2344,7 +2390,9 @@
       <c r="T25" s="5" t="n">
         <v>19.6</v>
       </c>
-      <c r="U25" s="5" t="inlineStr"/>
+      <c r="U25" s="5" t="n">
+        <v>18.7</v>
+      </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" s="6" t="n">
         <v>157.9</v>
@@ -2421,7 +2469,9 @@
       <c r="T26" s="5" t="n">
         <v>22.8</v>
       </c>
-      <c r="U26" s="5" t="inlineStr"/>
+      <c r="U26" s="5" t="n">
+        <v>21.8</v>
+      </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" s="5" t="n">
         <v>154.3</v>
@@ -2498,7 +2548,9 @@
       <c r="T27" s="5" t="n">
         <v>23.5</v>
       </c>
-      <c r="U27" s="5" t="inlineStr"/>
+      <c r="U27" s="5" t="n">
+        <v>24.6</v>
+      </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" s="5" t="n">
         <v>151.4</v>
@@ -2571,7 +2623,9 @@
       <c r="T28" s="5" t="n">
         <v>21.9</v>
       </c>
-      <c r="U28" s="5" t="inlineStr"/>
+      <c r="U28" s="5" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" s="5" t="n">
         <v>138.9</v>
@@ -2648,7 +2702,9 @@
       <c r="T29" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="U29" s="3" t="inlineStr"/>
+      <c r="U29" s="7" t="n">
+        <v>31.1</v>
+      </c>
       <c r="V29" s="1" t="inlineStr"/>
       <c r="W29" s="3" t="n">
         <v>137.6</v>
@@ -2725,7 +2781,9 @@
       <c r="T30" s="5" t="n">
         <v>23.4</v>
       </c>
-      <c r="U30" s="5" t="inlineStr"/>
+      <c r="U30" s="5" t="n">
+        <v>24.7</v>
+      </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" s="5" t="n">
         <v>139.9</v>
@@ -2802,8 +2860,14 @@
       <c r="T31" s="7" t="n">
         <v>27.9</v>
       </c>
-      <c r="U31" s="3" t="inlineStr"/>
-      <c r="V31" s="1" t="inlineStr"/>
+      <c r="U31" s="7" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="V31" s="7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W31" s="3" t="n">
         <v>146</v>
       </c>
@@ -2879,8 +2943,14 @@
       <c r="T32" s="4" t="n">
         <v>26.9</v>
       </c>
-      <c r="U32" s="5" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+      <c r="U32" s="4" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="V32" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W32" s="5" t="n">
         <v>132.8</v>
       </c>
@@ -2956,7 +3026,9 @@
       <c r="T33" s="5" t="n">
         <v>24.2</v>
       </c>
-      <c r="U33" s="5" t="inlineStr"/>
+      <c r="U33" s="5" t="n">
+        <v>23.2</v>
+      </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" s="5" t="n">
         <v>128.7</v>
@@ -3033,7 +3105,9 @@
       <c r="T34" s="5" t="n">
         <v>24.7</v>
       </c>
-      <c r="U34" s="5" t="inlineStr"/>
+      <c r="U34" s="5" t="n">
+        <v>23.4</v>
+      </c>
       <c r="V34" t="inlineStr"/>
       <c r="W34" s="5" t="n">
         <v>128.9</v>
@@ -3106,7 +3180,9 @@
       <c r="T35" s="5" t="n">
         <v>21.8</v>
       </c>
-      <c r="U35" s="5" t="inlineStr"/>
+      <c r="U35" s="5" t="n">
+        <v>21.4</v>
+      </c>
       <c r="V35" t="inlineStr"/>
       <c r="W35" s="5" t="n">
         <v>130.3</v>
@@ -3179,7 +3255,9 @@
       <c r="T36" s="5" t="n">
         <v>20.5</v>
       </c>
-      <c r="U36" s="5" t="inlineStr"/>
+      <c r="U36" s="5" t="n">
+        <v>16.4</v>
+      </c>
       <c r="V36" t="inlineStr"/>
       <c r="W36" s="5" t="n">
         <v>133.9</v>
@@ -3252,7 +3330,9 @@
       <c r="T37" s="5" t="n">
         <v>21.7</v>
       </c>
-      <c r="U37" s="5" t="inlineStr"/>
+      <c r="U37" s="5" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V37" t="inlineStr"/>
       <c r="W37" s="5" t="n">
         <v>136.8</v>
@@ -3325,7 +3405,9 @@
       <c r="T38" s="5" t="n">
         <v>19.9</v>
       </c>
-      <c r="U38" s="5" t="inlineStr"/>
+      <c r="U38" s="5" t="n">
+        <v>18.5</v>
+      </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" s="5" t="n">
         <v>136.4</v>
@@ -3398,7 +3480,9 @@
       <c r="T39" s="5" t="n">
         <v>19.8</v>
       </c>
-      <c r="U39" s="5" t="inlineStr"/>
+      <c r="U39" s="5" t="n">
+        <v>18.6</v>
+      </c>
       <c r="V39" t="inlineStr"/>
       <c r="W39" s="5" t="n">
         <v>140.8</v>
@@ -3471,7 +3555,9 @@
       <c r="T40" s="5" t="n">
         <v>19.3</v>
       </c>
-      <c r="U40" s="5" t="inlineStr"/>
+      <c r="U40" s="5" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V40" t="inlineStr"/>
       <c r="W40" s="5" t="n">
         <v>141.7</v>
@@ -3544,7 +3630,9 @@
       <c r="T41" s="5" t="n">
         <v>17.5</v>
       </c>
-      <c r="U41" s="5" t="inlineStr"/>
+      <c r="U41" s="5" t="n">
+        <v>13</v>
+      </c>
       <c r="V41" t="inlineStr"/>
       <c r="W41" s="5" t="n">
         <v>144</v>
@@ -3617,7 +3705,9 @@
       <c r="T42" s="5" t="n">
         <v>17.1</v>
       </c>
-      <c r="U42" s="5" t="inlineStr"/>
+      <c r="U42" s="5" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V42" t="inlineStr"/>
       <c r="W42" s="5" t="n">
         <v>148.7</v>
@@ -3694,7 +3784,9 @@
       <c r="T43" s="5" t="n">
         <v>18.3</v>
       </c>
-      <c r="U43" s="5" t="inlineStr"/>
+      <c r="U43" s="5" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V43" t="inlineStr"/>
       <c r="W43" s="5" t="n">
         <v>144.8</v>
@@ -3767,7 +3859,9 @@
       <c r="T44" s="5" t="n">
         <v>18.7</v>
       </c>
-      <c r="U44" s="5" t="inlineStr"/>
+      <c r="U44" s="5" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V44" t="inlineStr"/>
       <c r="W44" s="5" t="n">
         <v>140.9</v>
@@ -3840,7 +3934,9 @@
       <c r="T45" s="5" t="n">
         <v>21.6</v>
       </c>
-      <c r="U45" s="5" t="inlineStr"/>
+      <c r="U45" s="4" t="n">
+        <v>25.4</v>
+      </c>
       <c r="V45" t="inlineStr"/>
       <c r="W45" s="5" t="n">
         <v>139</v>
@@ -3913,7 +4009,9 @@
       <c r="T46" s="5" t="n">
         <v>22.3</v>
       </c>
-      <c r="U46" s="5" t="inlineStr"/>
+      <c r="U46" s="5" t="n">
+        <v>21.8</v>
+      </c>
       <c r="V46" t="inlineStr"/>
       <c r="W46" s="5" t="n">
         <v>148.6</v>
@@ -3986,7 +4084,9 @@
       <c r="T47" s="5" t="n">
         <v>21.8</v>
       </c>
-      <c r="U47" s="5" t="inlineStr"/>
+      <c r="U47" s="5" t="n">
+        <v>20.1</v>
+      </c>
       <c r="V47" t="inlineStr"/>
       <c r="W47" s="5" t="n">
         <v>143</v>
@@ -4059,7 +4159,9 @@
       <c r="T48" s="5" t="n">
         <v>21.5</v>
       </c>
-      <c r="U48" s="5" t="inlineStr"/>
+      <c r="U48" s="4" t="n">
+        <v>26.7</v>
+      </c>
       <c r="V48" t="inlineStr"/>
       <c r="W48" s="5" t="n">
         <v>144.3</v>
@@ -4132,8 +4234,14 @@
       <c r="T49" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="U49" s="3" t="inlineStr"/>
-      <c r="V49" s="1" t="inlineStr"/>
+      <c r="U49" s="7" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="V49" s="7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W49" s="3" t="n">
         <v>139.2</v>
       </c>
@@ -4209,8 +4317,14 @@
       <c r="T50" s="7" t="n">
         <v>45.3</v>
       </c>
-      <c r="U50" s="3" t="inlineStr"/>
-      <c r="V50" s="1" t="inlineStr"/>
+      <c r="U50" s="7" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="V50" s="7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W50" s="3" t="n">
         <v>136.5</v>
       </c>
@@ -4286,8 +4400,14 @@
       <c r="T51" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="U51" s="5" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
+      <c r="U51" s="4" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="V51" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W51" s="5" t="n">
         <v>133.8</v>
       </c>
@@ -4363,8 +4483,14 @@
       <c r="T52" s="4" t="n">
         <v>52.3</v>
       </c>
-      <c r="U52" s="5" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
+      <c r="U52" s="4" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="V52" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W52" s="5" t="n">
         <v>135.7</v>
       </c>
@@ -4436,8 +4562,14 @@
       <c r="T53" s="4" t="n">
         <v>33.6</v>
       </c>
-      <c r="U53" s="5" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
+      <c r="U53" s="4" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="V53" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W53" s="5" t="n">
         <v>142.2</v>
       </c>
@@ -4509,8 +4641,14 @@
       <c r="T54" s="7" t="n">
         <v>40.7</v>
       </c>
-      <c r="U54" s="3" t="inlineStr"/>
-      <c r="V54" s="1" t="inlineStr"/>
+      <c r="U54" s="7" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="V54" s="7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W54" s="3" t="n">
         <v>127.5</v>
       </c>
@@ -4582,8 +4720,14 @@
       <c r="T55" s="4" t="n">
         <v>37.6</v>
       </c>
-      <c r="U55" s="5" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
+      <c r="U55" s="4" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="V55" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W55" s="5" t="n">
         <v>128.6</v>
       </c>
@@ -4655,7 +4799,9 @@
       <c r="T56" s="4" t="n">
         <v>30.9</v>
       </c>
-      <c r="U56" s="5" t="inlineStr"/>
+      <c r="U56" s="4" t="n">
+        <v>28.5</v>
+      </c>
       <c r="V56" t="inlineStr"/>
       <c r="W56" s="5" t="n">
         <v>135.7</v>
@@ -4728,7 +4874,9 @@
       <c r="T57" s="4" t="n">
         <v>30.1</v>
       </c>
-      <c r="U57" s="5" t="inlineStr"/>
+      <c r="U57" s="4" t="n">
+        <v>26</v>
+      </c>
       <c r="V57" t="inlineStr"/>
       <c r="W57" s="5" t="n">
         <v>135.8</v>
@@ -4801,8 +4949,14 @@
       <c r="T58" s="7" t="n">
         <v>32.6</v>
       </c>
-      <c r="U58" s="3" t="inlineStr"/>
-      <c r="V58" s="1" t="inlineStr"/>
+      <c r="U58" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="V58" s="7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W58" s="3" t="n">
         <v>131.3</v>
       </c>
@@ -4874,8 +5028,14 @@
       <c r="T59" s="4" t="n">
         <v>29.6</v>
       </c>
-      <c r="U59" s="5" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
+      <c r="U59" s="4" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="V59" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W59" s="5" t="n">
         <v>130</v>
       </c>
@@ -4947,7 +5107,9 @@
       <c r="T60" s="4" t="n">
         <v>33.8</v>
       </c>
-      <c r="U60" s="5" t="inlineStr"/>
+      <c r="U60" s="4" t="n">
+        <v>30.6</v>
+      </c>
       <c r="V60" t="inlineStr"/>
       <c r="W60" s="4" t="n">
         <v>125.8</v>
@@ -5020,7 +5182,9 @@
       <c r="T61" s="4" t="n">
         <v>30.6</v>
       </c>
-      <c r="U61" s="5" t="inlineStr"/>
+      <c r="U61" s="4" t="n">
+        <v>29.1</v>
+      </c>
       <c r="V61" t="inlineStr"/>
       <c r="W61" s="4" t="n">
         <v>125.9</v>
@@ -5093,8 +5257,14 @@
       <c r="T62" s="4" t="n">
         <v>28.5</v>
       </c>
-      <c r="U62" s="5" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
+      <c r="U62" s="4" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="V62" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W62" s="4" t="n">
         <v>126.7</v>
       </c>
@@ -5166,7 +5336,9 @@
       <c r="T63" s="4" t="n">
         <v>26.5</v>
       </c>
-      <c r="U63" s="5" t="inlineStr"/>
+      <c r="U63" s="4" t="n">
+        <v>25.7</v>
+      </c>
       <c r="V63" t="inlineStr"/>
       <c r="W63" s="5" t="n">
         <v>129</v>
@@ -5239,7 +5411,9 @@
       <c r="T64" s="5" t="n">
         <v>24.8</v>
       </c>
-      <c r="U64" s="5" t="inlineStr"/>
+      <c r="U64" s="5" t="n">
+        <v>23.6</v>
+      </c>
       <c r="V64" t="inlineStr"/>
       <c r="W64" s="5" t="n">
         <v>132.4</v>
@@ -5312,7 +5486,9 @@
       <c r="T65" s="4" t="n">
         <v>25.1</v>
       </c>
-      <c r="U65" s="5" t="inlineStr"/>
+      <c r="U65" s="5" t="n">
+        <v>21.4</v>
+      </c>
       <c r="V65" t="inlineStr"/>
       <c r="W65" s="5" t="n">
         <v>131.3</v>
@@ -5385,7 +5561,9 @@
       <c r="T66" s="5" t="n">
         <v>24.2</v>
       </c>
-      <c r="U66" s="5" t="inlineStr"/>
+      <c r="U66" s="5" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V66" t="inlineStr"/>
       <c r="W66" s="5" t="n">
         <v>134.3</v>
@@ -5458,7 +5636,9 @@
       <c r="T67" s="5" t="n">
         <v>24.7</v>
       </c>
-      <c r="U67" s="5" t="inlineStr"/>
+      <c r="U67" s="5" t="n">
+        <v>22.9</v>
+      </c>
       <c r="V67" t="inlineStr"/>
       <c r="W67" s="5" t="n">
         <v>132.7</v>
@@ -5531,7 +5711,9 @@
       <c r="T68" s="5" t="n">
         <v>24.6</v>
       </c>
-      <c r="U68" s="5" t="inlineStr"/>
+      <c r="U68" s="4" t="n">
+        <v>27.5</v>
+      </c>
       <c r="V68" t="inlineStr"/>
       <c r="W68" s="5" t="n">
         <v>134.1</v>
@@ -5604,7 +5786,9 @@
       <c r="T69" s="5" t="n">
         <v>22.7</v>
       </c>
-      <c r="U69" s="5" t="inlineStr"/>
+      <c r="U69" s="5" t="n">
+        <v>20</v>
+      </c>
       <c r="V69" t="inlineStr"/>
       <c r="W69" s="5" t="n">
         <v>134.8</v>
@@ -5677,7 +5861,9 @@
       <c r="T70" s="5" t="n">
         <v>23.6</v>
       </c>
-      <c r="U70" s="5" t="inlineStr"/>
+      <c r="U70" s="5" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V70" t="inlineStr"/>
       <c r="W70" s="5" t="n">
         <v>134.1</v>
@@ -5750,7 +5936,9 @@
       <c r="T71" s="5" t="n">
         <v>24.8</v>
       </c>
-      <c r="U71" s="5" t="inlineStr"/>
+      <c r="U71" s="5" t="n">
+        <v>22.2</v>
+      </c>
       <c r="V71" t="inlineStr"/>
       <c r="W71" s="5" t="n">
         <v>133.2</v>
@@ -5823,7 +6011,9 @@
       <c r="T72" s="5" t="n">
         <v>23.5</v>
       </c>
-      <c r="U72" s="5" t="inlineStr"/>
+      <c r="U72" s="5" t="n">
+        <v>19.8</v>
+      </c>
       <c r="V72" t="inlineStr"/>
       <c r="W72" s="5" t="n">
         <v>132.2</v>
@@ -5896,7 +6086,9 @@
       <c r="T73" s="5" t="n">
         <v>22.5</v>
       </c>
-      <c r="U73" s="5" t="inlineStr"/>
+      <c r="U73" s="5" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V73" t="inlineStr"/>
       <c r="W73" s="5" t="n">
         <v>131.5</v>
@@ -5969,7 +6161,9 @@
       <c r="T74" s="5" t="n">
         <v>21.9</v>
       </c>
-      <c r="U74" s="5" t="inlineStr"/>
+      <c r="U74" s="4" t="n">
+        <v>26.9</v>
+      </c>
       <c r="V74" t="inlineStr"/>
       <c r="W74" s="5" t="n">
         <v>128.4</v>
@@ -6042,7 +6236,9 @@
       <c r="T75" s="5" t="n">
         <v>18.4</v>
       </c>
-      <c r="U75" s="5" t="inlineStr"/>
+      <c r="U75" s="5" t="n">
+        <v>18.7</v>
+      </c>
       <c r="V75" t="inlineStr"/>
       <c r="W75" s="5" t="n">
         <v>137.7</v>
@@ -6115,7 +6311,9 @@
       <c r="T76" s="5" t="n">
         <v>18.2</v>
       </c>
-      <c r="U76" s="5" t="inlineStr"/>
+      <c r="U76" s="5" t="n">
+        <v>15.4</v>
+      </c>
       <c r="V76" t="inlineStr"/>
       <c r="W76" s="5" t="n">
         <v>140.5</v>
@@ -6188,7 +6386,9 @@
       <c r="T77" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U77" s="5" t="inlineStr"/>
+      <c r="U77" s="5" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V77" t="inlineStr"/>
       <c r="W77" s="5" t="n">
         <v>138.9</v>
@@ -6261,7 +6461,9 @@
       <c r="T78" s="5" t="n">
         <v>17.8</v>
       </c>
-      <c r="U78" s="5" t="inlineStr"/>
+      <c r="U78" s="5" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V78" t="inlineStr"/>
       <c r="W78" s="5" t="n">
         <v>140.9</v>
@@ -6334,7 +6536,9 @@
       <c r="T79" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U79" s="5" t="inlineStr"/>
+      <c r="U79" s="5" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V79" t="inlineStr"/>
       <c r="W79" s="5" t="n">
         <v>136</v>
@@ -6407,7 +6611,9 @@
       <c r="T80" s="5" t="n">
         <v>18.1</v>
       </c>
-      <c r="U80" s="5" t="inlineStr"/>
+      <c r="U80" s="5" t="n">
+        <v>13.5</v>
+      </c>
       <c r="V80" t="inlineStr"/>
       <c r="W80" s="5" t="n">
         <v>135.9</v>
@@ -6480,7 +6686,9 @@
       <c r="T81" s="5" t="n">
         <v>18.1</v>
       </c>
-      <c r="U81" s="5" t="inlineStr"/>
+      <c r="U81" s="5" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V81" t="inlineStr"/>
       <c r="W81" s="5" t="n">
         <v>137.3</v>
@@ -6553,7 +6761,9 @@
       <c r="T82" s="5" t="n">
         <v>20.9</v>
       </c>
-      <c r="U82" s="5" t="inlineStr"/>
+      <c r="U82" s="5" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V82" t="inlineStr"/>
       <c r="W82" s="5" t="n">
         <v>137.3</v>
@@ -6626,7 +6836,9 @@
       <c r="T83" s="5" t="n">
         <v>20.3</v>
       </c>
-      <c r="U83" s="5" t="inlineStr"/>
+      <c r="U83" s="5" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V83" t="inlineStr"/>
       <c r="W83" s="5" t="n">
         <v>139</v>
@@ -6703,7 +6915,9 @@
       <c r="T84" s="5" t="n">
         <v>22.3</v>
       </c>
-      <c r="U84" s="5" t="inlineStr"/>
+      <c r="U84" s="5" t="n">
+        <v>21.7</v>
+      </c>
       <c r="V84" t="inlineStr"/>
       <c r="W84" s="5" t="n">
         <v>139.3</v>
@@ -6776,7 +6990,9 @@
       <c r="T85" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="U85" s="5" t="inlineStr"/>
+      <c r="U85" s="5" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" s="5" t="n">
         <v>140.9</v>
@@ -6849,7 +7065,9 @@
       <c r="T86" s="5" t="n">
         <v>19.3</v>
       </c>
-      <c r="U86" s="5" t="inlineStr"/>
+      <c r="U86" s="5" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" s="5" t="n">
         <v>137.6</v>
@@ -6922,7 +7140,9 @@
       <c r="T87" s="5" t="n">
         <v>19.2</v>
       </c>
-      <c r="U87" s="5" t="inlineStr"/>
+      <c r="U87" s="5" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V87" t="inlineStr"/>
       <c r="W87" s="5" t="n">
         <v>137.3</v>
@@ -6995,7 +7215,9 @@
       <c r="T88" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U88" s="5" t="inlineStr"/>
+      <c r="U88" s="5" t="n">
+        <v>17</v>
+      </c>
       <c r="V88" t="inlineStr"/>
       <c r="W88" s="5" t="n">
         <v>138.2</v>
@@ -7068,7 +7290,9 @@
       <c r="T89" s="5" t="n">
         <v>18.4</v>
       </c>
-      <c r="U89" s="5" t="inlineStr"/>
+      <c r="U89" s="5" t="n">
+        <v>13.3</v>
+      </c>
       <c r="V89" t="inlineStr"/>
       <c r="W89" s="5" t="n">
         <v>141</v>
@@ -7141,7 +7365,9 @@
       <c r="T90" s="5" t="n">
         <v>17.7</v>
       </c>
-      <c r="U90" s="5" t="inlineStr"/>
+      <c r="U90" s="5" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V90" t="inlineStr"/>
       <c r="W90" s="5" t="n">
         <v>141.6</v>
@@ -7214,7 +7440,9 @@
       <c r="T91" s="5" t="n">
         <v>17.6</v>
       </c>
-      <c r="U91" s="5" t="inlineStr"/>
+      <c r="U91" s="5" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V91" t="inlineStr"/>
       <c r="W91" s="5" t="n">
         <v>137.5</v>
@@ -7287,7 +7515,9 @@
       <c r="T92" s="5" t="n">
         <v>18.5</v>
       </c>
-      <c r="U92" s="5" t="inlineStr"/>
+      <c r="U92" s="5" t="n">
+        <v>19</v>
+      </c>
       <c r="V92" t="inlineStr"/>
       <c r="W92" s="5" t="n">
         <v>140.1</v>
@@ -7360,7 +7590,9 @@
       <c r="T93" s="5" t="n">
         <v>16.8</v>
       </c>
-      <c r="U93" s="5" t="inlineStr"/>
+      <c r="U93" s="5" t="n">
+        <v>14.3</v>
+      </c>
       <c r="V93" t="inlineStr"/>
       <c r="W93" s="5" t="n">
         <v>138.9</v>
@@ -7433,7 +7665,9 @@
       <c r="T94" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U94" s="5" t="inlineStr"/>
+      <c r="U94" s="5" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V94" t="inlineStr"/>
       <c r="W94" s="5" t="n">
         <v>139.2</v>
@@ -7506,7 +7740,9 @@
       <c r="T95" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="U95" s="5" t="inlineStr"/>
+      <c r="U95" s="5" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V95" t="inlineStr"/>
       <c r="W95" s="5" t="n">
         <v>141.2</v>
@@ -7579,7 +7815,9 @@
       <c r="T96" s="5" t="n">
         <v>17.3</v>
       </c>
-      <c r="U96" s="5" t="inlineStr"/>
+      <c r="U96" s="5" t="n">
+        <v>13.9</v>
+      </c>
       <c r="V96" t="inlineStr"/>
       <c r="W96" s="5" t="n">
         <v>141.4</v>
@@ -7652,7 +7890,9 @@
       <c r="T97" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="U97" s="5" t="inlineStr"/>
+      <c r="U97" s="5" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V97" t="inlineStr"/>
       <c r="W97" s="5" t="n">
         <v>145.6</v>
@@ -7725,7 +7965,9 @@
       <c r="T98" s="5" t="n">
         <v>20.8</v>
       </c>
-      <c r="U98" s="5" t="inlineStr"/>
+      <c r="U98" s="5" t="n">
+        <v>21.7</v>
+      </c>
       <c r="V98" t="inlineStr"/>
       <c r="W98" s="5" t="n">
         <v>149.6</v>
@@ -7798,7 +8040,9 @@
       <c r="T99" s="5" t="n">
         <v>19.1</v>
       </c>
-      <c r="U99" s="5" t="inlineStr"/>
+      <c r="U99" s="5" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V99" t="inlineStr"/>
       <c r="W99" s="6" t="n">
         <v>156.6</v>
@@ -7871,7 +8115,9 @@
       <c r="T100" s="5" t="n">
         <v>21.6</v>
       </c>
-      <c r="U100" s="5" t="inlineStr"/>
+      <c r="U100" s="5" t="n">
+        <v>21</v>
+      </c>
       <c r="V100" t="inlineStr"/>
       <c r="W100" s="5" t="n">
         <v>154.4</v>
@@ -7944,7 +8190,9 @@
       <c r="T101" s="5" t="n">
         <v>20.1</v>
       </c>
-      <c r="U101" s="5" t="inlineStr"/>
+      <c r="U101" s="5" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V101" t="inlineStr"/>
       <c r="W101" s="5" t="n">
         <v>148.4</v>
@@ -8017,7 +8265,9 @@
       <c r="T102" s="5" t="n">
         <v>20.6</v>
       </c>
-      <c r="U102" s="5" t="inlineStr"/>
+      <c r="U102" s="5" t="n">
+        <v>18.4</v>
+      </c>
       <c r="V102" t="inlineStr"/>
       <c r="W102" s="5" t="n">
         <v>149.2</v>
@@ -8090,7 +8340,9 @@
       <c r="T103" s="5" t="n">
         <v>19.8</v>
       </c>
-      <c r="U103" s="5" t="inlineStr"/>
+      <c r="U103" s="5" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V103" t="inlineStr"/>
       <c r="W103" s="5" t="n">
         <v>154.8</v>
@@ -8163,7 +8415,9 @@
       <c r="T104" s="5" t="n">
         <v>17.5</v>
       </c>
-      <c r="U104" s="5" t="inlineStr"/>
+      <c r="U104" s="5" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V104" t="inlineStr"/>
       <c r="W104" s="6" t="n">
         <v>155</v>
@@ -8236,7 +8490,9 @@
       <c r="T105" s="5" t="n">
         <v>16.8</v>
       </c>
-      <c r="U105" s="5" t="inlineStr"/>
+      <c r="U105" s="5" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V105" t="inlineStr"/>
       <c r="W105" s="5" t="n">
         <v>152.2</v>
@@ -8309,7 +8565,9 @@
       <c r="T106" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U106" s="5" t="inlineStr"/>
+      <c r="U106" s="5" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V106" t="inlineStr"/>
       <c r="W106" s="5" t="n">
         <v>147.5</v>
@@ -8382,7 +8640,9 @@
       <c r="T107" s="5" t="n">
         <v>16.3</v>
       </c>
-      <c r="U107" s="5" t="inlineStr"/>
+      <c r="U107" s="5" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V107" t="inlineStr"/>
       <c r="W107" s="5" t="n">
         <v>143.4</v>
@@ -8455,7 +8715,9 @@
       <c r="T108" s="5" t="n">
         <v>16.7</v>
       </c>
-      <c r="U108" s="5" t="inlineStr"/>
+      <c r="U108" s="5" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V108" t="inlineStr"/>
       <c r="W108" s="5" t="n">
         <v>139.6</v>
@@ -8528,7 +8790,9 @@
       <c r="T109" s="5" t="n">
         <v>16.8</v>
       </c>
-      <c r="U109" s="5" t="inlineStr"/>
+      <c r="U109" s="5" t="n">
+        <v>9.699999999999999</v>
+      </c>
       <c r="V109" t="inlineStr"/>
       <c r="W109" s="5" t="n">
         <v>140.1</v>
@@ -8601,7 +8865,9 @@
       <c r="T110" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U110" s="5" t="inlineStr"/>
+      <c r="U110" s="5" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V110" t="inlineStr"/>
       <c r="W110" s="5" t="n">
         <v>139.3</v>
@@ -8674,7 +8940,9 @@
       <c r="T111" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U111" s="5" t="inlineStr"/>
+      <c r="U111" s="5" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V111" t="inlineStr"/>
       <c r="W111" s="5" t="n">
         <v>141.4</v>
@@ -8747,7 +9015,9 @@
       <c r="T112" s="5" t="n">
         <v>17.8</v>
       </c>
-      <c r="U112" s="5" t="inlineStr"/>
+      <c r="U112" s="5" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V112" t="inlineStr"/>
       <c r="W112" s="5" t="n">
         <v>138</v>
@@ -8820,7 +9090,9 @@
       <c r="T113" s="5" t="n">
         <v>16.8</v>
       </c>
-      <c r="U113" s="5" t="inlineStr"/>
+      <c r="U113" s="5" t="n">
+        <v>10.5</v>
+      </c>
       <c r="V113" t="inlineStr"/>
       <c r="W113" s="5" t="n">
         <v>140.8</v>
@@ -8893,7 +9165,9 @@
       <c r="T114" s="5" t="n">
         <v>15.9</v>
       </c>
-      <c r="U114" s="5" t="inlineStr"/>
+      <c r="U114" s="5" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V114" t="inlineStr"/>
       <c r="W114" s="5" t="n">
         <v>141.8</v>
@@ -8966,7 +9240,9 @@
       <c r="T115" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U115" s="5" t="inlineStr"/>
+      <c r="U115" s="5" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V115" t="inlineStr"/>
       <c r="W115" s="5" t="n">
         <v>143.3</v>
@@ -9039,7 +9315,9 @@
       <c r="T116" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U116" s="5" t="inlineStr"/>
+      <c r="U116" s="5" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V116" t="inlineStr"/>
       <c r="W116" s="5" t="n">
         <v>145</v>
@@ -9112,7 +9390,9 @@
       <c r="T117" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U117" s="5" t="inlineStr"/>
+      <c r="U117" s="5" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V117" t="inlineStr"/>
       <c r="W117" s="5" t="n">
         <v>147</v>
@@ -9185,7 +9465,9 @@
       <c r="T118" s="5" t="n">
         <v>17.4</v>
       </c>
-      <c r="U118" s="5" t="inlineStr"/>
+      <c r="U118" s="5" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V118" t="inlineStr"/>
       <c r="W118" s="5" t="n">
         <v>143.7</v>
@@ -9258,7 +9540,9 @@
       <c r="T119" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U119" s="5" t="inlineStr"/>
+      <c r="U119" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V119" t="inlineStr"/>
       <c r="W119" s="5" t="n">
         <v>146.7</v>
@@ -9331,7 +9615,9 @@
       <c r="T120" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U120" s="5" t="inlineStr"/>
+      <c r="U120" s="5" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V120" t="inlineStr"/>
       <c r="W120" s="5" t="n">
         <v>151.1</v>
@@ -9404,7 +9690,9 @@
       <c r="T121" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U121" s="5" t="inlineStr"/>
+      <c r="U121" s="5" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V121" t="inlineStr"/>
       <c r="W121" s="5" t="n">
         <v>150.4</v>
@@ -9477,7 +9765,9 @@
       <c r="T122" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U122" s="5" t="inlineStr"/>
+      <c r="U122" s="5" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V122" t="inlineStr"/>
       <c r="W122" s="5" t="n">
         <v>154.8</v>
@@ -9550,7 +9840,9 @@
       <c r="T123" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U123" s="5" t="inlineStr"/>
+      <c r="U123" s="5" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V123" t="inlineStr"/>
       <c r="W123" s="5" t="n">
         <v>153.4</v>
@@ -9623,7 +9915,9 @@
       <c r="T124" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U124" s="5" t="inlineStr"/>
+      <c r="U124" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="V124" t="inlineStr"/>
       <c r="W124" s="6" t="n">
         <v>159.3</v>
@@ -9696,7 +9990,9 @@
       <c r="T125" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U125" s="5" t="inlineStr"/>
+      <c r="U125" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="V125" t="inlineStr"/>
       <c r="W125" s="6" t="n">
         <v>159.4</v>
@@ -9769,7 +10065,9 @@
       <c r="T126" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U126" s="5" t="inlineStr"/>
+      <c r="U126" s="5" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V126" t="inlineStr"/>
       <c r="W126" s="5" t="n">
         <v>145.6</v>
@@ -9842,7 +10140,9 @@
       <c r="T127" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="U127" s="5" t="inlineStr"/>
+      <c r="U127" s="5" t="n">
+        <v>7.9</v>
+      </c>
       <c r="V127" t="inlineStr"/>
       <c r="W127" s="5" t="n">
         <v>147.6</v>
@@ -9915,7 +10215,9 @@
       <c r="T128" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="U128" s="5" t="inlineStr"/>
+      <c r="U128" s="5" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V128" t="inlineStr"/>
       <c r="W128" s="5" t="n">
         <v>149.1</v>
@@ -9988,7 +10290,9 @@
       <c r="T129" s="5" t="n">
         <v>15.5</v>
       </c>
-      <c r="U129" s="5" t="inlineStr"/>
+      <c r="U129" s="5" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V129" t="inlineStr"/>
       <c r="W129" s="5" t="n">
         <v>154.1</v>
@@ -10061,7 +10365,9 @@
       <c r="T130" s="5" t="n">
         <v>16.7</v>
       </c>
-      <c r="U130" s="5" t="inlineStr"/>
+      <c r="U130" s="5" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V130" t="inlineStr"/>
       <c r="W130" s="5" t="n">
         <v>152.3</v>
@@ -10138,7 +10444,9 @@
       <c r="T131" s="5" t="n">
         <v>20.4</v>
       </c>
-      <c r="U131" s="5" t="inlineStr"/>
+      <c r="U131" s="5" t="n">
+        <v>20</v>
+      </c>
       <c r="V131" t="inlineStr"/>
       <c r="W131" s="6" t="n">
         <v>155.5</v>
@@ -10211,7 +10519,9 @@
       <c r="T132" s="5" t="n">
         <v>17.5</v>
       </c>
-      <c r="U132" s="5" t="inlineStr"/>
+      <c r="U132" s="5" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V132" t="inlineStr"/>
       <c r="W132" s="6" t="n">
         <v>159.3</v>
@@ -10288,7 +10598,9 @@
       <c r="T133" s="5" t="n">
         <v>17.9</v>
       </c>
-      <c r="U133" s="5" t="inlineStr"/>
+      <c r="U133" s="5" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V133" t="inlineStr"/>
       <c r="W133" s="5" t="n">
         <v>149.9</v>
@@ -10361,7 +10673,9 @@
       <c r="T134" s="5" t="n">
         <v>16.8</v>
       </c>
-      <c r="U134" s="5" t="inlineStr"/>
+      <c r="U134" s="5" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V134" t="inlineStr"/>
       <c r="W134" s="5" t="n">
         <v>149.7</v>
@@ -10434,7 +10748,9 @@
       <c r="T135" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U135" s="5" t="inlineStr"/>
+      <c r="U135" s="5" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V135" t="inlineStr"/>
       <c r="W135" s="5" t="n">
         <v>147</v>
@@ -10507,7 +10823,9 @@
       <c r="T136" s="5" t="n">
         <v>15.1</v>
       </c>
-      <c r="U136" s="5" t="inlineStr"/>
+      <c r="U136" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V136" t="inlineStr"/>
       <c r="W136" s="5" t="n">
         <v>147.5</v>
@@ -10580,7 +10898,9 @@
       <c r="T137" s="5" t="n">
         <v>16.2</v>
       </c>
-      <c r="U137" s="5" t="inlineStr"/>
+      <c r="U137" s="5" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V137" t="inlineStr"/>
       <c r="W137" s="5" t="n">
         <v>148.6</v>
@@ -10653,7 +10973,9 @@
       <c r="T138" s="5" t="n">
         <v>14.7</v>
       </c>
-      <c r="U138" s="5" t="inlineStr"/>
+      <c r="U138" s="5" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V138" t="inlineStr"/>
       <c r="W138" s="5" t="n">
         <v>151.4</v>
@@ -10726,7 +11048,9 @@
       <c r="T139" s="5" t="n">
         <v>14.5</v>
       </c>
-      <c r="U139" s="5" t="inlineStr"/>
+      <c r="U139" s="5" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V139" t="inlineStr"/>
       <c r="W139" s="5" t="n">
         <v>153.1</v>
@@ -10799,7 +11123,9 @@
       <c r="T140" s="5" t="n">
         <v>14.8</v>
       </c>
-      <c r="U140" s="5" t="inlineStr"/>
+      <c r="U140" s="5" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V140" t="inlineStr"/>
       <c r="W140" s="5" t="n">
         <v>150.6</v>
@@ -10872,7 +11198,9 @@
       <c r="T141" s="5" t="n">
         <v>15.1</v>
       </c>
-      <c r="U141" s="5" t="inlineStr"/>
+      <c r="U141" s="5" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V141" t="inlineStr"/>
       <c r="W141" s="5" t="n">
         <v>153.8</v>
@@ -10945,7 +11273,9 @@
       <c r="T142" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="U142" s="5" t="inlineStr"/>
+      <c r="U142" s="5" t="n">
+        <v>7.8</v>
+      </c>
       <c r="V142" t="inlineStr"/>
       <c r="W142" s="5" t="n">
         <v>153.9</v>
@@ -11022,7 +11352,9 @@
       <c r="T143" s="5" t="n">
         <v>15.6</v>
       </c>
-      <c r="U143" s="5" t="inlineStr"/>
+      <c r="U143" s="5" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V143" t="inlineStr"/>
       <c r="W143" s="5" t="n">
         <v>153.2</v>
@@ -11095,7 +11427,9 @@
       <c r="T144" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U144" s="5" t="inlineStr"/>
+      <c r="U144" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V144" t="inlineStr"/>
       <c r="W144" s="5" t="n">
         <v>144.6</v>
@@ -11168,7 +11502,9 @@
       <c r="T145" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U145" s="5" t="inlineStr"/>
+      <c r="U145" s="5" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V145" t="inlineStr"/>
       <c r="W145" s="5" t="n">
         <v>144.3</v>
@@ -11241,7 +11577,9 @@
       <c r="T146" s="5" t="n">
         <v>14.2</v>
       </c>
-      <c r="U146" s="5" t="inlineStr"/>
+      <c r="U146" s="5" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V146" t="inlineStr"/>
       <c r="W146" s="5" t="n">
         <v>146.4</v>
@@ -11318,7 +11656,9 @@
       <c r="T147" s="5" t="n">
         <v>14.8</v>
       </c>
-      <c r="U147" s="5" t="inlineStr"/>
+      <c r="U147" s="5" t="n">
+        <v>8.1</v>
+      </c>
       <c r="V147" t="inlineStr"/>
       <c r="W147" s="5" t="n">
         <v>150</v>
@@ -11391,7 +11731,9 @@
       <c r="T148" s="5" t="n">
         <v>14.6</v>
       </c>
-      <c r="U148" s="5" t="inlineStr"/>
+      <c r="U148" s="5" t="n">
+        <v>7.8</v>
+      </c>
       <c r="V148" t="inlineStr"/>
       <c r="W148" s="6" t="n">
         <v>156.5</v>
@@ -11464,7 +11806,9 @@
       <c r="T149" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U149" s="5" t="inlineStr"/>
+      <c r="U149" s="5" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V149" t="inlineStr"/>
       <c r="W149" s="5" t="n">
         <v>150.9</v>
@@ -11537,7 +11881,9 @@
       <c r="T150" s="5" t="n">
         <v>14.4</v>
       </c>
-      <c r="U150" s="5" t="inlineStr"/>
+      <c r="U150" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V150" t="inlineStr"/>
       <c r="W150" s="5" t="n">
         <v>152.5</v>
@@ -11614,7 +11960,9 @@
       <c r="T151" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U151" s="5" t="inlineStr"/>
+      <c r="U151" s="5" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V151" t="inlineStr"/>
       <c r="W151" s="5" t="n">
         <v>152.1</v>
@@ -11687,7 +12035,9 @@
       <c r="T152" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U152" s="5" t="inlineStr"/>
+      <c r="U152" s="5" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V152" t="inlineStr"/>
       <c r="W152" s="5" t="n">
         <v>151.5</v>
@@ -11760,7 +12110,9 @@
       <c r="T153" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U153" s="5" t="inlineStr"/>
+      <c r="U153" s="5" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V153" t="inlineStr"/>
       <c r="W153" s="5" t="n">
         <v>150.2</v>
@@ -11833,7 +12185,9 @@
       <c r="T154" s="5" t="n">
         <v>15.3</v>
       </c>
-      <c r="U154" s="5" t="inlineStr"/>
+      <c r="U154" s="5" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V154" t="inlineStr"/>
       <c r="W154" s="5" t="n">
         <v>154</v>
@@ -11906,7 +12260,9 @@
       <c r="T155" s="5" t="n">
         <v>15.2</v>
       </c>
-      <c r="U155" s="5" t="inlineStr"/>
+      <c r="U155" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="V155" t="inlineStr"/>
       <c r="W155" s="5" t="n">
         <v>148.2</v>
@@ -11979,7 +12335,9 @@
       <c r="T156" s="5" t="n">
         <v>15.1</v>
       </c>
-      <c r="U156" s="5" t="inlineStr"/>
+      <c r="U156" s="5" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V156" t="inlineStr"/>
       <c r="W156" s="5" t="n">
         <v>148.8</v>
@@ -12052,7 +12410,9 @@
       <c r="T157" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="U157" s="5" t="inlineStr"/>
+      <c r="U157" s="5" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V157" t="inlineStr"/>
       <c r="W157" s="5" t="n">
         <v>150.9</v>
@@ -12125,7 +12485,9 @@
       <c r="T158" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U158" s="5" t="inlineStr"/>
+      <c r="U158" s="5" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V158" t="inlineStr"/>
       <c r="W158" s="5" t="n">
         <v>151.9</v>
@@ -12198,7 +12560,9 @@
       <c r="T159" s="5" t="n">
         <v>14.7</v>
       </c>
-      <c r="U159" s="5" t="inlineStr"/>
+      <c r="U159" s="5" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V159" t="inlineStr"/>
       <c r="W159" s="5" t="n">
         <v>147.6</v>
@@ -12271,7 +12635,9 @@
       <c r="T160" s="5" t="n">
         <v>14.8</v>
       </c>
-      <c r="U160" s="5" t="inlineStr"/>
+      <c r="U160" s="5" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V160" t="inlineStr"/>
       <c r="W160" s="5" t="n">
         <v>149.5</v>
@@ -12344,7 +12710,9 @@
       <c r="T161" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U161" s="5" t="inlineStr"/>
+      <c r="U161" s="5" t="n">
+        <v>9</v>
+      </c>
       <c r="V161" t="inlineStr"/>
       <c r="W161" s="5" t="n">
         <v>152.1</v>
@@ -12417,7 +12785,9 @@
       <c r="T162" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U162" s="5" t="inlineStr"/>
+      <c r="U162" s="5" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V162" t="inlineStr"/>
       <c r="W162" s="5" t="n">
         <v>148.2</v>
@@ -12490,7 +12860,9 @@
       <c r="T163" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U163" s="5" t="inlineStr"/>
+      <c r="U163" s="5" t="n">
+        <v>14.8</v>
+      </c>
       <c r="V163" t="inlineStr"/>
       <c r="W163" s="5" t="n">
         <v>146.4</v>
@@ -12563,7 +12935,9 @@
       <c r="T164" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U164" s="5" t="inlineStr"/>
+      <c r="U164" s="5" t="n">
+        <v>14.4</v>
+      </c>
       <c r="V164" t="inlineStr"/>
       <c r="W164" s="5" t="n">
         <v>148.2</v>
@@ -12636,7 +13010,9 @@
       <c r="T165" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U165" s="5" t="inlineStr"/>
+      <c r="U165" s="5" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V165" t="inlineStr"/>
       <c r="W165" s="5" t="n">
         <v>147</v>
@@ -12709,7 +13085,9 @@
       <c r="T166" s="5" t="n">
         <v>16.1</v>
       </c>
-      <c r="U166" s="5" t="inlineStr"/>
+      <c r="U166" s="5" t="n">
+        <v>9.1</v>
+      </c>
       <c r="V166" t="inlineStr"/>
       <c r="W166" s="5" t="n">
         <v>145.5</v>
@@ -12782,7 +13160,9 @@
       <c r="T167" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U167" s="5" t="inlineStr"/>
+      <c r="U167" s="5" t="n">
+        <v>9.699999999999999</v>
+      </c>
       <c r="V167" t="inlineStr"/>
       <c r="W167" s="5" t="n">
         <v>146.5</v>
@@ -12855,7 +13235,9 @@
       <c r="T168" s="5" t="n">
         <v>16.2</v>
       </c>
-      <c r="U168" s="5" t="inlineStr"/>
+      <c r="U168" s="5" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V168" t="inlineStr"/>
       <c r="W168" s="5" t="n">
         <v>145.9</v>
@@ -12928,7 +13310,9 @@
       <c r="T169" s="5" t="n">
         <v>16.7</v>
       </c>
-      <c r="U169" s="5" t="inlineStr"/>
+      <c r="U169" s="5" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V169" t="inlineStr"/>
       <c r="W169" s="5" t="n">
         <v>145.9</v>
@@ -13001,7 +13385,9 @@
       <c r="T170" s="5" t="n">
         <v>15.3</v>
       </c>
-      <c r="U170" s="5" t="inlineStr"/>
+      <c r="U170" s="5" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V170" t="inlineStr"/>
       <c r="W170" s="5" t="n">
         <v>141.5</v>
@@ -13074,7 +13460,9 @@
       <c r="T171" s="5" t="n">
         <v>16.1</v>
       </c>
-      <c r="U171" s="5" t="inlineStr"/>
+      <c r="U171" s="5" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V171" t="inlineStr"/>
       <c r="W171" s="5" t="n">
         <v>143</v>
@@ -13147,7 +13535,9 @@
       <c r="T172" s="5" t="n">
         <v>16.3</v>
       </c>
-      <c r="U172" s="5" t="inlineStr"/>
+      <c r="U172" s="5" t="n">
+        <v>12</v>
+      </c>
       <c r="V172" t="inlineStr"/>
       <c r="W172" s="5" t="n">
         <v>143.4</v>
@@ -13220,7 +13610,9 @@
       <c r="T173" s="5" t="n">
         <v>16.3</v>
       </c>
-      <c r="U173" s="5" t="inlineStr"/>
+      <c r="U173" s="5" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V173" t="inlineStr"/>
       <c r="W173" s="5" t="n">
         <v>143.7</v>
@@ -13293,7 +13685,9 @@
       <c r="T174" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U174" s="5" t="inlineStr"/>
+      <c r="U174" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V174" t="inlineStr"/>
       <c r="W174" s="5" t="n">
         <v>145.9</v>
@@ -13366,7 +13760,9 @@
       <c r="T175" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U175" s="5" t="inlineStr"/>
+      <c r="U175" s="5" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V175" t="inlineStr"/>
       <c r="W175" s="5" t="n">
         <v>144.6</v>
@@ -13439,7 +13835,9 @@
       <c r="T176" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U176" s="5" t="inlineStr"/>
+      <c r="U176" s="5" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V176" t="inlineStr"/>
       <c r="W176" s="5" t="n">
         <v>142.5</v>
@@ -13512,7 +13910,9 @@
       <c r="T177" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U177" s="5" t="inlineStr"/>
+      <c r="U177" s="5" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V177" t="inlineStr"/>
       <c r="W177" s="5" t="n">
         <v>145.2</v>
@@ -13585,7 +13985,9 @@
       <c r="T178" s="5" t="n">
         <v>16.3</v>
       </c>
-      <c r="U178" s="5" t="inlineStr"/>
+      <c r="U178" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="V178" t="inlineStr"/>
       <c r="W178" s="5" t="n">
         <v>145.8</v>
@@ -13658,7 +14060,9 @@
       <c r="T179" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U179" s="5" t="inlineStr"/>
+      <c r="U179" s="5" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V179" t="inlineStr"/>
       <c r="W179" s="5" t="n">
         <v>145.3</v>
@@ -13735,7 +14139,9 @@
       <c r="T180" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="U180" s="3" t="inlineStr"/>
+      <c r="U180" s="7" t="n">
+        <v>25.7</v>
+      </c>
       <c r="V180" s="1" t="inlineStr"/>
       <c r="W180" s="3" t="n">
         <v>138.9</v>
@@ -13808,7 +14214,9 @@
       <c r="T181" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="U181" s="5" t="inlineStr"/>
+      <c r="U181" s="5" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V181" t="inlineStr"/>
       <c r="W181" s="5" t="n">
         <v>142.8</v>
@@ -13885,7 +14293,9 @@
       <c r="T182" s="5" t="n">
         <v>20.8</v>
       </c>
-      <c r="U182" s="5" t="inlineStr"/>
+      <c r="U182" s="5" t="n">
+        <v>17.7</v>
+      </c>
       <c r="V182" t="inlineStr"/>
       <c r="W182" s="5" t="n">
         <v>146.5</v>
@@ -13958,7 +14368,9 @@
       <c r="T183" s="5" t="n">
         <v>20.6</v>
       </c>
-      <c r="U183" s="5" t="inlineStr"/>
+      <c r="U183" s="5" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V183" t="inlineStr"/>
       <c r="W183" s="5" t="n">
         <v>145</v>
@@ -14035,7 +14447,9 @@
       <c r="T184" s="4" t="n">
         <v>25.3</v>
       </c>
-      <c r="U184" s="5" t="inlineStr"/>
+      <c r="U184" s="5" t="n">
+        <v>23.8</v>
+      </c>
       <c r="V184" t="inlineStr"/>
       <c r="W184" s="5" t="n">
         <v>147.1</v>
@@ -14108,7 +14522,9 @@
       <c r="T185" s="5" t="n">
         <v>20.8</v>
       </c>
-      <c r="U185" s="5" t="inlineStr"/>
+      <c r="U185" s="5" t="n">
+        <v>17.9</v>
+      </c>
       <c r="V185" t="inlineStr"/>
       <c r="W185" s="5" t="n">
         <v>147.6</v>
@@ -14181,7 +14597,9 @@
       <c r="T186" s="5" t="n">
         <v>18.2</v>
       </c>
-      <c r="U186" s="5" t="inlineStr"/>
+      <c r="U186" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V186" t="inlineStr"/>
       <c r="W186" s="5" t="n">
         <v>151.3</v>
@@ -14254,7 +14672,9 @@
       <c r="T187" s="5" t="n">
         <v>17.9</v>
       </c>
-      <c r="U187" s="5" t="inlineStr"/>
+      <c r="U187" s="5" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V187" t="inlineStr"/>
       <c r="W187" s="5" t="n">
         <v>149.9</v>
@@ -14327,7 +14747,9 @@
       <c r="T188" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U188" s="5" t="inlineStr"/>
+      <c r="U188" s="5" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V188" t="inlineStr"/>
       <c r="W188" s="5" t="n">
         <v>152.9</v>
@@ -14400,7 +14822,9 @@
       <c r="T189" s="5" t="n">
         <v>17.3</v>
       </c>
-      <c r="U189" s="5" t="inlineStr"/>
+      <c r="U189" s="5" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V189" t="inlineStr"/>
       <c r="W189" s="5" t="n">
         <v>154.3</v>
@@ -14473,7 +14897,9 @@
       <c r="T190" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U190" s="5" t="inlineStr"/>
+      <c r="U190" s="5" t="n">
+        <v>14.5</v>
+      </c>
       <c r="V190" t="inlineStr"/>
       <c r="W190" s="5" t="n">
         <v>153.5</v>
@@ -14546,7 +14972,9 @@
       <c r="T191" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U191" s="5" t="inlineStr"/>
+      <c r="U191" s="5" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V191" t="inlineStr"/>
       <c r="W191" s="5" t="n">
         <v>148.5</v>
@@ -14619,7 +15047,9 @@
       <c r="T192" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U192" s="5" t="inlineStr"/>
+      <c r="U192" s="5" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V192" t="inlineStr"/>
       <c r="W192" s="5" t="n">
         <v>140.4</v>
@@ -14692,7 +15122,9 @@
       <c r="T193" s="5" t="n">
         <v>16.9</v>
       </c>
-      <c r="U193" s="5" t="inlineStr"/>
+      <c r="U193" s="5" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V193" t="inlineStr"/>
       <c r="W193" s="5" t="n">
         <v>139.4</v>
@@ -14765,7 +15197,9 @@
       <c r="T194" s="5" t="n">
         <v>16.9</v>
       </c>
-      <c r="U194" s="5" t="inlineStr"/>
+      <c r="U194" s="5" t="n">
+        <v>14.2</v>
+      </c>
       <c r="V194" t="inlineStr"/>
       <c r="W194" s="5" t="n">
         <v>141.1</v>
@@ -14838,7 +15272,9 @@
       <c r="T195" s="5" t="n">
         <v>17.4</v>
       </c>
-      <c r="U195" s="5" t="inlineStr"/>
+      <c r="U195" s="5" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V195" t="inlineStr"/>
       <c r="W195" s="5" t="n">
         <v>142.8</v>
@@ -14911,7 +15347,9 @@
       <c r="T196" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U196" s="5" t="inlineStr"/>
+      <c r="U196" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="V196" t="inlineStr"/>
       <c r="W196" s="5" t="n">
         <v>142</v>
@@ -14984,7 +15422,9 @@
       <c r="T197" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="U197" s="5" t="inlineStr"/>
+      <c r="U197" s="5" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V197" t="inlineStr"/>
       <c r="W197" s="5" t="n">
         <v>144</v>
@@ -15057,7 +15497,9 @@
       <c r="T198" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="U198" s="5" t="inlineStr"/>
+      <c r="U198" s="5" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V198" t="inlineStr"/>
       <c r="W198" s="5" t="n">
         <v>143.6</v>
@@ -15134,7 +15576,9 @@
       <c r="T199" s="5" t="n">
         <v>19.5</v>
       </c>
-      <c r="U199" s="5" t="inlineStr"/>
+      <c r="U199" s="5" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V199" t="inlineStr"/>
       <c r="W199" s="5" t="n">
         <v>143.5</v>
@@ -15207,7 +15651,9 @@
       <c r="T200" s="5" t="n">
         <v>19.1</v>
       </c>
-      <c r="U200" s="5" t="inlineStr"/>
+      <c r="U200" s="5" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V200" t="inlineStr"/>
       <c r="W200" s="5" t="n">
         <v>141.3</v>
@@ -15280,7 +15726,9 @@
       <c r="T201" s="5" t="n">
         <v>17.6</v>
       </c>
-      <c r="U201" s="5" t="inlineStr"/>
+      <c r="U201" s="5" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V201" t="inlineStr"/>
       <c r="W201" s="5" t="n">
         <v>142.9</v>
@@ -15353,7 +15801,9 @@
       <c r="T202" s="5" t="n">
         <v>17.3</v>
       </c>
-      <c r="U202" s="5" t="inlineStr"/>
+      <c r="U202" s="5" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V202" t="inlineStr"/>
       <c r="W202" s="5" t="n">
         <v>143.4</v>
@@ -15426,7 +15876,9 @@
       <c r="T203" s="5" t="n">
         <v>17.5</v>
       </c>
-      <c r="U203" s="5" t="inlineStr"/>
+      <c r="U203" s="5" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V203" t="inlineStr"/>
       <c r="W203" s="5" t="n">
         <v>138.6</v>
@@ -15503,7 +15955,9 @@
       <c r="T204" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="U204" s="5" t="inlineStr"/>
+      <c r="U204" s="5" t="n">
+        <v>17</v>
+      </c>
       <c r="V204" t="inlineStr"/>
       <c r="W204" s="5" t="n">
         <v>142.5</v>
@@ -15576,7 +16030,9 @@
       <c r="T205" s="5" t="n">
         <v>19.8</v>
       </c>
-      <c r="U205" s="5" t="inlineStr"/>
+      <c r="U205" s="5" t="n">
+        <v>18.5</v>
+      </c>
       <c r="V205" t="inlineStr"/>
       <c r="W205" s="5" t="n">
         <v>137.9</v>
@@ -15653,7 +16109,9 @@
       <c r="T206" s="5" t="n">
         <v>22.4</v>
       </c>
-      <c r="U206" s="5" t="inlineStr"/>
+      <c r="U206" s="5" t="n">
+        <v>19.4</v>
+      </c>
       <c r="V206" t="inlineStr"/>
       <c r="W206" s="5" t="n">
         <v>140.9</v>
@@ -15726,7 +16184,9 @@
       <c r="T207" s="5" t="n">
         <v>24.7</v>
       </c>
-      <c r="U207" s="5" t="inlineStr"/>
+      <c r="U207" s="5" t="n">
+        <v>20.9</v>
+      </c>
       <c r="V207" t="inlineStr"/>
       <c r="W207" s="5" t="n">
         <v>143</v>
@@ -15799,7 +16259,9 @@
       <c r="T208" s="5" t="n">
         <v>23.7</v>
       </c>
-      <c r="U208" s="5" t="inlineStr"/>
+      <c r="U208" s="4" t="n">
+        <v>26.9</v>
+      </c>
       <c r="V208" t="inlineStr"/>
       <c r="W208" s="5" t="n">
         <v>143.1</v>
@@ -15872,8 +16334,14 @@
       <c r="T209" s="4" t="n">
         <v>26.4</v>
       </c>
-      <c r="U209" s="5" t="inlineStr"/>
-      <c r="V209" t="inlineStr"/>
+      <c r="U209" s="4" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="V209" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W209" s="5" t="n">
         <v>145</v>
       </c>
@@ -15945,7 +16413,9 @@
       <c r="T210" s="5" t="n">
         <v>23.4</v>
       </c>
-      <c r="U210" s="5" t="inlineStr"/>
+      <c r="U210" s="5" t="n">
+        <v>23.3</v>
+      </c>
       <c r="V210" t="inlineStr"/>
       <c r="W210" s="5" t="n">
         <v>148.3</v>
@@ -16018,7 +16488,9 @@
       <c r="T211" s="5" t="n">
         <v>20.5</v>
       </c>
-      <c r="U211" s="5" t="inlineStr"/>
+      <c r="U211" s="5" t="n">
+        <v>14.3</v>
+      </c>
       <c r="V211" t="inlineStr"/>
       <c r="W211" s="5" t="n">
         <v>148.6</v>
@@ -16091,7 +16563,9 @@
       <c r="T212" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U212" s="5" t="inlineStr"/>
+      <c r="U212" s="5" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V212" t="inlineStr"/>
       <c r="W212" s="5" t="n">
         <v>151.7</v>
@@ -16164,7 +16638,9 @@
       <c r="T213" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U213" s="5" t="inlineStr"/>
+      <c r="U213" s="5" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V213" t="inlineStr"/>
       <c r="W213" s="5" t="n">
         <v>145</v>
@@ -16237,7 +16713,9 @@
       <c r="T214" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U214" s="5" t="inlineStr"/>
+      <c r="U214" s="5" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V214" t="inlineStr"/>
       <c r="W214" s="5" t="n">
         <v>143</v>
@@ -16310,7 +16788,9 @@
       <c r="T215" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U215" s="5" t="inlineStr"/>
+      <c r="U215" s="5" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V215" t="inlineStr"/>
       <c r="W215" s="5" t="n">
         <v>144.9</v>
@@ -16383,7 +16863,9 @@
       <c r="T216" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U216" s="5" t="inlineStr"/>
+      <c r="U216" s="5" t="n">
+        <v>10.5</v>
+      </c>
       <c r="V216" t="inlineStr"/>
       <c r="W216" s="5" t="n">
         <v>144.9</v>
@@ -16456,7 +16938,9 @@
       <c r="T217" s="5" t="n">
         <v>16.1</v>
       </c>
-      <c r="U217" s="5" t="inlineStr"/>
+      <c r="U217" s="5" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="V217" t="inlineStr"/>
       <c r="W217" s="5" t="n">
         <v>149.2</v>
@@ -16529,7 +17013,9 @@
       <c r="T218" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U218" s="5" t="inlineStr"/>
+      <c r="U218" s="5" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V218" t="inlineStr"/>
       <c r="W218" s="5" t="n">
         <v>148.9</v>
@@ -16602,7 +17088,9 @@
       <c r="T219" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U219" s="5" t="inlineStr"/>
+      <c r="U219" s="5" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V219" t="inlineStr"/>
       <c r="W219" s="5" t="n">
         <v>148.8</v>
@@ -16675,7 +17163,9 @@
       <c r="T220" s="5" t="n">
         <v>16.7</v>
       </c>
-      <c r="U220" s="5" t="inlineStr"/>
+      <c r="U220" s="5" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V220" t="inlineStr"/>
       <c r="W220" s="5" t="n">
         <v>150.6</v>
@@ -16748,7 +17238,9 @@
       <c r="T221" s="5" t="n">
         <v>16.9</v>
       </c>
-      <c r="U221" s="5" t="inlineStr"/>
+      <c r="U221" s="5" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V221" t="inlineStr"/>
       <c r="W221" s="5" t="n">
         <v>150.3</v>
@@ -16821,7 +17313,9 @@
       <c r="T222" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U222" s="5" t="inlineStr"/>
+      <c r="U222" s="5" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V222" t="inlineStr"/>
       <c r="W222" s="5" t="n">
         <v>147.6</v>
@@ -16894,7 +17388,9 @@
       <c r="T223" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U223" s="5" t="inlineStr"/>
+      <c r="U223" s="5" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V223" t="inlineStr"/>
       <c r="W223" s="5" t="n">
         <v>148.3</v>
@@ -16971,7 +17467,9 @@
       <c r="T224" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U224" s="5" t="inlineStr"/>
+      <c r="U224" s="5" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V224" t="inlineStr"/>
       <c r="W224" s="5" t="n">
         <v>153.6</v>
@@ -17044,7 +17542,9 @@
       <c r="T225" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U225" s="5" t="inlineStr"/>
+      <c r="U225" s="5" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V225" t="inlineStr"/>
       <c r="W225" s="6" t="n">
         <v>161.9</v>
@@ -17117,7 +17617,9 @@
       <c r="T226" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U226" s="5" t="inlineStr"/>
+      <c r="U226" s="5" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V226" t="inlineStr"/>
       <c r="W226" s="6" t="n">
         <v>157</v>
@@ -17190,7 +17692,9 @@
       <c r="T227" s="5" t="n">
         <v>17.6</v>
       </c>
-      <c r="U227" s="5" t="inlineStr"/>
+      <c r="U227" s="5" t="n">
+        <v>16.9</v>
+      </c>
       <c r="V227" t="inlineStr"/>
       <c r="W227" s="5" t="n">
         <v>153.5</v>
@@ -17263,7 +17767,9 @@
       <c r="T228" s="5" t="n">
         <v>16.9</v>
       </c>
-      <c r="U228" s="5" t="inlineStr"/>
+      <c r="U228" s="5" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V228" t="inlineStr"/>
       <c r="W228" s="6" t="n">
         <v>155.4</v>
@@ -17336,7 +17842,9 @@
       <c r="T229" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U229" s="5" t="inlineStr"/>
+      <c r="U229" s="5" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V229" t="inlineStr"/>
       <c r="W229" s="6" t="n">
         <v>155.9</v>
@@ -17409,7 +17917,9 @@
       <c r="T230" s="5" t="n">
         <v>14.1</v>
       </c>
-      <c r="U230" s="5" t="inlineStr"/>
+      <c r="U230" s="5" t="n">
+        <v>7.7</v>
+      </c>
       <c r="V230" t="inlineStr"/>
       <c r="W230" s="6" t="n">
         <v>159.9</v>
@@ -17482,7 +17992,9 @@
       <c r="T231" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="U231" s="5" t="inlineStr"/>
+      <c r="U231" s="5" t="n">
+        <v>7.6</v>
+      </c>
       <c r="V231" t="inlineStr"/>
       <c r="W231" s="6" t="n">
         <v>160.5</v>
@@ -17555,7 +18067,9 @@
       <c r="T232" s="5" t="n">
         <v>13.5</v>
       </c>
-      <c r="U232" s="5" t="inlineStr"/>
+      <c r="U232" s="5" t="n">
+        <v>7.4</v>
+      </c>
       <c r="V232" t="inlineStr"/>
       <c r="W232" s="6" t="n">
         <v>160.5</v>
@@ -17628,7 +18142,9 @@
       <c r="T233" s="5" t="n">
         <v>13.6</v>
       </c>
-      <c r="U233" s="5" t="inlineStr"/>
+      <c r="U233" s="5" t="n">
+        <v>7.7</v>
+      </c>
       <c r="V233" t="inlineStr"/>
       <c r="W233" s="5" t="n">
         <v>151.4</v>
@@ -17701,7 +18217,9 @@
       <c r="T234" s="5" t="n">
         <v>14.2</v>
       </c>
-      <c r="U234" s="5" t="inlineStr"/>
+      <c r="U234" s="5" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="V234" t="inlineStr"/>
       <c r="W234" s="5" t="n">
         <v>150.5</v>
@@ -17778,7 +18296,9 @@
       <c r="T235" s="5" t="n">
         <v>14.3</v>
       </c>
-      <c r="U235" s="5" t="inlineStr"/>
+      <c r="U235" s="5" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V235" t="inlineStr"/>
       <c r="W235" s="5" t="n">
         <v>148.3</v>
@@ -17855,7 +18375,9 @@
       <c r="T236" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U236" s="5" t="inlineStr"/>
+      <c r="U236" s="5" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V236" t="inlineStr"/>
       <c r="W236" s="5" t="n">
         <v>148.7</v>
@@ -17928,7 +18450,9 @@
       <c r="T237" s="5" t="n">
         <v>14.5</v>
       </c>
-      <c r="U237" s="5" t="inlineStr"/>
+      <c r="U237" s="5" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V237" t="inlineStr"/>
       <c r="W237" s="5" t="n">
         <v>141.9</v>
@@ -18001,7 +18525,9 @@
       <c r="T238" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U238" s="5" t="inlineStr"/>
+      <c r="U238" s="5" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V238" t="inlineStr"/>
       <c r="W238" s="5" t="n">
         <v>142.4</v>
@@ -18074,7 +18600,9 @@
       <c r="T239" s="5" t="n">
         <v>14.8</v>
       </c>
-      <c r="U239" s="5" t="inlineStr"/>
+      <c r="U239" s="5" t="n">
+        <v>8</v>
+      </c>
       <c r="V239" t="inlineStr"/>
       <c r="W239" s="5" t="n">
         <v>146.2</v>
@@ -18147,7 +18675,9 @@
       <c r="T240" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U240" s="5" t="inlineStr"/>
+      <c r="U240" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="V240" t="inlineStr"/>
       <c r="W240" s="5" t="n">
         <v>143.6</v>
@@ -18220,7 +18750,9 @@
       <c r="T241" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U241" s="5" t="inlineStr"/>
+      <c r="U241" s="5" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V241" t="inlineStr"/>
       <c r="W241" s="5" t="n">
         <v>147.1</v>
@@ -18293,7 +18825,9 @@
       <c r="T242" s="5" t="n">
         <v>14.5</v>
       </c>
-      <c r="U242" s="5" t="inlineStr"/>
+      <c r="U242" s="5" t="n">
+        <v>8.5</v>
+      </c>
       <c r="V242" t="inlineStr"/>
       <c r="W242" s="5" t="n">
         <v>146</v>
@@ -18366,7 +18900,9 @@
       <c r="T243" s="5" t="n">
         <v>15.1</v>
       </c>
-      <c r="U243" s="5" t="inlineStr"/>
+      <c r="U243" s="5" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V243" t="inlineStr"/>
       <c r="W243" s="5" t="n">
         <v>149.8</v>
@@ -18439,7 +18975,9 @@
       <c r="T244" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="U244" s="5" t="inlineStr"/>
+      <c r="U244" s="5" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V244" t="inlineStr"/>
       <c r="W244" s="5" t="n">
         <v>151.6</v>
@@ -18512,7 +19050,9 @@
       <c r="T245" s="5" t="n">
         <v>16.8</v>
       </c>
-      <c r="U245" s="5" t="inlineStr"/>
+      <c r="U245" s="5" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V245" t="inlineStr"/>
       <c r="W245" s="5" t="n">
         <v>152.5</v>
@@ -18585,7 +19125,9 @@
       <c r="T246" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U246" s="5" t="inlineStr"/>
+      <c r="U246" s="5" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V246" t="inlineStr"/>
       <c r="W246" s="5" t="n">
         <v>151.6</v>
@@ -18662,7 +19204,9 @@
       <c r="T247" s="5" t="n">
         <v>15.9</v>
       </c>
-      <c r="U247" s="5" t="inlineStr"/>
+      <c r="U247" s="5" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V247" t="inlineStr"/>
       <c r="W247" s="5" t="n">
         <v>153.6</v>
@@ -18739,7 +19283,9 @@
       <c r="T248" s="5" t="n">
         <v>20.1</v>
       </c>
-      <c r="U248" s="5" t="inlineStr"/>
+      <c r="U248" s="5" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V248" t="inlineStr"/>
       <c r="W248" s="6" t="n">
         <v>155</v>
@@ -18812,7 +19358,9 @@
       <c r="T249" s="5" t="n">
         <v>16.9</v>
       </c>
-      <c r="U249" s="5" t="inlineStr"/>
+      <c r="U249" s="5" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V249" t="inlineStr"/>
       <c r="W249" s="5" t="n">
         <v>144.4</v>
@@ -18885,7 +19433,9 @@
       <c r="T250" s="5" t="n">
         <v>15.6</v>
       </c>
-      <c r="U250" s="5" t="inlineStr"/>
+      <c r="U250" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V250" t="inlineStr"/>
       <c r="W250" s="5" t="n">
         <v>141.3</v>
@@ -18958,7 +19508,9 @@
       <c r="T251" s="5" t="n">
         <v>16.1</v>
       </c>
-      <c r="U251" s="5" t="inlineStr"/>
+      <c r="U251" s="5" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V251" t="inlineStr"/>
       <c r="W251" s="5" t="n">
         <v>144</v>
@@ -19031,7 +19583,9 @@
       <c r="T252" s="5" t="n">
         <v>16.1</v>
       </c>
-      <c r="U252" s="5" t="inlineStr"/>
+      <c r="U252" s="5" t="n">
+        <v>9</v>
+      </c>
       <c r="V252" t="inlineStr"/>
       <c r="W252" s="5" t="n">
         <v>148.1</v>
@@ -19104,7 +19658,9 @@
       <c r="T253" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U253" s="5" t="inlineStr"/>
+      <c r="U253" s="5" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V253" t="inlineStr"/>
       <c r="W253" s="5" t="n">
         <v>147.2</v>
@@ -19177,7 +19733,9 @@
       <c r="T254" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U254" s="5" t="inlineStr"/>
+      <c r="U254" s="5" t="n">
+        <v>13.2</v>
+      </c>
       <c r="V254" t="inlineStr"/>
       <c r="W254" s="5" t="n">
         <v>145</v>
@@ -19250,7 +19808,9 @@
       <c r="T255" s="5" t="n">
         <v>16.9</v>
       </c>
-      <c r="U255" s="5" t="inlineStr"/>
+      <c r="U255" s="5" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V255" t="inlineStr"/>
       <c r="W255" s="5" t="n">
         <v>143.7</v>
@@ -19327,7 +19887,9 @@
       <c r="T256" s="5" t="n">
         <v>17.4</v>
       </c>
-      <c r="U256" s="5" t="inlineStr"/>
+      <c r="U256" s="5" t="n">
+        <v>16.4</v>
+      </c>
       <c r="V256" t="inlineStr"/>
       <c r="W256" s="5" t="n">
         <v>143.6</v>
@@ -19400,7 +19962,9 @@
       <c r="T257" s="5" t="n">
         <v>16.3</v>
       </c>
-      <c r="U257" s="5" t="inlineStr"/>
+      <c r="U257" s="5" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V257" t="inlineStr"/>
       <c r="W257" s="5" t="n">
         <v>146.6</v>
@@ -19477,7 +20041,9 @@
       <c r="T258" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="U258" s="5" t="inlineStr"/>
+      <c r="U258" s="5" t="n">
+        <v>14.5</v>
+      </c>
       <c r="V258" t="inlineStr"/>
       <c r="W258" s="5" t="n">
         <v>143.9</v>
@@ -19554,7 +20120,9 @@
       <c r="T259" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U259" s="5" t="inlineStr"/>
+      <c r="U259" s="5" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V259" t="inlineStr"/>
       <c r="W259" s="5" t="n">
         <v>143.2</v>
@@ -19627,7 +20195,9 @@
       <c r="T260" s="5" t="n">
         <v>21.8</v>
       </c>
-      <c r="U260" s="5" t="inlineStr"/>
+      <c r="U260" s="5" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V260" t="inlineStr"/>
       <c r="W260" s="5" t="n">
         <v>137.2</v>
@@ -19700,7 +20270,9 @@
       <c r="T261" s="5" t="n">
         <v>20.4</v>
       </c>
-      <c r="U261" s="5" t="inlineStr"/>
+      <c r="U261" s="5" t="n">
+        <v>15</v>
+      </c>
       <c r="V261" t="inlineStr"/>
       <c r="W261" s="5" t="n">
         <v>140.3</v>
@@ -19773,7 +20345,9 @@
       <c r="T262" s="5" t="n">
         <v>17.4</v>
       </c>
-      <c r="U262" s="5" t="inlineStr"/>
+      <c r="U262" s="5" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V262" t="inlineStr"/>
       <c r="W262" s="5" t="n">
         <v>145.2</v>
@@ -19850,7 +20424,9 @@
       <c r="T263" s="5" t="n">
         <v>17.8</v>
       </c>
-      <c r="U263" s="5" t="inlineStr"/>
+      <c r="U263" s="5" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V263" t="inlineStr"/>
       <c r="W263" s="5" t="n">
         <v>145.7</v>
@@ -19923,7 +20499,9 @@
       <c r="T264" s="5" t="n">
         <v>17.6</v>
       </c>
-      <c r="U264" s="5" t="inlineStr"/>
+      <c r="U264" s="5" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V264" t="inlineStr"/>
       <c r="W264" s="5" t="n">
         <v>143.8</v>
@@ -19996,7 +20574,9 @@
       <c r="T265" s="5" t="n">
         <v>20.8</v>
       </c>
-      <c r="U265" s="5" t="inlineStr"/>
+      <c r="U265" s="5" t="n">
+        <v>21.5</v>
+      </c>
       <c r="V265" t="inlineStr"/>
       <c r="W265" s="5" t="n">
         <v>142.5</v>
@@ -20069,7 +20649,9 @@
       <c r="T266" s="5" t="n">
         <v>20.6</v>
       </c>
-      <c r="U266" s="5" t="inlineStr"/>
+      <c r="U266" s="5" t="n">
+        <v>22.4</v>
+      </c>
       <c r="V266" t="inlineStr"/>
       <c r="W266" s="5" t="n">
         <v>139.4</v>
@@ -20142,7 +20724,9 @@
       <c r="T267" s="5" t="n">
         <v>20.3</v>
       </c>
-      <c r="U267" s="5" t="inlineStr"/>
+      <c r="U267" s="5" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V267" t="inlineStr"/>
       <c r="W267" s="5" t="n">
         <v>140.3</v>
@@ -20215,7 +20799,9 @@
       <c r="T268" s="5" t="n">
         <v>19.6</v>
       </c>
-      <c r="U268" s="5" t="inlineStr"/>
+      <c r="U268" s="5" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V268" t="inlineStr"/>
       <c r="W268" s="5" t="n">
         <v>139.2</v>
@@ -20288,7 +20874,9 @@
       <c r="T269" s="5" t="n">
         <v>20.2</v>
       </c>
-      <c r="U269" s="5" t="inlineStr"/>
+      <c r="U269" s="5" t="n">
+        <v>16.6</v>
+      </c>
       <c r="V269" t="inlineStr"/>
       <c r="W269" s="5" t="n">
         <v>141.2</v>
@@ -20361,7 +20949,9 @@
       <c r="T270" s="5" t="n">
         <v>19.1</v>
       </c>
-      <c r="U270" s="5" t="inlineStr"/>
+      <c r="U270" s="5" t="n">
+        <v>17.8</v>
+      </c>
       <c r="V270" t="inlineStr"/>
       <c r="W270" s="5" t="n">
         <v>145.5</v>
@@ -20434,7 +21024,9 @@
       <c r="T271" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="U271" s="5" t="inlineStr"/>
+      <c r="U271" s="5" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V271" t="inlineStr"/>
       <c r="W271" s="5" t="n">
         <v>141.4</v>
@@ -20507,7 +21099,9 @@
       <c r="T272" s="5" t="n">
         <v>19.5</v>
       </c>
-      <c r="U272" s="5" t="inlineStr"/>
+      <c r="U272" s="5" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V272" t="inlineStr"/>
       <c r="W272" s="5" t="n">
         <v>141.9</v>
@@ -20580,7 +21174,9 @@
       <c r="T273" s="5" t="n">
         <v>17.9</v>
       </c>
-      <c r="U273" s="5" t="inlineStr"/>
+      <c r="U273" s="5" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V273" t="inlineStr"/>
       <c r="W273" s="5" t="n">
         <v>146.1</v>
@@ -20657,7 +21253,9 @@
       <c r="T274" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U274" s="5" t="inlineStr"/>
+      <c r="U274" s="5" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V274" t="inlineStr"/>
       <c r="W274" s="5" t="n">
         <v>146.6</v>
@@ -20730,7 +21328,9 @@
       <c r="T275" s="5" t="n">
         <v>19.9</v>
       </c>
-      <c r="U275" s="5" t="inlineStr"/>
+      <c r="U275" s="5" t="n">
+        <v>19</v>
+      </c>
       <c r="V275" t="inlineStr"/>
       <c r="W275" s="5" t="n">
         <v>146.7</v>
@@ -20803,7 +21403,9 @@
       <c r="T276" s="5" t="n">
         <v>21.4</v>
       </c>
-      <c r="U276" s="5" t="inlineStr"/>
+      <c r="U276" s="5" t="n">
+        <v>16.3</v>
+      </c>
       <c r="V276" t="inlineStr"/>
       <c r="W276" s="5" t="n">
         <v>151.8</v>
@@ -20876,7 +21478,9 @@
       <c r="T277" s="5" t="n">
         <v>23.6</v>
       </c>
-      <c r="U277" s="5" t="inlineStr"/>
+      <c r="U277" s="5" t="n">
+        <v>20.3</v>
+      </c>
       <c r="V277" t="inlineStr"/>
       <c r="W277" s="5" t="n">
         <v>152.8</v>
@@ -20949,7 +21553,9 @@
       <c r="T278" s="5" t="n">
         <v>21.1</v>
       </c>
-      <c r="U278" s="5" t="inlineStr"/>
+      <c r="U278" s="5" t="n">
+        <v>17.8</v>
+      </c>
       <c r="V278" t="inlineStr"/>
       <c r="W278" s="5" t="n">
         <v>152.9</v>
@@ -21022,7 +21628,9 @@
       <c r="T279" s="5" t="n">
         <v>23.8</v>
       </c>
-      <c r="U279" s="5" t="inlineStr"/>
+      <c r="U279" s="5" t="n">
+        <v>21.9</v>
+      </c>
       <c r="V279" t="inlineStr"/>
       <c r="W279" s="5" t="n">
         <v>153.9</v>
@@ -21099,8 +21707,14 @@
       <c r="T280" s="4" t="n">
         <v>29.5</v>
       </c>
-      <c r="U280" s="5" t="inlineStr"/>
-      <c r="V280" t="inlineStr"/>
+      <c r="U280" s="4" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="V280" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W280" s="5" t="n">
         <v>151.8</v>
       </c>
@@ -21172,7 +21786,9 @@
       <c r="T281" s="4" t="n">
         <v>25.5</v>
       </c>
-      <c r="U281" s="5" t="inlineStr"/>
+      <c r="U281" s="5" t="n">
+        <v>22.7</v>
+      </c>
       <c r="V281" t="inlineStr"/>
       <c r="W281" s="6" t="n">
         <v>158</v>
@@ -21245,7 +21861,9 @@
       <c r="T282" s="5" t="n">
         <v>24.9</v>
       </c>
-      <c r="U282" s="5" t="inlineStr"/>
+      <c r="U282" s="5" t="n">
+        <v>21.3</v>
+      </c>
       <c r="V282" t="inlineStr"/>
       <c r="W282" s="5" t="n">
         <v>154.5</v>
@@ -21318,7 +21936,9 @@
       <c r="T283" s="5" t="n">
         <v>24.2</v>
       </c>
-      <c r="U283" s="5" t="inlineStr"/>
+      <c r="U283" s="5" t="n">
+        <v>19</v>
+      </c>
       <c r="V283" t="inlineStr"/>
       <c r="W283" s="5" t="n">
         <v>152.4</v>
@@ -21389,7 +22009,9 @@
       <c r="T284" s="4" t="n">
         <v>27.3</v>
       </c>
-      <c r="U284" s="5" t="inlineStr"/>
+      <c r="U284" s="5" t="n">
+        <v>24.2</v>
+      </c>
       <c r="V284" t="inlineStr"/>
       <c r="W284" s="5" t="n">
         <v>139.9</v>
@@ -21462,8 +22084,14 @@
       <c r="T285" s="4" t="n">
         <v>27.2</v>
       </c>
-      <c r="U285" s="5" t="inlineStr"/>
-      <c r="V285" t="inlineStr"/>
+      <c r="U285" s="4" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="V285" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W285" s="5" t="n">
         <v>137.8</v>
       </c>
@@ -21535,7 +22163,9 @@
       <c r="T286" s="5" t="n">
         <v>23.5</v>
       </c>
-      <c r="U286" s="5" t="inlineStr"/>
+      <c r="U286" s="5" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V286" t="inlineStr"/>
       <c r="W286" s="5" t="n">
         <v>141.5</v>
@@ -21608,7 +22238,9 @@
       <c r="T287" s="5" t="n">
         <v>22.4</v>
       </c>
-      <c r="U287" s="5" t="inlineStr"/>
+      <c r="U287" s="5" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V287" t="inlineStr"/>
       <c r="W287" s="5" t="n">
         <v>145</v>
@@ -21681,7 +22313,9 @@
       <c r="T288" s="4" t="n">
         <v>25.1</v>
       </c>
-      <c r="U288" s="5" t="inlineStr"/>
+      <c r="U288" s="5" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V288" t="inlineStr"/>
       <c r="W288" s="5" t="n">
         <v>136.5</v>
@@ -21754,7 +22388,9 @@
       <c r="T289" s="5" t="n">
         <v>24.1</v>
       </c>
-      <c r="U289" s="5" t="inlineStr"/>
+      <c r="U289" s="5" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V289" t="inlineStr"/>
       <c r="W289" s="5" t="n">
         <v>138.3</v>
@@ -21827,8 +22463,14 @@
       <c r="T290" s="4" t="n">
         <v>26.8</v>
       </c>
-      <c r="U290" s="5" t="inlineStr"/>
-      <c r="V290" t="inlineStr"/>
+      <c r="U290" s="4" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="V290" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W290" s="5" t="n">
         <v>139.1</v>
       </c>
@@ -21900,7 +22542,9 @@
       <c r="T291" s="4" t="n">
         <v>26.1</v>
       </c>
-      <c r="U291" s="5" t="inlineStr"/>
+      <c r="U291" s="5" t="n">
+        <v>23.2</v>
+      </c>
       <c r="V291" t="inlineStr"/>
       <c r="W291" s="5" t="n">
         <v>142</v>
@@ -21973,7 +22617,9 @@
       <c r="T292" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="U292" s="5" t="inlineStr"/>
+      <c r="U292" s="5" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V292" t="inlineStr"/>
       <c r="W292" s="5" t="n">
         <v>142.6</v>
@@ -22046,7 +22692,9 @@
       <c r="T293" s="4" t="n">
         <v>25.3</v>
       </c>
-      <c r="U293" s="5" t="inlineStr"/>
+      <c r="U293" s="5" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V293" t="inlineStr"/>
       <c r="W293" s="5" t="n">
         <v>140.9</v>
@@ -22119,7 +22767,9 @@
       <c r="T294" s="4" t="n">
         <v>27.4</v>
       </c>
-      <c r="U294" s="5" t="inlineStr"/>
+      <c r="U294" s="5" t="n">
+        <v>23.9</v>
+      </c>
       <c r="V294" t="inlineStr"/>
       <c r="W294" s="5" t="n">
         <v>144</v>
@@ -22196,8 +22846,14 @@
       <c r="T295" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="U295" s="5" t="inlineStr"/>
-      <c r="V295" t="inlineStr"/>
+      <c r="U295" s="4" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="V295" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W295" s="5" t="n">
         <v>139</v>
       </c>
@@ -22273,7 +22929,9 @@
       <c r="T296" s="4" t="n">
         <v>30.6</v>
       </c>
-      <c r="U296" s="5" t="inlineStr"/>
+      <c r="U296" s="5" t="n">
+        <v>23</v>
+      </c>
       <c r="V296" t="inlineStr"/>
       <c r="W296" s="5" t="n">
         <v>142.2</v>
@@ -22346,7 +23004,9 @@
       <c r="T297" s="4" t="n">
         <v>25.2</v>
       </c>
-      <c r="U297" s="5" t="inlineStr"/>
+      <c r="U297" s="5" t="n">
+        <v>19</v>
+      </c>
       <c r="V297" t="inlineStr"/>
       <c r="W297" s="5" t="n">
         <v>145.4</v>
@@ -22419,7 +23079,9 @@
       <c r="T298" s="5" t="n">
         <v>24.5</v>
       </c>
-      <c r="U298" s="5" t="inlineStr"/>
+      <c r="U298" s="5" t="n">
+        <v>23</v>
+      </c>
       <c r="V298" t="inlineStr"/>
       <c r="W298" s="5" t="n">
         <v>143.8</v>
@@ -22492,7 +23154,9 @@
       <c r="T299" s="5" t="n">
         <v>23.9</v>
       </c>
-      <c r="U299" s="5" t="inlineStr"/>
+      <c r="U299" s="4" t="n">
+        <v>27.6</v>
+      </c>
       <c r="V299" t="inlineStr"/>
       <c r="W299" s="5" t="n">
         <v>146.9</v>
@@ -22565,7 +23229,9 @@
       <c r="T300" s="5" t="n">
         <v>24.2</v>
       </c>
-      <c r="U300" s="5" t="inlineStr"/>
+      <c r="U300" s="5" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V300" t="inlineStr"/>
       <c r="W300" s="5" t="n">
         <v>147.6</v>
@@ -22638,8 +23304,14 @@
       <c r="T301" s="4" t="n">
         <v>25.8</v>
       </c>
-      <c r="U301" s="5" t="inlineStr"/>
-      <c r="V301" t="inlineStr"/>
+      <c r="U301" s="4" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="V301" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W301" s="5" t="n">
         <v>148.4</v>
       </c>
@@ -22711,7 +23383,9 @@
       <c r="T302" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="U302" s="5" t="inlineStr"/>
+      <c r="U302" s="5" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V302" t="inlineStr"/>
       <c r="W302" s="5" t="n">
         <v>150.4</v>
@@ -22784,7 +23458,9 @@
       <c r="T303" s="5" t="n">
         <v>19.5</v>
       </c>
-      <c r="U303" s="5" t="inlineStr"/>
+      <c r="U303" s="5" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V303" t="inlineStr"/>
       <c r="W303" s="5" t="n">
         <v>143.3</v>
@@ -22857,7 +23533,9 @@
       <c r="T304" s="5" t="n">
         <v>19.2</v>
       </c>
-      <c r="U304" s="5" t="inlineStr"/>
+      <c r="U304" s="5" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V304" t="inlineStr"/>
       <c r="W304" s="5" t="n">
         <v>144.2</v>
@@ -22930,7 +23608,9 @@
       <c r="T305" s="5" t="n">
         <v>19.1</v>
       </c>
-      <c r="U305" s="5" t="inlineStr"/>
+      <c r="U305" s="5" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V305" t="inlineStr"/>
       <c r="W305" s="6" t="n">
         <v>156.9</v>
@@ -23003,7 +23683,9 @@
       <c r="T306" s="5" t="n">
         <v>18.4</v>
       </c>
-      <c r="U306" s="5" t="inlineStr"/>
+      <c r="U306" s="5" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V306" t="inlineStr"/>
       <c r="W306" s="5" t="n">
         <v>149.9</v>
@@ -23076,7 +23758,9 @@
       <c r="T307" s="5" t="n">
         <v>18.2</v>
       </c>
-      <c r="U307" s="5" t="inlineStr"/>
+      <c r="U307" s="5" t="n">
+        <v>12.6</v>
+      </c>
       <c r="V307" t="inlineStr"/>
       <c r="W307" s="5" t="n">
         <v>139.2</v>
@@ -23149,7 +23833,9 @@
       <c r="T308" s="5" t="n">
         <v>17.9</v>
       </c>
-      <c r="U308" s="5" t="inlineStr"/>
+      <c r="U308" s="5" t="n">
+        <v>12</v>
+      </c>
       <c r="V308" t="inlineStr"/>
       <c r="W308" s="5" t="n">
         <v>140.7</v>
@@ -23222,7 +23908,9 @@
       <c r="T309" s="5" t="n">
         <v>17.5</v>
       </c>
-      <c r="U309" s="5" t="inlineStr"/>
+      <c r="U309" s="5" t="n">
+        <v>14.2</v>
+      </c>
       <c r="V309" t="inlineStr"/>
       <c r="W309" s="5" t="n">
         <v>141.8</v>
@@ -23295,7 +23983,9 @@
       <c r="T310" s="5" t="n">
         <v>18.9</v>
       </c>
-      <c r="U310" s="5" t="inlineStr"/>
+      <c r="U310" s="5" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V310" t="inlineStr"/>
       <c r="W310" s="5" t="n">
         <v>141.9</v>
@@ -23368,7 +24058,9 @@
       <c r="T311" s="5" t="n">
         <v>19.5</v>
       </c>
-      <c r="U311" s="5" t="inlineStr"/>
+      <c r="U311" s="5" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V311" t="inlineStr"/>
       <c r="W311" s="5" t="n">
         <v>140.9</v>
@@ -23441,7 +24133,9 @@
       <c r="T312" s="5" t="n">
         <v>18.9</v>
       </c>
-      <c r="U312" s="5" t="inlineStr"/>
+      <c r="U312" s="5" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V312" t="inlineStr"/>
       <c r="W312" s="5" t="n">
         <v>140.8</v>
@@ -23514,7 +24208,9 @@
       <c r="T313" s="5" t="n">
         <v>19.3</v>
       </c>
-      <c r="U313" s="5" t="inlineStr"/>
+      <c r="U313" s="5" t="n">
+        <v>14.8</v>
+      </c>
       <c r="V313" t="inlineStr"/>
       <c r="W313" s="5" t="n">
         <v>139.6</v>
@@ -23587,7 +24283,9 @@
       <c r="T314" s="5" t="n">
         <v>18.7</v>
       </c>
-      <c r="U314" s="5" t="inlineStr"/>
+      <c r="U314" s="5" t="n">
+        <v>16.6</v>
+      </c>
       <c r="V314" t="inlineStr"/>
       <c r="W314" s="5" t="n">
         <v>139.1</v>
@@ -23660,7 +24358,9 @@
       <c r="T315" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="U315" s="5" t="inlineStr"/>
+      <c r="U315" s="5" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V315" t="inlineStr"/>
       <c r="W315" s="5" t="n">
         <v>139.6</v>
@@ -23733,7 +24433,9 @@
       <c r="T316" s="5" t="n">
         <v>17.8</v>
       </c>
-      <c r="U316" s="5" t="inlineStr"/>
+      <c r="U316" s="5" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V316" t="inlineStr"/>
       <c r="W316" s="5" t="n">
         <v>138.2</v>
@@ -23806,7 +24508,9 @@
       <c r="T317" s="5" t="n">
         <v>18.8</v>
       </c>
-      <c r="U317" s="5" t="inlineStr"/>
+      <c r="U317" s="5" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V317" t="inlineStr"/>
       <c r="W317" s="5" t="n">
         <v>141.9</v>
@@ -23879,7 +24583,9 @@
       <c r="T318" s="5" t="n">
         <v>16.9</v>
       </c>
-      <c r="U318" s="5" t="inlineStr"/>
+      <c r="U318" s="5" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V318" t="inlineStr"/>
       <c r="W318" s="5" t="n">
         <v>143.3</v>
@@ -23952,7 +24658,9 @@
       <c r="T319" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="U319" s="5" t="inlineStr"/>
+      <c r="U319" s="5" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V319" t="inlineStr"/>
       <c r="W319" s="5" t="n">
         <v>141.4</v>
@@ -24025,7 +24733,9 @@
       <c r="T320" s="5" t="n">
         <v>18.3</v>
       </c>
-      <c r="U320" s="5" t="inlineStr"/>
+      <c r="U320" s="5" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V320" t="inlineStr"/>
       <c r="W320" s="5" t="n">
         <v>141.7</v>
@@ -24098,7 +24808,9 @@
       <c r="T321" s="5" t="n">
         <v>17.4</v>
       </c>
-      <c r="U321" s="5" t="inlineStr"/>
+      <c r="U321" s="5" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V321" t="inlineStr"/>
       <c r="W321" s="5" t="n">
         <v>138.7</v>
@@ -24171,7 +24883,9 @@
       <c r="T322" s="5" t="n">
         <v>17.4</v>
       </c>
-      <c r="U322" s="5" t="inlineStr"/>
+      <c r="U322" s="5" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V322" t="inlineStr"/>
       <c r="W322" s="5" t="n">
         <v>135.4</v>
@@ -24244,7 +24958,9 @@
       <c r="T323" s="5" t="n">
         <v>17.1</v>
       </c>
-      <c r="U323" s="5" t="inlineStr"/>
+      <c r="U323" s="5" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V323" t="inlineStr"/>
       <c r="W323" s="5" t="n">
         <v>136.1</v>
@@ -24317,7 +25033,9 @@
       <c r="T324" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U324" s="5" t="inlineStr"/>
+      <c r="U324" s="5" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V324" t="inlineStr"/>
       <c r="W324" s="5" t="n">
         <v>138.2</v>
@@ -24390,7 +25108,9 @@
       <c r="T325" s="5" t="n">
         <v>18.4</v>
       </c>
-      <c r="U325" s="5" t="inlineStr"/>
+      <c r="U325" s="5" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V325" t="inlineStr"/>
       <c r="W325" s="5" t="n">
         <v>140.2</v>
@@ -24463,7 +25183,9 @@
       <c r="T326" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="U326" s="5" t="inlineStr"/>
+      <c r="U326" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V326" t="inlineStr"/>
       <c r="W326" s="5" t="n">
         <v>139.4</v>
@@ -24536,7 +25258,9 @@
       <c r="T327" s="5" t="n">
         <v>17.9</v>
       </c>
-      <c r="U327" s="5" t="inlineStr"/>
+      <c r="U327" s="5" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V327" t="inlineStr"/>
       <c r="W327" s="5" t="n">
         <v>141.5</v>
@@ -24609,7 +25333,9 @@
       <c r="T328" s="5" t="n">
         <v>17.3</v>
       </c>
-      <c r="U328" s="5" t="inlineStr"/>
+      <c r="U328" s="5" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V328" t="inlineStr"/>
       <c r="W328" s="5" t="n">
         <v>139.3</v>
@@ -24682,7 +25408,9 @@
       <c r="T329" s="5" t="n">
         <v>18.4</v>
       </c>
-      <c r="U329" s="5" t="inlineStr"/>
+      <c r="U329" s="5" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V329" t="inlineStr"/>
       <c r="W329" s="5" t="n">
         <v>145.8</v>
@@ -24755,7 +25483,9 @@
       <c r="T330" s="5" t="n">
         <v>17.8</v>
       </c>
-      <c r="U330" s="5" t="inlineStr"/>
+      <c r="U330" s="5" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V330" t="inlineStr"/>
       <c r="W330" s="5" t="n">
         <v>138.4</v>
@@ -24828,7 +25558,9 @@
       <c r="T331" s="5" t="n">
         <v>18.1</v>
       </c>
-      <c r="U331" s="5" t="inlineStr"/>
+      <c r="U331" s="5" t="n">
+        <v>13.3</v>
+      </c>
       <c r="V331" t="inlineStr"/>
       <c r="W331" s="5" t="n">
         <v>135.5</v>
@@ -24901,7 +25633,9 @@
       <c r="T332" s="5" t="n">
         <v>17.4</v>
       </c>
-      <c r="U332" s="5" t="inlineStr"/>
+      <c r="U332" s="5" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V332" t="inlineStr"/>
       <c r="W332" s="5" t="n">
         <v>132.3</v>
@@ -24974,7 +25708,9 @@
       <c r="T333" s="5" t="n">
         <v>16.8</v>
       </c>
-      <c r="U333" s="5" t="inlineStr"/>
+      <c r="U333" s="5" t="n">
+        <v>14</v>
+      </c>
       <c r="V333" t="inlineStr"/>
       <c r="W333" s="5" t="n">
         <v>137</v>
@@ -25047,7 +25783,9 @@
       <c r="T334" s="5" t="n">
         <v>16.7</v>
       </c>
-      <c r="U334" s="5" t="inlineStr"/>
+      <c r="U334" s="5" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V334" t="inlineStr"/>
       <c r="W334" s="5" t="n">
         <v>137.4</v>
@@ -25120,7 +25858,9 @@
       <c r="T335" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="U335" s="5" t="inlineStr"/>
+      <c r="U335" s="5" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V335" t="inlineStr"/>
       <c r="W335" s="5" t="n">
         <v>139</v>
@@ -25193,7 +25933,9 @@
       <c r="T336" s="5" t="n">
         <v>16.3</v>
       </c>
-      <c r="U336" s="5" t="inlineStr"/>
+      <c r="U336" s="5" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V336" t="inlineStr"/>
       <c r="W336" s="5" t="n">
         <v>138.6</v>
@@ -25266,7 +26008,9 @@
       <c r="T337" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U337" s="5" t="inlineStr"/>
+      <c r="U337" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V337" t="inlineStr"/>
       <c r="W337" s="5" t="n">
         <v>139.5</v>
@@ -25339,7 +26083,9 @@
       <c r="T338" s="5" t="n">
         <v>15.3</v>
       </c>
-      <c r="U338" s="5" t="inlineStr"/>
+      <c r="U338" s="5" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V338" t="inlineStr"/>
       <c r="W338" s="5" t="n">
         <v>144.2</v>
@@ -25412,7 +26158,9 @@
       <c r="T339" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="U339" s="5" t="inlineStr"/>
+      <c r="U339" s="5" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V339" t="inlineStr"/>
       <c r="W339" s="5" t="n">
         <v>142.5</v>
@@ -25485,7 +26233,9 @@
       <c r="T340" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U340" s="5" t="inlineStr"/>
+      <c r="U340" s="5" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V340" t="inlineStr"/>
       <c r="W340" s="5" t="n">
         <v>143.2</v>
@@ -25558,7 +26308,9 @@
       <c r="T341" s="5" t="n">
         <v>16.1</v>
       </c>
-      <c r="U341" s="5" t="inlineStr"/>
+      <c r="U341" s="5" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V341" t="inlineStr"/>
       <c r="W341" s="5" t="n">
         <v>136.9</v>
@@ -25631,7 +26383,9 @@
       <c r="T342" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U342" s="5" t="inlineStr"/>
+      <c r="U342" s="5" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V342" t="inlineStr"/>
       <c r="W342" s="5" t="n">
         <v>142.1</v>
@@ -25708,7 +26462,9 @@
       <c r="T343" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="U343" s="3" t="inlineStr"/>
+      <c r="U343" s="7" t="n">
+        <v>28.7</v>
+      </c>
       <c r="V343" s="1" t="inlineStr"/>
       <c r="W343" s="3" t="n">
         <v>152.2</v>
@@ -25781,7 +26537,9 @@
       <c r="T344" s="5" t="n">
         <v>18.9</v>
       </c>
-      <c r="U344" s="5" t="inlineStr"/>
+      <c r="U344" s="5" t="n">
+        <v>16</v>
+      </c>
       <c r="V344" t="inlineStr"/>
       <c r="W344" s="5" t="n">
         <v>145</v>
@@ -25854,7 +26612,9 @@
       <c r="T345" s="5" t="n">
         <v>19.9</v>
       </c>
-      <c r="U345" s="5" t="inlineStr"/>
+      <c r="U345" s="5" t="n">
+        <v>20.6</v>
+      </c>
       <c r="V345" t="inlineStr"/>
       <c r="W345" s="5" t="n">
         <v>142</v>
@@ -25927,7 +26687,9 @@
       <c r="T346" s="5" t="n">
         <v>22.2</v>
       </c>
-      <c r="U346" s="5" t="inlineStr"/>
+      <c r="U346" s="5" t="n">
+        <v>23.9</v>
+      </c>
       <c r="V346" t="inlineStr"/>
       <c r="W346" s="5" t="n">
         <v>143.1</v>
@@ -26000,7 +26762,9 @@
       <c r="T347" s="5" t="n">
         <v>19.4</v>
       </c>
-      <c r="U347" s="5" t="inlineStr"/>
+      <c r="U347" s="5" t="n">
+        <v>21.1</v>
+      </c>
       <c r="V347" t="inlineStr"/>
       <c r="W347" s="5" t="n">
         <v>143</v>
@@ -26073,7 +26837,9 @@
       <c r="T348" s="5" t="n">
         <v>17.7</v>
       </c>
-      <c r="U348" s="5" t="inlineStr"/>
+      <c r="U348" s="5" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V348" t="inlineStr"/>
       <c r="W348" s="5" t="n">
         <v>142.6</v>
@@ -26146,7 +26912,9 @@
       <c r="T349" s="5" t="n">
         <v>16.2</v>
       </c>
-      <c r="U349" s="5" t="inlineStr"/>
+      <c r="U349" s="5" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V349" t="inlineStr"/>
       <c r="W349" s="5" t="n">
         <v>144.3</v>
@@ -26219,7 +26987,9 @@
       <c r="T350" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U350" s="5" t="inlineStr"/>
+      <c r="U350" s="5" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V350" t="inlineStr"/>
       <c r="W350" s="5" t="n">
         <v>142.7</v>
@@ -26296,7 +27066,9 @@
       <c r="T351" s="5" t="n">
         <v>18.4</v>
       </c>
-      <c r="U351" s="5" t="inlineStr"/>
+      <c r="U351" s="5" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V351" t="inlineStr"/>
       <c r="W351" s="5" t="n">
         <v>142.6</v>
@@ -26369,7 +27141,9 @@
       <c r="T352" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U352" s="5" t="inlineStr"/>
+      <c r="U352" s="5" t="n">
+        <v>15.7</v>
+      </c>
       <c r="V352" t="inlineStr"/>
       <c r="W352" s="5" t="n">
         <v>146.7</v>
@@ -26442,7 +27216,9 @@
       <c r="T353" s="5" t="n">
         <v>17.3</v>
       </c>
-      <c r="U353" s="5" t="inlineStr"/>
+      <c r="U353" s="5" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V353" t="inlineStr"/>
       <c r="W353" s="5" t="n">
         <v>141.9</v>
@@ -26519,7 +27295,9 @@
       <c r="T354" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="U354" s="3" t="inlineStr"/>
+      <c r="U354" s="3" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V354" s="1" t="inlineStr"/>
       <c r="W354" s="3" t="n">
         <v>143.1</v>
@@ -26592,7 +27370,9 @@
       <c r="T355" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U355" s="5" t="inlineStr"/>
+      <c r="U355" s="5" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V355" t="inlineStr"/>
       <c r="W355" s="5" t="n">
         <v>145.3</v>
@@ -26665,7 +27445,9 @@
       <c r="T356" s="5" t="n">
         <v>18.9</v>
       </c>
-      <c r="U356" s="5" t="inlineStr"/>
+      <c r="U356" s="5" t="n">
+        <v>16</v>
+      </c>
       <c r="V356" t="inlineStr"/>
       <c r="W356" s="5" t="n">
         <v>139.9</v>
@@ -26738,7 +27520,9 @@
       <c r="T357" s="5" t="n">
         <v>18.4</v>
       </c>
-      <c r="U357" s="5" t="inlineStr"/>
+      <c r="U357" s="5" t="n">
+        <v>17.6</v>
+      </c>
       <c r="V357" t="inlineStr"/>
       <c r="W357" s="5" t="n">
         <v>139.4</v>
@@ -26811,7 +27595,9 @@
       <c r="T358" s="5" t="n">
         <v>17.6</v>
       </c>
-      <c r="U358" s="5" t="inlineStr"/>
+      <c r="U358" s="5" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V358" t="inlineStr"/>
       <c r="W358" s="5" t="n">
         <v>144.5</v>
@@ -26884,7 +27670,9 @@
       <c r="T359" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U359" s="5" t="inlineStr"/>
+      <c r="U359" s="5" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V359" t="inlineStr"/>
       <c r="W359" s="5" t="n">
         <v>149.6</v>
@@ -26957,7 +27745,9 @@
       <c r="T360" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U360" s="5" t="inlineStr"/>
+      <c r="U360" s="5" t="n">
+        <v>13</v>
+      </c>
       <c r="V360" t="inlineStr"/>
       <c r="W360" s="5" t="n">
         <v>154.8</v>
@@ -27034,7 +27824,9 @@
       <c r="T361" s="5" t="n">
         <v>16.1</v>
       </c>
-      <c r="U361" s="5" t="inlineStr"/>
+      <c r="U361" s="5" t="n">
+        <v>13.2</v>
+      </c>
       <c r="V361" t="inlineStr"/>
       <c r="W361" s="5" t="n">
         <v>150</v>
@@ -27107,7 +27899,9 @@
       <c r="T362" s="5" t="n">
         <v>15.6</v>
       </c>
-      <c r="U362" s="5" t="inlineStr"/>
+      <c r="U362" s="5" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="V362" t="inlineStr"/>
       <c r="W362" s="5" t="n">
         <v>145.4</v>
@@ -27184,7 +27978,9 @@
       <c r="T363" s="5" t="n">
         <v>16.1</v>
       </c>
-      <c r="U363" s="5" t="inlineStr"/>
+      <c r="U363" s="5" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V363" t="inlineStr"/>
       <c r="W363" s="5" t="n">
         <v>145.7</v>
@@ -27257,7 +28053,9 @@
       <c r="T364" s="5" t="n">
         <v>16.9</v>
       </c>
-      <c r="U364" s="5" t="inlineStr"/>
+      <c r="U364" s="5" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V364" t="inlineStr"/>
       <c r="W364" s="5" t="n">
         <v>149.8</v>
@@ -27330,7 +28128,9 @@
       <c r="T365" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U365" s="5" t="inlineStr"/>
+      <c r="U365" s="5" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V365" t="inlineStr"/>
       <c r="W365" s="5" t="n">
         <v>144.7</v>
@@ -27403,7 +28203,9 @@
       <c r="T366" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="U366" s="5" t="inlineStr"/>
+      <c r="U366" s="5" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V366" t="inlineStr"/>
       <c r="W366" s="5" t="n">
         <v>144.3</v>
@@ -27480,7 +28282,9 @@
       <c r="T367" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U367" s="5" t="inlineStr"/>
+      <c r="U367" s="5" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V367" t="inlineStr"/>
       <c r="W367" s="5" t="n">
         <v>145.7</v>
@@ -27553,7 +28357,9 @@
       <c r="T368" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U368" s="5" t="inlineStr"/>
+      <c r="U368" s="5" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V368" t="inlineStr"/>
       <c r="W368" s="5" t="n">
         <v>145.1</v>
@@ -27626,7 +28432,9 @@
       <c r="T369" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U369" s="5" t="inlineStr"/>
+      <c r="U369" s="5" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V369" t="inlineStr"/>
       <c r="W369" s="5" t="n">
         <v>148.5</v>
@@ -27703,7 +28511,9 @@
       <c r="T370" s="5" t="n">
         <v>16.7</v>
       </c>
-      <c r="U370" s="5" t="inlineStr"/>
+      <c r="U370" s="5" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V370" t="inlineStr"/>
       <c r="W370" s="5" t="n">
         <v>145.7</v>
@@ -27776,7 +28586,9 @@
       <c r="T371" s="5" t="n">
         <v>18.8</v>
       </c>
-      <c r="U371" s="5" t="inlineStr"/>
+      <c r="U371" s="5" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V371" t="inlineStr"/>
       <c r="W371" s="5" t="n">
         <v>147.3</v>
@@ -27849,7 +28661,9 @@
       <c r="T372" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U372" s="5" t="inlineStr"/>
+      <c r="U372" s="5" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V372" t="inlineStr"/>
       <c r="W372" s="5" t="n">
         <v>146.1</v>
@@ -27922,7 +28736,9 @@
       <c r="T373" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="U373" s="5" t="inlineStr"/>
+      <c r="U373" s="5" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V373" t="inlineStr"/>
       <c r="W373" s="5" t="n">
         <v>151.7</v>
@@ -27995,7 +28811,9 @@
       <c r="T374" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U374" s="5" t="inlineStr"/>
+      <c r="U374" s="5" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V374" t="inlineStr"/>
       <c r="W374" s="5" t="n">
         <v>150.2</v>
@@ -28068,7 +28886,9 @@
       <c r="T375" s="5" t="n">
         <v>18.7</v>
       </c>
-      <c r="U375" s="5" t="inlineStr"/>
+      <c r="U375" s="5" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V375" t="inlineStr"/>
       <c r="W375" s="5" t="n">
         <v>145.9</v>
@@ -28141,7 +28961,9 @@
       <c r="T376" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U376" s="5" t="inlineStr"/>
+      <c r="U376" s="5" t="n">
+        <v>15.4</v>
+      </c>
       <c r="V376" t="inlineStr"/>
       <c r="W376" s="5" t="n">
         <v>147.3</v>
@@ -28214,7 +29036,9 @@
       <c r="T377" s="5" t="n">
         <v>18.7</v>
       </c>
-      <c r="U377" s="5" t="inlineStr"/>
+      <c r="U377" s="5" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V377" t="inlineStr"/>
       <c r="W377" s="5" t="n">
         <v>146.6</v>
@@ -28287,7 +29111,9 @@
       <c r="T378" s="5" t="n">
         <v>18.2</v>
       </c>
-      <c r="U378" s="5" t="inlineStr"/>
+      <c r="U378" s="5" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V378" t="inlineStr"/>
       <c r="W378" s="5" t="n">
         <v>143</v>
@@ -28364,7 +29190,9 @@
       <c r="T379" s="5" t="n">
         <v>20.7</v>
       </c>
-      <c r="U379" s="5" t="inlineStr"/>
+      <c r="U379" s="5" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V379" t="inlineStr"/>
       <c r="W379" s="5" t="n">
         <v>139.6</v>
@@ -28437,7 +29265,9 @@
       <c r="T380" s="5" t="n">
         <v>17.1</v>
       </c>
-      <c r="U380" s="5" t="inlineStr"/>
+      <c r="U380" s="5" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V380" t="inlineStr"/>
       <c r="W380" s="5" t="n">
         <v>139.9</v>
@@ -28510,7 +29340,9 @@
       <c r="T381" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="U381" s="5" t="inlineStr"/>
+      <c r="U381" s="5" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V381" t="inlineStr"/>
       <c r="W381" s="5" t="n">
         <v>141.2</v>
@@ -28583,7 +29415,9 @@
       <c r="T382" s="5" t="n">
         <v>15.9</v>
       </c>
-      <c r="U382" s="5" t="inlineStr"/>
+      <c r="U382" s="5" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V382" t="inlineStr"/>
       <c r="W382" s="5" t="n">
         <v>140</v>
@@ -28656,7 +29490,9 @@
       <c r="T383" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U383" s="5" t="inlineStr"/>
+      <c r="U383" s="5" t="n">
+        <v>13.9</v>
+      </c>
       <c r="V383" t="inlineStr"/>
       <c r="W383" s="4" t="n">
         <v>126.4</v>
@@ -28733,7 +29569,9 @@
       <c r="T384" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U384" s="5" t="inlineStr"/>
+      <c r="U384" s="5" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V384" t="inlineStr"/>
       <c r="W384" s="5" t="n">
         <v>133.3</v>
@@ -28806,7 +29644,9 @@
       <c r="T385" s="5" t="n">
         <v>15.1</v>
       </c>
-      <c r="U385" s="5" t="inlineStr"/>
+      <c r="U385" s="5" t="n">
+        <v>12.6</v>
+      </c>
       <c r="V385" t="inlineStr"/>
       <c r="W385" s="5" t="n">
         <v>134.7</v>
@@ -28879,7 +29719,9 @@
       <c r="T386" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U386" s="5" t="inlineStr"/>
+      <c r="U386" s="5" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V386" t="inlineStr"/>
       <c r="W386" s="5" t="n">
         <v>132.6</v>
@@ -28952,7 +29794,9 @@
       <c r="T387" s="5" t="n">
         <v>15.5</v>
       </c>
-      <c r="U387" s="5" t="inlineStr"/>
+      <c r="U387" s="5" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V387" t="inlineStr"/>
       <c r="W387" s="5" t="n">
         <v>137.1</v>
@@ -29029,7 +29873,9 @@
       <c r="T388" s="5" t="n">
         <v>15.3</v>
       </c>
-      <c r="U388" s="5" t="inlineStr"/>
+      <c r="U388" s="5" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V388" t="inlineStr"/>
       <c r="W388" s="5" t="n">
         <v>135.6</v>
@@ -29102,7 +29948,9 @@
       <c r="T389" s="5" t="n">
         <v>14.6</v>
       </c>
-      <c r="U389" s="5" t="inlineStr"/>
+      <c r="U389" s="5" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V389" t="inlineStr"/>
       <c r="W389" s="5" t="n">
         <v>136.5</v>
@@ -29175,7 +30023,9 @@
       <c r="T390" s="5" t="n">
         <v>14.6</v>
       </c>
-      <c r="U390" s="5" t="inlineStr"/>
+      <c r="U390" s="5" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V390" t="inlineStr"/>
       <c r="W390" s="5" t="n">
         <v>134.4</v>
@@ -29248,7 +30098,9 @@
       <c r="T391" s="5" t="n">
         <v>14.2</v>
       </c>
-      <c r="U391" s="5" t="inlineStr"/>
+      <c r="U391" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="V391" t="inlineStr"/>
       <c r="W391" s="5" t="n">
         <v>138.4</v>
@@ -29321,7 +30173,9 @@
       <c r="T392" s="5" t="n">
         <v>15.2</v>
       </c>
-      <c r="U392" s="5" t="inlineStr"/>
+      <c r="U392" s="5" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V392" t="inlineStr"/>
       <c r="W392" s="5" t="n">
         <v>142.9</v>
@@ -29398,7 +30252,9 @@
       <c r="T393" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U393" s="5" t="inlineStr"/>
+      <c r="U393" s="5" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V393" t="inlineStr"/>
       <c r="W393" s="5" t="n">
         <v>143.6</v>
@@ -29471,7 +30327,9 @@
       <c r="T394" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U394" s="5" t="inlineStr"/>
+      <c r="U394" s="5" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="V394" t="inlineStr"/>
       <c r="W394" s="5" t="n">
         <v>142.9</v>
@@ -29544,7 +30402,9 @@
       <c r="T395" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="U395" s="5" t="inlineStr"/>
+      <c r="U395" s="5" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V395" t="inlineStr"/>
       <c r="W395" s="5" t="n">
         <v>143.2</v>
@@ -29617,7 +30477,9 @@
       <c r="T396" s="5" t="n">
         <v>15.1</v>
       </c>
-      <c r="U396" s="5" t="inlineStr"/>
+      <c r="U396" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="V396" t="inlineStr"/>
       <c r="W396" s="5" t="n">
         <v>143.9</v>
@@ -29694,7 +30556,9 @@
       <c r="T397" s="5" t="n">
         <v>15.9</v>
       </c>
-      <c r="U397" s="5" t="inlineStr"/>
+      <c r="U397" s="5" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="V397" t="inlineStr"/>
       <c r="W397" s="5" t="n">
         <v>145.6</v>
@@ -29767,7 +30631,9 @@
       <c r="T398" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U398" s="5" t="inlineStr"/>
+      <c r="U398" s="5" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V398" t="inlineStr"/>
       <c r="W398" s="5" t="n">
         <v>143.3</v>
@@ -29840,7 +30706,9 @@
       <c r="T399" s="5" t="n">
         <v>15.2</v>
       </c>
-      <c r="U399" s="5" t="inlineStr"/>
+      <c r="U399" s="5" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V399" t="inlineStr"/>
       <c r="W399" s="5" t="n">
         <v>143</v>
@@ -29913,7 +30781,9 @@
       <c r="T400" s="5" t="n">
         <v>14.5</v>
       </c>
-      <c r="U400" s="5" t="inlineStr"/>
+      <c r="U400" s="5" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V400" t="inlineStr"/>
       <c r="W400" s="5" t="n">
         <v>144.1</v>
@@ -29990,7 +30860,9 @@
       <c r="T401" s="5" t="n">
         <v>14.4</v>
       </c>
-      <c r="U401" s="5" t="inlineStr"/>
+      <c r="U401" s="5" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V401" t="inlineStr"/>
       <c r="W401" s="5" t="n">
         <v>149.8</v>
@@ -30063,7 +30935,9 @@
       <c r="T402" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U402" s="5" t="inlineStr"/>
+      <c r="U402" s="5" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V402" t="inlineStr"/>
       <c r="W402" s="5" t="n">
         <v>148.5</v>
@@ -30136,7 +31010,9 @@
       <c r="T403" s="5" t="n">
         <v>16.3</v>
       </c>
-      <c r="U403" s="5" t="inlineStr"/>
+      <c r="U403" s="5" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V403" t="inlineStr"/>
       <c r="W403" s="5" t="n">
         <v>149.2</v>
@@ -30209,7 +31085,9 @@
       <c r="T404" s="5" t="n">
         <v>15.2</v>
       </c>
-      <c r="U404" s="5" t="inlineStr"/>
+      <c r="U404" s="5" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V404" t="inlineStr"/>
       <c r="W404" s="5" t="n">
         <v>144.1</v>
@@ -30282,7 +31160,9 @@
       <c r="T405" s="5" t="n">
         <v>14.3</v>
       </c>
-      <c r="U405" s="5" t="inlineStr"/>
+      <c r="U405" s="5" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V405" t="inlineStr"/>
       <c r="W405" s="5" t="n">
         <v>150.6</v>
@@ -30355,7 +31235,9 @@
       <c r="T406" s="5" t="n">
         <v>14.5</v>
       </c>
-      <c r="U406" s="5" t="inlineStr"/>
+      <c r="U406" s="5" t="n">
+        <v>12</v>
+      </c>
       <c r="V406" t="inlineStr"/>
       <c r="W406" s="5" t="n">
         <v>151.6</v>
@@ -30428,7 +31310,9 @@
       <c r="T407" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U407" s="5" t="inlineStr"/>
+      <c r="U407" s="5" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V407" t="inlineStr"/>
       <c r="W407" s="5" t="n">
         <v>148.9</v>
@@ -30505,7 +31389,9 @@
       <c r="T408" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U408" s="5" t="inlineStr"/>
+      <c r="U408" s="5" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V408" t="inlineStr"/>
       <c r="W408" s="5" t="n">
         <v>149.2</v>
@@ -30578,7 +31464,9 @@
       <c r="T409" s="5" t="n">
         <v>17.8</v>
       </c>
-      <c r="U409" s="5" t="inlineStr"/>
+      <c r="U409" s="5" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V409" t="inlineStr"/>
       <c r="W409" s="5" t="n">
         <v>147</v>
@@ -30651,7 +31539,9 @@
       <c r="T410" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U410" s="5" t="inlineStr"/>
+      <c r="U410" s="5" t="n">
+        <v>13</v>
+      </c>
       <c r="V410" t="inlineStr"/>
       <c r="W410" s="5" t="n">
         <v>154.5</v>
@@ -30724,7 +31614,9 @@
       <c r="T411" s="5" t="n">
         <v>17.1</v>
       </c>
-      <c r="U411" s="5" t="inlineStr"/>
+      <c r="U411" s="5" t="n">
+        <v>12</v>
+      </c>
       <c r="V411" t="inlineStr"/>
       <c r="W411" s="5" t="n">
         <v>152.1</v>
@@ -30797,7 +31689,9 @@
       <c r="T412" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U412" s="5" t="inlineStr"/>
+      <c r="U412" s="5" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="5" t="n">
         <v>146.6</v>
@@ -30870,7 +31764,9 @@
       <c r="T413" s="5" t="n">
         <v>17.7</v>
       </c>
-      <c r="U413" s="5" t="inlineStr"/>
+      <c r="U413" s="5" t="n">
+        <v>17</v>
+      </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="5" t="n">
         <v>145.9</v>
@@ -30943,7 +31839,9 @@
       <c r="T414" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U414" s="5" t="inlineStr"/>
+      <c r="U414" s="5" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="5" t="n">
         <v>145.7</v>
@@ -30967,22 +31865,22 @@
         <v>90.58</v>
       </c>
       <c r="E415" t="n">
-        <v>89.8</v>
+        <v>89.48</v>
       </c>
       <c r="F415" t="n">
-        <v>89.95</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="G415" t="n">
-        <v>743989</v>
+        <v>1575947</v>
       </c>
       <c r="H415" s="4" t="n">
-        <v>0.01</v>
+        <v>0.14</v>
       </c>
       <c r="I415" t="n">
         <v>5.3</v>
       </c>
       <c r="J415" t="n">
-        <v>89.2</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="K415" t="n">
         <v>89.44</v>
@@ -30994,7 +31892,7 @@
         <v>79.94</v>
       </c>
       <c r="N415" s="5" t="n">
-        <v>49.26</v>
+        <v>49.67</v>
       </c>
       <c r="O415" t="n">
         <v>29</v>
@@ -31014,10 +31912,10 @@
         <v>5</v>
       </c>
       <c r="T415" s="5" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="U415" s="5" t="n">
-        <v>7.5</v>
+        <v>10.1</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="5" t="inlineStr"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31796,7 +31796,7 @@
         <v>89.94</v>
       </c>
       <c r="G414" t="n">
-        <v>2809800</v>
+        <v>2837100</v>
       </c>
       <c r="H414" s="4" t="n">
         <v>3.43</v>
@@ -31862,37 +31862,37 @@
         <v>90.41</v>
       </c>
       <c r="D415" t="n">
-        <v>90.58</v>
+        <v>91.11</v>
       </c>
       <c r="E415" t="n">
         <v>89.48</v>
       </c>
       <c r="F415" t="n">
-        <v>90.06999999999999</v>
+        <v>91</v>
       </c>
       <c r="G415" t="n">
-        <v>1575947</v>
+        <v>3411492</v>
       </c>
       <c r="H415" s="4" t="n">
-        <v>0.14</v>
+        <v>1.18</v>
       </c>
       <c r="I415" t="n">
         <v>5.3</v>
       </c>
       <c r="J415" t="n">
-        <v>89.20999999999999</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="K415" t="n">
-        <v>89.44</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="L415" t="n">
-        <v>87.02</v>
+        <v>87.03</v>
       </c>
       <c r="M415" t="n">
-        <v>79.94</v>
+        <v>79.95</v>
       </c>
       <c r="N415" s="5" t="n">
-        <v>49.67</v>
+        <v>52.6</v>
       </c>
       <c r="O415" t="n">
         <v>29</v>
@@ -31912,13 +31912,15 @@
         <v>5</v>
       </c>
       <c r="T415" s="5" t="n">
-        <v>15.3</v>
+        <v>14.8</v>
       </c>
       <c r="U415" s="5" t="n">
-        <v>10.1</v>
+        <v>11.4</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="5" t="inlineStr"/>
+      <c r="W415" s="5" t="n">
+        <v>148.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -1282,13 +1282,13 @@
         <v>55.75</v>
       </c>
       <c r="F11" t="n">
-        <v>55.92</v>
+        <v>55.91</v>
       </c>
       <c r="G11" t="n">
         <v>4503400</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-2.53</v>
+        <v>-2.54</v>
       </c>
       <c r="I11" t="n">
         <v>5.3</v>
@@ -1297,7 +1297,7 @@
         <v>55.61</v>
       </c>
       <c r="K11" t="n">
-        <v>55.43</v>
+        <v>55.42</v>
       </c>
       <c r="L11" t="n">
         <v>52.32</v>
@@ -1306,7 +1306,7 @@
         <v>49.92</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>49.96</v>
+        <v>49.93</v>
       </c>
       <c r="O11" t="n">
         <v>38</v>
@@ -1363,7 +1363,7 @@
         <v>2721000</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I12" t="n">
         <v>5.3</v>
@@ -1531,7 +1531,7 @@
         <v>50.18</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>45.24</v>
+        <v>45.25</v>
       </c>
       <c r="O14" t="n">
         <v>41</v>
@@ -1606,7 +1606,7 @@
         <v>50.27</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>53.84</v>
+        <v>53.83</v>
       </c>
       <c r="O15" t="n">
         <v>47</v>
@@ -1681,7 +1681,7 @@
         <v>50.36</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>72.43000000000001</v>
+        <v>72.39</v>
       </c>
       <c r="O16" t="n">
         <v>44</v>
@@ -1756,7 +1756,7 @@
         <v>50.46</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>68.47</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="O17" t="n">
         <v>47</v>
@@ -1831,7 +1831,7 @@
         <v>50.56</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>70.23999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="O18" t="n">
         <v>48</v>
@@ -1906,7 +1906,7 @@
         <v>50.65</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>64.87</v>
+        <v>64.84</v>
       </c>
       <c r="O19" t="n">
         <v>44</v>
@@ -1981,7 +1981,7 @@
         <v>50.73</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>52.39</v>
+        <v>52.38</v>
       </c>
       <c r="O20" t="n">
         <v>37</v>
@@ -2139,7 +2139,7 @@
         <v>50.85</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>39.2</v>
+        <v>39.22</v>
       </c>
       <c r="O22" t="n">
         <v>24</v>
@@ -2214,7 +2214,7 @@
         <v>50.91</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>37.99</v>
+        <v>38.01</v>
       </c>
       <c r="O23" t="n">
         <v>21</v>
@@ -2289,7 +2289,7 @@
         <v>50.95</v>
       </c>
       <c r="N24" s="7" t="n">
-        <v>27.65</v>
+        <v>27.68</v>
       </c>
       <c r="O24" s="1" t="n">
         <v>13</v>
@@ -2368,7 +2368,7 @@
         <v>51</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>38.21</v>
+        <v>38.26</v>
       </c>
       <c r="O25" t="n">
         <v>21</v>
@@ -7487,7 +7487,7 @@
         <v>46.13</v>
       </c>
       <c r="L92" t="n">
-        <v>50.67</v>
+        <v>50.66</v>
       </c>
       <c r="M92" t="n">
         <v>50.63</v>
@@ -11323,7 +11323,7 @@
         <v>51.95</v>
       </c>
       <c r="M143" t="n">
-        <v>53.3</v>
+        <v>53.29</v>
       </c>
       <c r="N143" s="5" t="n">
         <v>49.89</v>
@@ -12886,7 +12886,7 @@
         <v>67.98999999999999</v>
       </c>
       <c r="E164" t="n">
-        <v>66.84</v>
+        <v>66.83</v>
       </c>
       <c r="F164" t="n">
         <v>67.38</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -12807,7 +12807,7 @@
         <v>67.98999999999999</v>
       </c>
       <c r="E163" t="n">
-        <v>66.84</v>
+        <v>66.83</v>
       </c>
       <c r="F163" t="n">
         <v>67.38</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -12807,7 +12807,7 @@
         <v>67.98999999999999</v>
       </c>
       <c r="E163" t="n">
-        <v>66.83</v>
+        <v>66.84</v>
       </c>
       <c r="F163" t="n">
         <v>67.38</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -12732,7 +12732,7 @@
         <v>67.98999999999999</v>
       </c>
       <c r="E162" t="n">
-        <v>66.84</v>
+        <v>66.83</v>
       </c>
       <c r="F162" t="n">
         <v>67.38</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -12732,7 +12732,7 @@
         <v>67.98999999999999</v>
       </c>
       <c r="E162" t="n">
-        <v>66.83</v>
+        <v>66.84</v>
       </c>
       <c r="F162" t="n">
         <v>67.38</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -12657,7 +12657,7 @@
         <v>67.98999999999999</v>
       </c>
       <c r="E161" t="n">
-        <v>66.84</v>
+        <v>66.83</v>
       </c>
       <c r="F161" t="n">
         <v>67.38</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2759,7 +2759,7 @@
         <v>5.3</v>
       </c>
       <c r="J30" t="n">
-        <v>53</v>
+        <v>52.99</v>
       </c>
       <c r="K30" t="n">
         <v>55</v>
@@ -12657,7 +12657,7 @@
         <v>67.98999999999999</v>
       </c>
       <c r="E161" t="n">
-        <v>66.83</v>
+        <v>66.84</v>
       </c>
       <c r="F161" t="n">
         <v>67.38</v>
@@ -28094,7 +28094,7 @@
         <v>5.3</v>
       </c>
       <c r="J365" t="n">
-        <v>93.14</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="K365" t="n">
         <v>90.17</v>
@@ -31666,7 +31666,7 @@
         <v>52.6</v>
       </c>
       <c r="O412" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31692,6 +31692,79 @@
       <c r="W412" s="2" t="n">
         <v>148.1</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>92.86</v>
+      </c>
+      <c r="D413" t="n">
+        <v>95.77</v>
+      </c>
+      <c r="E413" t="n">
+        <v>92.84999999999999</v>
+      </c>
+      <c r="F413" t="n">
+        <v>95.62</v>
+      </c>
+      <c r="G413" t="n">
+        <v>2654131</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="I413" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J413" t="n">
+        <v>89.56</v>
+      </c>
+      <c r="K413" t="n">
+        <v>89.52</v>
+      </c>
+      <c r="L413" t="n">
+        <v>87.34999999999999</v>
+      </c>
+      <c r="M413" t="n">
+        <v>80.06</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>63.11</v>
+      </c>
+      <c r="O413" t="n">
+        <v>34</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -20085,7 +20085,7 @@
         <v>71.26000000000001</v>
       </c>
       <c r="K259" t="n">
-        <v>70.91</v>
+        <v>70.92</v>
       </c>
       <c r="L259" t="n">
         <v>69.41</v>
@@ -31708,28 +31708,28 @@
         <v>92.86</v>
       </c>
       <c r="D413" t="n">
-        <v>95.77</v>
+        <v>96.73</v>
       </c>
       <c r="E413" t="n">
         <v>92.84999999999999</v>
       </c>
       <c r="F413" t="n">
-        <v>95.62</v>
+        <v>96.27</v>
       </c>
       <c r="G413" t="n">
-        <v>2654131</v>
+        <v>4263840</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>5.08</v>
+        <v>5.79</v>
       </c>
       <c r="I413" t="n">
         <v>5.3</v>
       </c>
       <c r="J413" t="n">
-        <v>89.56</v>
+        <v>89.59</v>
       </c>
       <c r="K413" t="n">
-        <v>89.52</v>
+        <v>89.53</v>
       </c>
       <c r="L413" t="n">
         <v>87.34999999999999</v>
@@ -31738,7 +31738,7 @@
         <v>80.06</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>63.11</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="O413" t="n">
         <v>34</v>
@@ -31755,13 +31755,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31717,7 +31717,7 @@
         <v>96.27</v>
       </c>
       <c r="G413" t="n">
-        <v>4263840</v>
+        <v>4312400</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>5.79</v>
@@ -31764,7 +31764,9 @@
         <v>10</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>142.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31693,6 +31693,79 @@
         <v>142.2</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>96.13</v>
+      </c>
+      <c r="D413" t="n">
+        <v>97.52</v>
+      </c>
+      <c r="E413" t="n">
+        <v>96.13</v>
+      </c>
+      <c r="F413" t="n">
+        <v>97.38</v>
+      </c>
+      <c r="G413" t="n">
+        <v>1329529</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I413" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J413" t="n">
+        <v>90.08</v>
+      </c>
+      <c r="K413" t="n">
+        <v>89.67</v>
+      </c>
+      <c r="L413" t="n">
+        <v>87.66</v>
+      </c>
+      <c r="M413" t="n">
+        <v>80.19</v>
+      </c>
+      <c r="N413" s="1" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="O413" t="n">
+        <v>37</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31708,19 +31708,19 @@
         <v>96.13</v>
       </c>
       <c r="D413" t="n">
-        <v>97.52</v>
+        <v>97.7</v>
       </c>
       <c r="E413" t="n">
         <v>96.13</v>
       </c>
       <c r="F413" t="n">
-        <v>97.38</v>
+        <v>97.45999999999999</v>
       </c>
       <c r="G413" t="n">
-        <v>1329529</v>
+        <v>2926734</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="I413" t="n">
         <v>5.3</v>
@@ -31738,10 +31738,10 @@
         <v>80.19</v>
       </c>
       <c r="N413" s="1" t="n">
-        <v>73.7</v>
+        <v>73.8</v>
       </c>
       <c r="O413" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31758,10 +31758,10 @@
         <v>4.95</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>6.7</v>
+        <v>8.1</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -2684,7 +2684,7 @@
         <v>5.3</v>
       </c>
       <c r="J29" t="n">
-        <v>52.99</v>
+        <v>53</v>
       </c>
       <c r="K29" t="n">
         <v>55</v>
@@ -12582,7 +12582,7 @@
         <v>67.98999999999999</v>
       </c>
       <c r="E160" t="n">
-        <v>66.84</v>
+        <v>66.83</v>
       </c>
       <c r="F160" t="n">
         <v>67.38</v>
@@ -20010,7 +20010,7 @@
         <v>71.26000000000001</v>
       </c>
       <c r="K258" t="n">
-        <v>70.92</v>
+        <v>70.91</v>
       </c>
       <c r="L258" t="n">
         <v>69.41</v>
@@ -28019,7 +28019,7 @@
         <v>5.3</v>
       </c>
       <c r="J364" t="n">
-        <v>93.15000000000001</v>
+        <v>93.14</v>
       </c>
       <c r="K364" t="n">
         <v>90.17</v>
@@ -31642,7 +31642,7 @@
         <v>96.27</v>
       </c>
       <c r="G412" t="n">
-        <v>4361300</v>
+        <v>4420700</v>
       </c>
       <c r="H412" s="3" t="n">
         <v>5.79</v>
@@ -31708,28 +31708,28 @@
         <v>96.13</v>
       </c>
       <c r="D413" t="n">
-        <v>97.7</v>
+        <v>98.05</v>
       </c>
       <c r="E413" t="n">
         <v>96.13</v>
       </c>
       <c r="F413" t="n">
-        <v>97.45999999999999</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="G413" t="n">
-        <v>2926734</v>
+        <v>3610604</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="I413" t="n">
         <v>5.3</v>
       </c>
       <c r="J413" t="n">
-        <v>90.08</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="K413" t="n">
-        <v>89.67</v>
+        <v>89.68000000000001</v>
       </c>
       <c r="L413" t="n">
         <v>87.66</v>
@@ -31738,10 +31738,10 @@
         <v>80.19</v>
       </c>
       <c r="N413" s="1" t="n">
-        <v>73.8</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="O413" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31755,16 +31755,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>4.95</v>
+        <v>4.97</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>144.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -12507,7 +12507,7 @@
         <v>67.98999999999999</v>
       </c>
       <c r="E159" t="n">
-        <v>66.84</v>
+        <v>66.83</v>
       </c>
       <c r="F159" t="n">
         <v>67.38</v>
@@ -31663,19 +31663,11 @@
         </is>
       </c>
       <c r="R412" t="inlineStr"/>
-      <c r="S412" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="T412" s="2" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="U412" s="2" t="n">
-        <v>8.800000000000001</v>
-      </c>
+      <c r="S412" t="inlineStr"/>
+      <c r="T412" s="2" t="inlineStr"/>
+      <c r="U412" s="2" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
-      <c r="W412" s="2" t="n">
-        <v>144.8</v>
-      </c>
+      <c r="W412" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -12507,7 +12507,7 @@
         <v>67.98999999999999</v>
       </c>
       <c r="E159" t="n">
-        <v>66.83</v>
+        <v>66.84</v>
       </c>
       <c r="F159" t="n">
         <v>67.38</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31626,31 +31626,47 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>97.68000000000001</v>
+      </c>
+      <c r="D412" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="E412" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="F412" t="n">
+        <v>95.86</v>
+      </c>
       <c r="G412" t="n">
-        <v>3610604</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
+        <v>2030060</v>
+      </c>
+      <c r="H412" s="1" t="n">
+        <v>-0.43</v>
       </c>
       <c r="I412" t="n">
         <v>5.3</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>90</v>
+      </c>
+      <c r="K412" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="L412" t="n">
+        <v>87.64</v>
+      </c>
+      <c r="M412" t="n">
+        <v>80.18000000000001</v>
+      </c>
       <c r="N412" s="1" t="n">
-        <v>72.15000000000001</v>
+        <v>70.61</v>
       </c>
       <c r="O412" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31663,9 +31679,15 @@
         </is>
       </c>
       <c r="R412" t="inlineStr"/>
-      <c r="S412" t="inlineStr"/>
-      <c r="T412" s="2" t="inlineStr"/>
-      <c r="U412" s="2" t="inlineStr"/>
+      <c r="S412" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="T412" s="2" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="U412" s="2" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="inlineStr"/>
     </row>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2609,7 +2609,7 @@
         <v>5.3</v>
       </c>
       <c r="J28" t="n">
-        <v>53</v>
+        <v>52.99</v>
       </c>
       <c r="K28" t="n">
         <v>55</v>
@@ -19935,7 +19935,7 @@
         <v>71.26000000000001</v>
       </c>
       <c r="K257" t="n">
-        <v>70.91</v>
+        <v>70.92</v>
       </c>
       <c r="L257" t="n">
         <v>69.41</v>
@@ -27944,7 +27944,7 @@
         <v>5.3</v>
       </c>
       <c r="J363" t="n">
-        <v>93.14</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="K363" t="n">
         <v>90.17</v>
@@ -31626,47 +31626,47 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C412" t="n">
-        <v>97.68000000000001</v>
+        <v>96.13</v>
       </c>
       <c r="D412" t="n">
-        <v>97.7</v>
+        <v>98.05</v>
       </c>
       <c r="E412" t="n">
-        <v>95.38</v>
+        <v>96.13</v>
       </c>
       <c r="F412" t="n">
-        <v>95.86</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="G412" t="n">
-        <v>2030060</v>
-      </c>
-      <c r="H412" s="1" t="n">
-        <v>-0.43</v>
+        <v>3678400</v>
+      </c>
+      <c r="H412" s="3" t="n">
+        <v>1.61</v>
       </c>
       <c r="I412" t="n">
         <v>5.3</v>
       </c>
       <c r="J412" t="n">
-        <v>90</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="K412" t="n">
-        <v>89.64</v>
+        <v>89.68000000000001</v>
       </c>
       <c r="L412" t="n">
-        <v>87.64</v>
+        <v>87.66</v>
       </c>
       <c r="M412" t="n">
-        <v>80.18000000000001</v>
+        <v>80.19</v>
       </c>
       <c r="N412" s="1" t="n">
-        <v>70.61</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="O412" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31679,17 +31679,84 @@
         </is>
       </c>
       <c r="R412" t="inlineStr"/>
-      <c r="S412" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="T412" s="2" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="U412" s="2" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="S412" t="inlineStr"/>
+      <c r="T412" s="2" t="inlineStr"/>
+      <c r="U412" s="2" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>97.68000000000001</v>
+      </c>
+      <c r="D413" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="E413" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="F413" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="G413" t="n">
+        <v>3677236</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="I413" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J413" t="n">
+        <v>90.45999999999999</v>
+      </c>
+      <c r="K413" t="n">
+        <v>89.72</v>
+      </c>
+      <c r="L413" t="n">
+        <v>87.94</v>
+      </c>
+      <c r="M413" t="n">
+        <v>80.31</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>67.92</v>
+      </c>
+      <c r="O413" t="n">
+        <v>35</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31706,13 +31706,13 @@
         <v>95.38</v>
       </c>
       <c r="F413" t="n">
-        <v>96.09999999999999</v>
+        <v>96.16</v>
       </c>
       <c r="G413" t="n">
-        <v>3677236</v>
+        <v>3757642</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>-1.76</v>
+        <v>-1.7</v>
       </c>
       <c r="I413" t="n">
         <v>5.3</v>
@@ -31730,7 +31730,7 @@
         <v>80.31</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>67.92</v>
+        <v>68.11</v>
       </c>
       <c r="O413" t="n">
         <v>35</v>
@@ -31753,10 +31753,12 @@
         <v>15.2</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>146.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31696,41 +31696,25 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="C413" t="n">
-        <v>97.68000000000001</v>
-      </c>
-      <c r="D413" t="n">
-        <v>97.7</v>
-      </c>
-      <c r="E413" t="n">
-        <v>95.38</v>
-      </c>
-      <c r="F413" t="n">
-        <v>96.16</v>
-      </c>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr"/>
       <c r="G413" t="n">
         <v>3757642</v>
       </c>
-      <c r="H413" s="1" t="n">
-        <v>-1.7</v>
+      <c r="H413" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I413" t="n">
         <v>5.3</v>
       </c>
-      <c r="J413" t="n">
-        <v>90.45999999999999</v>
-      </c>
-      <c r="K413" t="n">
-        <v>89.72</v>
-      </c>
-      <c r="L413" t="n">
-        <v>87.94</v>
-      </c>
-      <c r="M413" t="n">
-        <v>80.31</v>
-      </c>
-      <c r="N413" s="2" t="n">
-        <v>68.11</v>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
+      <c r="N413" s="1" t="n">
+        <v>73.76000000000001</v>
       </c>
       <c r="O413" t="n">
         <v>35</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31733,7 +31733,7 @@
         <v>68.20999999999999</v>
       </c>
       <c r="O413" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31759,6 +31759,79 @@
       <c r="W413" s="2" t="n">
         <v>146.1</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="D414" t="n">
+        <v>96.48</v>
+      </c>
+      <c r="E414" t="n">
+        <v>94.45</v>
+      </c>
+      <c r="F414" t="n">
+        <v>95.81999999999999</v>
+      </c>
+      <c r="G414" t="n">
+        <v>2737687</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="I414" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J414" t="n">
+        <v>90.79000000000001</v>
+      </c>
+      <c r="K414" t="n">
+        <v>89.68000000000001</v>
+      </c>
+      <c r="L414" t="n">
+        <v>88.19</v>
+      </c>
+      <c r="M414" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>63.73</v>
+      </c>
+      <c r="O414" t="n">
+        <v>35</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31709,7 +31709,7 @@
         <v>96.16</v>
       </c>
       <c r="G413" t="n">
-        <v>3821700</v>
+        <v>3835700</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-1.67</v>
@@ -31781,34 +31781,34 @@
         <v>94.45</v>
       </c>
       <c r="F414" t="n">
-        <v>95.81999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="G414" t="n">
-        <v>2737687</v>
+        <v>3586097</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-0.35</v>
+        <v>-0.06</v>
       </c>
       <c r="I414" t="n">
         <v>5.3</v>
       </c>
       <c r="J414" t="n">
-        <v>90.79000000000001</v>
+        <v>90.8</v>
       </c>
       <c r="K414" t="n">
         <v>89.68000000000001</v>
       </c>
       <c r="L414" t="n">
-        <v>88.19</v>
+        <v>88.2</v>
       </c>
       <c r="M414" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>63.73</v>
+        <v>64.64</v>
       </c>
       <c r="O414" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31822,16 +31822,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.18</v>
+        <v>5.16</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.6</v>
+        <v>12.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>146</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -2210,7 +2210,7 @@
         <v>5.3</v>
       </c>
       <c r="J23" t="n">
-        <v>55.5</v>
+        <v>55.51</v>
       </c>
       <c r="K23" t="n">
         <v>55.83</v>
@@ -9055,7 +9055,7 @@
         <v>57.47</v>
       </c>
       <c r="K113" t="n">
-        <v>51.88</v>
+        <v>51.89</v>
       </c>
       <c r="L113" t="n">
         <v>50.87</v>
@@ -10410,7 +10410,7 @@
         <v>5.3</v>
       </c>
       <c r="J131" t="n">
-        <v>61.01</v>
+        <v>61</v>
       </c>
       <c r="K131" t="n">
         <v>56.96</v>
@@ -12828,7 +12828,7 @@
         <v>62.42</v>
       </c>
       <c r="L163" t="n">
-        <v>55.48</v>
+        <v>55.49</v>
       </c>
       <c r="M163" t="n">
         <v>54.68</v>
@@ -30828,7 +30828,7 @@
         <v>90.25</v>
       </c>
       <c r="L401" t="n">
-        <v>85.05</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="M401" t="n">
         <v>79</v>
@@ -31771,41 +31771,25 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C414" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="D414" t="n">
-        <v>96.48</v>
-      </c>
-      <c r="E414" t="n">
-        <v>94.45</v>
-      </c>
-      <c r="F414" t="n">
-        <v>96.09999999999999</v>
-      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
         <v>3586097</v>
       </c>
-      <c r="H414" s="1" t="n">
-        <v>-0.06</v>
+      <c r="H414" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I414" t="n">
         <v>5.3</v>
       </c>
-      <c r="J414" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="K414" t="n">
-        <v>89.68000000000001</v>
-      </c>
-      <c r="L414" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="M414" t="n">
-        <v>80.40000000000001</v>
-      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
       <c r="N414" s="2" t="n">
-        <v>64.64</v>
+        <v>64.84</v>
       </c>
       <c r="O414" t="n">
         <v>36</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -2210,7 +2210,7 @@
         <v>5.3</v>
       </c>
       <c r="J23" t="n">
-        <v>55.51</v>
+        <v>55.5</v>
       </c>
       <c r="K23" t="n">
         <v>55.83</v>
@@ -9055,7 +9055,7 @@
         <v>57.47</v>
       </c>
       <c r="K113" t="n">
-        <v>51.89</v>
+        <v>51.88</v>
       </c>
       <c r="L113" t="n">
         <v>50.87</v>
@@ -10410,7 +10410,7 @@
         <v>5.3</v>
       </c>
       <c r="J131" t="n">
-        <v>61</v>
+        <v>61.01</v>
       </c>
       <c r="K131" t="n">
         <v>56.96</v>
@@ -12828,7 +12828,7 @@
         <v>62.42</v>
       </c>
       <c r="L163" t="n">
-        <v>55.49</v>
+        <v>55.48</v>
       </c>
       <c r="M163" t="n">
         <v>54.68</v>
@@ -30828,7 +30828,7 @@
         <v>90.25</v>
       </c>
       <c r="L401" t="n">
-        <v>85.04000000000001</v>
+        <v>85.05</v>
       </c>
       <c r="M401" t="n">
         <v>79</v>
@@ -31771,25 +31771,41 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="D414" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="E414" t="n">
+        <v>94.45</v>
+      </c>
+      <c r="F414" t="n">
+        <v>96.09999999999999</v>
+      </c>
       <c r="G414" t="n">
-        <v>3586097</v>
-      </c>
-      <c r="H414" s="2" t="n">
-        <v>0</v>
+        <v>3604600</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-0.06</v>
       </c>
       <c r="I414" t="n">
         <v>5.3</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="K414" t="n">
+        <v>89.68000000000001</v>
+      </c>
+      <c r="L414" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="M414" t="n">
+        <v>80.40000000000001</v>
+      </c>
       <c r="N414" s="2" t="n">
-        <v>64.84</v>
+        <v>64.64</v>
       </c>
       <c r="O414" t="n">
         <v>36</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31679,11 +31679,19 @@
         </is>
       </c>
       <c r="R412" t="inlineStr"/>
-      <c r="S412" t="inlineStr"/>
-      <c r="T412" s="2" t="inlineStr"/>
-      <c r="U412" s="2" t="inlineStr"/>
+      <c r="S412" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="T412" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="U412" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="V412" t="inlineStr"/>
-      <c r="W412" s="2" t="inlineStr"/>
+      <c r="W412" s="2" t="n">
+        <v>144.8</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31843,6 +31843,79 @@
         <v>146</v>
       </c>
     </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>96.52</v>
+      </c>
+      <c r="D415" t="n">
+        <v>97.31999999999999</v>
+      </c>
+      <c r="E415" t="n">
+        <v>95.70999999999999</v>
+      </c>
+      <c r="F415" t="n">
+        <v>97.11</v>
+      </c>
+      <c r="G415" t="n">
+        <v>2497352</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I415" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J415" t="n">
+        <v>91.09</v>
+      </c>
+      <c r="K415" t="n">
+        <v>89.73999999999999</v>
+      </c>
+      <c r="L415" t="n">
+        <v>88.48</v>
+      </c>
+      <c r="M415" t="n">
+        <v>80.52</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="O415" t="n">
+        <v>38</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31792,7 +31792,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="G414" t="n">
-        <v>3604600</v>
+        <v>3633900</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>-0.06</v>
@@ -31864,22 +31864,22 @@
         <v>95.70999999999999</v>
       </c>
       <c r="F415" t="n">
-        <v>97.11</v>
+        <v>96.95</v>
       </c>
       <c r="G415" t="n">
-        <v>2497352</v>
+        <v>3208896</v>
       </c>
       <c r="H415" s="3" t="n">
-        <v>1.05</v>
+        <v>0.88</v>
       </c>
       <c r="I415" t="n">
         <v>5.3</v>
       </c>
       <c r="J415" t="n">
-        <v>91.09</v>
+        <v>91.08</v>
       </c>
       <c r="K415" t="n">
-        <v>89.73999999999999</v>
+        <v>89.73</v>
       </c>
       <c r="L415" t="n">
         <v>88.48</v>
@@ -31888,10 +31888,10 @@
         <v>80.52</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>65.90000000000001</v>
+        <v>65.62</v>
       </c>
       <c r="O415" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31905,16 +31905,18 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.2</v>
+        <v>5.18</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>11.2</v>
+        <v>12.5</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="n">
+        <v>144.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -8505,7 +8505,7 @@
         <v>59.05</v>
       </c>
       <c r="D106" t="n">
-        <v>59.24</v>
+        <v>59.23</v>
       </c>
       <c r="E106" t="n">
         <v>58.22</v>
@@ -31775,25 +31775,41 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>96.52</v>
+      </c>
+      <c r="D414" t="n">
+        <v>97.31999999999999</v>
+      </c>
+      <c r="E414" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="F414" t="n">
+        <v>96.95</v>
+      </c>
       <c r="G414" t="n">
-        <v>3208896</v>
-      </c>
-      <c r="H414" s="2" t="n">
-        <v>0</v>
+        <v>3219100</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>0.88</v>
       </c>
       <c r="I414" t="n">
         <v>5.3</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>91.08</v>
+      </c>
+      <c r="K414" t="n">
+        <v>89.73</v>
+      </c>
+      <c r="L414" t="n">
+        <v>88.48</v>
+      </c>
+      <c r="M414" t="n">
+        <v>80.52</v>
+      </c>
       <c r="N414" s="2" t="n">
-        <v>64.11</v>
+        <v>65.62</v>
       </c>
       <c r="O414" t="n">
         <v>37</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31689,6 +31689,79 @@
         <v>144.9</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>95.88</v>
+      </c>
+      <c r="D413" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="E413" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="F413" t="n">
+        <v>94.11</v>
+      </c>
+      <c r="G413" t="n">
+        <v>1754762</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="I413" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J413" t="n">
+        <v>91.28</v>
+      </c>
+      <c r="K413" t="n">
+        <v>89.79000000000001</v>
+      </c>
+      <c r="L413" t="n">
+        <v>88.73</v>
+      </c>
+      <c r="M413" t="n">
+        <v>80.63</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="O413" t="n">
+        <v>34</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -1981,7 +1981,7 @@
         <v>5.3</v>
       </c>
       <c r="J20" t="n">
-        <v>55.5</v>
+        <v>55.51</v>
       </c>
       <c r="K20" t="n">
         <v>55.83</v>
@@ -10181,7 +10181,7 @@
         <v>5.3</v>
       </c>
       <c r="J128" t="n">
-        <v>61.01</v>
+        <v>61</v>
       </c>
       <c r="K128" t="n">
         <v>56.96</v>
@@ -31710,31 +31710,31 @@
         <v>93.59999999999999</v>
       </c>
       <c r="F413" t="n">
-        <v>94.11</v>
+        <v>94.87</v>
       </c>
       <c r="G413" t="n">
-        <v>1754762</v>
+        <v>3824732</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>-2.93</v>
+        <v>-2.15</v>
       </c>
       <c r="I413" t="n">
         <v>5.3</v>
       </c>
       <c r="J413" t="n">
-        <v>91.28</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="K413" t="n">
-        <v>89.79000000000001</v>
+        <v>89.81</v>
       </c>
       <c r="L413" t="n">
-        <v>88.73</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="M413" t="n">
         <v>80.63</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>57.87</v>
+        <v>59.86</v>
       </c>
       <c r="O413" t="n">
         <v>34</v>
@@ -31751,16 +31751,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>16.5</v>
+        <v>16.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>9.5</v>
+        <v>11.3</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>146.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31689,6 +31689,79 @@
         <v>146.2</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>95.81</v>
+      </c>
+      <c r="D413" t="n">
+        <v>95.84</v>
+      </c>
+      <c r="E413" t="n">
+        <v>94.73999999999999</v>
+      </c>
+      <c r="F413" t="n">
+        <v>94.81999999999999</v>
+      </c>
+      <c r="G413" t="n">
+        <v>1237436</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I413" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J413" t="n">
+        <v>91.55</v>
+      </c>
+      <c r="K413" t="n">
+        <v>89.83</v>
+      </c>
+      <c r="L413" t="n">
+        <v>88.97</v>
+      </c>
+      <c r="M413" t="n">
+        <v>80.73999999999999</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>61.25</v>
+      </c>
+      <c r="O413" t="n">
+        <v>33</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -22741,7 +22741,7 @@
         <v>5.3</v>
       </c>
       <c r="J294" t="n">
-        <v>63.35</v>
+        <v>63.34</v>
       </c>
       <c r="K294" t="n">
         <v>67.37</v>
@@ -30524,7 +30524,7 @@
         <v>90.25</v>
       </c>
       <c r="L397" t="n">
-        <v>85.05</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="M397" t="n">
         <v>79</v>
@@ -31638,7 +31638,7 @@
         <v>94.87</v>
       </c>
       <c r="G412" t="n">
-        <v>3858700</v>
+        <v>3881500</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>-2.15</v>
@@ -31707,25 +31707,25 @@
         <v>95.84</v>
       </c>
       <c r="E413" t="n">
-        <v>94.73999999999999</v>
+        <v>94.55</v>
       </c>
       <c r="F413" t="n">
-        <v>94.81999999999999</v>
+        <v>95.22</v>
       </c>
       <c r="G413" t="n">
-        <v>1237436</v>
-      </c>
-      <c r="H413" s="1" t="n">
-        <v>-0.05</v>
+        <v>2846635</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>0.37</v>
       </c>
       <c r="I413" t="n">
         <v>5.3</v>
       </c>
       <c r="J413" t="n">
-        <v>91.55</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="K413" t="n">
-        <v>89.83</v>
+        <v>89.84</v>
       </c>
       <c r="L413" t="n">
         <v>88.97</v>
@@ -31734,10 +31734,10 @@
         <v>80.73999999999999</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>61.25</v>
+        <v>62.01</v>
       </c>
       <c r="O413" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31751,13 +31751,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.27</v>
+        <v>5.26</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>10</v>
+        <v>11.7</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31625,25 +31625,41 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>95.81</v>
+      </c>
+      <c r="D412" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="E412" t="n">
+        <v>94.55</v>
+      </c>
+      <c r="F412" t="n">
+        <v>95.22</v>
+      </c>
       <c r="G412" t="n">
-        <v>2873624</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
+        <v>2895200</v>
+      </c>
+      <c r="H412" s="1" t="n">
+        <v>0.37</v>
       </c>
       <c r="I412" t="n">
         <v>5.3</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="K412" t="n">
+        <v>89.84</v>
+      </c>
+      <c r="L412" t="n">
+        <v>88.97</v>
+      </c>
+      <c r="M412" t="n">
+        <v>80.73999999999999</v>
+      </c>
       <c r="N412" s="2" t="n">
-        <v>61.39</v>
+        <v>62.01</v>
       </c>
       <c r="O412" t="n">
         <v>32</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31662,7 +31662,7 @@
         <v>62.01</v>
       </c>
       <c r="O412" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31689,6 +31689,79 @@
         <v>144.6</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>95.78</v>
+      </c>
+      <c r="D413" t="n">
+        <v>97.04000000000001</v>
+      </c>
+      <c r="E413" t="n">
+        <v>95.67</v>
+      </c>
+      <c r="F413" t="n">
+        <v>96.34</v>
+      </c>
+      <c r="G413" t="n">
+        <v>2229343</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="I413" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J413" t="n">
+        <v>91.98999999999999</v>
+      </c>
+      <c r="K413" t="n">
+        <v>89.95</v>
+      </c>
+      <c r="L413" t="n">
+        <v>89.20999999999999</v>
+      </c>
+      <c r="M413" t="n">
+        <v>80.86</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="O413" t="n">
+        <v>33</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -608,7 +608,7 @@
         <v>2.36</v>
       </c>
       <c r="I2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J2" t="n">
         <v>55.81</v>
@@ -683,7 +683,7 @@
         <v>-0.47</v>
       </c>
       <c r="I3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J3" t="n">
         <v>56.03</v>
@@ -758,7 +758,7 @@
         <v>0.11</v>
       </c>
       <c r="I4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J4" t="n">
         <v>56.25</v>
@@ -833,7 +833,7 @@
         <v>2.86</v>
       </c>
       <c r="I5" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J5" t="n">
         <v>56.44</v>
@@ -908,7 +908,7 @@
         <v>0.75</v>
       </c>
       <c r="I6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J6" t="n">
         <v>56.69</v>
@@ -983,7 +983,7 @@
         <v>0.44</v>
       </c>
       <c r="I7" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J7" t="n">
         <v>56.86</v>
@@ -1058,7 +1058,7 @@
         <v>0.05</v>
       </c>
       <c r="I8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J8" t="n">
         <v>57</v>
@@ -1133,7 +1133,7 @@
         <v>-0.88</v>
       </c>
       <c r="I9" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J9" t="n">
         <v>57.04</v>
@@ -1208,7 +1208,7 @@
         <v>-4.18</v>
       </c>
       <c r="I10" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J10" t="n">
         <v>56.95</v>
@@ -1287,7 +1287,7 @@
         <v>-2.41</v>
       </c>
       <c r="I11" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J11" t="n">
         <v>56.83</v>
@@ -1366,7 +1366,7 @@
         <v>-2.53</v>
       </c>
       <c r="I12" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J12" t="n">
         <v>56.8</v>
@@ -1441,7 +1441,7 @@
         <v>0.45</v>
       </c>
       <c r="I13" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J13" t="n">
         <v>56.7</v>
@@ -1516,7 +1516,7 @@
         <v>-5.51</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>56.47</v>
@@ -1595,7 +1595,7 @@
         <v>3.08</v>
       </c>
       <c r="I15" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J15" t="n">
         <v>56.29</v>
@@ -1670,7 +1670,7 @@
         <v>-4.27</v>
       </c>
       <c r="I16" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J16" t="n">
         <v>56.01</v>
@@ -1749,7 +1749,7 @@
         <v>-0.74</v>
       </c>
       <c r="I17" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J17" t="n">
         <v>55.76</v>
@@ -1828,7 +1828,7 @@
         <v>2.61</v>
       </c>
       <c r="I18" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J18" t="n">
         <v>55.51</v>
@@ -1903,7 +1903,7 @@
         <v>-5.49</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>55.08</v>
@@ -1982,7 +1982,7 @@
         <v>1.39</v>
       </c>
       <c r="I20" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J20" t="n">
         <v>54.67</v>
@@ -2061,7 +2061,7 @@
         <v>-7.59</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>54.14</v>
@@ -2144,7 +2144,7 @@
         <v>-0.73</v>
       </c>
       <c r="I22" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J22" t="n">
         <v>53.53</v>
@@ -2227,7 +2227,7 @@
         <v>2.31</v>
       </c>
       <c r="I23" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J23" t="n">
         <v>52.98</v>
@@ -2306,7 +2306,7 @@
         <v>-3.65</v>
       </c>
       <c r="I24" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J24" t="n">
         <v>52.35</v>
@@ -2385,7 +2385,7 @@
         <v>4.76</v>
       </c>
       <c r="I25" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J25" t="n">
         <v>51.74</v>
@@ -2460,7 +2460,7 @@
         <v>1.29</v>
       </c>
       <c r="I26" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J26" t="n">
         <v>51.14</v>
@@ -2535,7 +2535,7 @@
         <v>-3.38</v>
       </c>
       <c r="I27" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J27" t="n">
         <v>50.44</v>
@@ -2610,7 +2610,7 @@
         <v>2.53</v>
       </c>
       <c r="I28" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J28" t="n">
         <v>49.8</v>
@@ -2685,7 +2685,7 @@
         <v>-0.67</v>
       </c>
       <c r="I29" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J29" t="n">
         <v>49.18</v>
@@ -2760,7 +2760,7 @@
         <v>0.71</v>
       </c>
       <c r="I30" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J30" t="n">
         <v>48.69</v>
@@ -2835,7 +2835,7 @@
         <v>4.22</v>
       </c>
       <c r="I31" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J31" t="n">
         <v>48.37</v>
@@ -2910,7 +2910,7 @@
         <v>1.19</v>
       </c>
       <c r="I32" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J32" t="n">
         <v>48.14</v>
@@ -2985,7 +2985,7 @@
         <v>-3.68</v>
       </c>
       <c r="I33" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J33" t="n">
         <v>47.82</v>
@@ -3064,7 +3064,7 @@
         <v>-1.18</v>
       </c>
       <c r="I34" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J34" t="n">
         <v>47.61</v>
@@ -3110,77 +3110,77 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>QLD</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>2025-03-28</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" s="4" t="n">
         <v>46.44</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="4" t="n">
         <v>46.57</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="4" t="n">
         <v>44.15</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35" s="4" t="n">
         <v>44.34</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G35" s="4" t="n">
         <v>8245800</v>
       </c>
-      <c r="H35" s="3" t="n">
+      <c r="H35" s="5" t="n">
         <v>-5.28</v>
       </c>
-      <c r="I35" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J35" t="n">
+      <c r="I35" s="4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J35" s="4" t="n">
         <v>47.21</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K35" s="4" t="n">
         <v>52.9</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L35" s="4" t="n">
         <v>53.23</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M35" s="4" t="n">
         <v>51.19</v>
       </c>
-      <c r="N35" s="2" t="n">
+      <c r="N35" s="7" t="n">
         <v>47.07</v>
       </c>
-      <c r="O35" t="n">
+      <c r="O35" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="P35" s="4" t="inlineStr">
         <is>
           <t>fear</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q35" s="4" t="inlineStr">
         <is>
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="n">
+      <c r="R35" s="4" t="inlineStr"/>
+      <c r="S35" s="4" t="n">
         <v>4.26</v>
       </c>
-      <c r="T35" s="2" t="n">
+      <c r="T35" s="7" t="n">
         <v>21.6</v>
       </c>
-      <c r="U35" s="1" t="n">
+      <c r="U35" s="6" t="n">
         <v>25.4</v>
       </c>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" s="2" t="n">
+      <c r="V35" s="4" t="inlineStr"/>
+      <c r="W35" s="7" t="n">
         <v>139</v>
       </c>
     </row>
@@ -3214,7 +3214,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J36" t="n">
         <v>46.91</v>
@@ -3289,7 +3289,7 @@
         <v>1.58</v>
       </c>
       <c r="I37" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J37" t="n">
         <v>46.67</v>
@@ -3364,7 +3364,7 @@
         <v>1.44</v>
       </c>
       <c r="I38" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J38" t="n">
         <v>46.39</v>
@@ -3439,7 +3439,7 @@
         <v>-10.69</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>46.01</v>
@@ -3518,7 +3518,7 @@
         <v>-12.21</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>45.35</v>
@@ -3601,7 +3601,7 @@
         <v>0.31</v>
       </c>
       <c r="I41" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J41" t="n">
         <v>44.88</v>
@@ -3684,7 +3684,7 @@
         <v>-3.73</v>
       </c>
       <c r="I42" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J42" t="n">
         <v>44.36</v>
@@ -3767,7 +3767,7 @@
         <v>23.49</v>
       </c>
       <c r="I43" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J43" t="n">
         <v>44.19</v>
@@ -3846,7 +3846,7 @@
         <v>-8.18</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>43.94</v>
@@ -3925,7 +3925,7 @@
         <v>3.55</v>
       </c>
       <c r="I45" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J45" t="n">
         <v>43.64</v>
@@ -4004,7 +4004,7 @@
         <v>1.38</v>
       </c>
       <c r="I46" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J46" t="n">
         <v>43.35</v>
@@ -4079,7 +4079,7 @@
         <v>0.24</v>
       </c>
       <c r="I47" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J47" t="n">
         <v>43.14</v>
@@ -4154,7 +4154,7 @@
         <v>-6.01</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>42.75</v>
@@ -4233,7 +4233,7 @@
         <v>-0.15</v>
       </c>
       <c r="I49" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J49" t="n">
         <v>42.37</v>
@@ -4312,7 +4312,7 @@
         <v>-4.91</v>
       </c>
       <c r="I50" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J50" t="n">
         <v>41.88</v>
@@ -4387,7 +4387,7 @@
         <v>5.11</v>
       </c>
       <c r="I51" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J51" t="n">
         <v>41.38</v>
@@ -4462,7 +4462,7 @@
         <v>4.45</v>
       </c>
       <c r="I52" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J52" t="n">
         <v>40.94</v>
@@ -4541,7 +4541,7 @@
         <v>5.69</v>
       </c>
       <c r="I53" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J53" t="n">
         <v>40.71</v>
@@ -4616,7 +4616,7 @@
         <v>2.2</v>
       </c>
       <c r="I54" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J54" t="n">
         <v>40.55</v>
@@ -4691,7 +4691,7 @@
         <v>-0.05</v>
       </c>
       <c r="I55" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J55" t="n">
         <v>40.52</v>
@@ -4766,7 +4766,7 @@
         <v>1.24</v>
       </c>
       <c r="I56" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J56" t="n">
         <v>40.51</v>
@@ -4841,7 +4841,7 @@
         <v>-0.02</v>
       </c>
       <c r="I57" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J57" t="n">
         <v>40.47</v>
@@ -4916,7 +4916,7 @@
         <v>2.45</v>
       </c>
       <c r="I58" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J58" t="n">
         <v>40.44</v>
@@ -4991,7 +4991,7 @@
         <v>3.09</v>
       </c>
       <c r="I59" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J59" t="n">
         <v>40.74</v>
@@ -5066,7 +5066,7 @@
         <v>-1.18</v>
       </c>
       <c r="I60" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J60" t="n">
         <v>41.25</v>
@@ -5141,7 +5141,7 @@
         <v>-1.84</v>
       </c>
       <c r="I61" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J61" t="n">
         <v>41.72</v>
@@ -5216,7 +5216,7 @@
         <v>0.75</v>
       </c>
       <c r="I62" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J62" t="n">
         <v>42.27</v>
@@ -5291,7 +5291,7 @@
         <v>2</v>
       </c>
       <c r="I63" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J63" t="n">
         <v>42.46</v>
@@ -5366,7 +5366,7 @@
         <v>-0.17</v>
       </c>
       <c r="I64" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J64" t="n">
         <v>42.82</v>
@@ -5441,7 +5441,7 @@
         <v>8.140000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J65" t="n">
         <v>43.3</v>
@@ -5516,7 +5516,7 @@
         <v>3.01</v>
       </c>
       <c r="I66" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J66" t="n">
         <v>43.83</v>
@@ -5591,7 +5591,7 @@
         <v>1.18</v>
       </c>
       <c r="I67" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J67" t="n">
         <v>44.38</v>
@@ -5666,7 +5666,7 @@
         <v>0.23</v>
       </c>
       <c r="I68" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J68" t="n">
         <v>45.06</v>
@@ -5741,7 +5741,7 @@
         <v>0.86</v>
       </c>
       <c r="I69" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J69" t="n">
         <v>45.77</v>
@@ -5816,7 +5816,7 @@
         <v>0.13</v>
       </c>
       <c r="I70" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J70" t="n">
         <v>46.58</v>
@@ -5891,7 +5891,7 @@
         <v>-0.72</v>
       </c>
       <c r="I71" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J71" t="n">
         <v>47.27</v>
@@ -5966,7 +5966,7 @@
         <v>-2.78</v>
       </c>
       <c r="I72" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J72" t="n">
         <v>47.81</v>
@@ -6041,7 +6041,7 @@
         <v>0.37</v>
       </c>
       <c r="I73" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J73" t="n">
         <v>48.24</v>
@@ -6116,7 +6116,7 @@
         <v>-1.89</v>
       </c>
       <c r="I74" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J74" t="n">
         <v>48.57</v>
@@ -6195,7 +6195,7 @@
         <v>4.63</v>
       </c>
       <c r="I75" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J75" t="n">
         <v>49.02</v>
@@ -6270,7 +6270,7 @@
         <v>-0.85</v>
       </c>
       <c r="I76" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J76" t="n">
         <v>49.42</v>
@@ -6345,7 +6345,7 @@
         <v>0.36</v>
       </c>
       <c r="I77" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J77" t="n">
         <v>49.84</v>
@@ -6420,7 +6420,7 @@
         <v>-0.36</v>
       </c>
       <c r="I78" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J78" t="n">
         <v>50.18</v>
@@ -6495,7 +6495,7 @@
         <v>1.55</v>
       </c>
       <c r="I79" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J79" t="n">
         <v>50.5</v>
@@ -6570,7 +6570,7 @@
         <v>1.58</v>
       </c>
       <c r="I80" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J80" t="n">
         <v>50.89</v>
@@ -6645,7 +6645,7 @@
         <v>0.52</v>
       </c>
       <c r="I81" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J81" t="n">
         <v>51.34</v>
@@ -6720,7 +6720,7 @@
         <v>-1.57</v>
       </c>
       <c r="I82" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J82" t="n">
         <v>51.72</v>
@@ -6795,7 +6795,7 @@
         <v>1.93</v>
       </c>
       <c r="I83" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J83" t="n">
         <v>52.11</v>
@@ -6870,7 +6870,7 @@
         <v>0.28</v>
       </c>
       <c r="I84" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J84" t="n">
         <v>52.52</v>
@@ -6945,7 +6945,7 @@
         <v>1.34</v>
       </c>
       <c r="I85" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J85" t="n">
         <v>52.77</v>
@@ -7020,7 +7020,7 @@
         <v>-0.71</v>
       </c>
       <c r="I86" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J86" t="n">
         <v>52.92</v>
@@ -7095,7 +7095,7 @@
         <v>0.46</v>
       </c>
       <c r="I87" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J87" t="n">
         <v>53.06</v>
@@ -7170,7 +7170,7 @@
         <v>-2.56</v>
       </c>
       <c r="I88" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J88" t="n">
         <v>53.12</v>
@@ -7245,7 +7245,7 @@
         <v>2.76</v>
       </c>
       <c r="I89" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J89" t="n">
         <v>53.23</v>
@@ -7320,7 +7320,7 @@
         <v>-2</v>
       </c>
       <c r="I90" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J90" t="n">
         <v>53.29</v>
@@ -7395,7 +7395,7 @@
         <v>-0.06</v>
       </c>
       <c r="I91" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J91" t="n">
         <v>53.36</v>
@@ -7470,7 +7470,7 @@
         <v>-0.89</v>
       </c>
       <c r="I92" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J92" t="n">
         <v>53.48</v>
@@ -7545,7 +7545,7 @@
         <v>2.09</v>
       </c>
       <c r="I93" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J93" t="n">
         <v>53.65</v>
@@ -7620,7 +7620,7 @@
         <v>3.02</v>
       </c>
       <c r="I94" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J94" t="n">
         <v>53.95</v>
@@ -7695,7 +7695,7 @@
         <v>0.48</v>
       </c>
       <c r="I95" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J95" t="n">
         <v>54.14</v>
@@ -7770,7 +7770,7 @@
         <v>1.89</v>
       </c>
       <c r="I96" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J96" t="n">
         <v>54.41</v>
@@ -7845,7 +7845,7 @@
         <v>0.66</v>
       </c>
       <c r="I97" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J97" t="n">
         <v>54.69</v>
@@ -7920,7 +7920,7 @@
         <v>1.28</v>
       </c>
       <c r="I98" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J98" t="n">
         <v>55.02</v>
@@ -7995,7 +7995,7 @@
         <v>-1.74</v>
       </c>
       <c r="I99" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J99" t="n">
         <v>55.25</v>
@@ -8070,7 +8070,7 @@
         <v>1.4</v>
       </c>
       <c r="I100" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J100" t="n">
         <v>55.49</v>
@@ -8145,7 +8145,7 @@
         <v>1.88</v>
       </c>
       <c r="I101" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J101" t="n">
         <v>55.76</v>
@@ -8220,7 +8220,7 @@
         <v>-1.49</v>
       </c>
       <c r="I102" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J102" t="n">
         <v>56.04</v>
@@ -8295,7 +8295,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I103" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J103" t="n">
         <v>56.26</v>
@@ -8370,7 +8370,7 @@
         <v>1.41</v>
       </c>
       <c r="I104" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J104" t="n">
         <v>56.52</v>
@@ -8445,7 +8445,7 @@
         <v>-0.32</v>
       </c>
       <c r="I105" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J105" t="n">
         <v>56.73</v>
@@ -8520,7 +8520,7 @@
         <v>-0.47</v>
       </c>
       <c r="I106" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J106" t="n">
         <v>56.95</v>
@@ -8595,7 +8595,7 @@
         <v>0.68</v>
       </c>
       <c r="I107" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J107" t="n">
         <v>57.17</v>
@@ -8670,13 +8670,13 @@
         <v>0.15</v>
       </c>
       <c r="I108" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J108" t="n">
         <v>57.47</v>
       </c>
       <c r="K108" t="n">
-        <v>51.88</v>
+        <v>51.89</v>
       </c>
       <c r="L108" t="n">
         <v>50.87</v>
@@ -8745,7 +8745,7 @@
         <v>0.22</v>
       </c>
       <c r="I109" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J109" t="n">
         <v>57.7</v>
@@ -8820,7 +8820,7 @@
         <v>1.61</v>
       </c>
       <c r="I110" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J110" t="n">
         <v>58.04</v>
@@ -8895,7 +8895,7 @@
         <v>-0.25</v>
       </c>
       <c r="I111" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J111" t="n">
         <v>58.37</v>
@@ -8970,7 +8970,7 @@
         <v>1.02</v>
       </c>
       <c r="I112" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J112" t="n">
         <v>58.75</v>
@@ -9045,7 +9045,7 @@
         <v>-1.05</v>
       </c>
       <c r="I113" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J113" t="n">
         <v>59.05</v>
@@ -9120,7 +9120,7 @@
         <v>0.89</v>
       </c>
       <c r="I114" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J114" t="n">
         <v>59.29</v>
@@ -9195,7 +9195,7 @@
         <v>0.44</v>
       </c>
       <c r="I115" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J115" t="n">
         <v>59.53</v>
@@ -9270,7 +9270,7 @@
         <v>0.41</v>
       </c>
       <c r="I116" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J116" t="n">
         <v>59.73</v>
@@ -9345,7 +9345,7 @@
         <v>0.63</v>
       </c>
       <c r="I117" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J117" t="n">
         <v>59.93</v>
@@ -9420,7 +9420,7 @@
         <v>-0.31</v>
       </c>
       <c r="I118" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J118" t="n">
         <v>60.08</v>
@@ -9495,7 +9495,7 @@
         <v>0.24</v>
       </c>
       <c r="I119" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J119" t="n">
         <v>60.29</v>
@@ -9570,7 +9570,7 @@
         <v>-1.11</v>
       </c>
       <c r="I120" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J120" t="n">
         <v>60.43</v>
@@ -9645,7 +9645,7 @@
         <v>-4</v>
       </c>
       <c r="I121" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J121" t="n">
         <v>60.39</v>
@@ -9724,7 +9724,7 @@
         <v>3.67</v>
       </c>
       <c r="I122" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J122" t="n">
         <v>60.5</v>
@@ -9799,7 +9799,7 @@
         <v>-1.38</v>
       </c>
       <c r="I123" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J123" t="n">
         <v>60.57</v>
@@ -9878,7 +9878,7 @@
         <v>2.51</v>
       </c>
       <c r="I124" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J124" t="n">
         <v>60.67</v>
@@ -9953,7 +9953,7 @@
         <v>0.66</v>
       </c>
       <c r="I125" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J125" t="n">
         <v>60.8</v>
@@ -10028,7 +10028,7 @@
         <v>1.82</v>
       </c>
       <c r="I126" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J126" t="n">
         <v>61</v>
@@ -10103,7 +10103,7 @@
         <v>-0.65</v>
       </c>
       <c r="I127" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J127" t="n">
         <v>61.17</v>
@@ -10178,7 +10178,7 @@
         <v>2.55</v>
       </c>
       <c r="I128" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J128" t="n">
         <v>61.4</v>
@@ -10253,7 +10253,7 @@
         <v>0.08</v>
       </c>
       <c r="I129" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J129" t="n">
         <v>61.64</v>
@@ -10328,7 +10328,7 @@
         <v>-0.19</v>
       </c>
       <c r="I130" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J130" t="n">
         <v>61.82</v>
@@ -10403,7 +10403,7 @@
         <v>-0.93</v>
       </c>
       <c r="I131" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J131" t="n">
         <v>61.97</v>
@@ -10478,7 +10478,7 @@
         <v>-0.06</v>
       </c>
       <c r="I132" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J132" t="n">
         <v>62.1</v>
@@ -10553,7 +10553,7 @@
         <v>-2.75</v>
       </c>
       <c r="I133" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J133" t="n">
         <v>62.17</v>
@@ -10632,7 +10632,7 @@
         <v>-1.21</v>
       </c>
       <c r="I134" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J134" t="n">
         <v>62.17</v>
@@ -10707,7 +10707,7 @@
         <v>-0.92</v>
       </c>
       <c r="I135" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J135" t="n">
         <v>62.13</v>
@@ -10782,7 +10782,7 @@
         <v>3.04</v>
       </c>
       <c r="I136" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J136" t="n">
         <v>62.18</v>
@@ -10857,7 +10857,7 @@
         <v>-0.61</v>
       </c>
       <c r="I137" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J137" t="n">
         <v>62.18</v>
@@ -10936,7 +10936,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I138" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J138" t="n">
         <v>62.22</v>
@@ -11011,7 +11011,7 @@
         <v>0.29</v>
       </c>
       <c r="I139" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J139" t="n">
         <v>62.26</v>
@@ -11086,7 +11086,7 @@
         <v>1.21</v>
       </c>
       <c r="I140" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J140" t="n">
         <v>62.37</v>
@@ -11161,7 +11161,7 @@
         <v>-2.39</v>
       </c>
       <c r="I141" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J141" t="n">
         <v>62.53</v>
@@ -11240,7 +11240,7 @@
         <v>-1.66</v>
       </c>
       <c r="I142" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J142" t="n">
         <v>62.53</v>
@@ -11315,7 +11315,7 @@
         <v>1.53</v>
       </c>
       <c r="I143" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J143" t="n">
         <v>62.61</v>
@@ -11390,7 +11390,7 @@
         <v>1.83</v>
       </c>
       <c r="I144" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J144" t="n">
         <v>62.68</v>
@@ -11465,7 +11465,7 @@
         <v>0.22</v>
       </c>
       <c r="I145" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J145" t="n">
         <v>62.74</v>
@@ -11540,7 +11540,7 @@
         <v>0.98</v>
       </c>
       <c r="I146" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J146" t="n">
         <v>62.77</v>
@@ -11615,7 +11615,7 @@
         <v>0.53</v>
       </c>
       <c r="I147" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J147" t="n">
         <v>62.83</v>
@@ -11690,7 +11690,7 @@
         <v>0.06</v>
       </c>
       <c r="I148" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J148" t="n">
         <v>62.82</v>
@@ -11765,7 +11765,7 @@
         <v>1.14</v>
       </c>
       <c r="I149" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J149" t="n">
         <v>62.85</v>
@@ -11840,7 +11840,7 @@
         <v>0.86</v>
       </c>
       <c r="I150" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J150" t="n">
         <v>62.9</v>
@@ -11915,7 +11915,7 @@
         <v>1.7</v>
       </c>
       <c r="I151" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J151" t="n">
         <v>63.04</v>
@@ -11990,7 +11990,7 @@
         <v>-0.23</v>
       </c>
       <c r="I152" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J152" t="n">
         <v>63.18</v>
@@ -12065,7 +12065,7 @@
         <v>-0.42</v>
       </c>
       <c r="I153" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J153" t="n">
         <v>63.39</v>
@@ -12140,7 +12140,7 @@
         <v>1.84</v>
       </c>
       <c r="I154" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J154" t="n">
         <v>63.7</v>
@@ -12215,7 +12215,7 @@
         <v>1.31</v>
       </c>
       <c r="I155" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J155" t="n">
         <v>64.08</v>
@@ -12290,7 +12290,7 @@
         <v>1.16</v>
       </c>
       <c r="I156" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J156" t="n">
         <v>64.41</v>
@@ -12365,7 +12365,7 @@
         <v>-1.35</v>
       </c>
       <c r="I157" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J157" t="n">
         <v>64.70999999999999</v>
@@ -12440,7 +12440,7 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="I158" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J158" t="n">
         <v>64.95999999999999</v>
@@ -12515,7 +12515,7 @@
         <v>-0.9</v>
       </c>
       <c r="I159" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J159" t="n">
         <v>65.18000000000001</v>
@@ -12590,7 +12590,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I160" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J160" t="n">
         <v>65.38</v>
@@ -12665,7 +12665,7 @@
         <v>0.89</v>
       </c>
       <c r="I161" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J161" t="n">
         <v>65.69</v>
@@ -12740,7 +12740,7 @@
         <v>0.5</v>
       </c>
       <c r="I162" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J162" t="n">
         <v>66.06</v>
@@ -12815,7 +12815,7 @@
         <v>0.96</v>
       </c>
       <c r="I163" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J163" t="n">
         <v>66.43000000000001</v>
@@ -12890,7 +12890,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I164" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J164" t="n">
         <v>66.76000000000001</v>
@@ -12965,7 +12965,7 @@
         <v>-0.9</v>
       </c>
       <c r="I165" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J165" t="n">
         <v>67.06</v>
@@ -13040,7 +13040,7 @@
         <v>1.51</v>
       </c>
       <c r="I166" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J166" t="n">
         <v>67.37</v>
@@ -13115,7 +13115,7 @@
         <v>-1.07</v>
       </c>
       <c r="I167" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J167" t="n">
         <v>67.64</v>
@@ -13190,7 +13190,7 @@
         <v>2.28</v>
       </c>
       <c r="I168" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J168" t="n">
         <v>67.98</v>
@@ -13265,7 +13265,7 @@
         <v>-0.27</v>
       </c>
       <c r="I169" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J169" t="n">
         <v>68.27</v>
@@ -13340,7 +13340,7 @@
         <v>-7.01</v>
       </c>
       <c r="I170" s="4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>68.29000000000001</v>
@@ -13419,7 +13419,7 @@
         <v>4.25</v>
       </c>
       <c r="I171" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J171" t="n">
         <v>68.39</v>
@@ -13494,7 +13494,7 @@
         <v>-1.33</v>
       </c>
       <c r="I172" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J172" t="n">
         <v>68.45</v>
@@ -13573,7 +13573,7 @@
         <v>1.36</v>
       </c>
       <c r="I173" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J173" t="n">
         <v>68.58</v>
@@ -13648,7 +13648,7 @@
         <v>-0.74</v>
       </c>
       <c r="I174" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J174" t="n">
         <v>68.61</v>
@@ -13727,7 +13727,7 @@
         <v>1.28</v>
       </c>
       <c r="I175" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J175" t="n">
         <v>68.65000000000001</v>
@@ -13802,7 +13802,7 @@
         <v>2.49</v>
       </c>
       <c r="I176" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J176" t="n">
         <v>68.73999999999999</v>
@@ -13877,7 +13877,7 @@
         <v>-0.06</v>
       </c>
       <c r="I177" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J177" t="n">
         <v>68.86</v>
@@ -13952,7 +13952,7 @@
         <v>-1.98</v>
       </c>
       <c r="I178" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J178" t="n">
         <v>68.95</v>
@@ -14027,7 +14027,7 @@
         <v>1.72</v>
       </c>
       <c r="I179" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J179" t="n">
         <v>69.12</v>
@@ -14102,7 +14102,7 @@
         <v>2.03</v>
       </c>
       <c r="I180" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J180" t="n">
         <v>69.33</v>
@@ -14177,7 +14177,7 @@
         <v>3.59</v>
       </c>
       <c r="I181" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J181" t="n">
         <v>69.65000000000001</v>
@@ -14252,7 +14252,7 @@
         <v>1.5</v>
       </c>
       <c r="I182" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J182" t="n">
         <v>70</v>
@@ -14327,7 +14327,7 @@
         <v>0.91</v>
       </c>
       <c r="I183" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J183" t="n">
         <v>70.36</v>
@@ -14402,7 +14402,7 @@
         <v>-3.08</v>
       </c>
       <c r="I184" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J184" t="n">
         <v>70.56999999999999</v>
@@ -14477,7 +14477,7 @@
         <v>0.96</v>
       </c>
       <c r="I185" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J185" t="n">
         <v>70.84</v>
@@ -14552,7 +14552,7 @@
         <v>0.9</v>
       </c>
       <c r="I186" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J186" t="n">
         <v>71.09999999999999</v>
@@ -14627,7 +14627,7 @@
         <v>-4.1</v>
       </c>
       <c r="I187" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J187" t="n">
         <v>71.23999999999999</v>
@@ -14702,7 +14702,7 @@
         <v>1.32</v>
       </c>
       <c r="I188" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J188" t="n">
         <v>71.34999999999999</v>
@@ -14777,7 +14777,7 @@
         <v>-3.73</v>
       </c>
       <c r="I189" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J189" t="n">
         <v>71.34</v>
@@ -14856,7 +14856,7 @@
         <v>-0.68</v>
       </c>
       <c r="I190" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J190" t="n">
         <v>71.54000000000001</v>
@@ -14931,7 +14931,7 @@
         <v>4.39</v>
       </c>
       <c r="I191" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J191" t="n">
         <v>71.76000000000001</v>
@@ -15006,7 +15006,7 @@
         <v>-0.53</v>
       </c>
       <c r="I192" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J192" t="n">
         <v>72.01000000000001</v>
@@ -15081,7 +15081,7 @@
         <v>-0.18</v>
       </c>
       <c r="I193" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J193" t="n">
         <v>72.2</v>
@@ -15156,7 +15156,7 @@
         <v>-4.11</v>
       </c>
       <c r="I194" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J194" t="n">
         <v>72.28</v>
@@ -15235,7 +15235,7 @@
         <v>0.1</v>
       </c>
       <c r="I195" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J195" t="n">
         <v>72.31</v>
@@ -15310,7 +15310,7 @@
         <v>-1.71</v>
       </c>
       <c r="I196" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J196" t="n">
         <v>72.19</v>
@@ -15389,7 +15389,7 @@
         <v>-2.43</v>
       </c>
       <c r="I197" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J197" t="n">
         <v>71.98999999999999</v>
@@ -15464,7 +15464,7 @@
         <v>1.14</v>
       </c>
       <c r="I198" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J198" t="n">
         <v>71.91</v>
@@ -15539,7 +15539,7 @@
         <v>-4.71</v>
       </c>
       <c r="I199" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J199" t="n">
         <v>71.59999999999999</v>
@@ -15618,7 +15618,7 @@
         <v>1.46</v>
       </c>
       <c r="I200" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J200" t="n">
         <v>71.27</v>
@@ -15693,7 +15693,7 @@
         <v>5.16</v>
       </c>
       <c r="I201" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J201" t="n">
         <v>70.98</v>
@@ -15768,7 +15768,7 @@
         <v>1.14</v>
       </c>
       <c r="I202" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J202" t="n">
         <v>70.67</v>
@@ -15843,7 +15843,7 @@
         <v>1.77</v>
       </c>
       <c r="I203" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J203" t="n">
         <v>70.39</v>
@@ -15918,7 +15918,7 @@
         <v>1.5</v>
       </c>
       <c r="I204" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J204" t="n">
         <v>70.28</v>
@@ -15993,7 +15993,7 @@
         <v>-0.63</v>
       </c>
       <c r="I205" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J205" t="n">
         <v>70.11</v>
@@ -16068,7 +16068,7 @@
         <v>1.56</v>
       </c>
       <c r="I206" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J206" t="n">
         <v>69.95999999999999</v>
@@ -16143,7 +16143,7 @@
         <v>0.44</v>
       </c>
       <c r="I207" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J207" t="n">
         <v>69.98</v>
@@ -16218,7 +16218,7 @@
         <v>-0.23</v>
       </c>
       <c r="I208" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J208" t="n">
         <v>69.95</v>
@@ -16293,7 +16293,7 @@
         <v>0.83</v>
       </c>
       <c r="I209" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J209" t="n">
         <v>70.09</v>
@@ -16368,7 +16368,7 @@
         <v>-0.45</v>
       </c>
       <c r="I210" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J210" t="n">
         <v>70.23</v>
@@ -16443,7 +16443,7 @@
         <v>0.29</v>
       </c>
       <c r="I211" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J211" t="n">
         <v>70.23</v>
@@ -16518,7 +16518,7 @@
         <v>0.77</v>
       </c>
       <c r="I212" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J212" t="n">
         <v>70.27</v>
@@ -16593,7 +16593,7 @@
         <v>-0.65</v>
       </c>
       <c r="I213" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J213" t="n">
         <v>70.3</v>
@@ -16668,7 +16668,7 @@
         <v>-3.87</v>
       </c>
       <c r="I214" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J214" t="n">
         <v>70.34</v>
@@ -16747,7 +16747,7 @@
         <v>-1.01</v>
       </c>
       <c r="I215" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J215" t="n">
         <v>70.33</v>
@@ -16822,7 +16822,7 @@
         <v>0.39</v>
       </c>
       <c r="I216" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J216" t="n">
         <v>70.40000000000001</v>
@@ -16897,7 +16897,7 @@
         <v>-3.75</v>
       </c>
       <c r="I217" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J217" t="n">
         <v>70.43000000000001</v>
@@ -16972,7 +16972,7 @@
         <v>2.92</v>
       </c>
       <c r="I218" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J218" t="n">
         <v>70.51000000000001</v>
@@ -17047,7 +17047,7 @@
         <v>2.62</v>
       </c>
       <c r="I219" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J219" t="n">
         <v>70.84</v>
@@ -17122,7 +17122,7 @@
         <v>0.86</v>
       </c>
       <c r="I220" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J220" t="n">
         <v>71.15000000000001</v>
@@ -17197,7 +17197,7 @@
         <v>0.96</v>
       </c>
       <c r="I221" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J221" t="n">
         <v>71.34</v>
@@ -17272,7 +17272,7 @@
         <v>0.55</v>
       </c>
       <c r="I222" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J222" t="n">
         <v>71.5</v>
@@ -17347,7 +17347,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="I223" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J223" t="n">
         <v>71.59999999999999</v>
@@ -17422,7 +17422,7 @@
         <v>-0.99</v>
       </c>
       <c r="I224" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J224" t="n">
         <v>71.59999999999999</v>
@@ -17497,7 +17497,7 @@
         <v>-0.49</v>
       </c>
       <c r="I225" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J225" t="n">
         <v>71.62</v>
@@ -17576,7 +17576,7 @@
         <v>-1.68</v>
       </c>
       <c r="I226" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J226" t="n">
         <v>71.52</v>
@@ -17655,7 +17655,7 @@
         <v>-0.44</v>
       </c>
       <c r="I227" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J227" t="n">
         <v>71.38</v>
@@ -17730,7 +17730,7 @@
         <v>1.57</v>
       </c>
       <c r="I228" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J228" t="n">
         <v>71.31</v>
@@ -17805,7 +17805,7 @@
         <v>1.77</v>
       </c>
       <c r="I229" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J229" t="n">
         <v>71.28</v>
@@ -17880,7 +17880,7 @@
         <v>0.18</v>
       </c>
       <c r="I230" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J230" t="n">
         <v>71.26000000000001</v>
@@ -17955,7 +17955,7 @@
         <v>-1.16</v>
       </c>
       <c r="I231" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J231" t="n">
         <v>71.2</v>
@@ -18030,7 +18030,7 @@
         <v>1.94</v>
       </c>
       <c r="I232" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J232" t="n">
         <v>71.17</v>
@@ -18105,7 +18105,7 @@
         <v>0.18</v>
       </c>
       <c r="I233" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J233" t="n">
         <v>71.18000000000001</v>
@@ -18180,7 +18180,7 @@
         <v>-0.36</v>
       </c>
       <c r="I234" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J234" t="n">
         <v>71.31</v>
@@ -18255,7 +18255,7 @@
         <v>-2.08</v>
       </c>
       <c r="I235" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J235" t="n">
         <v>71.41</v>
@@ -18330,7 +18330,7 @@
         <v>0.63</v>
       </c>
       <c r="I236" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J236" t="n">
         <v>71.51000000000001</v>
@@ -18405,7 +18405,7 @@
         <v>-0.26</v>
       </c>
       <c r="I237" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J237" t="n">
         <v>71.73999999999999</v>
@@ -18484,7 +18484,7 @@
         <v>-4.21</v>
       </c>
       <c r="I238" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J238" t="n">
         <v>71.70999999999999</v>
@@ -18563,7 +18563,7 @@
         <v>2.64</v>
       </c>
       <c r="I239" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J239" t="n">
         <v>71.69</v>
@@ -18638,7 +18638,7 @@
         <v>1.52</v>
       </c>
       <c r="I240" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J240" t="n">
         <v>71.68000000000001</v>
@@ -18713,7 +18713,7 @@
         <v>0.62</v>
       </c>
       <c r="I241" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J241" t="n">
         <v>71.67</v>
@@ -18788,7 +18788,7 @@
         <v>0.85</v>
       </c>
       <c r="I242" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J242" t="n">
         <v>71.67</v>
@@ -18863,7 +18863,7 @@
         <v>1.78</v>
       </c>
       <c r="I243" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J243" t="n">
         <v>71.73</v>
@@ -18938,7 +18938,7 @@
         <v>0.54</v>
       </c>
       <c r="I244" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J244" t="n">
         <v>71.84999999999999</v>
@@ -19013,7 +19013,7 @@
         <v>-1.12</v>
       </c>
       <c r="I245" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J245" t="n">
         <v>71.95</v>
@@ -19088,7 +19088,7 @@
         <v>-2.46</v>
       </c>
       <c r="I246" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J246" t="n">
         <v>72.01000000000001</v>
@@ -19167,7 +19167,7 @@
         <v>1.42</v>
       </c>
       <c r="I247" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J247" t="n">
         <v>72.14</v>
@@ -19242,7 +19242,7 @@
         <v>-3.12</v>
       </c>
       <c r="I248" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J248" t="n">
         <v>72.11</v>
@@ -19321,7 +19321,7 @@
         <v>-3.52</v>
       </c>
       <c r="I249" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J249" t="n">
         <v>71.88</v>
@@ -19400,7 +19400,7 @@
         <v>-2.86</v>
       </c>
       <c r="I250" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J250" t="n">
         <v>71.55</v>
@@ -19475,7 +19475,7 @@
         <v>4.17</v>
       </c>
       <c r="I251" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J251" t="n">
         <v>71.41</v>
@@ -19550,7 +19550,7 @@
         <v>1.51</v>
       </c>
       <c r="I252" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J252" t="n">
         <v>71.23999999999999</v>
@@ -19625,7 +19625,7 @@
         <v>-0.93</v>
       </c>
       <c r="I253" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J253" t="n">
         <v>71.04000000000001</v>
@@ -19704,7 +19704,7 @@
         <v>0.49</v>
       </c>
       <c r="I254" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J254" t="n">
         <v>70.86</v>
@@ -19779,7 +19779,7 @@
         <v>-4.08</v>
       </c>
       <c r="I255" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J255" t="n">
         <v>70.62</v>
@@ -19854,7 +19854,7 @@
         <v>0.35</v>
       </c>
       <c r="I256" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J256" t="n">
         <v>70.37</v>
@@ -19929,7 +19929,7 @@
         <v>-0.22</v>
       </c>
       <c r="I257" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J257" t="n">
         <v>70.12</v>
@@ -20004,7 +20004,7 @@
         <v>1.47</v>
       </c>
       <c r="I258" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J258" t="n">
         <v>70.06999999999999</v>
@@ -20079,7 +20079,7 @@
         <v>-0.75</v>
       </c>
       <c r="I259" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J259" t="n">
         <v>69.91</v>
@@ -20154,7 +20154,7 @@
         <v>1.73</v>
       </c>
       <c r="I260" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J260" t="n">
         <v>69.75</v>
@@ -20229,7 +20229,7 @@
         <v>-2.42</v>
       </c>
       <c r="I261" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J261" t="n">
         <v>69.48</v>
@@ -20304,7 +20304,7 @@
         <v>2.07</v>
       </c>
       <c r="I262" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J262" t="n">
         <v>69.26000000000001</v>
@@ -20379,7 +20379,7 @@
         <v>2.87</v>
       </c>
       <c r="I263" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J263" t="n">
         <v>69.06</v>
@@ -20454,7 +20454,7 @@
         <v>-2.34</v>
       </c>
       <c r="I264" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J264" t="n">
         <v>68.77</v>
@@ -20533,7 +20533,7 @@
         <v>-0.66</v>
       </c>
       <c r="I265" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J265" t="n">
         <v>68.48999999999999</v>
@@ -20608,7 +20608,7 @@
         <v>0.21</v>
       </c>
       <c r="I266" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J266" t="n">
         <v>68.31</v>
@@ -20683,7 +20683,7 @@
         <v>-2.13</v>
       </c>
       <c r="I267" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J267" t="n">
         <v>68.01000000000001</v>
@@ -20758,7 +20758,7 @@
         <v>2.96</v>
       </c>
       <c r="I268" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J268" t="n">
         <v>67.92</v>
@@ -20833,7 +20833,7 @@
         <v>-0.57</v>
       </c>
       <c r="I269" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J269" t="n">
         <v>67.93000000000001</v>
@@ -20908,7 +20908,7 @@
         <v>-3.04</v>
       </c>
       <c r="I270" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J270" t="n">
         <v>67.94</v>
@@ -20991,7 +20991,7 @@
         <v>2.65</v>
       </c>
       <c r="I271" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J271" t="n">
         <v>67.90000000000001</v>
@@ -21066,7 +21066,7 @@
         <v>-0.04</v>
       </c>
       <c r="I272" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J272" t="n">
         <v>67.8</v>
@@ -21141,7 +21141,7 @@
         <v>-0.01</v>
       </c>
       <c r="I273" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J273" t="n">
         <v>67.73999999999999</v>
@@ -21216,7 +21216,7 @@
         <v>-3.42</v>
       </c>
       <c r="I274" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J274" t="n">
         <v>67.54000000000001</v>
@@ -21289,7 +21289,7 @@
         <v>-1.24</v>
       </c>
       <c r="I275" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J275" t="n">
         <v>67.44</v>
@@ -21368,7 +21368,7 @@
         <v>2.2</v>
       </c>
       <c r="I276" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J276" t="n">
         <v>67.41</v>
@@ -21443,7 +21443,7 @@
         <v>1</v>
       </c>
       <c r="I277" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J277" t="n">
         <v>67.41</v>
@@ -21518,7 +21518,7 @@
         <v>-2.83</v>
       </c>
       <c r="I278" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J278" t="n">
         <v>67.27</v>
@@ -21593,7 +21593,7 @@
         <v>-0.65</v>
       </c>
       <c r="I279" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J279" t="n">
         <v>67.14</v>
@@ -21668,7 +21668,7 @@
         <v>-3.72</v>
       </c>
       <c r="I280" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J280" t="n">
         <v>66.81999999999999</v>
@@ -21747,7 +21747,7 @@
         <v>2.34</v>
       </c>
       <c r="I281" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J281" t="n">
         <v>66.67</v>
@@ -21822,7 +21822,7 @@
         <v>-1.48</v>
       </c>
       <c r="I282" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J282" t="n">
         <v>66.39</v>
@@ -21897,7 +21897,7 @@
         <v>1.28</v>
       </c>
       <c r="I283" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J283" t="n">
         <v>66.06</v>
@@ -21972,7 +21972,7 @@
         <v>-4.73</v>
       </c>
       <c r="I284" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J284" t="n">
         <v>65.66</v>
@@ -22047,7 +22047,7 @@
         <v>-3.93</v>
       </c>
       <c r="I285" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J285" t="n">
         <v>65.17</v>
@@ -22130,7 +22130,7 @@
         <v>-1.53</v>
       </c>
       <c r="I286" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J286" t="n">
         <v>64.62</v>
@@ -22209,7 +22209,7 @@
         <v>6.71</v>
       </c>
       <c r="I287" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J287" t="n">
         <v>64.34</v>
@@ -22284,7 +22284,7 @@
         <v>2.45</v>
       </c>
       <c r="I288" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J288" t="n">
         <v>64.03</v>
@@ -22359,7 +22359,7 @@
         <v>0.18</v>
       </c>
       <c r="I289" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J289" t="n">
         <v>63.75</v>
@@ -22434,7 +22434,7 @@
         <v>1.2</v>
       </c>
       <c r="I290" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J290" t="n">
         <v>63.61</v>
@@ -22509,7 +22509,7 @@
         <v>0.06</v>
       </c>
       <c r="I291" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J291" t="n">
         <v>63.38</v>
@@ -22588,7 +22588,7 @@
         <v>5.83</v>
       </c>
       <c r="I292" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J292" t="n">
         <v>63.34</v>
@@ -22663,10 +22663,10 @@
         <v>1.39</v>
       </c>
       <c r="I293" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J293" t="n">
-        <v>63.34</v>
+        <v>63.35</v>
       </c>
       <c r="K293" t="n">
         <v>67.37</v>
@@ -22738,7 +22738,7 @@
         <v>0.26</v>
       </c>
       <c r="I294" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J294" t="n">
         <v>63.48</v>
@@ -22813,7 +22813,7 @@
         <v>2.04</v>
       </c>
       <c r="I295" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J295" t="n">
         <v>63.72</v>
@@ -22888,7 +22888,7 @@
         <v>3.61</v>
       </c>
       <c r="I296" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J296" t="n">
         <v>64.01000000000001</v>
@@ -22963,7 +22963,7 @@
         <v>2.79</v>
       </c>
       <c r="I297" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J297" t="n">
         <v>64.38</v>
@@ -23038,7 +23038,7 @@
         <v>0.93</v>
       </c>
       <c r="I298" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J298" t="n">
         <v>64.87</v>
@@ -23113,7 +23113,7 @@
         <v>2.58</v>
       </c>
       <c r="I299" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J299" t="n">
         <v>65.48</v>
@@ -23188,7 +23188,7 @@
         <v>-0.6</v>
       </c>
       <c r="I300" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J300" t="n">
         <v>66.19</v>
@@ -23263,7 +23263,7 @@
         <v>-0.79</v>
       </c>
       <c r="I301" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J301" t="n">
         <v>66.79000000000001</v>
@@ -23338,7 +23338,7 @@
         <v>3.32</v>
       </c>
       <c r="I302" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J302" t="n">
         <v>67.56999999999999</v>
@@ -23413,7 +23413,7 @@
         <v>-1.13</v>
       </c>
       <c r="I303" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J303" t="n">
         <v>68.26000000000001</v>
@@ -23488,7 +23488,7 @@
         <v>3.79</v>
       </c>
       <c r="I304" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J304" t="n">
         <v>69.25</v>
@@ -23563,7 +23563,7 @@
         <v>0.06</v>
       </c>
       <c r="I305" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J305" t="n">
         <v>70.36</v>
@@ -23638,7 +23638,7 @@
         <v>-2.01</v>
       </c>
       <c r="I306" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J306" t="n">
         <v>71.44</v>
@@ -23713,7 +23713,7 @@
         <v>1.22</v>
       </c>
       <c r="I307" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J307" t="n">
         <v>72.37</v>
@@ -23788,7 +23788,7 @@
         <v>1.77</v>
       </c>
       <c r="I308" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J308" t="n">
         <v>73.29000000000001</v>
@@ -23863,7 +23863,7 @@
         <v>1.91</v>
       </c>
       <c r="I309" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J309" t="n">
         <v>74.29000000000001</v>
@@ -23938,7 +23938,7 @@
         <v>-0.39</v>
       </c>
       <c r="I310" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J310" t="n">
         <v>75.23999999999999</v>
@@ -24013,7 +24013,7 @@
         <v>2.57</v>
       </c>
       <c r="I311" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J311" t="n">
         <v>76.29000000000001</v>
@@ -24088,7 +24088,7 @@
         <v>4.1</v>
       </c>
       <c r="I312" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J312" t="n">
         <v>77.31999999999999</v>
@@ -24163,7 +24163,7 @@
         <v>-0.22</v>
       </c>
       <c r="I313" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J313" t="n">
         <v>78.31</v>
@@ -24238,7 +24238,7 @@
         <v>4.62</v>
       </c>
       <c r="I314" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J314" t="n">
         <v>79.48</v>
@@ -24313,7 +24313,7 @@
         <v>0.59</v>
       </c>
       <c r="I315" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J315" t="n">
         <v>80.61</v>
@@ -24388,7 +24388,7 @@
         <v>-1.7</v>
       </c>
       <c r="I316" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J316" t="n">
         <v>81.54000000000001</v>
@@ -24463,7 +24463,7 @@
         <v>2.05</v>
       </c>
       <c r="I317" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J317" t="n">
         <v>82.45999999999999</v>
@@ -24538,7 +24538,7 @@
         <v>1.46</v>
       </c>
       <c r="I318" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J318" t="n">
         <v>83.42</v>
@@ -24613,7 +24613,7 @@
         <v>-3.06</v>
       </c>
       <c r="I319" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J319" t="n">
         <v>84.13</v>
@@ -24688,7 +24688,7 @@
         <v>-0.91</v>
       </c>
       <c r="I320" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J320" t="n">
         <v>84.83</v>
@@ -24763,7 +24763,7 @@
         <v>-1.18</v>
       </c>
       <c r="I321" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J321" t="n">
         <v>85.5</v>
@@ -24838,7 +24838,7 @@
         <v>3.27</v>
       </c>
       <c r="I322" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J322" t="n">
         <v>86.19</v>
@@ -24913,7 +24913,7 @@
         <v>0.36</v>
       </c>
       <c r="I323" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J323" t="n">
         <v>86.94</v>
@@ -24988,7 +24988,7 @@
         <v>0.78</v>
       </c>
       <c r="I324" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J324" t="n">
         <v>87.59</v>
@@ -25063,7 +25063,7 @@
         <v>3.55</v>
       </c>
       <c r="I325" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J325" t="n">
         <v>88.39</v>
@@ -25138,7 +25138,7 @@
         <v>-0.22</v>
       </c>
       <c r="I326" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J326" t="n">
         <v>89.27</v>
@@ -25213,7 +25213,7 @@
         <v>1.66</v>
       </c>
       <c r="I327" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J327" t="n">
         <v>90.17</v>
@@ -25288,7 +25288,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I328" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J328" t="n">
         <v>91.04000000000001</v>
@@ -25363,7 +25363,7 @@
         <v>1.19</v>
       </c>
       <c r="I329" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J329" t="n">
         <v>91.90000000000001</v>
@@ -25438,7 +25438,7 @@
         <v>0.9</v>
       </c>
       <c r="I330" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J330" t="n">
         <v>92.81</v>
@@ -25513,7 +25513,7 @@
         <v>-0.53</v>
       </c>
       <c r="I331" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J331" t="n">
         <v>93.59</v>
@@ -25588,7 +25588,7 @@
         <v>-0.98</v>
       </c>
       <c r="I332" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J332" t="n">
         <v>94.15000000000001</v>
@@ -25663,7 +25663,7 @@
         <v>-9.57</v>
       </c>
       <c r="I333" s="4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J333" s="4" t="n">
         <v>94.23999999999999</v>
@@ -25742,7 +25742,7 @@
         <v>3.02</v>
       </c>
       <c r="I334" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J334" t="n">
         <v>94.27</v>
@@ -25817,7 +25817,7 @@
         <v>-2.31</v>
       </c>
       <c r="I335" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J335" t="n">
         <v>94.16</v>
@@ -25892,7 +25892,7 @@
         <v>-4</v>
       </c>
       <c r="I336" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J336" t="n">
         <v>93.95</v>
@@ -25967,7 +25967,7 @@
         <v>6.55</v>
       </c>
       <c r="I337" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J337" t="n">
         <v>93.93000000000001</v>
@@ -26042,7 +26042,7 @@
         <v>1.3</v>
       </c>
       <c r="I338" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J338" t="n">
         <v>93.91</v>
@@ -26117,7 +26117,7 @@
         <v>6.22</v>
       </c>
       <c r="I339" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J339" t="n">
         <v>94.31</v>
@@ -26192,7 +26192,7 @@
         <v>-3.75</v>
       </c>
       <c r="I340" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J340" t="n">
         <v>94.58</v>
@@ -26267,7 +26267,7 @@
         <v>-1.99</v>
       </c>
       <c r="I341" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J341" t="n">
         <v>94.8</v>
@@ -26346,7 +26346,7 @@
         <v>4.65</v>
       </c>
       <c r="I342" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J342" t="n">
         <v>95.09</v>
@@ -26421,7 +26421,7 @@
         <v>-0.24</v>
       </c>
       <c r="I343" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J343" t="n">
         <v>95.36</v>
@@ -26496,7 +26496,7 @@
         <v>-6.62</v>
       </c>
       <c r="I344" s="4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J344" s="4" t="n">
         <v>95.26000000000001</v>
@@ -26575,7 +26575,7 @@
         <v>-0.86</v>
       </c>
       <c r="I345" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J345" t="n">
         <v>94.95999999999999</v>
@@ -26650,7 +26650,7 @@
         <v>1.54</v>
       </c>
       <c r="I346" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J346" t="n">
         <v>94.75</v>
@@ -26725,7 +26725,7 @@
         <v>-2.88</v>
       </c>
       <c r="I347" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J347" t="n">
         <v>94.31999999999999</v>
@@ -26800,7 +26800,7 @@
         <v>5.11</v>
       </c>
       <c r="I348" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J348" t="n">
         <v>94.08</v>
@@ -26875,7 +26875,7 @@
         <v>3.29</v>
       </c>
       <c r="I349" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J349" t="n">
         <v>93.94</v>
@@ -26950,7 +26950,7 @@
         <v>-2.96</v>
       </c>
       <c r="I350" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J350" t="n">
         <v>93.61</v>
@@ -27025,7 +27025,7 @@
         <v>-3.5</v>
       </c>
       <c r="I351" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J351" t="n">
         <v>93.14</v>
@@ -27104,7 +27104,7 @@
         <v>2.79</v>
       </c>
       <c r="I352" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J352" t="n">
         <v>92.84999999999999</v>
@@ -27179,7 +27179,7 @@
         <v>-3.69</v>
       </c>
       <c r="I353" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J353" t="n">
         <v>92.86</v>
@@ -27258,7 +27258,7 @@
         <v>0.5</v>
       </c>
       <c r="I354" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J354" t="n">
         <v>92.76000000000001</v>
@@ -27333,7 +27333,7 @@
         <v>3.32</v>
       </c>
       <c r="I355" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J355" t="n">
         <v>92.92</v>
@@ -27408,7 +27408,7 @@
         <v>0.6</v>
       </c>
       <c r="I356" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J356" t="n">
         <v>93.28</v>
@@ -27483,7 +27483,7 @@
         <v>-3.8</v>
       </c>
       <c r="I357" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J357" t="n">
         <v>93.18000000000001</v>
@@ -27562,7 +27562,7 @@
         <v>2.21</v>
       </c>
       <c r="I358" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J358" t="n">
         <v>93.12</v>
@@ -27637,7 +27637,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="I359" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J359" t="n">
         <v>92.73999999999999</v>
@@ -27712,7 +27712,7 @@
         <v>-3.31</v>
       </c>
       <c r="I360" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J360" t="n">
         <v>92.40000000000001</v>
@@ -27791,7 +27791,7 @@
         <v>-3</v>
       </c>
       <c r="I361" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J361" t="n">
         <v>92.02</v>
@@ -27866,7 +27866,7 @@
         <v>0.14</v>
       </c>
       <c r="I362" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J362" t="n">
         <v>91.43000000000001</v>
@@ -27941,7 +27941,7 @@
         <v>3.72</v>
       </c>
       <c r="I363" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J363" t="n">
         <v>91.01000000000001</v>
@@ -28016,7 +28016,7 @@
         <v>-1.06</v>
       </c>
       <c r="I364" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J364" t="n">
         <v>90.87</v>
@@ -28091,7 +28091,7 @@
         <v>-3.72</v>
       </c>
       <c r="I365" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J365" t="n">
         <v>90.59999999999999</v>
@@ -28166,7 +28166,7 @@
         <v>-2.35</v>
       </c>
       <c r="I366" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J366" t="n">
         <v>90.16</v>
@@ -28241,7 +28241,7 @@
         <v>-0.63</v>
       </c>
       <c r="I367" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J367" t="n">
         <v>89.83</v>
@@ -28316,7 +28316,7 @@
         <v>-1.95</v>
       </c>
       <c r="I368" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J368" t="n">
         <v>89.19</v>
@@ -28391,7 +28391,7 @@
         <v>-4.07</v>
       </c>
       <c r="I369" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J369" t="n">
         <v>88.23</v>
@@ -28470,7 +28470,7 @@
         <v>6.58</v>
       </c>
       <c r="I370" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J370" t="n">
         <v>87.67</v>
@@ -28545,7 +28545,7 @@
         <v>1.2</v>
       </c>
       <c r="I371" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J371" t="n">
         <v>87.33</v>
@@ -28620,7 +28620,7 @@
         <v>3.53</v>
       </c>
       <c r="I372" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J372" t="n">
         <v>87</v>
@@ -28695,7 +28695,7 @@
         <v>6.73</v>
       </c>
       <c r="I373" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J373" t="n">
         <v>87.14</v>
@@ -28770,7 +28770,7 @@
         <v>-1.8</v>
       </c>
       <c r="I374" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J374" t="n">
         <v>87.17</v>
@@ -28849,7 +28849,7 @@
         <v>-0.73</v>
       </c>
       <c r="I375" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J375" t="n">
         <v>87.02</v>
@@ -28924,7 +28924,7 @@
         <v>2.3</v>
       </c>
       <c r="I376" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J376" t="n">
         <v>86.95</v>
@@ -28999,7 +28999,7 @@
         <v>-0.63</v>
       </c>
       <c r="I377" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J377" t="n">
         <v>87.02</v>
@@ -29074,7 +29074,7 @@
         <v>-0.71</v>
       </c>
       <c r="I378" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J378" t="n">
         <v>86.95999999999999</v>
@@ -29153,7 +29153,7 @@
         <v>1.47</v>
       </c>
       <c r="I379" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J379" t="n">
         <v>87</v>
@@ -29228,7 +29228,7 @@
         <v>2.29</v>
       </c>
       <c r="I380" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J380" t="n">
         <v>87.29000000000001</v>
@@ -29303,7 +29303,7 @@
         <v>-0.3</v>
       </c>
       <c r="I381" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J381" t="n">
         <v>87.7</v>
@@ -29378,7 +29378,7 @@
         <v>-0.33</v>
       </c>
       <c r="I382" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J382" t="n">
         <v>88.09</v>
@@ -29453,7 +29453,7 @@
         <v>-3.4</v>
       </c>
       <c r="I383" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J383" t="n">
         <v>88.16</v>
@@ -29532,7 +29532,7 @@
         <v>-0.43</v>
       </c>
       <c r="I384" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J384" t="n">
         <v>88.26000000000001</v>
@@ -29607,7 +29607,7 @@
         <v>-1.44</v>
       </c>
       <c r="I385" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J385" t="n">
         <v>88.45999999999999</v>
@@ -29682,7 +29682,7 @@
         <v>0.65</v>
       </c>
       <c r="I386" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J386" t="n">
         <v>88.79000000000001</v>
@@ -29757,7 +29757,7 @@
         <v>-2.02</v>
       </c>
       <c r="I387" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J387" t="n">
         <v>89.05</v>
@@ -29836,7 +29836,7 @@
         <v>1.23</v>
       </c>
       <c r="I388" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J388" t="n">
         <v>89.44</v>
@@ -29911,7 +29911,7 @@
         <v>0.15</v>
       </c>
       <c r="I389" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J389" t="n">
         <v>90.01000000000001</v>
@@ -29986,7 +29986,7 @@
         <v>2.74</v>
       </c>
       <c r="I390" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J390" t="n">
         <v>90.45</v>
@@ -30061,7 +30061,7 @@
         <v>-1.31</v>
       </c>
       <c r="I391" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J391" t="n">
         <v>90.77</v>
@@ -30140,7 +30140,7 @@
         <v>0.08</v>
       </c>
       <c r="I392" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J392" t="n">
         <v>90.95</v>
@@ -30215,7 +30215,7 @@
         <v>-2.57</v>
       </c>
       <c r="I393" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J393" t="n">
         <v>90.73</v>
@@ -30290,7 +30290,7 @@
         <v>0.44</v>
       </c>
       <c r="I394" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J394" t="n">
         <v>90.59999999999999</v>
@@ -30365,7 +30365,7 @@
         <v>2.34</v>
       </c>
       <c r="I395" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J395" t="n">
         <v>90.62</v>
@@ -30440,7 +30440,7 @@
         <v>0.32</v>
       </c>
       <c r="I396" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J396" t="n">
         <v>90.54000000000001</v>
@@ -30515,7 +30515,7 @@
         <v>-0.15</v>
       </c>
       <c r="I397" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J397" t="n">
         <v>90.48</v>
@@ -30590,7 +30590,7 @@
         <v>-0.61</v>
       </c>
       <c r="I398" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J398" t="n">
         <v>90.43000000000001</v>
@@ -30669,7 +30669,7 @@
         <v>-2.18</v>
       </c>
       <c r="I399" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J399" t="n">
         <v>90.22</v>
@@ -30744,7 +30744,7 @@
         <v>1.74</v>
       </c>
       <c r="I400" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J400" t="n">
         <v>89.98</v>
@@ -30819,7 +30819,7 @@
         <v>-1.62</v>
       </c>
       <c r="I401" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J401" t="n">
         <v>89.67</v>
@@ -30894,7 +30894,7 @@
         <v>-1.29</v>
       </c>
       <c r="I402" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J402" t="n">
         <v>89.33</v>
@@ -30969,7 +30969,7 @@
         <v>0</v>
       </c>
       <c r="I403" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J403" t="n">
         <v>89.15000000000001</v>
@@ -31044,7 +31044,7 @@
         <v>3.43</v>
       </c>
       <c r="I404" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J404" t="n">
         <v>89.13</v>
@@ -31119,7 +31119,7 @@
         <v>1.17</v>
       </c>
       <c r="I405" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J405" t="n">
         <v>89.23</v>
@@ -31194,7 +31194,7 @@
         <v>5.79</v>
       </c>
       <c r="I406" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J406" t="n">
         <v>89.56999999999999</v>
@@ -31269,7 +31269,7 @@
         <v>1.61</v>
       </c>
       <c r="I407" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J407" t="n">
         <v>90.06999999999999</v>
@@ -31344,7 +31344,7 @@
         <v>-1.67</v>
       </c>
       <c r="I408" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J408" t="n">
         <v>90.44</v>
@@ -31419,7 +31419,7 @@
         <v>-0.06</v>
       </c>
       <c r="I409" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J409" t="n">
         <v>90.8</v>
@@ -31494,7 +31494,7 @@
         <v>0.88</v>
       </c>
       <c r="I410" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J410" t="n">
         <v>91.08</v>
@@ -31569,7 +31569,7 @@
         <v>-2.15</v>
       </c>
       <c r="I411" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J411" t="n">
         <v>91.31999999999999</v>
@@ -31638,13 +31638,13 @@
         <v>95.22</v>
       </c>
       <c r="G412" t="n">
-        <v>2895200</v>
+        <v>2920400</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>0.37</v>
       </c>
       <c r="I412" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J412" t="n">
         <v>91.56999999999999</v>
@@ -31707,37 +31707,37 @@
         <v>97.04000000000001</v>
       </c>
       <c r="E413" t="n">
-        <v>95.67</v>
+        <v>95.61</v>
       </c>
       <c r="F413" t="n">
-        <v>96.34</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="G413" t="n">
-        <v>2229343</v>
+        <v>3589038</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>1.18</v>
+        <v>0.45</v>
       </c>
       <c r="I413" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J413" t="n">
-        <v>91.98999999999999</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="K413" t="n">
-        <v>89.95</v>
+        <v>89.94</v>
       </c>
       <c r="L413" t="n">
         <v>89.20999999999999</v>
       </c>
       <c r="M413" t="n">
-        <v>80.86</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>69.8</v>
+        <v>68.78</v>
       </c>
       <c r="O413" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31751,16 +31751,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.3</v>
+        <v>5.29</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.9</v>
+        <v>16.3</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>141.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31713,7 +31713,7 @@
         <v>95.65000000000001</v>
       </c>
       <c r="G413" t="n">
-        <v>3589038</v>
+        <v>3621200</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>0.45</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31737,7 +31737,7 @@
         <v>68.78</v>
       </c>
       <c r="O413" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31764,6 +31764,79 @@
         <v>141.9</v>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>96.41</v>
+      </c>
+      <c r="D414" t="n">
+        <v>96.73</v>
+      </c>
+      <c r="E414" t="n">
+        <v>94.76000000000001</v>
+      </c>
+      <c r="F414" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="G414" t="n">
+        <v>2508154</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="I414" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J414" t="n">
+        <v>92.31</v>
+      </c>
+      <c r="K414" t="n">
+        <v>90.03</v>
+      </c>
+      <c r="L414" t="n">
+        <v>89.43000000000001</v>
+      </c>
+      <c r="M414" t="n">
+        <v>80.98</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>65.37</v>
+      </c>
+      <c r="O414" t="n">
+        <v>27</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31713,7 +31713,7 @@
         <v>95.65000000000001</v>
       </c>
       <c r="G413" t="n">
-        <v>3621200</v>
+        <v>3684300</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>0.45</v>
@@ -31779,40 +31779,40 @@
         <v>96.41</v>
       </c>
       <c r="D414" t="n">
-        <v>96.73</v>
+        <v>96.91</v>
       </c>
       <c r="E414" t="n">
         <v>94.76000000000001</v>
       </c>
       <c r="F414" t="n">
-        <v>95.40000000000001</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="G414" t="n">
-        <v>2508154</v>
-      </c>
-      <c r="H414" s="3" t="n">
-        <v>-0.26</v>
+        <v>5182131</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>0.62</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
       </c>
       <c r="J414" t="n">
-        <v>92.31</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="K414" t="n">
-        <v>90.03</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="L414" t="n">
-        <v>89.43000000000001</v>
+        <v>89.44</v>
       </c>
       <c r="M414" t="n">
         <v>80.98</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>65.37</v>
+        <v>67.27</v>
       </c>
       <c r="O414" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31826,16 +31826,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.3</v>
+        <v>16.4</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>142.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31775,41 +31775,25 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C414" t="n">
-        <v>96.41</v>
-      </c>
-      <c r="D414" t="n">
-        <v>96.91</v>
-      </c>
-      <c r="E414" t="n">
-        <v>94.76000000000001</v>
-      </c>
-      <c r="F414" t="n">
-        <v>96.23999999999999</v>
-      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
         <v>5182131</v>
       </c>
-      <c r="H414" s="1" t="n">
-        <v>0.62</v>
+      <c r="H414" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
       </c>
-      <c r="J414" t="n">
-        <v>92.34999999999999</v>
-      </c>
-      <c r="K414" t="n">
-        <v>90.04000000000001</v>
-      </c>
-      <c r="L414" t="n">
-        <v>89.44</v>
-      </c>
-      <c r="M414" t="n">
-        <v>80.98</v>
-      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
       <c r="N414" s="2" t="n">
-        <v>67.27</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="O414" t="n">
         <v>28</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31775,28 +31775,44 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>96.41</v>
+      </c>
+      <c r="D414" t="n">
+        <v>96.91</v>
+      </c>
+      <c r="E414" t="n">
+        <v>94.75</v>
+      </c>
+      <c r="F414" t="n">
+        <v>96.23999999999999</v>
+      </c>
       <c r="G414" t="n">
-        <v>5182131</v>
-      </c>
-      <c r="H414" s="2" t="n">
-        <v>0</v>
+        <v>5192900</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>0.62</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>92.34999999999999</v>
+      </c>
+      <c r="K414" t="n">
+        <v>90.04000000000001</v>
+      </c>
+      <c r="L414" t="n">
+        <v>89.44</v>
+      </c>
+      <c r="M414" t="n">
+        <v>80.98</v>
+      </c>
       <c r="N414" s="2" t="n">
-        <v>66.23999999999999</v>
+        <v>67.27</v>
       </c>
       <c r="O414" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31812,7 +31812,7 @@
         <v>67.27</v>
       </c>
       <c r="O414" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31838,6 +31838,79 @@
       <c r="W414" s="2" t="n">
         <v>142.8</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>98.62</v>
+      </c>
+      <c r="D415" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="E415" t="n">
+        <v>97.64</v>
+      </c>
+      <c r="F415" t="n">
+        <v>97.97</v>
+      </c>
+      <c r="G415" t="n">
+        <v>2333330</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I415" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J415" t="n">
+        <v>92.73</v>
+      </c>
+      <c r="K415" t="n">
+        <v>90.12</v>
+      </c>
+      <c r="L415" t="n">
+        <v>89.68000000000001</v>
+      </c>
+      <c r="M415" t="n">
+        <v>81.13</v>
+      </c>
+      <c r="N415" s="3" t="n">
+        <v>75.09</v>
+      </c>
+      <c r="O415" t="n">
+        <v>31</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -8676,7 +8676,7 @@
         <v>57.47</v>
       </c>
       <c r="K108" t="n">
-        <v>51.89</v>
+        <v>51.88</v>
       </c>
       <c r="L108" t="n">
         <v>50.87</v>
@@ -25369,7 +25369,7 @@
         <v>91.90000000000001</v>
       </c>
       <c r="K329" t="n">
-        <v>76.64</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="L329" t="n">
         <v>73.5</v>
@@ -30449,7 +30449,7 @@
         <v>90.25</v>
       </c>
       <c r="L396" t="n">
-        <v>85.04000000000001</v>
+        <v>85.05</v>
       </c>
       <c r="M396" t="n">
         <v>79</v>
@@ -31788,7 +31788,7 @@
         <v>96.23999999999999</v>
       </c>
       <c r="G414" t="n">
-        <v>5192900</v>
+        <v>5229000</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>0.62</v>
@@ -31860,22 +31860,22 @@
         <v>97.64</v>
       </c>
       <c r="F415" t="n">
-        <v>97.97</v>
+        <v>98.13</v>
       </c>
       <c r="G415" t="n">
-        <v>2333330</v>
+        <v>4334116</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="I415" t="n">
         <v>5.2</v>
       </c>
       <c r="J415" t="n">
-        <v>92.73</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="K415" t="n">
-        <v>90.12</v>
+        <v>90.13</v>
       </c>
       <c r="L415" t="n">
         <v>89.68000000000001</v>
@@ -31884,7 +31884,7 @@
         <v>81.13</v>
       </c>
       <c r="N415" s="3" t="n">
-        <v>75.09</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="O415" t="n">
         <v>31</v>
@@ -31901,13 +31901,13 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.25</v>
+        <v>5.28</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>15.8</v>
+        <v>15.3</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="2" t="inlineStr"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31775,25 +31775,41 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>98.62</v>
+      </c>
+      <c r="D414" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="E414" t="n">
+        <v>97.64</v>
+      </c>
+      <c r="F414" t="n">
+        <v>98.13</v>
+      </c>
       <c r="G414" t="n">
-        <v>4356001</v>
-      </c>
-      <c r="H414" s="2" t="n">
-        <v>0</v>
+        <v>4367800</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>1.96</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>92.73999999999999</v>
+      </c>
+      <c r="K414" t="n">
+        <v>90.13</v>
+      </c>
+      <c r="L414" t="n">
+        <v>89.68000000000001</v>
+      </c>
+      <c r="M414" t="n">
+        <v>81.13</v>
+      </c>
       <c r="N414" s="1" t="n">
-        <v>72.69</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="O414" t="n">
         <v>31</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -8055,7 +8055,7 @@
         <v>59.05</v>
       </c>
       <c r="D100" t="n">
-        <v>59.24</v>
+        <v>59.23</v>
       </c>
       <c r="E100" t="n">
         <v>58.22</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -7980,7 +7980,7 @@
         <v>59.05</v>
       </c>
       <c r="D99" t="n">
-        <v>59.24</v>
+        <v>59.23</v>
       </c>
       <c r="E99" t="n">
         <v>58.22</v>
@@ -31662,7 +31662,7 @@
         <v>75.29000000000001</v>
       </c>
       <c r="O412" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1606,7 +1606,7 @@
         <v>5.2</v>
       </c>
       <c r="J15" t="n">
-        <v>55.51</v>
+        <v>55.5</v>
       </c>
       <c r="K15" t="n">
         <v>55.83</v>
@@ -8451,7 +8451,7 @@
         <v>57.47</v>
       </c>
       <c r="K105" t="n">
-        <v>51.89</v>
+        <v>51.88</v>
       </c>
       <c r="L105" t="n">
         <v>50.87</v>
@@ -9806,7 +9806,7 @@
         <v>5.2</v>
       </c>
       <c r="J123" t="n">
-        <v>61</v>
+        <v>61.01</v>
       </c>
       <c r="K123" t="n">
         <v>56.96</v>
@@ -31662,7 +31662,7 @@
         <v>75.29000000000001</v>
       </c>
       <c r="O412" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31688,6 +31688,79 @@
       <c r="W412" s="2" t="n">
         <v>144.9</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>98.08</v>
+      </c>
+      <c r="D413" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="E413" t="n">
+        <v>98.02</v>
+      </c>
+      <c r="F413" t="n">
+        <v>99.53</v>
+      </c>
+      <c r="G413" t="n">
+        <v>1744708</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I413" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J413" t="n">
+        <v>93.19</v>
+      </c>
+      <c r="K413" t="n">
+        <v>90.22</v>
+      </c>
+      <c r="L413" t="n">
+        <v>89.91</v>
+      </c>
+      <c r="M413" t="n">
+        <v>81.27</v>
+      </c>
+      <c r="N413" s="3" t="n">
+        <v>81.27</v>
+      </c>
+      <c r="O413" t="n">
+        <v>44</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31563,7 +31563,7 @@
         <v>98.13</v>
       </c>
       <c r="G411" t="n">
-        <v>4367800</v>
+        <v>4386600</v>
       </c>
       <c r="H411" s="1" t="n">
         <v>1.96</v>
@@ -31625,25 +31625,41 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>98.08</v>
+      </c>
+      <c r="D412" t="n">
+        <v>100.06</v>
+      </c>
+      <c r="E412" t="n">
+        <v>98.02</v>
+      </c>
+      <c r="F412" t="n">
+        <v>99.84</v>
+      </c>
       <c r="G412" t="n">
-        <v>3068592</v>
-      </c>
-      <c r="H412" s="3" t="n">
-        <v>0</v>
+        <v>3085200</v>
+      </c>
+      <c r="H412" s="1" t="n">
+        <v>1.74</v>
       </c>
       <c r="I412" t="n">
         <v>5.2</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="K412" t="n">
+        <v>90.23</v>
+      </c>
+      <c r="L412" t="n">
+        <v>89.91</v>
+      </c>
+      <c r="M412" t="n">
+        <v>81.28</v>
+      </c>
       <c r="N412" s="2" t="n">
-        <v>79.87</v>
+        <v>81.56</v>
       </c>
       <c r="O412" t="n">
         <v>43</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,14 +433,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
@@ -7905,7 +7905,7 @@
         <v>59.05</v>
       </c>
       <c r="D98" t="n">
-        <v>59.24</v>
+        <v>59.23</v>
       </c>
       <c r="E98" t="n">
         <v>58.22</v>
@@ -31662,7 +31662,7 @@
         <v>81.56</v>
       </c>
       <c r="O412" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31688,6 +31688,79 @@
       <c r="W412" s="3" t="n">
         <v>143</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>100.98</v>
+      </c>
+      <c r="D413" t="n">
+        <v>101.41</v>
+      </c>
+      <c r="E413" t="n">
+        <v>100.64</v>
+      </c>
+      <c r="F413" t="n">
+        <v>101.35</v>
+      </c>
+      <c r="G413" t="n">
+        <v>1266660</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I413" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J413" t="n">
+        <v>93.73999999999999</v>
+      </c>
+      <c r="K413" t="n">
+        <v>90.42</v>
+      </c>
+      <c r="L413" t="n">
+        <v>90.14</v>
+      </c>
+      <c r="M413" t="n">
+        <v>81.45</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>82.81999999999999</v>
+      </c>
+      <c r="O413" t="n">
+        <v>48</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="T413" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U413" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -8376,7 +8376,7 @@
         <v>57.47</v>
       </c>
       <c r="K104" t="n">
-        <v>51.88</v>
+        <v>51.89</v>
       </c>
       <c r="L104" t="n">
         <v>50.87</v>
@@ -31638,7 +31638,7 @@
         <v>99.84</v>
       </c>
       <c r="G412" t="n">
-        <v>3085200</v>
+        <v>3124500</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>1.74</v>
@@ -31704,37 +31704,37 @@
         <v>100.98</v>
       </c>
       <c r="D413" t="n">
-        <v>101.41</v>
+        <v>101.61</v>
       </c>
       <c r="E413" t="n">
         <v>100.64</v>
       </c>
       <c r="F413" t="n">
-        <v>101.35</v>
+        <v>100.76</v>
       </c>
       <c r="G413" t="n">
-        <v>1266660</v>
+        <v>3858338</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>1.51</v>
+        <v>0.92</v>
       </c>
       <c r="I413" t="n">
         <v>5.2</v>
       </c>
       <c r="J413" t="n">
-        <v>93.73999999999999</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="K413" t="n">
-        <v>90.42</v>
+        <v>90.41</v>
       </c>
       <c r="L413" t="n">
-        <v>90.14</v>
+        <v>90.13</v>
       </c>
       <c r="M413" t="n">
-        <v>81.45</v>
+        <v>81.44</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>82.81999999999999</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="O413" t="n">
         <v>48</v>
@@ -31751,13 +31751,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.28</v>
+        <v>5.27</v>
       </c>
       <c r="T413" s="3" t="n">
-        <v>15.4</v>
+        <v>15.1</v>
       </c>
       <c r="U413" s="3" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="3" t="inlineStr"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -440,7 +440,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
@@ -31625,25 +31625,41 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>100.98</v>
+      </c>
+      <c r="D412" t="n">
+        <v>101.62</v>
+      </c>
+      <c r="E412" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="F412" t="n">
+        <v>100.77</v>
+      </c>
       <c r="G412" t="n">
-        <v>3937625</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
+        <v>3935700</v>
+      </c>
+      <c r="H412" s="1" t="n">
+        <v>0.93</v>
       </c>
       <c r="I412" t="n">
         <v>5.2</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>93.72</v>
+      </c>
+      <c r="K412" t="n">
+        <v>90.41</v>
+      </c>
+      <c r="L412" t="n">
+        <v>90.13</v>
+      </c>
+      <c r="M412" t="n">
+        <v>81.44</v>
+      </c>
       <c r="N412" s="3" t="n">
-        <v>81.56</v>
+        <v>82.36</v>
       </c>
       <c r="O412" t="n">
         <v>47</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31689,6 +31689,79 @@
         <v>141.2</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>99.19</v>
+      </c>
+      <c r="D413" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="E413" t="n">
+        <v>98.67</v>
+      </c>
+      <c r="F413" t="n">
+        <v>99.36</v>
+      </c>
+      <c r="G413" t="n">
+        <v>993894</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="I413" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J413" t="n">
+        <v>94.18000000000001</v>
+      </c>
+      <c r="K413" t="n">
+        <v>90.53</v>
+      </c>
+      <c r="L413" t="n">
+        <v>90.34</v>
+      </c>
+      <c r="M413" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="N413" s="3" t="n">
+        <v>73.84</v>
+      </c>
+      <c r="O413" t="n">
+        <v>42</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31638,7 +31638,7 @@
         <v>100.77</v>
       </c>
       <c r="G412" t="n">
-        <v>3935700</v>
+        <v>3959300</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>0.93</v>
@@ -31704,28 +31704,28 @@
         <v>99.19</v>
       </c>
       <c r="D413" t="n">
-        <v>99.45999999999999</v>
+        <v>100.36</v>
       </c>
       <c r="E413" t="n">
         <v>98.67</v>
       </c>
       <c r="F413" t="n">
-        <v>99.36</v>
+        <v>100.23</v>
       </c>
       <c r="G413" t="n">
-        <v>993894</v>
+        <v>3074702</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>-1.4</v>
+        <v>-0.54</v>
       </c>
       <c r="I413" t="n">
         <v>5.2</v>
       </c>
       <c r="J413" t="n">
-        <v>94.18000000000001</v>
+        <v>94.23</v>
       </c>
       <c r="K413" t="n">
-        <v>90.53</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="L413" t="n">
         <v>90.34</v>
@@ -31734,10 +31734,10 @@
         <v>81.59999999999999</v>
       </c>
       <c r="N413" s="3" t="n">
-        <v>73.84</v>
+        <v>77.23</v>
       </c>
       <c r="O413" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31751,13 +31751,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.32</v>
+        <v>5.28</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.8</v>
+        <v>15.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>7.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31700,41 +31700,25 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="C413" t="n">
-        <v>99.19</v>
-      </c>
-      <c r="D413" t="n">
-        <v>100.36</v>
-      </c>
-      <c r="E413" t="n">
-        <v>98.67</v>
-      </c>
-      <c r="F413" t="n">
-        <v>100.23</v>
-      </c>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr"/>
       <c r="G413" t="n">
-        <v>3074702</v>
-      </c>
-      <c r="H413" s="3" t="n">
-        <v>-0.54</v>
+        <v>3097438</v>
+      </c>
+      <c r="H413" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I413" t="n">
         <v>5.2</v>
       </c>
-      <c r="J413" t="n">
-        <v>94.23</v>
-      </c>
-      <c r="K413" t="n">
-        <v>90.54000000000001</v>
-      </c>
-      <c r="L413" t="n">
-        <v>90.34</v>
-      </c>
-      <c r="M413" t="n">
-        <v>81.59999999999999</v>
-      </c>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
       <c r="N413" s="3" t="n">
-        <v>77.23</v>
+        <v>79.5</v>
       </c>
       <c r="O413" t="n">
         <v>45</v>
@@ -31760,7 +31744,9 @@
         <v>9.300000000000001</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>141.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31700,25 +31700,41 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr"/>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="C413" t="n">
+        <v>99.19</v>
+      </c>
+      <c r="D413" t="n">
+        <v>100.37</v>
+      </c>
+      <c r="E413" t="n">
+        <v>98.65000000000001</v>
+      </c>
+      <c r="F413" t="n">
+        <v>100.23</v>
+      </c>
       <c r="G413" t="n">
-        <v>3097438</v>
-      </c>
-      <c r="H413" s="2" t="n">
-        <v>0</v>
+        <v>3103700</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>-0.54</v>
       </c>
       <c r="I413" t="n">
         <v>5.2</v>
       </c>
-      <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr"/>
-      <c r="M413" t="inlineStr"/>
+      <c r="J413" t="n">
+        <v>94.23</v>
+      </c>
+      <c r="K413" t="n">
+        <v>90.54000000000001</v>
+      </c>
+      <c r="L413" t="n">
+        <v>90.34</v>
+      </c>
+      <c r="M413" t="n">
+        <v>81.59999999999999</v>
+      </c>
       <c r="N413" s="3" t="n">
-        <v>79.5</v>
+        <v>77.23</v>
       </c>
       <c r="O413" t="n">
         <v>45</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7830,7 +7830,7 @@
         <v>59.05</v>
       </c>
       <c r="D97" t="n">
-        <v>59.23</v>
+        <v>59.24</v>
       </c>
       <c r="E97" t="n">
         <v>58.22</v>
@@ -31737,7 +31737,7 @@
         <v>77.23</v>
       </c>
       <c r="O413" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31763,6 +31763,79 @@
       <c r="W413" s="2" t="n">
         <v>141.8</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>99.23</v>
+      </c>
+      <c r="D414" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="E414" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="F414" t="n">
+        <v>99.26000000000001</v>
+      </c>
+      <c r="G414" t="n">
+        <v>1229978</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="I414" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J414" t="n">
+        <v>94.79000000000001</v>
+      </c>
+      <c r="K414" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="L414" t="n">
+        <v>90.53</v>
+      </c>
+      <c r="M414" t="n">
+        <v>81.73999999999999</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>71.98999999999999</v>
+      </c>
+      <c r="O414" t="n">
+        <v>41</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -7830,7 +7830,7 @@
         <v>59.05</v>
       </c>
       <c r="D97" t="n">
-        <v>59.24</v>
+        <v>59.23</v>
       </c>
       <c r="E97" t="n">
         <v>58.22</v>
@@ -31713,7 +31713,7 @@
         <v>100.23</v>
       </c>
       <c r="G413" t="n">
-        <v>3103700</v>
+        <v>3134700</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>-0.54</v>
@@ -31782,37 +31782,37 @@
         <v>100.05</v>
       </c>
       <c r="E414" t="n">
-        <v>98.75</v>
+        <v>96.39</v>
       </c>
       <c r="F414" t="n">
-        <v>99.26000000000001</v>
+        <v>97.54000000000001</v>
       </c>
       <c r="G414" t="n">
-        <v>1229978</v>
+        <v>4844085</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>-0.97</v>
+        <v>-2.68</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
       </c>
       <c r="J414" t="n">
-        <v>94.79000000000001</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="K414" t="n">
-        <v>90.67</v>
+        <v>90.64</v>
       </c>
       <c r="L414" t="n">
-        <v>90.53</v>
+        <v>90.52</v>
       </c>
       <c r="M414" t="n">
-        <v>81.73999999999999</v>
-      </c>
-      <c r="N414" s="3" t="n">
-        <v>71.98999999999999</v>
+        <v>81.73</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>65.97</v>
       </c>
       <c r="O414" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31826,13 +31826,13 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.3</v>
+        <v>5.23</v>
       </c>
       <c r="T414" s="2" t="n">
         <v>15.4</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>7.6</v>
+        <v>10.2</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31779,7 +31779,7 @@
         <v>99.23</v>
       </c>
       <c r="D414" t="n">
-        <v>100.05</v>
+        <v>100.08</v>
       </c>
       <c r="E414" t="n">
         <v>96.39</v>
@@ -31788,7 +31788,7 @@
         <v>97.54000000000001</v>
       </c>
       <c r="G414" t="n">
-        <v>4844085</v>
+        <v>4879300</v>
       </c>
       <c r="H414" s="3" t="n">
         <v>-2.68</v>
@@ -31835,7 +31835,9 @@
         <v>10.2</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>149.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31812,7 +31812,7 @@
         <v>65.97</v>
       </c>
       <c r="O414" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31838,6 +31838,79 @@
       <c r="W414" s="2" t="n">
         <v>149.2</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>98.78</v>
+      </c>
+      <c r="D415" t="n">
+        <v>98.86</v>
+      </c>
+      <c r="E415" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="F415" t="n">
+        <v>98.23</v>
+      </c>
+      <c r="G415" t="n">
+        <v>1565222</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="I415" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J415" t="n">
+        <v>95.14</v>
+      </c>
+      <c r="K415" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="L415" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="M415" t="n">
+        <v>81.87</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>56.22</v>
+      </c>
+      <c r="O415" t="n">
+        <v>44</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31788,7 +31788,7 @@
         <v>97.54000000000001</v>
       </c>
       <c r="G414" t="n">
-        <v>4879300</v>
+        <v>4946200</v>
       </c>
       <c r="H414" s="3" t="n">
         <v>-2.68</v>
@@ -31860,22 +31860,22 @@
         <v>97.7</v>
       </c>
       <c r="F415" t="n">
-        <v>98.23</v>
+        <v>98.42</v>
       </c>
       <c r="G415" t="n">
-        <v>1565222</v>
+        <v>2638169</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>0.71</v>
+        <v>0.9</v>
       </c>
       <c r="I415" t="n">
         <v>5.2</v>
       </c>
       <c r="J415" t="n">
-        <v>95.14</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="K415" t="n">
-        <v>90.8</v>
+        <v>90.81</v>
       </c>
       <c r="L415" t="n">
         <v>90.7</v>
@@ -31884,10 +31884,10 @@
         <v>81.87</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>56.22</v>
+        <v>56.74</v>
       </c>
       <c r="O415" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31901,13 +31901,13 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>7.3</v>
+        <v>9.1</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="2" t="inlineStr"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31850,41 +31850,25 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="C415" t="n">
-        <v>98.78</v>
-      </c>
-      <c r="D415" t="n">
-        <v>98.86</v>
-      </c>
-      <c r="E415" t="n">
-        <v>97.7</v>
-      </c>
-      <c r="F415" t="n">
-        <v>98.42</v>
-      </c>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
       <c r="G415" t="n">
-        <v>2638169</v>
-      </c>
-      <c r="H415" s="1" t="n">
-        <v>0.9</v>
+        <v>2650051</v>
+      </c>
+      <c r="H415" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I415" t="n">
         <v>5.2</v>
       </c>
-      <c r="J415" t="n">
-        <v>95.15000000000001</v>
-      </c>
-      <c r="K415" t="n">
-        <v>90.81</v>
-      </c>
-      <c r="L415" t="n">
-        <v>90.7</v>
-      </c>
-      <c r="M415" t="n">
-        <v>81.87</v>
-      </c>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
       <c r="N415" s="2" t="n">
-        <v>56.74</v>
+        <v>54.25</v>
       </c>
       <c r="O415" t="n">
         <v>45</v>
@@ -31910,7 +31894,9 @@
         <v>9.1</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="n">
+        <v>154.3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31850,25 +31850,41 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>98.78</v>
+      </c>
+      <c r="D415" t="n">
+        <v>98.86</v>
+      </c>
+      <c r="E415" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="F415" t="n">
+        <v>98.42</v>
+      </c>
       <c r="G415" t="n">
-        <v>2650051</v>
-      </c>
-      <c r="H415" s="2" t="n">
-        <v>0</v>
+        <v>2655900</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>0.9</v>
       </c>
       <c r="I415" t="n">
         <v>5.2</v>
       </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
+      <c r="J415" t="n">
+        <v>95.15000000000001</v>
+      </c>
+      <c r="K415" t="n">
+        <v>90.81</v>
+      </c>
+      <c r="L415" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="M415" t="n">
+        <v>81.87</v>
+      </c>
       <c r="N415" s="2" t="n">
-        <v>54.25</v>
+        <v>56.74</v>
       </c>
       <c r="O415" t="n">
         <v>45</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -7755,7 +7755,7 @@
         <v>59.05</v>
       </c>
       <c r="D96" t="n">
-        <v>59.23</v>
+        <v>59.24</v>
       </c>
       <c r="E96" t="n">
         <v>58.22</v>
@@ -8226,7 +8226,7 @@
         <v>57.47</v>
       </c>
       <c r="K102" t="n">
-        <v>51.89</v>
+        <v>51.88</v>
       </c>
       <c r="L102" t="n">
         <v>50.87</v>
@@ -24919,7 +24919,7 @@
         <v>91.90000000000001</v>
       </c>
       <c r="K323" t="n">
-        <v>76.64</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="L323" t="n">
         <v>73.5</v>
@@ -29999,7 +29999,7 @@
         <v>90.25</v>
       </c>
       <c r="L390" t="n">
-        <v>85.05</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="M390" t="n">
         <v>79</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -7755,7 +7755,7 @@
         <v>59.05</v>
       </c>
       <c r="D96" t="n">
-        <v>59.24</v>
+        <v>59.23</v>
       </c>
       <c r="E96" t="n">
         <v>58.22</v>
@@ -8226,7 +8226,7 @@
         <v>57.47</v>
       </c>
       <c r="K102" t="n">
-        <v>51.88</v>
+        <v>51.89</v>
       </c>
       <c r="L102" t="n">
         <v>50.87</v>
@@ -24919,7 +24919,7 @@
         <v>91.90000000000001</v>
       </c>
       <c r="K323" t="n">
-        <v>76.65000000000001</v>
+        <v>76.64</v>
       </c>
       <c r="L323" t="n">
         <v>73.5</v>
@@ -29999,7 +29999,7 @@
         <v>90.25</v>
       </c>
       <c r="L390" t="n">
-        <v>85.04000000000001</v>
+        <v>85.05</v>
       </c>
       <c r="M390" t="n">
         <v>79</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31737,11 +31737,11 @@
         <v>56.74</v>
       </c>
       <c r="O413" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">
@@ -31762,6 +31762,81 @@
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="n">
         <v>154.3</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>98.02</v>
+      </c>
+      <c r="D414" t="n">
+        <v>98.05</v>
+      </c>
+      <c r="E414" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="F414" t="n">
+        <v>97.08</v>
+      </c>
+      <c r="G414" t="n">
+        <v>2214932</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="I414" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J414" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="K414" t="n">
+        <v>90.98999999999999</v>
+      </c>
+      <c r="L414" t="n">
+        <v>90.88</v>
+      </c>
+      <c r="M414" t="n">
+        <v>81.98999999999999</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>47.78</v>
+      </c>
+      <c r="O414" t="n">
+        <v>46</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="1" t="n">
+        <v>155.1</v>
       </c>
     </row>
   </sheetData>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31764,6 +31764,83 @@
         <v>155.1</v>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>95.31</v>
+      </c>
+      <c r="D414" t="n">
+        <v>96.56999999999999</v>
+      </c>
+      <c r="E414" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="F414" t="n">
+        <v>95.98</v>
+      </c>
+      <c r="G414" t="n">
+        <v>2053679</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="I414" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J414" t="n">
+        <v>96.05</v>
+      </c>
+      <c r="K414" t="n">
+        <v>91.16</v>
+      </c>
+      <c r="L414" t="n">
+        <v>91.03</v>
+      </c>
+      <c r="M414" t="n">
+        <v>82.11</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="O414" t="n">
+        <v>44</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -8076,7 +8076,7 @@
         <v>57.47</v>
       </c>
       <c r="K100" t="n">
-        <v>51.89</v>
+        <v>51.88</v>
       </c>
       <c r="L100" t="n">
         <v>50.87</v>
@@ -29849,7 +29849,7 @@
         <v>90.25</v>
       </c>
       <c r="L388" t="n">
-        <v>85.05</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="M388" t="n">
         <v>79</v>
@@ -31713,7 +31713,7 @@
         <v>97.08</v>
       </c>
       <c r="G413" t="n">
-        <v>2253500</v>
+        <v>2288000</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-1.36</v>
@@ -31785,34 +31785,34 @@
         <v>95.2</v>
       </c>
       <c r="F414" t="n">
-        <v>95.98</v>
+        <v>96.44</v>
       </c>
       <c r="G414" t="n">
-        <v>2053679</v>
+        <v>2898706</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-1.13</v>
+        <v>-0.66</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
       </c>
       <c r="J414" t="n">
-        <v>96.05</v>
+        <v>96.08</v>
       </c>
       <c r="K414" t="n">
-        <v>91.16</v>
+        <v>91.17</v>
       </c>
       <c r="L414" t="n">
-        <v>91.03</v>
+        <v>91.04000000000001</v>
       </c>
       <c r="M414" t="n">
         <v>82.11</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>49.42</v>
+        <v>50.93</v>
       </c>
       <c r="O414" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31824,20 +31824,12 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R414" t="inlineStr">
-        <is>
-          <t>1st: MA20, 10% cash</t>
-        </is>
-      </c>
+      <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
         <v>5.22</v>
       </c>
-      <c r="T414" s="2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="U414" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="T414" s="2" t="inlineStr"/>
+      <c r="U414" s="2" t="inlineStr"/>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>
     </row>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31737,7 +31737,7 @@
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7997,7 +7997,7 @@
         <v>57.47</v>
       </c>
       <c r="K99" t="n">
-        <v>51.88</v>
+        <v>51.89</v>
       </c>
       <c r="L99" t="n">
         <v>50.87</v>
@@ -29770,7 +29770,7 @@
         <v>90.25</v>
       </c>
       <c r="L387" t="n">
-        <v>85.04000000000001</v>
+        <v>85.05</v>
       </c>
       <c r="M387" t="n">
         <v>79</v>
@@ -31733,11 +31733,11 @@
         <v>50.93</v>
       </c>
       <c r="O413" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">
@@ -31759,6 +31759,83 @@
       <c r="W413" s="2" t="n">
         <v>154.7</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>94.95</v>
+      </c>
+      <c r="D414" t="n">
+        <v>95.59</v>
+      </c>
+      <c r="E414" t="n">
+        <v>94.09</v>
+      </c>
+      <c r="F414" t="n">
+        <v>94.52</v>
+      </c>
+      <c r="G414" t="n">
+        <v>1660048</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-1.99</v>
+      </c>
+      <c r="I414" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J414" t="n">
+        <v>96.45</v>
+      </c>
+      <c r="K414" t="n">
+        <v>91.26000000000001</v>
+      </c>
+      <c r="L414" t="n">
+        <v>91.18000000000001</v>
+      </c>
+      <c r="M414" t="n">
+        <v>82.22</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>45.31</v>
+      </c>
+      <c r="O414" t="n">
+        <v>37</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -7997,7 +7997,7 @@
         <v>57.47</v>
       </c>
       <c r="K99" t="n">
-        <v>51.89</v>
+        <v>51.88</v>
       </c>
       <c r="L99" t="n">
         <v>50.87</v>
@@ -29770,7 +29770,7 @@
         <v>90.25</v>
       </c>
       <c r="L387" t="n">
-        <v>85.05</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="M387" t="n">
         <v>79</v>
@@ -31778,37 +31778,37 @@
         <v>95.59</v>
       </c>
       <c r="E414" t="n">
-        <v>94.09</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="F414" t="n">
-        <v>94.52</v>
+        <v>92.22</v>
       </c>
       <c r="G414" t="n">
-        <v>1660048</v>
+        <v>3693311</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-1.99</v>
+        <v>-4.38</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
       </c>
       <c r="J414" t="n">
-        <v>96.45</v>
+        <v>96.34</v>
       </c>
       <c r="K414" t="n">
-        <v>91.26000000000001</v>
+        <v>91.22</v>
       </c>
       <c r="L414" t="n">
-        <v>91.18000000000001</v>
+        <v>91.16</v>
       </c>
       <c r="M414" t="n">
-        <v>82.22</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>45.31</v>
+        <v>39.86</v>
       </c>
       <c r="O414" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31826,13 +31826,13 @@
         </is>
       </c>
       <c r="S414" t="n">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>15.7</v>
+        <v>17.2</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>8.1</v>
+        <v>14</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -1152,7 +1152,7 @@
         <v>5.2</v>
       </c>
       <c r="J9" t="n">
-        <v>55.51</v>
+        <v>55.5</v>
       </c>
       <c r="K9" t="n">
         <v>55.83</v>
@@ -9352,7 +9352,7 @@
         <v>5.2</v>
       </c>
       <c r="J117" t="n">
-        <v>61</v>
+        <v>61.01</v>
       </c>
       <c r="K117" t="n">
         <v>56.96</v>
@@ -29770,7 +29770,7 @@
         <v>90.25</v>
       </c>
       <c r="L387" t="n">
-        <v>85.04000000000001</v>
+        <v>85.05</v>
       </c>
       <c r="M387" t="n">
         <v>79</v>
@@ -31709,7 +31709,7 @@
         <v>96.44</v>
       </c>
       <c r="G413" t="n">
-        <v>2880500</v>
+        <v>2911100</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-0.66</v>
@@ -31781,19 +31781,19 @@
         <v>91.95999999999999</v>
       </c>
       <c r="F414" t="n">
-        <v>92.22</v>
+        <v>92.55</v>
       </c>
       <c r="G414" t="n">
-        <v>3693311</v>
+        <v>4894545</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-4.38</v>
+        <v>-4.03</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
       </c>
       <c r="J414" t="n">
-        <v>96.34</v>
+        <v>96.36</v>
       </c>
       <c r="K414" t="n">
         <v>91.22</v>
@@ -31805,10 +31805,10 @@
         <v>82.20999999999999</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>39.86</v>
+        <v>40.56</v>
       </c>
       <c r="O414" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31829,13 +31829,15 @@
         <v>5.19</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.2</v>
+        <v>16.9</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="1" t="n">
+        <v>157.3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31775,16 +31775,16 @@
         <v>94.95</v>
       </c>
       <c r="D414" t="n">
-        <v>95.59</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="E414" t="n">
-        <v>91.95999999999999</v>
+        <v>91.95</v>
       </c>
       <c r="F414" t="n">
         <v>92.55</v>
       </c>
       <c r="G414" t="n">
-        <v>4894545</v>
+        <v>4893500</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>-4.03</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31808,7 +31808,7 @@
         <v>40.56</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31808,7 +31808,7 @@
         <v>40.56</v>
       </c>
       <c r="O414" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31838,6 +31838,83 @@
       <c r="W414" s="1" t="n">
         <v>157.3</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>89.95999999999999</v>
+      </c>
+      <c r="D415" t="n">
+        <v>90.59</v>
+      </c>
+      <c r="E415" t="n">
+        <v>89.16</v>
+      </c>
+      <c r="F415" t="n">
+        <v>90.31999999999999</v>
+      </c>
+      <c r="G415" t="n">
+        <v>1931352</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-2.41</v>
+      </c>
+      <c r="I415" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J415" t="n">
+        <v>96.38</v>
+      </c>
+      <c r="K415" t="n">
+        <v>91.26000000000001</v>
+      </c>
+      <c r="L415" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="M415" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>33.58</v>
+      </c>
+      <c r="O415" t="n">
+        <v>24</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>3x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>3rd: MA120, 50% cash, 5d</t>
+        </is>
+      </c>
+      <c r="S415" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31854,64 +31854,60 @@
         <v>89.95999999999999</v>
       </c>
       <c r="D415" t="n">
-        <v>90.59</v>
+        <v>92.09</v>
       </c>
       <c r="E415" t="n">
         <v>89.16</v>
       </c>
       <c r="F415" t="n">
-        <v>90.31999999999999</v>
+        <v>91.59</v>
       </c>
       <c r="G415" t="n">
-        <v>1931352</v>
+        <v>4166606</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>-2.41</v>
+        <v>-1.04</v>
       </c>
       <c r="I415" t="n">
         <v>5.2</v>
       </c>
       <c r="J415" t="n">
-        <v>96.38</v>
+        <v>96.44</v>
       </c>
       <c r="K415" t="n">
+        <v>91.28</v>
+      </c>
+      <c r="L415" t="n">
         <v>91.26000000000001</v>
       </c>
-      <c r="L415" t="n">
-        <v>91.25</v>
-      </c>
       <c r="M415" t="n">
-        <v>82.3</v>
+        <v>82.31</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>33.58</v>
+        <v>35.84</v>
       </c>
       <c r="O415" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
-          <t>extreme fear</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="Q415" t="inlineStr">
         <is>
-          <t>3x BUY</t>
-        </is>
-      </c>
-      <c r="R415" t="inlineStr">
-        <is>
-          <t>3rd: MA120, 50% cash, 5d</t>
-        </is>
-      </c>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.05</v>
+        <v>5.08</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>17.6</v>
+        <v>16.8</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>10.7</v>
+        <v>12.5</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="2" t="inlineStr"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31784,7 +31784,7 @@
         <v>92.55</v>
       </c>
       <c r="G414" t="n">
-        <v>4893500</v>
+        <v>5139800</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>-4.03</v>
@@ -31854,40 +31854,40 @@
         <v>89.95999999999999</v>
       </c>
       <c r="D415" t="n">
-        <v>92.09</v>
+        <v>92.69</v>
       </c>
       <c r="E415" t="n">
         <v>89.16</v>
       </c>
       <c r="F415" t="n">
-        <v>91.59</v>
+        <v>92.36</v>
       </c>
       <c r="G415" t="n">
-        <v>4166606</v>
+        <v>5111630</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>-1.04</v>
+        <v>-0.21</v>
       </c>
       <c r="I415" t="n">
         <v>5.2</v>
       </c>
       <c r="J415" t="n">
-        <v>96.44</v>
+        <v>96.48</v>
       </c>
       <c r="K415" t="n">
-        <v>91.28</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="L415" t="n">
-        <v>91.26000000000001</v>
+        <v>91.27</v>
       </c>
       <c r="M415" t="n">
         <v>82.31</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>35.84</v>
+        <v>37.36</v>
       </c>
       <c r="O415" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31901,16 +31901,18 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.08</v>
+        <v>5.09</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="1" t="n">
+        <v>160.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31850,41 +31850,25 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="C415" t="n">
-        <v>89.95999999999999</v>
-      </c>
-      <c r="D415" t="n">
-        <v>92.69</v>
-      </c>
-      <c r="E415" t="n">
-        <v>89.16</v>
-      </c>
-      <c r="F415" t="n">
-        <v>92.36</v>
-      </c>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
       <c r="G415" t="n">
         <v>5111630</v>
       </c>
-      <c r="H415" s="1" t="n">
-        <v>-0.21</v>
+      <c r="H415" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I415" t="n">
         <v>5.2</v>
       </c>
-      <c r="J415" t="n">
-        <v>96.48</v>
-      </c>
-      <c r="K415" t="n">
-        <v>91.29000000000001</v>
-      </c>
-      <c r="L415" t="n">
-        <v>91.27</v>
-      </c>
-      <c r="M415" t="n">
-        <v>82.31</v>
-      </c>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
       <c r="N415" s="2" t="n">
-        <v>37.36</v>
+        <v>37.75</v>
       </c>
       <c r="O415" t="n">
         <v>32</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31850,28 +31850,44 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>89.95999999999999</v>
+      </c>
+      <c r="D415" t="n">
+        <v>92.69</v>
+      </c>
+      <c r="E415" t="n">
+        <v>89.16</v>
+      </c>
+      <c r="F415" t="n">
+        <v>92.36</v>
+      </c>
       <c r="G415" t="n">
-        <v>5111630</v>
-      </c>
-      <c r="H415" s="2" t="n">
-        <v>0</v>
+        <v>5144500</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-0.21</v>
       </c>
       <c r="I415" t="n">
         <v>5.2</v>
       </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
+      <c r="J415" t="n">
+        <v>96.48</v>
+      </c>
+      <c r="K415" t="n">
+        <v>91.29000000000001</v>
+      </c>
+      <c r="L415" t="n">
+        <v>91.27</v>
+      </c>
+      <c r="M415" t="n">
+        <v>82.31</v>
+      </c>
       <c r="N415" s="2" t="n">
-        <v>37.75</v>
+        <v>37.36</v>
       </c>
       <c r="O415" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31887,7 +31887,7 @@
         <v>37.36</v>
       </c>
       <c r="O415" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31887,7 +31887,7 @@
         <v>37.36</v>
       </c>
       <c r="O415" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31913,6 +31913,83 @@
       <c r="W415" s="1" t="n">
         <v>160.4</v>
       </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="D416" t="n">
+        <v>91.78</v>
+      </c>
+      <c r="E416" t="n">
+        <v>89.59</v>
+      </c>
+      <c r="F416" t="n">
+        <v>89.76000000000001</v>
+      </c>
+      <c r="G416" t="n">
+        <v>1654512</v>
+      </c>
+      <c r="H416" s="1" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="I416" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J416" t="n">
+        <v>96.42</v>
+      </c>
+      <c r="K416" t="n">
+        <v>91.37</v>
+      </c>
+      <c r="L416" t="n">
+        <v>91.34</v>
+      </c>
+      <c r="M416" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="N416" s="2" t="n">
+        <v>36.31</v>
+      </c>
+      <c r="O416" t="n">
+        <v>30</v>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>3rd: MA120, 50% cash, 5d</t>
+        </is>
+      </c>
+      <c r="S416" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="T416" s="2" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U416" s="2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V416" t="inlineStr"/>
+      <c r="W416" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31932,46 +31932,46 @@
         <v>91.78</v>
       </c>
       <c r="E416" t="n">
-        <v>89.59</v>
+        <v>87.04000000000001</v>
       </c>
       <c r="F416" t="n">
-        <v>89.76000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="G416" t="n">
-        <v>1654512</v>
+        <v>5096963</v>
       </c>
       <c r="H416" s="1" t="n">
-        <v>-2.82</v>
+        <v>-4.94</v>
       </c>
       <c r="I416" t="n">
         <v>5.2</v>
       </c>
       <c r="J416" t="n">
-        <v>96.42</v>
+        <v>96.31999999999999</v>
       </c>
       <c r="K416" t="n">
-        <v>91.37</v>
+        <v>91.34</v>
       </c>
       <c r="L416" t="n">
-        <v>91.34</v>
+        <v>91.33</v>
       </c>
       <c r="M416" t="n">
-        <v>82.40000000000001</v>
+        <v>82.39</v>
       </c>
       <c r="N416" s="2" t="n">
-        <v>36.31</v>
+        <v>32.86</v>
       </c>
       <c r="O416" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P416" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>extreme fear</t>
         </is>
       </c>
       <c r="Q416" t="inlineStr">
         <is>
-          <t>2x BUY</t>
+          <t>3x BUY</t>
         </is>
       </c>
       <c r="R416" t="inlineStr">
@@ -31980,13 +31980,13 @@
         </is>
       </c>
       <c r="S416" t="n">
-        <v>5.09</v>
+        <v>5.1</v>
       </c>
       <c r="T416" s="2" t="n">
-        <v>15.9</v>
+        <v>21.3</v>
       </c>
       <c r="U416" s="2" t="n">
-        <v>8.1</v>
+        <v>22</v>
       </c>
       <c r="V416" t="inlineStr"/>
       <c r="W416" s="2" t="inlineStr"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -7526,7 +7526,7 @@
         <v>59.05</v>
       </c>
       <c r="D93" t="n">
-        <v>59.23</v>
+        <v>59.24</v>
       </c>
       <c r="E93" t="n">
         <v>58.22</v>
@@ -31863,7 +31863,7 @@
         <v>92.36</v>
       </c>
       <c r="G415" t="n">
-        <v>5144500</v>
+        <v>5253000</v>
       </c>
       <c r="H415" s="1" t="n">
         <v>-0.21</v>
@@ -31935,13 +31935,13 @@
         <v>87.04000000000001</v>
       </c>
       <c r="F416" t="n">
-        <v>87.8</v>
+        <v>87.72</v>
       </c>
       <c r="G416" t="n">
-        <v>5096963</v>
+        <v>6539785</v>
       </c>
       <c r="H416" s="1" t="n">
-        <v>-4.94</v>
+        <v>-5.02</v>
       </c>
       <c r="I416" t="n">
         <v>5.2</v>
@@ -31959,7 +31959,7 @@
         <v>82.39</v>
       </c>
       <c r="N416" s="2" t="n">
-        <v>32.86</v>
+        <v>32.74</v>
       </c>
       <c r="O416" t="n">
         <v>18</v>
@@ -31983,13 +31983,15 @@
         <v>5.1</v>
       </c>
       <c r="T416" s="2" t="n">
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="U416" s="2" t="n">
-        <v>22</v>
+        <v>23.3</v>
       </c>
       <c r="V416" t="inlineStr"/>
-      <c r="W416" s="2" t="inlineStr"/>
+      <c r="W416" s="1" t="n">
+        <v>168.6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31846,25 +31846,41 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="D415" t="n">
+        <v>91.78</v>
+      </c>
+      <c r="E415" t="n">
+        <v>87.05</v>
+      </c>
+      <c r="F415" t="n">
+        <v>87.72</v>
+      </c>
       <c r="G415" t="n">
-        <v>6539785</v>
-      </c>
-      <c r="H415" s="2" t="n">
-        <v>0</v>
+        <v>6607100</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-5.02</v>
       </c>
       <c r="I415" t="n">
         <v>5.2</v>
       </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
+      <c r="J415" t="n">
+        <v>96.31999999999999</v>
+      </c>
+      <c r="K415" t="n">
+        <v>91.34</v>
+      </c>
+      <c r="L415" t="n">
+        <v>91.33</v>
+      </c>
+      <c r="M415" t="n">
+        <v>82.39</v>
+      </c>
       <c r="N415" s="2" t="n">
-        <v>42.19</v>
+        <v>32.74</v>
       </c>
       <c r="O415" t="n">
         <v>18</v>
@@ -31879,7 +31895,11 @@
           <t>3x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr"/>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>3rd: MA120, 50% cash, 5d</t>
+        </is>
+      </c>
       <c r="S415" t="n">
         <v>5.1</v>
       </c>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -7447,7 +7447,7 @@
         <v>59.05</v>
       </c>
       <c r="D92" t="n">
-        <v>59.23</v>
+        <v>59.24</v>
       </c>
       <c r="E92" t="n">
         <v>58.22</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -7447,7 +7447,7 @@
         <v>59.05</v>
       </c>
       <c r="D92" t="n">
-        <v>59.24</v>
+        <v>59.23</v>
       </c>
       <c r="E92" t="n">
         <v>58.22</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -12743,7 +12743,7 @@
         <v>5.2</v>
       </c>
       <c r="J162" t="n">
-        <v>68.62</v>
+        <v>68.61</v>
       </c>
       <c r="K162" t="n">
         <v>64.83</v>
@@ -24461,7 +24461,7 @@
         <v>91.90000000000001</v>
       </c>
       <c r="K317" t="n">
-        <v>76.65000000000001</v>
+        <v>76.64</v>
       </c>
       <c r="L317" t="n">
         <v>73.5</v>
@@ -29541,7 +29541,7 @@
         <v>90.25</v>
       </c>
       <c r="L384" t="n">
-        <v>85.04000000000001</v>
+        <v>85.05</v>
       </c>
       <c r="M384" t="n">
         <v>79</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31733,7 +31733,7 @@
         <v>32.74</v>
       </c>
       <c r="O413" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -923,7 +923,7 @@
         <v>5.2</v>
       </c>
       <c r="J6" t="n">
-        <v>55.5</v>
+        <v>55.51</v>
       </c>
       <c r="K6" t="n">
         <v>55.83</v>
@@ -9123,7 +9123,7 @@
         <v>5.2</v>
       </c>
       <c r="J114" t="n">
-        <v>61.01</v>
+        <v>61</v>
       </c>
       <c r="K114" t="n">
         <v>56.96</v>
@@ -29541,7 +29541,7 @@
         <v>90.25</v>
       </c>
       <c r="L384" t="n">
-        <v>85.05</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="M384" t="n">
         <v>79</v>
@@ -31733,7 +31733,7 @@
         <v>32.74</v>
       </c>
       <c r="O413" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31763,6 +31763,79 @@
       <c r="W413" s="7" t="n">
         <v>168.6</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>90.11</v>
+      </c>
+      <c r="D414" t="n">
+        <v>91.33</v>
+      </c>
+      <c r="E414" t="n">
+        <v>89.38</v>
+      </c>
+      <c r="F414" t="n">
+        <v>90.13</v>
+      </c>
+      <c r="G414" t="n">
+        <v>3943235</v>
+      </c>
+      <c r="H414" s="5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="I414" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J414" t="n">
+        <v>96.01000000000001</v>
+      </c>
+      <c r="K414" t="n">
+        <v>91.45999999999999</v>
+      </c>
+      <c r="L414" t="n">
+        <v>91.42</v>
+      </c>
+      <c r="M414" t="n">
+        <v>82.48999999999999</v>
+      </c>
+      <c r="N414" s="6" t="n">
+        <v>38.82</v>
+      </c>
+      <c r="O414" t="n">
+        <v>24</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>3x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="T414" s="6" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="U414" s="6" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -29541,7 +29541,7 @@
         <v>90.25</v>
       </c>
       <c r="L384" t="n">
-        <v>85.04000000000001</v>
+        <v>85.05</v>
       </c>
       <c r="M384" t="n">
         <v>79</v>
@@ -31785,22 +31785,22 @@
         <v>89.38</v>
       </c>
       <c r="F414" t="n">
-        <v>90.13</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="G414" t="n">
-        <v>3943235</v>
+        <v>6312993</v>
       </c>
       <c r="H414" s="5" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
       </c>
       <c r="J414" t="n">
-        <v>96.01000000000001</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="K414" t="n">
-        <v>91.45999999999999</v>
+        <v>91.45</v>
       </c>
       <c r="L414" t="n">
         <v>91.42</v>
@@ -31809,10 +31809,10 @@
         <v>82.48999999999999</v>
       </c>
       <c r="N414" s="6" t="n">
-        <v>38.82</v>
+        <v>37.9</v>
       </c>
       <c r="O414" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31826,16 +31826,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.13</v>
+        <v>5.14</v>
       </c>
       <c r="T414" s="6" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="U414" s="6" t="n">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="6" t="inlineStr"/>
+      <c r="W414" s="7" t="n">
+        <v>161.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31733,7 +31733,7 @@
         <v>37.9</v>
       </c>
       <c r="O413" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31759,6 +31759,79 @@
       <c r="W413" s="3" t="n">
         <v>161.9</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>88.98999999999999</v>
+      </c>
+      <c r="D414" t="n">
+        <v>90.84999999999999</v>
+      </c>
+      <c r="E414" t="n">
+        <v>87.81</v>
+      </c>
+      <c r="F414" t="n">
+        <v>90.51000000000001</v>
+      </c>
+      <c r="G414" t="n">
+        <v>1521592</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I414" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J414" t="n">
+        <v>95.63</v>
+      </c>
+      <c r="K414" t="n">
+        <v>91.58</v>
+      </c>
+      <c r="L414" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="M414" t="n">
+        <v>82.59</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>38.69</v>
+      </c>
+      <c r="O414" t="n">
+        <v>28</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31781,22 +31781,22 @@
         <v>87.81</v>
       </c>
       <c r="F414" t="n">
-        <v>90.51000000000001</v>
+        <v>89.83</v>
       </c>
       <c r="G414" t="n">
-        <v>1521592</v>
+        <v>2605956</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>0.8</v>
+        <v>0.04</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
       </c>
       <c r="J414" t="n">
-        <v>95.63</v>
+        <v>95.59</v>
       </c>
       <c r="K414" t="n">
-        <v>91.58</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="L414" t="n">
         <v>91.51000000000001</v>
@@ -31805,10 +31805,10 @@
         <v>82.59</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>38.69</v>
+        <v>36.8</v>
       </c>
       <c r="O414" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31822,13 +31822,13 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.08</v>
+        <v>5.12</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31709,7 +31709,7 @@
         <v>89.79000000000001</v>
       </c>
       <c r="G413" t="n">
-        <v>6336000</v>
+        <v>6398700</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>2.36</v>
@@ -31781,31 +31781,31 @@
         <v>87.81</v>
       </c>
       <c r="F414" t="n">
-        <v>89.83</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="G414" t="n">
-        <v>2605956</v>
-      </c>
-      <c r="H414" s="1" t="n">
-        <v>0.04</v>
+        <v>3053608</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>-0.28</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
       </c>
       <c r="J414" t="n">
-        <v>95.59</v>
+        <v>95.58</v>
       </c>
       <c r="K414" t="n">
         <v>91.56999999999999</v>
       </c>
       <c r="L414" t="n">
-        <v>91.51000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="M414" t="n">
         <v>82.59</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>36.8</v>
+        <v>36.27</v>
       </c>
       <c r="O414" t="n">
         <v>27</v>
@@ -31825,13 +31825,15 @@
         <v>5.12</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="3" t="n">
+        <v>160.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31733,7 +31733,7 @@
         <v>36.27</v>
       </c>
       <c r="O413" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31733,7 +31733,7 @@
         <v>36.27</v>
       </c>
       <c r="O413" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31759,6 +31759,77 @@
       <c r="W413" s="1" t="n">
         <v>160.4</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>88.98999999999999</v>
+      </c>
+      <c r="D414" t="n">
+        <v>90.93000000000001</v>
+      </c>
+      <c r="E414" t="n">
+        <v>90.45999999999999</v>
+      </c>
+      <c r="F414" t="n">
+        <v>90.78</v>
+      </c>
+      <c r="G414" t="n">
+        <v>406228</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I414" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J414" t="n">
+        <v>95.31</v>
+      </c>
+      <c r="K414" t="n">
+        <v>91.73</v>
+      </c>
+      <c r="L414" t="n">
+        <v>91.59</v>
+      </c>
+      <c r="M414" t="n">
+        <v>82.69</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>38.08</v>
+      </c>
+      <c r="O414" t="n">
+        <v>29</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T414" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="U414" s="3" t="inlineStr"/>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31733,7 +31733,7 @@
         <v>36.27</v>
       </c>
       <c r="O413" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31772,43 +31772,43 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>88.98999999999999</v>
+        <v>90.75</v>
       </c>
       <c r="D414" t="n">
-        <v>90.93000000000001</v>
+        <v>92.14</v>
       </c>
       <c r="E414" t="n">
-        <v>90.45999999999999</v>
+        <v>90.19</v>
       </c>
       <c r="F414" t="n">
-        <v>90.78</v>
+        <v>91.95</v>
       </c>
       <c r="G414" t="n">
-        <v>406228</v>
+        <v>2109830</v>
       </c>
       <c r="H414" s="2" t="n">
-        <v>1.38</v>
+        <v>2.69</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
       </c>
       <c r="J414" t="n">
-        <v>95.31</v>
+        <v>95.37</v>
       </c>
       <c r="K414" t="n">
-        <v>91.73</v>
+        <v>91.75</v>
       </c>
       <c r="L414" t="n">
-        <v>91.59</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="M414" t="n">
         <v>82.69</v>
       </c>
       <c r="N414" s="3" t="n">
-        <v>38.08</v>
+        <v>41.09</v>
       </c>
       <c r="O414" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31822,12 +31822,14 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.1</v>
+        <v>5.11</v>
       </c>
       <c r="T414" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="U414" s="3" t="inlineStr"/>
+        <v>16.6</v>
+      </c>
+      <c r="U414" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="3" t="inlineStr"/>
     </row>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -769,7 +769,7 @@
         <v>5.2</v>
       </c>
       <c r="J4" t="n">
-        <v>55.51</v>
+        <v>55.5</v>
       </c>
       <c r="K4" t="n">
         <v>55.83</v>
@@ -6945,7 +6945,7 @@
         <v>50.5</v>
       </c>
       <c r="M85" t="n">
-        <v>51.36</v>
+        <v>51.37</v>
       </c>
       <c r="N85" s="3" t="n">
         <v>61.11</v>
@@ -8969,7 +8969,7 @@
         <v>5.2</v>
       </c>
       <c r="J112" t="n">
-        <v>61</v>
+        <v>61.01</v>
       </c>
       <c r="K112" t="n">
         <v>56.96</v>
@@ -31709,7 +31709,7 @@
         <v>89.54000000000001</v>
       </c>
       <c r="G413" t="n">
-        <v>3115600</v>
+        <v>3233800</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-0.28</v>
@@ -31781,34 +31781,34 @@
         <v>90.19</v>
       </c>
       <c r="F414" t="n">
-        <v>91.95</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="G414" t="n">
-        <v>2109830</v>
+        <v>4604998</v>
       </c>
       <c r="H414" s="2" t="n">
-        <v>2.69</v>
+        <v>2.14</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
       </c>
       <c r="J414" t="n">
-        <v>95.37</v>
+        <v>95.34</v>
       </c>
       <c r="K414" t="n">
-        <v>91.75</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="L414" t="n">
-        <v>91.59999999999999</v>
+        <v>91.59</v>
       </c>
       <c r="M414" t="n">
         <v>82.69</v>
       </c>
       <c r="N414" s="3" t="n">
-        <v>41.09</v>
+        <v>39.86</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31822,16 +31822,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.11</v>
+        <v>5.15</v>
       </c>
       <c r="T414" s="3" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="U414" s="3" t="n">
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="3" t="inlineStr"/>
+      <c r="W414" s="3" t="n">
+        <v>150.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31771,41 +31771,25 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="C414" t="n">
-        <v>90.75</v>
-      </c>
-      <c r="D414" t="n">
-        <v>92.14</v>
-      </c>
-      <c r="E414" t="n">
-        <v>90.19</v>
-      </c>
-      <c r="F414" t="n">
-        <v>91.45999999999999</v>
-      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
         <v>4604998</v>
       </c>
-      <c r="H414" s="2" t="n">
-        <v>2.14</v>
+      <c r="H414" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
       </c>
-      <c r="J414" t="n">
-        <v>95.34</v>
-      </c>
-      <c r="K414" t="n">
-        <v>91.73999999999999</v>
-      </c>
-      <c r="L414" t="n">
-        <v>91.59</v>
-      </c>
-      <c r="M414" t="n">
-        <v>82.69</v>
-      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
       <c r="N414" s="3" t="n">
-        <v>39.86</v>
+        <v>34.53</v>
       </c>
       <c r="O414" t="n">
         <v>31</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31771,28 +31771,44 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="D414" t="n">
+        <v>92.15000000000001</v>
+      </c>
+      <c r="E414" t="n">
+        <v>90.14</v>
+      </c>
+      <c r="F414" t="n">
+        <v>91.45999999999999</v>
+      </c>
       <c r="G414" t="n">
-        <v>4604998</v>
-      </c>
-      <c r="H414" s="3" t="n">
-        <v>0</v>
+        <v>4646900</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>2.14</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>95.34</v>
+      </c>
+      <c r="K414" t="n">
+        <v>91.73999999999999</v>
+      </c>
+      <c r="L414" t="n">
+        <v>91.59</v>
+      </c>
+      <c r="M414" t="n">
+        <v>82.69</v>
+      </c>
       <c r="N414" s="3" t="n">
-        <v>34.53</v>
+        <v>39.86</v>
       </c>
       <c r="O414" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31808,7 +31808,7 @@
         <v>39.86</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31834,6 +31834,77 @@
       <c r="W414" s="3" t="n">
         <v>150.4</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="D415" t="n">
+        <v>88.79000000000001</v>
+      </c>
+      <c r="E415" t="n">
+        <v>88.23</v>
+      </c>
+      <c r="F415" t="n">
+        <v>88.54000000000001</v>
+      </c>
+      <c r="G415" t="n">
+        <v>665865</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-3.19</v>
+      </c>
+      <c r="I415" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J415" t="n">
+        <v>94.97</v>
+      </c>
+      <c r="K415" t="n">
+        <v>91.93000000000001</v>
+      </c>
+      <c r="L415" t="n">
+        <v>91.64</v>
+      </c>
+      <c r="M415" t="n">
+        <v>82.77</v>
+      </c>
+      <c r="N415" s="3" t="n">
+        <v>30.52</v>
+      </c>
+      <c r="O415" t="n">
+        <v>28</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="T415" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="U415" s="3" t="inlineStr"/>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31808,7 +31808,7 @@
         <v>39.86</v>
       </c>
       <c r="O414" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31836,75 +31836,77 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>QLD</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
+      <c r="A415" s="4" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B415" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="C415" t="n">
-        <v>90.75</v>
-      </c>
-      <c r="D415" t="n">
-        <v>88.79000000000001</v>
-      </c>
-      <c r="E415" t="n">
-        <v>88.23</v>
-      </c>
-      <c r="F415" t="n">
-        <v>88.54000000000001</v>
-      </c>
-      <c r="G415" t="n">
-        <v>665865</v>
-      </c>
-      <c r="H415" s="1" t="n">
-        <v>-3.19</v>
-      </c>
-      <c r="I415" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J415" t="n">
-        <v>94.97</v>
-      </c>
-      <c r="K415" t="n">
-        <v>91.93000000000001</v>
-      </c>
-      <c r="L415" t="n">
-        <v>91.64</v>
-      </c>
-      <c r="M415" t="n">
-        <v>82.77</v>
-      </c>
-      <c r="N415" s="3" t="n">
-        <v>30.52</v>
-      </c>
-      <c r="O415" t="n">
-        <v>28</v>
-      </c>
-      <c r="P415" t="inlineStr">
-        <is>
-          <t>fear</t>
-        </is>
-      </c>
-      <c r="Q415" t="inlineStr">
+      <c r="C415" s="4" t="n">
+        <v>88.53</v>
+      </c>
+      <c r="D415" s="4" t="n">
+        <v>88.98</v>
+      </c>
+      <c r="E415" s="4" t="n">
+        <v>85.97</v>
+      </c>
+      <c r="F415" s="4" t="n">
+        <v>86.48999999999999</v>
+      </c>
+      <c r="G415" s="4" t="n">
+        <v>3954005</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>-5.43</v>
+      </c>
+      <c r="I415" s="4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J415" s="4" t="n">
+        <v>94.86</v>
+      </c>
+      <c r="K415" s="4" t="n">
+        <v>91.89</v>
+      </c>
+      <c r="L415" s="4" t="n">
+        <v>91.62</v>
+      </c>
+      <c r="M415" s="4" t="n">
+        <v>82.76000000000001</v>
+      </c>
+      <c r="N415" s="6" t="n">
+        <v>28.17</v>
+      </c>
+      <c r="O415" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="P415" s="4" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q415" s="4" t="inlineStr">
         <is>
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr"/>
-      <c r="S415" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="T415" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="U415" s="3" t="inlineStr"/>
-      <c r="V415" t="inlineStr"/>
-      <c r="W415" s="3" t="inlineStr"/>
+      <c r="R415" s="4" t="inlineStr"/>
+      <c r="S415" s="4" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T415" s="7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="U415" s="7" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="V415" s="4" t="inlineStr"/>
+      <c r="W415" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31784,7 +31784,7 @@
         <v>91.45999999999999</v>
       </c>
       <c r="G414" t="n">
-        <v>4646900</v>
+        <v>4922100</v>
       </c>
       <c r="H414" s="2" t="n">
         <v>2.14</v>
@@ -31853,22 +31853,22 @@
         <v>88.98</v>
       </c>
       <c r="E415" s="4" t="n">
-        <v>85.97</v>
+        <v>85.59</v>
       </c>
       <c r="F415" s="4" t="n">
-        <v>86.48999999999999</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="G415" s="4" t="n">
-        <v>3954005</v>
+        <v>6099674</v>
       </c>
       <c r="H415" s="5" t="n">
-        <v>-5.43</v>
+        <v>-5.69</v>
       </c>
       <c r="I415" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="J415" s="4" t="n">
-        <v>94.86</v>
+        <v>94.84999999999999</v>
       </c>
       <c r="K415" s="4" t="n">
         <v>91.89</v>
@@ -31880,10 +31880,10 @@
         <v>82.76000000000001</v>
       </c>
       <c r="N415" s="6" t="n">
-        <v>28.17</v>
+        <v>27.93</v>
       </c>
       <c r="O415" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
@@ -31900,13 +31900,15 @@
         <v>4.95</v>
       </c>
       <c r="T415" s="7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="U415" s="7" t="n">
-        <v>14.7</v>
+        <v>15.2</v>
       </c>
       <c r="V415" s="4" t="inlineStr"/>
-      <c r="W415" s="7" t="inlineStr"/>
+      <c r="W415" s="7" t="n">
+        <v>152.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31836,77 +31836,61 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="4" t="inlineStr">
-        <is>
-          <t>QLD</t>
-        </is>
-      </c>
-      <c r="B415" s="4" t="inlineStr">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="C415" s="4" t="n">
-        <v>88.53</v>
-      </c>
-      <c r="D415" s="4" t="n">
-        <v>88.98</v>
-      </c>
-      <c r="E415" s="4" t="n">
-        <v>85.59</v>
-      </c>
-      <c r="F415" s="4" t="n">
-        <v>86.26000000000001</v>
-      </c>
-      <c r="G415" s="4" t="n">
-        <v>6099674</v>
-      </c>
-      <c r="H415" s="5" t="n">
-        <v>-5.69</v>
-      </c>
-      <c r="I415" s="4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J415" s="4" t="n">
-        <v>94.84999999999999</v>
-      </c>
-      <c r="K415" s="4" t="n">
-        <v>91.89</v>
-      </c>
-      <c r="L415" s="4" t="n">
-        <v>91.62</v>
-      </c>
-      <c r="M415" s="4" t="n">
-        <v>82.76000000000001</v>
-      </c>
-      <c r="N415" s="6" t="n">
-        <v>27.93</v>
-      </c>
-      <c r="O415" s="4" t="n">
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="n">
+        <v>6103668</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I415" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
+      <c r="N415" s="3" t="n">
+        <v>34.62</v>
+      </c>
+      <c r="O415" t="n">
         <v>20</v>
       </c>
-      <c r="P415" s="4" t="inlineStr">
+      <c r="P415" t="inlineStr">
         <is>
           <t>extreme fear</t>
         </is>
       </c>
-      <c r="Q415" s="4" t="inlineStr">
-        <is>
-          <t>2x BUY</t>
-        </is>
-      </c>
-      <c r="R415" s="4" t="inlineStr"/>
-      <c r="S415" s="4" t="n">
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>3x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
         <v>4.95</v>
       </c>
-      <c r="T415" s="7" t="n">
+      <c r="T415" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="U415" s="7" t="n">
+      <c r="U415" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="V415" s="4" t="inlineStr"/>
-      <c r="W415" s="7" t="n">
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="3" t="n">
         <v>152.4</v>
       </c>
     </row>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31836,61 +31836,77 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>QLD</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
+      <c r="A415" s="4" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B415" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
-      <c r="G415" t="n">
-        <v>6103668</v>
-      </c>
-      <c r="H415" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I415" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
-      <c r="N415" s="3" t="n">
-        <v>34.62</v>
-      </c>
-      <c r="O415" t="n">
+      <c r="C415" s="4" t="n">
+        <v>88.53</v>
+      </c>
+      <c r="D415" s="4" t="n">
+        <v>88.98999999999999</v>
+      </c>
+      <c r="E415" s="4" t="n">
+        <v>85.59</v>
+      </c>
+      <c r="F415" s="4" t="n">
+        <v>86.26000000000001</v>
+      </c>
+      <c r="G415" s="4" t="n">
+        <v>6106100</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>-5.69</v>
+      </c>
+      <c r="I415" s="4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J415" s="4" t="n">
+        <v>94.84999999999999</v>
+      </c>
+      <c r="K415" s="4" t="n">
+        <v>91.89</v>
+      </c>
+      <c r="L415" s="4" t="n">
+        <v>91.62</v>
+      </c>
+      <c r="M415" s="4" t="n">
+        <v>82.76000000000001</v>
+      </c>
+      <c r="N415" s="6" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="O415" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="P415" t="inlineStr">
+      <c r="P415" s="4" t="inlineStr">
         <is>
           <t>extreme fear</t>
         </is>
       </c>
-      <c r="Q415" t="inlineStr">
-        <is>
-          <t>3x BUY</t>
-        </is>
-      </c>
-      <c r="R415" t="inlineStr"/>
-      <c r="S415" t="n">
+      <c r="Q415" s="4" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" s="4" t="inlineStr"/>
+      <c r="S415" s="4" t="n">
         <v>4.95</v>
       </c>
-      <c r="T415" s="3" t="n">
+      <c r="T415" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="U415" s="3" t="n">
+      <c r="U415" s="7" t="n">
         <v>15.2</v>
       </c>
-      <c r="V415" t="inlineStr"/>
-      <c r="W415" s="3" t="n">
+      <c r="V415" s="4" t="inlineStr"/>
+      <c r="W415" s="7" t="n">
         <v>152.4</v>
       </c>
     </row>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31883,7 +31883,7 @@
         <v>27.93</v>
       </c>
       <c r="O415" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7143,7 +7143,7 @@
         <v>59.05</v>
       </c>
       <c r="D88" t="n">
-        <v>59.23</v>
+        <v>59.24</v>
       </c>
       <c r="E88" t="n">
         <v>58.22</v>
@@ -31883,7 +31883,7 @@
         <v>27.93</v>
       </c>
       <c r="O415" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
@@ -31909,6 +31909,79 @@
       <c r="W415" s="7" t="n">
         <v>152.4</v>
       </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>85.61</v>
+      </c>
+      <c r="D416" t="n">
+        <v>87.34</v>
+      </c>
+      <c r="E416" t="n">
+        <v>85.39</v>
+      </c>
+      <c r="F416" t="n">
+        <v>86.56</v>
+      </c>
+      <c r="G416" t="n">
+        <v>3267162</v>
+      </c>
+      <c r="H416" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I416" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J416" t="n">
+        <v>94.33</v>
+      </c>
+      <c r="K416" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="L416" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="M416" t="n">
+        <v>82.83</v>
+      </c>
+      <c r="N416" s="2" t="n">
+        <v>23.94</v>
+      </c>
+      <c r="O416" t="n">
+        <v>20</v>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr"/>
+      <c r="S416" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="T416" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="U416" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="V416" t="inlineStr"/>
+      <c r="W416" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31859,7 +31859,7 @@
         <v>86.26000000000001</v>
       </c>
       <c r="G415" s="4" t="n">
-        <v>6106100</v>
+        <v>6212800</v>
       </c>
       <c r="H415" s="5" t="n">
         <v>-5.69</v>
@@ -31931,19 +31931,19 @@
         <v>85.39</v>
       </c>
       <c r="F416" t="n">
-        <v>86.56</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="G416" t="n">
-        <v>3267162</v>
-      </c>
-      <c r="H416" s="2" t="n">
-        <v>0.35</v>
+        <v>3977972</v>
+      </c>
+      <c r="H416" s="1" t="n">
+        <v>-0.13</v>
       </c>
       <c r="I416" t="n">
         <v>5.2</v>
       </c>
       <c r="J416" t="n">
-        <v>94.33</v>
+        <v>94.31</v>
       </c>
       <c r="K416" t="n">
         <v>91.95</v>
@@ -31955,10 +31955,10 @@
         <v>82.83</v>
       </c>
       <c r="N416" s="2" t="n">
-        <v>23.94</v>
+        <v>22.93</v>
       </c>
       <c r="O416" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P416" t="inlineStr">
         <is>
@@ -31972,16 +31972,18 @@
       </c>
       <c r="R416" t="inlineStr"/>
       <c r="S416" t="n">
-        <v>4.98</v>
+        <v>4.99</v>
       </c>
       <c r="T416" s="3" t="n">
-        <v>20.1</v>
+        <v>19.5</v>
       </c>
       <c r="U416" s="3" t="n">
-        <v>15.5</v>
+        <v>16.8</v>
       </c>
       <c r="V416" t="inlineStr"/>
-      <c r="W416" s="3" t="inlineStr"/>
+      <c r="W416" s="3" t="n">
+        <v>151.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31842,25 +31842,41 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>85.61</v>
+      </c>
+      <c r="D415" t="n">
+        <v>87.34999999999999</v>
+      </c>
+      <c r="E415" t="n">
+        <v>85.39</v>
+      </c>
+      <c r="F415" t="n">
+        <v>86.15000000000001</v>
+      </c>
       <c r="G415" t="n">
-        <v>3977972</v>
-      </c>
-      <c r="H415" s="3" t="n">
-        <v>0</v>
+        <v>3990400</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-0.13</v>
       </c>
       <c r="I415" t="n">
         <v>5.2</v>
       </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
+      <c r="J415" t="n">
+        <v>94.31</v>
+      </c>
+      <c r="K415" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="L415" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="M415" t="n">
+        <v>82.83</v>
+      </c>
       <c r="N415" s="2" t="n">
-        <v>23.03</v>
+        <v>22.93</v>
       </c>
       <c r="O415" t="n">
         <v>21</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6712,7 +6712,7 @@
         <v>50.5</v>
       </c>
       <c r="M82" t="n">
-        <v>51.37</v>
+        <v>51.36</v>
       </c>
       <c r="N82" s="6" t="n">
         <v>61.11</v>
@@ -8736,7 +8736,7 @@
         <v>5.2</v>
       </c>
       <c r="J109" t="n">
-        <v>61.01</v>
+        <v>61</v>
       </c>
       <c r="K109" t="n">
         <v>56.96</v>
@@ -31725,7 +31725,7 @@
         <v>22.93</v>
       </c>
       <c r="O413" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31751,6 +31751,79 @@
       <c r="W413" s="6" t="n">
         <v>151.8</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="D414" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="E414" t="n">
+        <v>86.45999999999999</v>
+      </c>
+      <c r="F414" t="n">
+        <v>88.25</v>
+      </c>
+      <c r="G414" t="n">
+        <v>2441709</v>
+      </c>
+      <c r="H414" s="5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I414" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J414" t="n">
+        <v>93.98</v>
+      </c>
+      <c r="K414" t="n">
+        <v>92.02</v>
+      </c>
+      <c r="L414" t="n">
+        <v>91.69</v>
+      </c>
+      <c r="M414" t="n">
+        <v>82.91</v>
+      </c>
+      <c r="N414" s="5" t="n">
+        <v>26.34</v>
+      </c>
+      <c r="O414" t="n">
+        <v>27</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="T414" s="6" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="U414" s="6" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -29154,7 +29154,7 @@
         <v>90.25</v>
       </c>
       <c r="L379" t="n">
-        <v>85.05</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="M379" t="n">
         <v>79</v>
@@ -31773,19 +31773,19 @@
         <v>86.45999999999999</v>
       </c>
       <c r="F414" t="n">
-        <v>88.25</v>
+        <v>88.03</v>
       </c>
       <c r="G414" t="n">
-        <v>2441709</v>
+        <v>4513346</v>
       </c>
       <c r="H414" s="5" t="n">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
       </c>
       <c r="J414" t="n">
-        <v>93.98</v>
+        <v>93.97</v>
       </c>
       <c r="K414" t="n">
         <v>92.02</v>
@@ -31797,7 +31797,7 @@
         <v>82.91</v>
       </c>
       <c r="N414" s="5" t="n">
-        <v>26.34</v>
+        <v>25.72</v>
       </c>
       <c r="O414" t="n">
         <v>27</v>
@@ -31814,16 +31814,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
       <c r="T414" s="6" t="n">
         <v>18.4</v>
       </c>
       <c r="U414" s="6" t="n">
-        <v>9.1</v>
+        <v>10.5</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="6" t="inlineStr"/>
+      <c r="W414" s="6" t="n">
+        <v>151</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31622,7 +31622,7 @@
         <v>86.15000000000001</v>
       </c>
       <c r="G412" t="n">
-        <v>3990400</v>
+        <v>4014500</v>
       </c>
       <c r="H412" s="7" t="n">
         <v>-0.13</v>
@@ -31684,28 +31684,44 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr"/>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="C413" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="D413" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="E413" t="n">
+        <v>86.45999999999999</v>
+      </c>
+      <c r="F413" t="n">
+        <v>88.03</v>
+      </c>
       <c r="G413" t="n">
-        <v>4513346</v>
-      </c>
-      <c r="H413" s="2" t="n">
-        <v>0</v>
+        <v>4603800</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>2.18</v>
       </c>
       <c r="I413" t="n">
         <v>5.2</v>
       </c>
-      <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr"/>
-      <c r="M413" t="inlineStr"/>
+      <c r="J413" t="n">
+        <v>93.97</v>
+      </c>
+      <c r="K413" t="n">
+        <v>92.02</v>
+      </c>
+      <c r="L413" t="n">
+        <v>91.69</v>
+      </c>
+      <c r="M413" t="n">
+        <v>82.91</v>
+      </c>
       <c r="N413" s="1" t="n">
-        <v>19.99</v>
+        <v>25.72</v>
       </c>
       <c r="O413" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7302,7 +7302,7 @@
         <v>57.47</v>
       </c>
       <c r="K90" t="n">
-        <v>51.88</v>
+        <v>51.89</v>
       </c>
       <c r="L90" t="n">
         <v>50.87</v>
@@ -21292,7 +21292,7 @@
         <v>5.2</v>
       </c>
       <c r="J275" t="n">
-        <v>63.35</v>
+        <v>63.34</v>
       </c>
       <c r="K275" t="n">
         <v>67.37</v>
@@ -29075,7 +29075,7 @@
         <v>90.25</v>
       </c>
       <c r="L378" t="n">
-        <v>85.04000000000001</v>
+        <v>85.05</v>
       </c>
       <c r="M378" t="n">
         <v>79</v>
@@ -31721,7 +31721,7 @@
         <v>25.72</v>
       </c>
       <c r="O413" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31747,6 +31747,79 @@
       <c r="W413" s="2" t="n">
         <v>151</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>88.78</v>
+      </c>
+      <c r="D414" t="n">
+        <v>89.53</v>
+      </c>
+      <c r="E414" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="F414" t="n">
+        <v>88.83</v>
+      </c>
+      <c r="G414" t="n">
+        <v>682228</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I414" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J414" t="n">
+        <v>93.65000000000001</v>
+      </c>
+      <c r="K414" t="n">
+        <v>92.06</v>
+      </c>
+      <c r="L414" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="M414" t="n">
+        <v>82.98999999999999</v>
+      </c>
+      <c r="N414" s="1" t="n">
+        <v>28.49</v>
+      </c>
+      <c r="O414" t="n">
+        <v>32</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -7302,7 +7302,7 @@
         <v>57.47</v>
       </c>
       <c r="K90" t="n">
-        <v>51.89</v>
+        <v>51.88</v>
       </c>
       <c r="L90" t="n">
         <v>50.87</v>
@@ -21292,7 +21292,7 @@
         <v>5.2</v>
       </c>
       <c r="J275" t="n">
-        <v>63.34</v>
+        <v>63.35</v>
       </c>
       <c r="K275" t="n">
         <v>67.37</v>
@@ -29075,7 +29075,7 @@
         <v>90.25</v>
       </c>
       <c r="L378" t="n">
-        <v>85.05</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="M378" t="n">
         <v>79</v>
@@ -31697,7 +31697,7 @@
         <v>88.03</v>
       </c>
       <c r="G413" t="n">
-        <v>4603800</v>
+        <v>4639300</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>2.18</v>
@@ -31763,40 +31763,40 @@
         <v>88.78</v>
       </c>
       <c r="D414" t="n">
-        <v>89.53</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="E414" t="n">
-        <v>88.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="F414" t="n">
-        <v>88.83</v>
+        <v>90.27</v>
       </c>
       <c r="G414" t="n">
-        <v>682228</v>
+        <v>2548279</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>0.91</v>
+        <v>2.54</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
       </c>
       <c r="J414" t="n">
-        <v>93.65000000000001</v>
+        <v>93.72</v>
       </c>
       <c r="K414" t="n">
-        <v>92.06</v>
+        <v>92.08</v>
       </c>
       <c r="L414" t="n">
-        <v>91.7</v>
+        <v>91.70999999999999</v>
       </c>
       <c r="M414" t="n">
-        <v>82.98999999999999</v>
-      </c>
-      <c r="N414" s="1" t="n">
-        <v>28.49</v>
+        <v>83</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>32.18</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31810,13 +31810,13 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -21292,7 +21292,7 @@
         <v>5.2</v>
       </c>
       <c r="J275" t="n">
-        <v>63.35</v>
+        <v>63.34</v>
       </c>
       <c r="K275" t="n">
         <v>67.37</v>
@@ -29463,7 +29463,7 @@
         <v>51.22</v>
       </c>
       <c r="O383" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P383" t="inlineStr">
         <is>
@@ -29538,7 +29538,7 @@
         <v>44.13</v>
       </c>
       <c r="O384" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P384" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>45.56</v>
       </c>
       <c r="O386" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P386" t="inlineStr">
         <is>
@@ -29763,7 +29763,7 @@
         <v>52.57</v>
       </c>
       <c r="O387" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P387" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>68.20999999999999</v>
       </c>
       <c r="O390" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P390" t="inlineStr">
         <is>
@@ -30063,7 +30063,7 @@
         <v>64.64</v>
       </c>
       <c r="O391" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P391" t="inlineStr">
         <is>
@@ -30213,7 +30213,7 @@
         <v>59.86</v>
       </c>
       <c r="O393" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P393" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>62.01</v>
       </c>
       <c r="O394" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P394" t="inlineStr">
         <is>
@@ -30513,7 +30513,7 @@
         <v>75.29000000000001</v>
       </c>
       <c r="O397" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P397" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>81.56</v>
       </c>
       <c r="O398" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P398" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>77.23</v>
       </c>
       <c r="O400" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P400" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>65.97</v>
       </c>
       <c r="O401" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P401" t="inlineStr">
         <is>
@@ -30888,11 +30888,11 @@
         <v>56.74</v>
       </c>
       <c r="O402" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P402" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="Q402" t="inlineStr">
@@ -30963,7 +30963,7 @@
         <v>47.78</v>
       </c>
       <c r="O403" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P403" t="inlineStr">
         <is>
@@ -31038,11 +31038,11 @@
         <v>50.93</v>
       </c>
       <c r="O404" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P404" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q404" t="inlineStr">
@@ -31113,7 +31113,7 @@
         <v>40.56</v>
       </c>
       <c r="O405" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P405" t="inlineStr">
         <is>
@@ -31192,7 +31192,7 @@
         <v>37.36</v>
       </c>
       <c r="O406" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P406" t="inlineStr">
         <is>
@@ -31267,7 +31267,7 @@
         <v>32.74</v>
       </c>
       <c r="O407" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="P407" t="inlineStr">
         <is>
@@ -31346,7 +31346,7 @@
         <v>37.9</v>
       </c>
       <c r="O408" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P408" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>36.27</v>
       </c>
       <c r="O409" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P409" t="inlineStr">
         <is>
@@ -31496,7 +31496,7 @@
         <v>39.86</v>
       </c>
       <c r="O410" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="P410" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>27.93</v>
       </c>
       <c r="O411" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P411" s="3" t="inlineStr">
         <is>
@@ -31646,7 +31646,7 @@
         <v>22.93</v>
       </c>
       <c r="O412" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31721,7 +31721,7 @@
         <v>25.72</v>
       </c>
       <c r="O413" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31769,13 +31769,13 @@
         <v>88.40000000000001</v>
       </c>
       <c r="F414" t="n">
-        <v>90.27</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="G414" t="n">
-        <v>2548279</v>
+        <v>2938998</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
@@ -31793,10 +31793,10 @@
         <v>83</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>32.18</v>
+        <v>32.22</v>
       </c>
       <c r="O414" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31819,7 +31819,9 @@
         <v>12.5</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>149.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31717,7 +31717,7 @@
         <v>32.22</v>
       </c>
       <c r="O413" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31743,6 +31743,79 @@
       <c r="W413" s="7" t="n">
         <v>149.2</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>90.98999999999999</v>
+      </c>
+      <c r="D414" t="n">
+        <v>91.12</v>
+      </c>
+      <c r="E414" t="n">
+        <v>90.04000000000001</v>
+      </c>
+      <c r="F414" t="n">
+        <v>90.69</v>
+      </c>
+      <c r="G414" t="n">
+        <v>1649041</v>
+      </c>
+      <c r="H414" s="6" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I414" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J414" t="n">
+        <v>93.48</v>
+      </c>
+      <c r="K414" t="n">
+        <v>92.05</v>
+      </c>
+      <c r="L414" t="n">
+        <v>91.73</v>
+      </c>
+      <c r="M414" t="n">
+        <v>83.08</v>
+      </c>
+      <c r="N414" s="7" t="n">
+        <v>36.66</v>
+      </c>
+      <c r="O414" t="n">
+        <v>35</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="T414" s="7" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="U414" s="7" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -21213,7 +21213,7 @@
         <v>5.2</v>
       </c>
       <c r="J274" t="n">
-        <v>63.34</v>
+        <v>63.35</v>
       </c>
       <c r="K274" t="n">
         <v>67.37</v>
@@ -28996,7 +28996,7 @@
         <v>90.25</v>
       </c>
       <c r="L377" t="n">
-        <v>85.04000000000001</v>
+        <v>85.05</v>
       </c>
       <c r="M377" t="n">
         <v>79</v>
@@ -31693,7 +31693,7 @@
         <v>90.29000000000001</v>
       </c>
       <c r="G413" t="n">
-        <v>2965300</v>
+        <v>3023600</v>
       </c>
       <c r="H413" s="6" t="n">
         <v>2.57</v>
@@ -31759,40 +31759,40 @@
         <v>90.98999999999999</v>
       </c>
       <c r="D414" t="n">
-        <v>91.12</v>
+        <v>91.48</v>
       </c>
       <c r="E414" t="n">
         <v>90.04000000000001</v>
       </c>
       <c r="F414" t="n">
-        <v>90.69</v>
+        <v>91.39</v>
       </c>
       <c r="G414" t="n">
-        <v>1649041</v>
+        <v>4249851</v>
       </c>
       <c r="H414" s="6" t="n">
-        <v>0.44</v>
+        <v>1.22</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
       </c>
       <c r="J414" t="n">
-        <v>93.48</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="K414" t="n">
-        <v>92.05</v>
+        <v>92.06</v>
       </c>
       <c r="L414" t="n">
-        <v>91.73</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="M414" t="n">
-        <v>83.08</v>
+        <v>83.09</v>
       </c>
       <c r="N414" s="7" t="n">
-        <v>36.66</v>
+        <v>38.34</v>
       </c>
       <c r="O414" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31806,16 +31806,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.02</v>
+        <v>5.05</v>
       </c>
       <c r="T414" s="7" t="n">
-        <v>17.3</v>
+        <v>16.9</v>
       </c>
       <c r="U414" s="7" t="n">
-        <v>14.4</v>
+        <v>13.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="7" t="inlineStr"/>
+      <c r="W414" s="7" t="n">
+        <v>148.7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31768,7 +31768,7 @@
         <v>91.39</v>
       </c>
       <c r="G414" t="n">
-        <v>4249851</v>
+        <v>4226500</v>
       </c>
       <c r="H414" s="6" t="n">
         <v>1.22</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31792,7 +31792,7 @@
         <v>38.34</v>
       </c>
       <c r="O414" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31818,6 +31818,79 @@
       <c r="W414" s="7" t="n">
         <v>148.7</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>89.06999999999999</v>
+      </c>
+      <c r="D415" t="n">
+        <v>89.43000000000001</v>
+      </c>
+      <c r="E415" t="n">
+        <v>87.84</v>
+      </c>
+      <c r="F415" t="n">
+        <v>88.77</v>
+      </c>
+      <c r="G415" t="n">
+        <v>2313982</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>-2.87</v>
+      </c>
+      <c r="I415" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J415" t="n">
+        <v>93.14</v>
+      </c>
+      <c r="K415" t="n">
+        <v>92.03</v>
+      </c>
+      <c r="L415" t="n">
+        <v>91.72</v>
+      </c>
+      <c r="M415" t="n">
+        <v>83.17</v>
+      </c>
+      <c r="N415" s="7" t="n">
+        <v>32.84</v>
+      </c>
+      <c r="O415" t="n">
+        <v>35</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5</v>
+      </c>
+      <c r="T415" s="7" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="U415" s="7" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31768,7 +31768,7 @@
         <v>91.39</v>
       </c>
       <c r="G414" t="n">
-        <v>4226500</v>
+        <v>4318000</v>
       </c>
       <c r="H414" s="6" t="n">
         <v>1.22</v>
@@ -31840,13 +31840,13 @@
         <v>87.84</v>
       </c>
       <c r="F415" t="n">
-        <v>88.77</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="G415" t="n">
-        <v>2313982</v>
+        <v>4227459</v>
       </c>
       <c r="H415" s="5" t="n">
-        <v>-2.87</v>
+        <v>-2.9</v>
       </c>
       <c r="I415" t="n">
         <v>5.2</v>
@@ -31864,7 +31864,7 @@
         <v>83.17</v>
       </c>
       <c r="N415" s="7" t="n">
-        <v>32.84</v>
+        <v>32.8</v>
       </c>
       <c r="O415" t="n">
         <v>35</v>
@@ -31881,16 +31881,18 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="T415" s="7" t="n">
-        <v>16.3</v>
+        <v>17.2</v>
       </c>
       <c r="U415" s="7" t="n">
-        <v>10.2</v>
+        <v>13.6</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="7" t="inlineStr"/>
+      <c r="W415" s="7" t="n">
+        <v>151</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31834,16 +31834,16 @@
         <v>89.06999999999999</v>
       </c>
       <c r="D415" t="n">
-        <v>89.43000000000001</v>
+        <v>89.45</v>
       </c>
       <c r="E415" t="n">
-        <v>87.84</v>
+        <v>87.83</v>
       </c>
       <c r="F415" t="n">
         <v>88.73999999999999</v>
       </c>
       <c r="G415" t="n">
-        <v>4227459</v>
+        <v>4320300</v>
       </c>
       <c r="H415" s="5" t="n">
         <v>-2.9</v>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31867,7 +31867,7 @@
         <v>32.8</v>
       </c>
       <c r="O415" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31867,7 +31867,7 @@
         <v>32.8</v>
       </c>
       <c r="O415" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31893,6 +31893,83 @@
       <c r="W415" s="7" t="n">
         <v>151</v>
       </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B416" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C416" s="1" t="n">
+        <v>84.26000000000001</v>
+      </c>
+      <c r="D416" s="1" t="n">
+        <v>84.56</v>
+      </c>
+      <c r="E416" s="1" t="n">
+        <v>83.11</v>
+      </c>
+      <c r="F416" s="1" t="n">
+        <v>83.18000000000001</v>
+      </c>
+      <c r="G416" s="1" t="n">
+        <v>3250962</v>
+      </c>
+      <c r="H416" s="2" t="n">
+        <v>-6.27</v>
+      </c>
+      <c r="I416" s="1" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J416" s="1" t="n">
+        <v>92.39</v>
+      </c>
+      <c r="K416" s="1" t="n">
+        <v>91.92</v>
+      </c>
+      <c r="L416" s="1" t="n">
+        <v>91.64</v>
+      </c>
+      <c r="M416" s="1" t="n">
+        <v>83.22</v>
+      </c>
+      <c r="N416" s="3" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="O416" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="P416" s="1" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q416" s="1" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R416" s="1" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S416" s="1" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T416" s="4" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="U416" s="4" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="V416" s="1" t="inlineStr"/>
+      <c r="W416" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31843,7 +31843,7 @@
         <v>88.73999999999999</v>
       </c>
       <c r="G415" t="n">
-        <v>4320300</v>
+        <v>4498400</v>
       </c>
       <c r="H415" s="5" t="n">
         <v>-2.9</v>
@@ -31912,25 +31912,25 @@
         <v>84.56</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>83.11</v>
+        <v>80.81999999999999</v>
       </c>
       <c r="F416" s="1" t="n">
-        <v>83.18000000000001</v>
+        <v>82.59</v>
       </c>
       <c r="G416" s="1" t="n">
-        <v>3250962</v>
+        <v>7937919</v>
       </c>
       <c r="H416" s="2" t="n">
-        <v>-6.27</v>
+        <v>-6.93</v>
       </c>
       <c r="I416" s="1" t="n">
         <v>5.2</v>
       </c>
       <c r="J416" s="1" t="n">
-        <v>92.39</v>
+        <v>92.36</v>
       </c>
       <c r="K416" s="1" t="n">
-        <v>91.92</v>
+        <v>91.91</v>
       </c>
       <c r="L416" s="1" t="n">
         <v>91.64</v>
@@ -31939,10 +31939,10 @@
         <v>83.22</v>
       </c>
       <c r="N416" s="3" t="n">
-        <v>28.52</v>
+        <v>28.01</v>
       </c>
       <c r="O416" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P416" s="1" t="inlineStr">
         <is>
@@ -31960,13 +31960,13 @@
         </is>
       </c>
       <c r="S416" s="1" t="n">
-        <v>4.95</v>
+        <v>4.93</v>
       </c>
       <c r="T416" s="4" t="n">
         <v>19.4</v>
       </c>
       <c r="U416" s="4" t="n">
-        <v>12.7</v>
+        <v>19.3</v>
       </c>
       <c r="V416" s="1" t="inlineStr"/>
       <c r="W416" s="4" t="inlineStr"/>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -31812,61 +31812,81 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>QLD</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
+      <c r="A415" s="4" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="B415" s="4" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
-      <c r="G415" t="n">
-        <v>8035708</v>
-      </c>
-      <c r="H415" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I415" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
-      <c r="N415" s="3" t="n">
-        <v>34.44</v>
-      </c>
-      <c r="O415" t="n">
+      <c r="C415" s="4" t="n">
+        <v>84.26000000000001</v>
+      </c>
+      <c r="D415" s="4" t="n">
+        <v>84.56999999999999</v>
+      </c>
+      <c r="E415" s="4" t="n">
+        <v>80.81999999999999</v>
+      </c>
+      <c r="F415" s="4" t="n">
+        <v>82.59</v>
+      </c>
+      <c r="G415" s="4" t="n">
+        <v>8100200</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>-6.93</v>
+      </c>
+      <c r="I415" s="4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J415" s="4" t="n">
+        <v>92.36</v>
+      </c>
+      <c r="K415" s="4" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="L415" s="4" t="n">
+        <v>91.64</v>
+      </c>
+      <c r="M415" s="4" t="n">
+        <v>83.22</v>
+      </c>
+      <c r="N415" s="7" t="n">
+        <v>28.01</v>
+      </c>
+      <c r="O415" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="P415" t="inlineStr">
+      <c r="P415" s="4" t="inlineStr">
         <is>
           <t>fear</t>
         </is>
       </c>
-      <c r="Q415" t="inlineStr">
+      <c r="Q415" s="4" t="inlineStr">
         <is>
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr"/>
-      <c r="S415" t="n">
+      <c r="R415" s="4" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S415" s="4" t="n">
         <v>4.93</v>
       </c>
-      <c r="T415" s="3" t="n">
+      <c r="T415" s="6" t="n">
         <v>19.4</v>
       </c>
-      <c r="U415" s="3" t="n">
+      <c r="U415" s="6" t="n">
         <v>19.3</v>
       </c>
-      <c r="V415" t="inlineStr"/>
-      <c r="W415" s="3" t="n">
+      <c r="V415" s="4" t="inlineStr"/>
+      <c r="W415" s="6" t="n">
         <v>149.8</v>
       </c>
     </row>

--- a/US_stock/QLD_table.xlsx
+++ b/US_stock/QLD_table.xlsx
@@ -6669,7 +6669,7 @@
         <v>59.05</v>
       </c>
       <c r="D82" t="n">
-        <v>59.23</v>
+        <v>59.24</v>
       </c>
       <c r="E82" t="n">
         <v>58.22</v>
